--- a/results/surrogate_comparison.xlsx
+++ b/results/surrogate_comparison.xlsx
@@ -465,16 +465,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.6626520156860352</v>
+        <v>-0.3072641484405483</v>
       </c>
       <c r="D2" t="n">
-        <v>19.98324394226074</v>
+        <v>17.78658916173356</v>
       </c>
       <c r="E2" t="n">
-        <v>29.54415330702348</v>
+        <v>26.19705973824611</v>
       </c>
       <c r="F2" t="n">
-        <v>24.85508918762207</v>
+        <v>22.65103009560166</v>
       </c>
       <c r="G2" t="n">
         <v>89</v>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.6946488618850708</v>
+        <v>-0.3465122657973161</v>
       </c>
       <c r="D3" t="n">
-        <v>293.9443054199219</v>
+        <v>284.0645796650588</v>
       </c>
       <c r="E3" t="n">
-        <v>390.1102608558252</v>
+        <v>347.7384042594837</v>
       </c>
       <c r="F3" t="n">
-        <v>34.7059440612793</v>
+        <v>36.55196720430772</v>
       </c>
       <c r="G3" t="n">
         <v>99</v>
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.4478422403335571</v>
+        <v>-0.0843912241645246</v>
       </c>
       <c r="D4" t="n">
-        <v>266.127197265625</v>
+        <v>240.8351089313466</v>
       </c>
       <c r="E4" t="n">
-        <v>385.867832780863</v>
+        <v>333.9419110601584</v>
       </c>
       <c r="F4" t="n">
-        <v>25.61861038208008</v>
+        <v>22.84011131083356</v>
       </c>
       <c r="G4" t="n">
         <v>93</v>
@@ -546,16 +546,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.265122652053833</v>
+        <v>-0.156898204465231</v>
       </c>
       <c r="D5" t="n">
-        <v>6.557991027832031</v>
+        <v>6.001259186328986</v>
       </c>
       <c r="E5" t="n">
-        <v>9.807352647610355</v>
+        <v>9.378492721033419</v>
       </c>
       <c r="F5" t="n">
-        <v>62.52229309082031</v>
+        <v>53.39400253438625</v>
       </c>
       <c r="G5" t="n">
         <v>78</v>
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-6.917234420776367</v>
+        <v>-5.953406757707963</v>
       </c>
       <c r="D6" t="n">
-        <v>249.4482727050781</v>
+        <v>233.2503853903876</v>
       </c>
       <c r="E6" t="n">
-        <v>266.843894557286</v>
+        <v>250.074481363366</v>
       </c>
       <c r="F6" t="n">
-        <v>89.95378875732422</v>
+        <v>84.17094205932058</v>
       </c>
       <c r="G6" t="n">
         <v>18</v>
@@ -600,16 +600,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.4628845453262329</v>
+        <v>-0.3562135824898545</v>
       </c>
       <c r="D7" t="n">
-        <v>18.97312545776367</v>
+        <v>18.05010769876202</v>
       </c>
       <c r="E7" t="n">
-        <v>27.71251228962008</v>
+        <v>26.6830161927196</v>
       </c>
       <c r="F7" t="n">
-        <v>23.84638214111328</v>
+        <v>22.61665948545714</v>
       </c>
       <c r="G7" t="n">
         <v>89</v>
@@ -627,16 +627,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.5372471809387207</v>
+        <v>-0.2126494740735947</v>
       </c>
       <c r="D8" t="n">
-        <v>293.8240661621094</v>
+        <v>259.2783704044843</v>
       </c>
       <c r="E8" t="n">
-        <v>371.5517923183792</v>
+        <v>330.000912892615</v>
       </c>
       <c r="F8" t="n">
-        <v>36.27837753295898</v>
+        <v>31.59391640024469</v>
       </c>
       <c r="G8" t="n">
         <v>99</v>
@@ -654,16 +654,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.1144182682037354</v>
+        <v>-0.1674362721357603</v>
       </c>
       <c r="D9" t="n">
-        <v>238.8594207763672</v>
+        <v>246.2278455508653</v>
       </c>
       <c r="E9" t="n">
-        <v>338.5338217039769</v>
+        <v>346.49304561538</v>
       </c>
       <c r="F9" t="n">
-        <v>22.99322509765625</v>
+        <v>24.09703788464843</v>
       </c>
       <c r="G9" t="n">
         <v>93</v>
@@ -681,16 +681,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.236364483833313</v>
+        <v>-0.2190301553017804</v>
       </c>
       <c r="D10" t="n">
-        <v>6.492736339569092</v>
+        <v>6.271222952084663</v>
       </c>
       <c r="E10" t="n">
-        <v>9.695243644623547</v>
+        <v>9.627038234086605</v>
       </c>
       <c r="F10" t="n">
-        <v>60.91835403442383</v>
+        <v>57.98680114990958</v>
       </c>
       <c r="G10" t="n">
         <v>78</v>
@@ -708,16 +708,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-6.724701881408691</v>
+        <v>-6.130273246065486</v>
       </c>
       <c r="D11" t="n">
-        <v>246.4514770507812</v>
+        <v>237.3195865419176</v>
       </c>
       <c r="E11" t="n">
-        <v>263.5793583059948</v>
+        <v>253.2349508522515</v>
       </c>
       <c r="F11" t="n">
-        <v>89.01868438720703</v>
+        <v>85.9969832682841</v>
       </c>
       <c r="G11" t="n">
         <v>18</v>
@@ -735,16 +735,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.644457221031189</v>
+        <v>-0.4936522320197756</v>
       </c>
       <c r="D12" t="n">
-        <v>20.98045349121094</v>
+        <v>20.07610929682014</v>
       </c>
       <c r="E12" t="n">
-        <v>29.38205429758263</v>
+        <v>28.00242360611291</v>
       </c>
       <c r="F12" t="n">
-        <v>25.70307922363281</v>
+        <v>25.18497008971853</v>
       </c>
       <c r="G12" t="n">
         <v>89</v>
@@ -762,16 +762,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.5555485486984253</v>
+        <v>-0.5703311507458499</v>
       </c>
       <c r="D13" t="n">
-        <v>305.7254028320312</v>
+        <v>311.3123267587989</v>
       </c>
       <c r="E13" t="n">
-        <v>373.7569606375245</v>
+        <v>375.5286905220995</v>
       </c>
       <c r="F13" t="n">
-        <v>40.04337692260742</v>
+        <v>40.26112515905412</v>
       </c>
       <c r="G13" t="n">
         <v>99</v>
@@ -789,16 +789,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.4859455823898315</v>
+        <v>-0.3023972443355452</v>
       </c>
       <c r="D14" t="n">
-        <v>304.6522521972656</v>
+        <v>288.2823033486643</v>
       </c>
       <c r="E14" t="n">
-        <v>390.9123543072027</v>
+        <v>365.9735218748763</v>
       </c>
       <c r="F14" t="n">
-        <v>30.95909309387207</v>
+        <v>29.50074257876374</v>
       </c>
       <c r="G14" t="n">
         <v>93</v>
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.6480234861373901</v>
+        <v>-0.5625398920205991</v>
       </c>
       <c r="D15" t="n">
-        <v>7.442412376403809</v>
+        <v>7.291862845420837</v>
       </c>
       <c r="E15" t="n">
-        <v>11.19353267047627</v>
+        <v>10.8993607962309</v>
       </c>
       <c r="F15" t="n">
-        <v>70.24599456787109</v>
+        <v>70.49442013191025</v>
       </c>
       <c r="G15" t="n">
         <v>78</v>
@@ -843,16 +843,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-7.170844078063965</v>
+        <v>-6.514974862399907</v>
       </c>
       <c r="D16" t="n">
-        <v>255.34814453125</v>
+        <v>245.0524733861288</v>
       </c>
       <c r="E16" t="n">
-        <v>271.0840650287287</v>
+        <v>259.9766392208243</v>
       </c>
       <c r="F16" t="n">
-        <v>93.60150146484375</v>
+        <v>90.02255155222686</v>
       </c>
       <c r="G16" t="n">
         <v>18</v>
@@ -870,16 +870,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.7326492071151733</v>
+        <v>-0.592261629853911</v>
       </c>
       <c r="D17" t="n">
-        <v>21.79874992370605</v>
+        <v>21.14445360590902</v>
       </c>
       <c r="E17" t="n">
-        <v>30.15964197244805</v>
+        <v>28.91199697831197</v>
       </c>
       <c r="F17" t="n">
-        <v>26.68477249145508</v>
+        <v>26.17478300571639</v>
       </c>
       <c r="G17" t="n">
         <v>89</v>
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.759346604347229</v>
+        <v>-0.5250174577575086</v>
       </c>
       <c r="D18" t="n">
-        <v>323.5857849121094</v>
+        <v>299.6331321639244</v>
       </c>
       <c r="E18" t="n">
-        <v>397.4872442921911</v>
+        <v>370.0708755153819</v>
       </c>
       <c r="F18" t="n">
-        <v>41.95559310913086</v>
+        <v>38.5736470498556</v>
       </c>
       <c r="G18" t="n">
         <v>99</v>
@@ -924,16 +924,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.4600852727890015</v>
+        <v>-0.3043011636924173</v>
       </c>
       <c r="D19" t="n">
-        <v>301.9212341308594</v>
+        <v>290.0358476536248</v>
       </c>
       <c r="E19" t="n">
-        <v>387.4958467519361</v>
+        <v>366.2409247781038</v>
       </c>
       <c r="F19" t="n">
-        <v>30.0482120513916</v>
+        <v>29.33559820892856</v>
       </c>
       <c r="G19" t="n">
         <v>93</v>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.6444275379180908</v>
+        <v>-0.6011122095914649</v>
       </c>
       <c r="D20" t="n">
-        <v>7.529441833496094</v>
+        <v>7.31931205590566</v>
       </c>
       <c r="E20" t="n">
-        <v>11.18131362103721</v>
+        <v>11.03306957394549</v>
       </c>
       <c r="F20" t="n">
-        <v>70.48500061035156</v>
+        <v>69.90194024014485</v>
       </c>
       <c r="G20" t="n">
         <v>78</v>
@@ -978,16 +978,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-7.041417121887207</v>
+        <v>-6.639855798617955</v>
       </c>
       <c r="D21" t="n">
-        <v>252.8927154541016</v>
+        <v>246.6724683973524</v>
       </c>
       <c r="E21" t="n">
-        <v>268.928487241497</v>
+        <v>262.1278345664948</v>
       </c>
       <c r="F21" t="n">
-        <v>92.38341522216797</v>
+        <v>90.31635146045154</v>
       </c>
       <c r="G21" t="n">
         <v>18</v>
@@ -1005,16 +1005,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.441370964050293</v>
+        <v>-0.3190428523755027</v>
       </c>
       <c r="D22" t="n">
-        <v>18.82789993286133</v>
+        <v>17.56953151574296</v>
       </c>
       <c r="E22" t="n">
-        <v>27.50798334937003</v>
+        <v>26.31481538147835</v>
       </c>
       <c r="F22" t="n">
-        <v>23.85956192016602</v>
+        <v>22.28724507592869</v>
       </c>
       <c r="G22" t="n">
         <v>89</v>
@@ -1032,16 +1032,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.8262529373168945</v>
+        <v>-0.3325667461566131</v>
       </c>
       <c r="D23" t="n">
-        <v>307.8800659179688</v>
+        <v>281.4172358657374</v>
       </c>
       <c r="E23" t="n">
-        <v>404.9747677325095</v>
+        <v>345.9329939685035</v>
       </c>
       <c r="F23" t="n">
-        <v>36.09373092651367</v>
+        <v>35.62225782888974</v>
       </c>
       <c r="G23" t="n">
         <v>99</v>
@@ -1059,16 +1059,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.5223838090896606</v>
+        <v>-0.2772937491028276</v>
       </c>
       <c r="D24" t="n">
-        <v>273.1160888671875</v>
+        <v>267.9284963300151</v>
       </c>
       <c r="E24" t="n">
-        <v>395.6762802468705</v>
+        <v>362.4293202181124</v>
       </c>
       <c r="F24" t="n">
-        <v>27.1580638885498</v>
+        <v>26.56927439142802</v>
       </c>
       <c r="G24" t="n">
         <v>93</v>
@@ -1086,16 +1086,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.2793750762939453</v>
+        <v>-0.2332150604697607</v>
       </c>
       <c r="D25" t="n">
-        <v>6.507838249206543</v>
+        <v>6.410100288880177</v>
       </c>
       <c r="E25" t="n">
-        <v>9.862440790305671</v>
+        <v>9.682887411323394</v>
       </c>
       <c r="F25" t="n">
-        <v>62.89726638793945</v>
+        <v>63.88330338888119</v>
       </c>
       <c r="G25" t="n">
         <v>78</v>
@@ -1113,16 +1113,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-6.915245056152344</v>
+        <v>-6.755483744892608</v>
       </c>
       <c r="D26" t="n">
-        <v>250.2720336914062</v>
+        <v>246.2555590735541</v>
       </c>
       <c r="E26" t="n">
-        <v>266.8103844493314</v>
+        <v>264.1040159319073</v>
       </c>
       <c r="F26" t="n">
-        <v>90.62649536132812</v>
+        <v>87.84528889508135</v>
       </c>
       <c r="G26" t="n">
         <v>18</v>
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-1.187028646469116</v>
+        <v>-1.040303095091922</v>
       </c>
       <c r="D27" t="n">
-        <v>24.38615036010742</v>
+        <v>23.98492455214597</v>
       </c>
       <c r="E27" t="n">
-        <v>33.88426706729098</v>
+        <v>32.72790600505611</v>
       </c>
       <c r="F27" t="n">
-        <v>28.45199966430664</v>
+        <v>28.30041748576344</v>
       </c>
       <c r="G27" t="n">
         <v>89</v>
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-1.038893938064575</v>
+        <v>-1.072889654062955</v>
       </c>
       <c r="D28" t="n">
-        <v>343.7292785644531</v>
+        <v>353.6823023015803</v>
       </c>
       <c r="E28" t="n">
-        <v>427.9024969254094</v>
+        <v>431.4550850641374</v>
       </c>
       <c r="F28" t="n">
-        <v>39.62713623046875</v>
+        <v>40.58623559583062</v>
       </c>
       <c r="G28" t="n">
         <v>99</v>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.7165753841400146</v>
+        <v>-0.7903189867696965</v>
       </c>
       <c r="D29" t="n">
-        <v>328.3087768554688</v>
+        <v>341.4309525028352</v>
       </c>
       <c r="E29" t="n">
-        <v>420.1548635622347</v>
+        <v>429.0848094450324</v>
       </c>
       <c r="F29" t="n">
-        <v>29.12045097351074</v>
+        <v>30.9397860855669</v>
       </c>
       <c r="G29" t="n">
         <v>93</v>
@@ -1221,16 +1221,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.5695809125900269</v>
+        <v>-0.5866542723655261</v>
       </c>
       <c r="D30" t="n">
-        <v>7.726769924163818</v>
+        <v>7.690622659829947</v>
       </c>
       <c r="E30" t="n">
-        <v>10.92388976018505</v>
+        <v>10.98314266536361</v>
       </c>
       <c r="F30" t="n">
-        <v>72.96757507324219</v>
+        <v>72.22647384751426</v>
       </c>
       <c r="G30" t="n">
         <v>78</v>
@@ -1248,16 +1248,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-7.370685577392578</v>
+        <v>-7.078967031045412</v>
       </c>
       <c r="D31" t="n">
-        <v>257.4879150390625</v>
+        <v>252.7446058061388</v>
       </c>
       <c r="E31" t="n">
-        <v>274.3791144338431</v>
+        <v>269.5556734564208</v>
       </c>
       <c r="F31" t="n">
-        <v>93.61501312255859</v>
+        <v>91.72107226166149</v>
       </c>
       <c r="G31" t="n">
         <v>18</v>
@@ -1275,16 +1275,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-1.320595502853394</v>
+        <v>-0.6887375210439668</v>
       </c>
       <c r="D32" t="n">
-        <v>27.72087287902832</v>
+        <v>20.73987802226892</v>
       </c>
       <c r="E32" t="n">
-        <v>34.90362883231574</v>
+        <v>29.77501242677582</v>
       </c>
       <c r="F32" t="n">
-        <v>32.81915664672852</v>
+        <v>24.4808748485773</v>
       </c>
       <c r="G32" t="n">
         <v>89</v>
@@ -1302,16 +1302,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.9720724821090698</v>
+        <v>-0.3686207661977268</v>
       </c>
       <c r="D33" t="n">
-        <v>341.3817749023438</v>
+        <v>285.1443421334931</v>
       </c>
       <c r="E33" t="n">
-        <v>420.8321740908126</v>
+        <v>350.5815546372194</v>
       </c>
       <c r="F33" t="n">
-        <v>39.27030944824219</v>
+        <v>33.77669032280083</v>
       </c>
       <c r="G33" t="n">
         <v>99</v>
@@ -1329,16 +1329,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-1.502936601638794</v>
+        <v>-8.290178894312195</v>
       </c>
       <c r="D34" t="n">
-        <v>360.1879272460938</v>
+        <v>829.401377688172</v>
       </c>
       <c r="E34" t="n">
-        <v>507.3444034874141</v>
+        <v>977.4396888922822</v>
       </c>
       <c r="F34" t="n">
-        <v>46.38333129882812</v>
+        <v>98.99495757703627</v>
       </c>
       <c r="G34" t="n">
         <v>93</v>
@@ -1356,16 +1356,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-0.484951376914978</v>
+        <v>-0.2546967979455157</v>
       </c>
       <c r="D35" t="n">
-        <v>7.714691162109375</v>
+        <v>6.708555606695322</v>
       </c>
       <c r="E35" t="n">
-        <v>10.62530947963804</v>
+        <v>9.766857851832505</v>
       </c>
       <c r="F35" t="n">
-        <v>107.0978012084961</v>
+        <v>67.40555461532048</v>
       </c>
       <c r="G35" t="n">
         <v>78</v>
@@ -1383,16 +1383,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-4.881899356842041</v>
+        <v>-2.520468750780295</v>
       </c>
       <c r="D36" t="n">
-        <v>215.7876739501953</v>
+        <v>157.5548351075914</v>
       </c>
       <c r="E36" t="n">
-        <v>230.0007812486731</v>
+        <v>177.9388608667372</v>
       </c>
       <c r="F36" t="n">
-        <v>79.84633636474609</v>
+        <v>57.76817954644618</v>
       </c>
       <c r="G36" t="n">
         <v>18</v>
@@ -1410,16 +1410,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-1.523374319076538</v>
+        <v>-0.9031867519468004</v>
       </c>
       <c r="D37" t="n">
-        <v>27.98704719543457</v>
+        <v>23.76065354936578</v>
       </c>
       <c r="E37" t="n">
-        <v>36.39667423691088</v>
+        <v>31.60905979009016</v>
       </c>
       <c r="F37" t="n">
-        <v>33.02116394042969</v>
+        <v>28.60230451716832</v>
       </c>
       <c r="G37" t="n">
         <v>89</v>
@@ -1437,16 +1437,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-0.4932440519332886</v>
+        <v>-0.3996542227901694</v>
       </c>
       <c r="D38" t="n">
-        <v>300.0797424316406</v>
+        <v>292.9044896906072</v>
       </c>
       <c r="E38" t="n">
-        <v>366.1954097541366</v>
+        <v>354.5339907753966</v>
       </c>
       <c r="F38" t="n">
-        <v>35.86332321166992</v>
+        <v>35.34564287841501</v>
       </c>
       <c r="G38" t="n">
         <v>99</v>
@@ -1464,16 +1464,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-1.150233030319214</v>
+        <v>0.4769441903239487</v>
       </c>
       <c r="D39" t="n">
-        <v>285.2008666992188</v>
+        <v>184.8829713226646</v>
       </c>
       <c r="E39" t="n">
-        <v>470.2412279883592</v>
+        <v>231.9273395442031</v>
       </c>
       <c r="F39" t="n">
-        <v>33.55212783813477</v>
+        <v>20.67754337034225</v>
       </c>
       <c r="G39" t="n">
         <v>93</v>
@@ -1491,16 +1491,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-0.70366370677948</v>
+        <v>-0.5016864578997249</v>
       </c>
       <c r="D40" t="n">
-        <v>8.226603507995605</v>
+        <v>7.260508194947854</v>
       </c>
       <c r="E40" t="n">
-        <v>11.38092088134444</v>
+        <v>10.68501421648082</v>
       </c>
       <c r="F40" t="n">
-        <v>73.29778289794922</v>
+        <v>64.16286033762766</v>
       </c>
       <c r="G40" t="n">
         <v>78</v>
@@ -1518,16 +1518,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-3.434506416320801</v>
+        <v>-4.126228556117708</v>
       </c>
       <c r="D41" t="n">
-        <v>173.1810150146484</v>
+        <v>195.7884472741021</v>
       </c>
       <c r="E41" t="n">
-        <v>199.7069434978414</v>
+        <v>214.7185382388743</v>
       </c>
       <c r="F41" t="n">
-        <v>60.00871658325195</v>
+        <v>67.92346195398073</v>
       </c>
       <c r="G41" t="n">
         <v>18</v>
@@ -1545,16 +1545,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-1.935007333755493</v>
+        <v>-0.6073658732630696</v>
       </c>
       <c r="D42" t="n">
-        <v>33.25981140136719</v>
+        <v>22.22232687875126</v>
       </c>
       <c r="E42" t="n">
-        <v>39.25323589616928</v>
+        <v>29.04880335857041</v>
       </c>
       <c r="F42" t="n">
-        <v>40.92390823364258</v>
+        <v>26.97099939307425</v>
       </c>
       <c r="G42" t="n">
         <v>89</v>
@@ -1572,16 +1572,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-0.2319610118865967</v>
+        <v>0.09592182583488251</v>
       </c>
       <c r="D43" t="n">
-        <v>271.4116821289062</v>
+        <v>222.1371254969125</v>
       </c>
       <c r="E43" t="n">
-        <v>332.6181768371957</v>
+        <v>284.9380791856747</v>
       </c>
       <c r="F43" t="n">
-        <v>39.72050857543945</v>
+        <v>36.9338021111279</v>
       </c>
       <c r="G43" t="n">
         <v>99</v>
@@ -1599,16 +1599,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-1.239883184432983</v>
+        <v>-3.865217447812372</v>
       </c>
       <c r="D44" t="n">
-        <v>386.9430847167969</v>
+        <v>657.1819871471774</v>
       </c>
       <c r="E44" t="n">
-        <v>479.9440885405299</v>
+        <v>707.3413693661138</v>
       </c>
       <c r="F44" t="n">
-        <v>51.26304626464844</v>
+        <v>80.56230023227077</v>
       </c>
       <c r="G44" t="n">
         <v>93</v>
@@ -1626,16 +1626,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.5673437118530273</v>
+        <v>-0.4137607763614504</v>
       </c>
       <c r="D45" t="n">
-        <v>8.327948570251465</v>
+        <v>7.590343395868937</v>
       </c>
       <c r="E45" t="n">
-        <v>10.91610211570003</v>
+        <v>10.3674854928677</v>
       </c>
       <c r="F45" t="n">
-        <v>81.80752563476562</v>
+        <v>84.06196489090652</v>
       </c>
       <c r="G45" t="n">
         <v>78</v>
@@ -1653,16 +1653,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-3.480775833129883</v>
+        <v>-1.964722082961699</v>
       </c>
       <c r="D46" t="n">
-        <v>180.5526123046875</v>
+        <v>140.0951025221083</v>
       </c>
       <c r="E46" t="n">
-        <v>200.7461083059893</v>
+        <v>163.2911145164973</v>
       </c>
       <c r="F46" t="n">
-        <v>64.39886474609375</v>
+        <v>52.11919073258375</v>
       </c>
       <c r="G46" t="n">
         <v>18</v>
@@ -1680,16 +1680,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.545744776725769</v>
+        <v>-0.8029031812242198</v>
       </c>
       <c r="D47" t="n">
-        <v>20.74157524108887</v>
+        <v>22.94288939572452</v>
       </c>
       <c r="E47" t="n">
-        <v>28.48654338976344</v>
+        <v>30.7650111996374</v>
       </c>
       <c r="F47" t="n">
-        <v>25.25020790100098</v>
+        <v>27.58231326003771</v>
       </c>
       <c r="G47" t="n">
         <v>89</v>
@@ -1707,16 +1707,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-1.43766188621521</v>
+        <v>-0.6901756179470575</v>
       </c>
       <c r="D48" t="n">
-        <v>391.3989562988281</v>
+        <v>325.1736567333491</v>
       </c>
       <c r="E48" t="n">
-        <v>467.8797254637136</v>
+        <v>389.5950372527197</v>
       </c>
       <c r="F48" t="n">
-        <v>46.25778961181641</v>
+        <v>40.00038952705444</v>
       </c>
       <c r="G48" t="n">
         <v>99</v>
@@ -1734,16 +1734,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.6216145753860474</v>
+        <v>-1.13309948485514</v>
       </c>
       <c r="D49" t="n">
-        <v>307.0024719238281</v>
+        <v>406.5952410954301</v>
       </c>
       <c r="E49" t="n">
-        <v>408.3680554965092</v>
+        <v>468.3639785445299</v>
       </c>
       <c r="F49" t="n">
-        <v>36.33509826660156</v>
+        <v>52.6464160461428</v>
       </c>
       <c r="G49" t="n">
         <v>93</v>
@@ -1761,16 +1761,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.4557232856750488</v>
+        <v>-0.3530611250626676</v>
       </c>
       <c r="D50" t="n">
-        <v>7.827347278594971</v>
+        <v>7.129007944693933</v>
       </c>
       <c r="E50" t="n">
-        <v>10.52022131219299</v>
+        <v>10.14248047642301</v>
       </c>
       <c r="F50" t="n">
-        <v>80.734130859375</v>
+        <v>66.25284197338944</v>
       </c>
       <c r="G50" t="n">
         <v>78</v>
@@ -1788,16 +1788,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-3.376873016357422</v>
+        <v>-1.507637289072617</v>
       </c>
       <c r="D51" t="n">
-        <v>179.830810546875</v>
+        <v>129.7535845438639</v>
       </c>
       <c r="E51" t="n">
-        <v>198.4049481174802</v>
+        <v>150.1768251407771</v>
       </c>
       <c r="F51" t="n">
-        <v>62.58461380004883</v>
+        <v>47.25746321548785</v>
       </c>
       <c r="G51" t="n">
         <v>18</v>
@@ -1815,16 +1815,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.8109550476074219</v>
+        <v>-1.388696760533941</v>
       </c>
       <c r="D52" t="n">
-        <v>22.89310836791992</v>
+        <v>28.15463207544905</v>
       </c>
       <c r="E52" t="n">
-        <v>30.83363344888429</v>
+        <v>35.41207581071647</v>
       </c>
       <c r="F52" t="n">
-        <v>27.35861206054688</v>
+        <v>33.42160971997356</v>
       </c>
       <c r="G52" t="n">
         <v>89</v>
@@ -1842,16 +1842,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-2.336365461349487</v>
+        <v>-0.5785131323079133</v>
       </c>
       <c r="D53" t="n">
-        <v>467.3806457519531</v>
+        <v>316.1964240796638</v>
       </c>
       <c r="E53" t="n">
-        <v>547.3741864574909</v>
+        <v>376.5057382359775</v>
       </c>
       <c r="F53" t="n">
-        <v>56.27709197998047</v>
+        <v>38.39208546384418</v>
       </c>
       <c r="G53" t="n">
         <v>99</v>
@@ -1869,16 +1869,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-1.620073080062866</v>
+        <v>0.2889272756895652</v>
       </c>
       <c r="D54" t="n">
-        <v>390.439697265625</v>
+        <v>190.2254067697833</v>
       </c>
       <c r="E54" t="n">
-        <v>519.0804369266867</v>
+        <v>270.4175919483293</v>
       </c>
       <c r="F54" t="n">
-        <v>43.96062088012695</v>
+        <v>20.07786198347624</v>
       </c>
       <c r="G54" t="n">
         <v>93</v>
@@ -1896,16 +1896,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-0.5376663208007812</v>
+        <v>-0.5398361406289216</v>
       </c>
       <c r="D55" t="n">
-        <v>7.987552642822266</v>
+        <v>7.547737048222468</v>
       </c>
       <c r="E55" t="n">
-        <v>10.81226079599026</v>
+        <v>10.81988703156064</v>
       </c>
       <c r="F55" t="n">
-        <v>82.58750915527344</v>
+        <v>69.29105275692513</v>
       </c>
       <c r="G55" t="n">
         <v>78</v>
@@ -1923,16 +1923,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-2.576368808746338</v>
+        <v>-2.667159129964999</v>
       </c>
       <c r="D56" t="n">
-        <v>159.7616577148438</v>
+        <v>160.3341348436144</v>
       </c>
       <c r="E56" t="n">
-        <v>179.3459961307333</v>
+        <v>181.6081929232232</v>
       </c>
       <c r="F56" t="n">
-        <v>55.85829544067383</v>
+        <v>57.72136479545487</v>
       </c>
       <c r="G56" t="n">
         <v>18</v>
@@ -1950,16 +1950,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-0.5061053037643433</v>
+        <v>-0.712612010935548</v>
       </c>
       <c r="D57" t="n">
-        <v>19.95759010314941</v>
+        <v>22.15713590986273</v>
       </c>
       <c r="E57" t="n">
-        <v>28.11891318683199</v>
+        <v>29.98474554856081</v>
       </c>
       <c r="F57" t="n">
-        <v>24.12807273864746</v>
+        <v>26.46629967631079</v>
       </c>
       <c r="G57" t="n">
         <v>89</v>
@@ -1977,16 +1977,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-1.698440313339233</v>
+        <v>-0.6784445221405448</v>
       </c>
       <c r="D58" t="n">
-        <v>408.1531982421875</v>
+        <v>322.9315535420119</v>
       </c>
       <c r="E58" t="n">
-        <v>492.2706001276127</v>
+        <v>388.2406410681739</v>
       </c>
       <c r="F58" t="n">
-        <v>46.32808303833008</v>
+        <v>37.79107198383351</v>
       </c>
       <c r="G58" t="n">
         <v>99</v>
@@ -2004,16 +2004,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-0.000948786735534668</v>
+        <v>-0.02217820535706827</v>
       </c>
       <c r="D59" t="n">
-        <v>250.7775115966797</v>
+        <v>269.418691983787</v>
       </c>
       <c r="E59" t="n">
-        <v>320.8365773645518</v>
+        <v>324.2210735461169</v>
       </c>
       <c r="F59" t="n">
-        <v>29.07797431945801</v>
+        <v>34.17419424001673</v>
       </c>
       <c r="G59" t="n">
         <v>93</v>
@@ -2031,16 +2031,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-0.6698958873748779</v>
+        <v>-0.5098301449884124</v>
       </c>
       <c r="D60" t="n">
-        <v>8.493245124816895</v>
+        <v>7.598719009986291</v>
       </c>
       <c r="E60" t="n">
-        <v>11.26756712195034</v>
+        <v>10.7139476063095</v>
       </c>
       <c r="F60" t="n">
-        <v>78.75202941894531</v>
+        <v>73.06407608655935</v>
       </c>
       <c r="G60" t="n">
         <v>78</v>
@@ -2058,16 +2058,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-3.168978214263916</v>
+        <v>-1.562177349127126</v>
       </c>
       <c r="D61" t="n">
-        <v>172.6443481445312</v>
+        <v>131.2283100552029</v>
       </c>
       <c r="E61" t="n">
-        <v>193.63566182718</v>
+        <v>151.8011818833562</v>
       </c>
       <c r="F61" t="n">
-        <v>61.35543441772461</v>
+        <v>48.19410375702947</v>
       </c>
       <c r="G61" t="n">
         <v>18</v>
@@ -2085,16 +2085,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-0.4843051433563232</v>
+        <v>-0.9561016447504809</v>
       </c>
       <c r="D62" t="n">
-        <v>21.11804580688477</v>
+        <v>24.59569491697161</v>
       </c>
       <c r="E62" t="n">
-        <v>27.91466816443407</v>
+        <v>32.0454654628026</v>
       </c>
       <c r="F62" t="n">
-        <v>25.59572792053223</v>
+        <v>29.65577881898939</v>
       </c>
       <c r="G62" t="n">
         <v>89</v>
@@ -2112,16 +2112,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-2.710286378860474</v>
+        <v>-1.010680123885915</v>
       </c>
       <c r="D63" t="n">
-        <v>484.8235473632812</v>
+        <v>359.9001786973741</v>
       </c>
       <c r="E63" t="n">
-        <v>577.2330822553399</v>
+        <v>424.9315645428971</v>
       </c>
       <c r="F63" t="n">
-        <v>55.61269378662109</v>
+        <v>42.70344374607338</v>
       </c>
       <c r="G63" t="n">
         <v>99</v>
@@ -2139,16 +2139,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-1.75297737121582</v>
+        <v>0.2191522760674934</v>
       </c>
       <c r="D64" t="n">
-        <v>402.6878356933594</v>
+        <v>201.5814359931535</v>
       </c>
       <c r="E64" t="n">
-        <v>532.0828765333461</v>
+        <v>283.3747209275528</v>
       </c>
       <c r="F64" t="n">
-        <v>48.58880233764648</v>
+        <v>21.81242916628523</v>
       </c>
       <c r="G64" t="n">
         <v>93</v>
@@ -2166,16 +2166,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-0.3867497444152832</v>
+        <v>-0.2766191155782776</v>
       </c>
       <c r="D65" t="n">
-        <v>6.850553035736084</v>
+        <v>6.542743912109962</v>
       </c>
       <c r="E65" t="n">
-        <v>10.26796803669251</v>
+        <v>9.851812635317803</v>
       </c>
       <c r="F65" t="n">
-        <v>64.06484985351562</v>
+        <v>65.00816710839401</v>
       </c>
       <c r="G65" t="n">
         <v>78</v>
@@ -2193,16 +2193,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-3.451298713684082</v>
+        <v>-2.494549600966554</v>
       </c>
       <c r="D66" t="n">
-        <v>182.04833984375</v>
+        <v>161.992542690701</v>
       </c>
       <c r="E66" t="n">
-        <v>200.0847086236227</v>
+        <v>177.282620942239</v>
       </c>
       <c r="F66" t="n">
-        <v>67.49765777587891</v>
+        <v>60.22770724432731</v>
       </c>
       <c r="G66" t="n">
         <v>18</v>
@@ -2220,16 +2220,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-1.023640394210815</v>
+        <v>-1.23412200952765</v>
       </c>
       <c r="D67" t="n">
-        <v>24.56477928161621</v>
+        <v>26.76355713404966</v>
       </c>
       <c r="E67" t="n">
-        <v>32.59399156490061</v>
+        <v>34.24714074031103</v>
       </c>
       <c r="F67" t="n">
-        <v>28.69792556762695</v>
+        <v>31.84071388607514</v>
       </c>
       <c r="G67" t="n">
         <v>89</v>
@@ -2247,16 +2247,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-2.432473659515381</v>
+        <v>-0.8744280587701148</v>
       </c>
       <c r="D68" t="n">
-        <v>482.2876281738281</v>
+        <v>337.7421407988577</v>
       </c>
       <c r="E68" t="n">
-        <v>555.2021028418391</v>
+        <v>410.2814561820248</v>
       </c>
       <c r="F68" t="n">
-        <v>57.64926528930664</v>
+        <v>39.96154195121211</v>
       </c>
       <c r="G68" t="n">
         <v>99</v>
@@ -2274,16 +2274,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-0.5501370429992676</v>
+        <v>0.3574849420823776</v>
       </c>
       <c r="D69" t="n">
-        <v>292.1448364257812</v>
+        <v>182.488272061912</v>
       </c>
       <c r="E69" t="n">
-        <v>399.2666128353334</v>
+        <v>257.0511707226869</v>
       </c>
       <c r="F69" t="n">
-        <v>33.60988616943359</v>
+        <v>18.66330340161542</v>
       </c>
       <c r="G69" t="n">
         <v>93</v>
@@ -2301,16 +2301,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-0.6752541065216064</v>
+        <v>-0.4978579724313059</v>
       </c>
       <c r="D70" t="n">
-        <v>8.166138648986816</v>
+        <v>7.474532414705325</v>
       </c>
       <c r="E70" t="n">
-        <v>11.28563015511526</v>
+        <v>10.67138503055381</v>
       </c>
       <c r="F70" t="n">
-        <v>71.24816131591797</v>
+        <v>66.20355771670083</v>
       </c>
       <c r="G70" t="n">
         <v>78</v>
@@ -2328,16 +2328,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-3.220242500305176</v>
+        <v>-3.974120065601638</v>
       </c>
       <c r="D71" t="n">
-        <v>166.6603393554688</v>
+        <v>191.9554409450955</v>
       </c>
       <c r="E71" t="n">
-        <v>194.8225554831884</v>
+        <v>211.5089217029002</v>
       </c>
       <c r="F71" t="n">
-        <v>57.04840469360352</v>
+        <v>67.1966081191585</v>
       </c>
       <c r="G71" t="n">
         <v>18</v>
@@ -2355,16 +2355,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-0.4999995231628418</v>
+        <v>-0.8969940112900641</v>
       </c>
       <c r="D72" t="n">
-        <v>20.19708251953125</v>
+        <v>23.40047116226025</v>
       </c>
       <c r="E72" t="n">
-        <v>28.06185837587761</v>
+        <v>31.55759185003268</v>
       </c>
       <c r="F72" t="n">
-        <v>24.61699485778809</v>
+        <v>27.87750812937442</v>
       </c>
       <c r="G72" t="n">
         <v>89</v>
@@ -2382,16 +2382,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-2.566028118133545</v>
+        <v>-1.884606654742357</v>
       </c>
       <c r="D73" t="n">
-        <v>486.3197937011719</v>
+        <v>430.098183371804</v>
       </c>
       <c r="E73" t="n">
-        <v>565.9002507067831</v>
+        <v>508.9683777873696</v>
       </c>
       <c r="F73" t="n">
-        <v>56.5872917175293</v>
+        <v>49.3924755656981</v>
       </c>
       <c r="G73" t="n">
         <v>99</v>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.232972264289856</v>
+        <v>-0.1630218632553682</v>
       </c>
       <c r="D74" t="n">
-        <v>218.1105651855469</v>
+        <v>282.3343322097614</v>
       </c>
       <c r="E74" t="n">
-        <v>280.8558488130521</v>
+        <v>345.83733074613</v>
       </c>
       <c r="F74" t="n">
-        <v>26.03631401062012</v>
+        <v>37.06336303538314</v>
       </c>
       <c r="G74" t="n">
         <v>93</v>
@@ -2436,16 +2436,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-0.4564485549926758</v>
+        <v>-0.4115700939486044</v>
       </c>
       <c r="D75" t="n">
-        <v>7.506270885467529</v>
+        <v>7.335883748837007</v>
       </c>
       <c r="E75" t="n">
-        <v>10.522841540753</v>
+        <v>10.35944994909358</v>
       </c>
       <c r="F75" t="n">
-        <v>73.71947479248047</v>
+        <v>74.9187239520605</v>
       </c>
       <c r="G75" t="n">
         <v>78</v>
@@ -2463,16 +2463,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-3.433014392852783</v>
+        <v>-3.500269670717614</v>
       </c>
       <c r="D76" t="n">
-        <v>180.1533050537109</v>
+        <v>182.3565283881293</v>
       </c>
       <c r="E76" t="n">
-        <v>199.6733465250182</v>
+        <v>201.1823276501243</v>
       </c>
       <c r="F76" t="n">
-        <v>62.99911880493164</v>
+        <v>64.43595583752786</v>
       </c>
       <c r="G76" t="n">
         <v>18</v>
@@ -2490,16 +2490,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-1.499779224395752</v>
+        <v>-1.549231633359118</v>
       </c>
       <c r="D77" t="n">
-        <v>27.91402053833008</v>
+        <v>29.12890151377474</v>
       </c>
       <c r="E77" t="n">
-        <v>36.22610843876537</v>
+        <v>36.58268053392933</v>
       </c>
       <c r="F77" t="n">
-        <v>33.39768600463867</v>
+        <v>35.33817030687494</v>
       </c>
       <c r="G77" t="n">
         <v>89</v>
@@ -2517,16 +2517,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-1.772791385650635</v>
+        <v>-0.6432047888541312</v>
       </c>
       <c r="D78" t="n">
-        <v>387.5658874511719</v>
+        <v>316.7615882025825</v>
       </c>
       <c r="E78" t="n">
-        <v>499.0063877346662</v>
+        <v>384.1433734091705</v>
       </c>
       <c r="F78" t="n">
-        <v>47.51460647583008</v>
+        <v>37.57718408147151</v>
       </c>
       <c r="G78" t="n">
         <v>99</v>
@@ -2544,16 +2544,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-4.117164611816406</v>
+        <v>-0.007173693541636217</v>
       </c>
       <c r="D79" t="n">
-        <v>389.7226867675781</v>
+        <v>245.9248729418683</v>
       </c>
       <c r="E79" t="n">
-        <v>725.4252201295458</v>
+        <v>321.8326623972031</v>
       </c>
       <c r="F79" t="n">
-        <v>48.16383361816406</v>
+        <v>23.12370983633483</v>
       </c>
       <c r="G79" t="n">
         <v>93</v>
@@ -2571,16 +2571,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-0.5655907392501831</v>
+        <v>-0.4894839003153706</v>
       </c>
       <c r="D80" t="n">
-        <v>7.757068157196045</v>
+        <v>7.324220250814389</v>
       </c>
       <c r="E80" t="n">
-        <v>10.90999576110478</v>
+        <v>10.64151297320386</v>
       </c>
       <c r="F80" t="n">
-        <v>72.61260986328125</v>
+        <v>67.37045194568285</v>
       </c>
       <c r="G80" t="n">
         <v>78</v>
@@ -2598,16 +2598,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-3.950966835021973</v>
+        <v>-5.296140249254645</v>
       </c>
       <c r="D81" t="n">
-        <v>189.9278259277344</v>
+        <v>215.7366598976983</v>
       </c>
       <c r="E81" t="n">
-        <v>211.0160779567519</v>
+        <v>237.9620797324347</v>
       </c>
       <c r="F81" t="n">
-        <v>67.806640625</v>
+        <v>73.95924010762748</v>
       </c>
       <c r="G81" t="n">
         <v>18</v>
@@ -2625,16 +2625,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-1.182681083679199</v>
+        <v>-1.471639320853854</v>
       </c>
       <c r="D82" t="n">
-        <v>25.4930305480957</v>
+        <v>27.51576805114746</v>
       </c>
       <c r="E82" t="n">
-        <v>33.85057172419231</v>
+        <v>36.02163512978397</v>
       </c>
       <c r="F82" t="n">
-        <v>31.16018676757812</v>
+        <v>32.34854275170433</v>
       </c>
       <c r="G82" t="n">
         <v>89</v>
@@ -2652,16 +2652,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-0.7740155458450317</v>
+        <v>-1.215198924684078</v>
       </c>
       <c r="D83" t="n">
-        <v>311.4525451660156</v>
+        <v>369.7394799126519</v>
       </c>
       <c r="E83" t="n">
-        <v>399.14087425369</v>
+        <v>446.0195198816821</v>
       </c>
       <c r="F83" t="n">
-        <v>38.68706893920898</v>
+        <v>43.27805505367751</v>
       </c>
       <c r="G83" t="n">
         <v>99</v>
@@ -2679,16 +2679,16 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-4.442421913146973</v>
+        <v>0.1224780929247532</v>
       </c>
       <c r="D84" t="n">
-        <v>423.7393798828125</v>
+        <v>231.7278691773774</v>
       </c>
       <c r="E84" t="n">
-        <v>748.1247807017222</v>
+        <v>300.4048325025429</v>
       </c>
       <c r="F84" t="n">
-        <v>55.44403076171875</v>
+        <v>25.56728717971516</v>
       </c>
       <c r="G84" t="n">
         <v>93</v>
@@ -2706,16 +2706,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-0.6085501909255981</v>
+        <v>-0.6352777245902743</v>
       </c>
       <c r="D85" t="n">
-        <v>8.072028160095215</v>
+        <v>7.975412708062392</v>
       </c>
       <c r="E85" t="n">
-        <v>11.05866653488499</v>
+        <v>11.15016342109965</v>
       </c>
       <c r="F85" t="n">
-        <v>81.01585388183594</v>
+        <v>73.7908922035902</v>
       </c>
       <c r="G85" t="n">
         <v>78</v>
@@ -2733,16 +2733,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-4.024644374847412</v>
+        <v>-5.283701956703678</v>
       </c>
       <c r="D86" t="n">
-        <v>188.6929168701172</v>
+        <v>218.0422744750977</v>
       </c>
       <c r="E86" t="n">
-        <v>212.5803892060601</v>
+        <v>237.7269114296623</v>
       </c>
       <c r="F86" t="n">
-        <v>64.73207092285156</v>
+        <v>76.06983393658727</v>
       </c>
       <c r="G86" t="n">
         <v>18</v>
@@ -2760,16 +2760,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-1.664239406585693</v>
+        <v>-1.389030043204086</v>
       </c>
       <c r="D87" t="n">
-        <v>28.65798950195312</v>
+        <v>26.91502095340343</v>
       </c>
       <c r="E87" t="n">
-        <v>37.39878593555044</v>
+        <v>35.41454615767072</v>
       </c>
       <c r="F87" t="n">
-        <v>34.20377731323242</v>
+        <v>32.38512177211038</v>
       </c>
       <c r="G87" t="n">
         <v>89</v>
@@ -2787,16 +2787,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-1.095797777175903</v>
+        <v>-1.002709445526146</v>
       </c>
       <c r="D88" t="n">
-        <v>346.0488586425781</v>
+        <v>357.4730622262666</v>
       </c>
       <c r="E88" t="n">
-        <v>433.832611009131</v>
+        <v>424.0884776417598</v>
       </c>
       <c r="F88" t="n">
-        <v>42.88098526000977</v>
+        <v>42.72816845696019</v>
       </c>
       <c r="G88" t="n">
         <v>99</v>
@@ -2814,16 +2814,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-5.738356113433838</v>
+        <v>0.1974920760436352</v>
       </c>
       <c r="D89" t="n">
-        <v>343.3712463378906</v>
+        <v>211.1936317361811</v>
       </c>
       <c r="E89" t="n">
-        <v>832.443804409643</v>
+        <v>287.2781502328453</v>
       </c>
       <c r="F89" t="n">
-        <v>45.14860916137695</v>
+        <v>20.43244152786891</v>
       </c>
       <c r="G89" t="n">
         <v>93</v>
@@ -2841,16 +2841,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-0.5569497346878052</v>
+        <v>-0.5033404311527419</v>
       </c>
       <c r="D90" t="n">
-        <v>7.335121154785156</v>
+        <v>7.2030723461738</v>
       </c>
       <c r="E90" t="n">
-        <v>10.87984630420059</v>
+        <v>10.69089689061536</v>
       </c>
       <c r="F90" t="n">
-        <v>66.29560852050781</v>
+        <v>66.85184262361365</v>
       </c>
       <c r="G90" t="n">
         <v>78</v>
@@ -2868,16 +2868,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-3.654270648956299</v>
+        <v>-5.442559650857128</v>
       </c>
       <c r="D91" t="n">
-        <v>184.2505187988281</v>
+        <v>220.1774340735541</v>
       </c>
       <c r="E91" t="n">
-        <v>204.59562823714</v>
+        <v>240.7131317866134</v>
       </c>
       <c r="F91" t="n">
-        <v>63.27410888671875</v>
+        <v>76.34565548902457</v>
       </c>
       <c r="G91" t="n">
         <v>18</v>
@@ -2895,16 +2895,16 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-0.5142660140991211</v>
+        <v>-0.2570850724143601</v>
       </c>
       <c r="D92" t="n">
-        <v>19.04547500610352</v>
+        <v>17.61364126741216</v>
       </c>
       <c r="E92" t="n">
-        <v>28.19499103619737</v>
+        <v>25.68935555383979</v>
       </c>
       <c r="F92" t="n">
-        <v>23.89116859436035</v>
+        <v>22.48992653425854</v>
       </c>
       <c r="G92" t="n">
         <v>89</v>
@@ -2922,16 +2922,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-0.8983868360519409</v>
+        <v>-0.2026257004567971</v>
       </c>
       <c r="D93" t="n">
-        <v>322.2178955078125</v>
+        <v>258.7381479282572</v>
       </c>
       <c r="E93" t="n">
-        <v>412.8952273277084</v>
+        <v>328.6341871388381</v>
       </c>
       <c r="F93" t="n">
-        <v>39.30694580078125</v>
+        <v>32.07150539183605</v>
       </c>
       <c r="G93" t="n">
         <v>99</v>
@@ -2949,16 +2949,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-0.06576645374298096</v>
+        <v>-0.1498895716296738</v>
       </c>
       <c r="D94" t="n">
-        <v>238.0951995849609</v>
+        <v>250.7450659967238</v>
       </c>
       <c r="E94" t="n">
-        <v>331.0617153568198</v>
+        <v>343.8792720780625</v>
       </c>
       <c r="F94" t="n">
-        <v>22.99976539611816</v>
+        <v>24.81727555162303</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
@@ -2976,16 +2976,16 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-0.1833243370056152</v>
+        <v>-0.1830178658587442</v>
       </c>
       <c r="D95" t="n">
-        <v>6.236217975616455</v>
+        <v>6.258523351106888</v>
       </c>
       <c r="E95" t="n">
-        <v>9.48500041376494</v>
+        <v>9.483772421721717</v>
       </c>
       <c r="F95" t="n">
-        <v>56.66319274902344</v>
+        <v>59.67610140848139</v>
       </c>
       <c r="G95" t="n">
         <v>78</v>
@@ -3003,16 +3003,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-6.967392444610596</v>
+        <v>-6.151845667325443</v>
       </c>
       <c r="D96" t="n">
-        <v>251.0869140625</v>
+        <v>237.4648608101739</v>
       </c>
       <c r="E96" t="n">
-        <v>267.6878429252998</v>
+        <v>253.617738799916</v>
       </c>
       <c r="F96" t="n">
-        <v>90.92041015625</v>
+        <v>85.94680093957292</v>
       </c>
       <c r="G96" t="n">
         <v>18</v>
@@ -3030,16 +3030,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-0.7229915857315063</v>
+        <v>-0.3530784381472216</v>
       </c>
       <c r="D97" t="n">
-        <v>20.5059700012207</v>
+        <v>18.11343638816576</v>
       </c>
       <c r="E97" t="n">
-        <v>30.07547167680054</v>
+        <v>26.65215692746227</v>
       </c>
       <c r="F97" t="n">
-        <v>25.55831718444824</v>
+        <v>22.85026761363112</v>
       </c>
       <c r="G97" t="n">
         <v>89</v>
@@ -3057,16 +3057,16 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-0.5410767793655396</v>
+        <v>-0.1396847239236756</v>
       </c>
       <c r="D98" t="n">
-        <v>290.6260070800781</v>
+        <v>250.9837720466383</v>
       </c>
       <c r="E98" t="n">
-        <v>372.0143016404074</v>
+        <v>319.918874666805</v>
       </c>
       <c r="F98" t="n">
-        <v>35.20963668823242</v>
+        <v>30.53908230884521</v>
       </c>
       <c r="G98" t="n">
         <v>99</v>
@@ -3084,16 +3084,16 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-0.3515936136245728</v>
+        <v>-0.1705221817995277</v>
       </c>
       <c r="D99" t="n">
-        <v>257.2498779296875</v>
+        <v>256.3892359579763</v>
       </c>
       <c r="E99" t="n">
-        <v>372.8215474593709</v>
+        <v>346.9506896878131</v>
       </c>
       <c r="F99" t="n">
-        <v>24.49388885498047</v>
+        <v>25.87939729728357</v>
       </c>
       <c r="G99" t="n">
         <v>93</v>
@@ -3111,16 +3111,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-0.2607822418212891</v>
+        <v>-0.169926881412269</v>
       </c>
       <c r="D100" t="n">
-        <v>6.45624303817749</v>
+        <v>6.199532252091628</v>
       </c>
       <c r="E100" t="n">
-        <v>9.790514376320056</v>
+        <v>9.431153905528097</v>
       </c>
       <c r="F100" t="n">
-        <v>60.29620361328125</v>
+        <v>56.78333217753499</v>
       </c>
       <c r="G100" t="n">
         <v>78</v>
@@ -3138,16 +3138,16 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-7.17038631439209</v>
+        <v>-6.122575966890341</v>
       </c>
       <c r="D101" t="n">
-        <v>254.7510375976562</v>
+        <v>237.1753910912408</v>
       </c>
       <c r="E101" t="n">
-        <v>271.0764709911209</v>
+        <v>253.0982277291369</v>
       </c>
       <c r="F101" t="n">
-        <v>92.63571166992188</v>
+        <v>86.1801103321517</v>
       </c>
       <c r="G101" t="n">
         <v>18</v>
@@ -3165,16 +3165,16 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-0.8171988725662231</v>
+        <v>-0.6767156101956449</v>
       </c>
       <c r="D102" t="n">
-        <v>22.32387924194336</v>
+        <v>21.87050054314431</v>
       </c>
       <c r="E102" t="n">
-        <v>30.88674122809666</v>
+        <v>29.66884084209764</v>
       </c>
       <c r="F102" t="n">
-        <v>27.26198768615723</v>
+        <v>26.82193788604062</v>
       </c>
       <c r="G102" t="n">
         <v>89</v>
@@ -3192,16 +3192,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-0.8217297792434692</v>
+        <v>-0.4115967816098458</v>
       </c>
       <c r="D103" t="n">
-        <v>323.2607421875</v>
+        <v>288.1707820699672</v>
       </c>
       <c r="E103" t="n">
-        <v>404.4729402259192</v>
+        <v>356.0433098440271</v>
       </c>
       <c r="F103" t="n">
-        <v>41.28470993041992</v>
+        <v>37.15099874364159</v>
       </c>
       <c r="G103" t="n">
         <v>99</v>
@@ -3219,16 +3219,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-0.2525676488876343</v>
+        <v>-0.4544465018555139</v>
       </c>
       <c r="D104" t="n">
-        <v>279.5342407226562</v>
+        <v>301.2230365712156</v>
       </c>
       <c r="E104" t="n">
-        <v>358.904202486541</v>
+        <v>386.7468693060013</v>
       </c>
       <c r="F104" t="n">
-        <v>27.82763862609863</v>
+        <v>30.50805931037572</v>
       </c>
       <c r="G104" t="n">
         <v>93</v>
@@ -3246,16 +3246,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-0.6352399587631226</v>
+        <v>-0.6276911289332823</v>
       </c>
       <c r="D105" t="n">
-        <v>7.555397987365723</v>
+        <v>7.517317194205064</v>
       </c>
       <c r="E105" t="n">
-        <v>11.15003430827384</v>
+        <v>11.12426869976479</v>
       </c>
       <c r="F105" t="n">
-        <v>73.0831298828125</v>
+        <v>72.90617490816005</v>
       </c>
       <c r="G105" t="n">
         <v>78</v>
@@ -3273,16 +3273,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>-7.21419620513916</v>
+        <v>-6.666026803164889</v>
       </c>
       <c r="D106" t="n">
-        <v>256.19091796875</v>
+        <v>245.7406954235501</v>
       </c>
       <c r="E106" t="n">
-        <v>271.8022603842728</v>
+        <v>262.5764218147352</v>
       </c>
       <c r="F106" t="n">
-        <v>94.02942657470703</v>
+        <v>89.26161711708028</v>
       </c>
       <c r="G106" t="n">
         <v>18</v>
@@ -3300,16 +3300,16 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>-0.5741279125213623</v>
+        <v>-0.5052568231541132</v>
       </c>
       <c r="D107" t="n">
-        <v>20.57030487060547</v>
+        <v>20.00652131069912</v>
       </c>
       <c r="E107" t="n">
-        <v>28.74688969248999</v>
+        <v>28.1109923681545</v>
       </c>
       <c r="F107" t="n">
-        <v>25.40769577026367</v>
+        <v>24.70006248289159</v>
       </c>
       <c r="G107" t="n">
         <v>89</v>
@@ -3327,16 +3327,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>-0.5025385618209839</v>
+        <v>-0.3580515197443044</v>
       </c>
       <c r="D108" t="n">
-        <v>301.4007568359375</v>
+        <v>286.2276651401713</v>
       </c>
       <c r="E108" t="n">
-        <v>367.3332955232891</v>
+        <v>349.2252386820446</v>
       </c>
       <c r="F108" t="n">
-        <v>39.69993209838867</v>
+        <v>37.23221173650085</v>
       </c>
       <c r="G108" t="n">
         <v>99</v>
@@ -3354,16 +3354,16 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>-0.4365205764770508</v>
+        <v>-0.4248261172339993</v>
       </c>
       <c r="D109" t="n">
-        <v>300.288818359375</v>
+        <v>297.9818732148858</v>
       </c>
       <c r="E109" t="n">
-        <v>384.3561784009722</v>
+        <v>382.7884847943502</v>
       </c>
       <c r="F109" t="n">
-        <v>30.45828628540039</v>
+        <v>30.07757604301327</v>
       </c>
       <c r="G109" t="n">
         <v>93</v>
@@ -3381,16 +3381,16 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>-0.5924137830734253</v>
+        <v>-0.6010503843694646</v>
       </c>
       <c r="D110" t="n">
-        <v>7.3678297996521</v>
+        <v>7.354301969210307</v>
       </c>
       <c r="E110" t="n">
-        <v>11.00305861518333</v>
+        <v>11.03285655684505</v>
       </c>
       <c r="F110" t="n">
-        <v>71.08771514892578</v>
+        <v>71.76877658501866</v>
       </c>
       <c r="G110" t="n">
         <v>78</v>
@@ -3408,16 +3408,16 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>-7.08067798614502</v>
+        <v>-6.666264216543272</v>
       </c>
       <c r="D111" t="n">
-        <v>253.5892791748047</v>
+        <v>247.5233608881632</v>
       </c>
       <c r="E111" t="n">
-        <v>269.58419950917</v>
+        <v>262.5804877196911</v>
       </c>
       <c r="F111" t="n">
-        <v>92.81449890136719</v>
+        <v>91.0171921089588</v>
       </c>
       <c r="G111" t="n">
         <v>18</v>
@@ -3435,16 +3435,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>-0.633481502532959</v>
+        <v>-0.5348925668426003</v>
       </c>
       <c r="D112" t="n">
-        <v>20.2027702331543</v>
+        <v>19.68904253070274</v>
       </c>
       <c r="E112" t="n">
-        <v>29.28383668203865</v>
+        <v>28.38637047095544</v>
       </c>
       <c r="F112" t="n">
-        <v>25.04327964782715</v>
+        <v>24.37800941468251</v>
       </c>
       <c r="G112" t="n">
         <v>89</v>
@@ -3462,16 +3462,16 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>-0.7688535451889038</v>
+        <v>-0.7235706407040736</v>
       </c>
       <c r="D113" t="n">
-        <v>312.726318359375</v>
+        <v>309.7161211726641</v>
       </c>
       <c r="E113" t="n">
-        <v>398.5597508529932</v>
+        <v>393.425081775846</v>
       </c>
       <c r="F113" t="n">
-        <v>36.95484924316406</v>
+        <v>38.37262486416343</v>
       </c>
       <c r="G113" t="n">
         <v>99</v>
@@ -3489,16 +3489,16 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>-0.1529954671859741</v>
+        <v>-0.5569021384023682</v>
       </c>
       <c r="D114" t="n">
-        <v>245.6272430419922</v>
+        <v>273.784171811996</v>
       </c>
       <c r="E114" t="n">
-        <v>344.3433855724544</v>
+        <v>400.1368866028785</v>
       </c>
       <c r="F114" t="n">
-        <v>23.79395294189453</v>
+        <v>28.0110378861938</v>
       </c>
       <c r="G114" t="n">
         <v>93</v>
@@ -3516,16 +3516,16 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>-0.3786603212356567</v>
+        <v>-0.3396354277203011</v>
       </c>
       <c r="D115" t="n">
-        <v>6.779677867889404</v>
+        <v>6.679340824102744</v>
       </c>
       <c r="E115" t="n">
-        <v>10.23797572035536</v>
+        <v>10.09203584312609</v>
       </c>
       <c r="F115" t="n">
-        <v>63.55553817749023</v>
+        <v>62.03568320833757</v>
       </c>
       <c r="G115" t="n">
         <v>78</v>
@@ -3543,16 +3543,16 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>-6.871171951293945</v>
+        <v>-6.533716841068441</v>
       </c>
       <c r="D116" t="n">
-        <v>247.7027435302734</v>
+        <v>242.6494998931885</v>
       </c>
       <c r="E116" t="n">
-        <v>266.0665300963276</v>
+        <v>260.3006218401051</v>
       </c>
       <c r="F116" t="n">
-        <v>88.37351989746094</v>
+        <v>86.80668227194305</v>
       </c>
       <c r="G116" t="n">
         <v>18</v>
@@ -3570,16 +3570,16 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>-1.120407104492188</v>
+        <v>-1.172412305400828</v>
       </c>
       <c r="D117" t="n">
-        <v>23.44917297363281</v>
+        <v>24.22419187995825</v>
       </c>
       <c r="E117" t="n">
-        <v>33.3641829088002</v>
+        <v>33.77085079837414</v>
       </c>
       <c r="F117" t="n">
-        <v>27.93440246582031</v>
+        <v>28.49451651217407</v>
       </c>
       <c r="G117" t="n">
         <v>89</v>
@@ -3597,16 +3597,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>-0.8711706399917603</v>
+        <v>-1.745034850826802</v>
       </c>
       <c r="D118" t="n">
-        <v>319.8936767578125</v>
+        <v>421.0036970966994</v>
       </c>
       <c r="E118" t="n">
-        <v>409.924802555298</v>
+        <v>496.5024904006485</v>
       </c>
       <c r="F118" t="n">
-        <v>37.36661529541016</v>
+        <v>48.96888752957938</v>
       </c>
       <c r="G118" t="n">
         <v>99</v>
@@ -3624,16 +3624,16 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>-0.691428542137146</v>
+        <v>-0.4502566788311921</v>
       </c>
       <c r="D119" t="n">
-        <v>308.1048278808594</v>
+        <v>272.0021171980007</v>
       </c>
       <c r="E119" t="n">
-        <v>417.0659794924539</v>
+        <v>386.1894168347771</v>
       </c>
       <c r="F119" t="n">
-        <v>28.69095420837402</v>
+        <v>24.55857392532573</v>
       </c>
       <c r="G119" t="n">
         <v>93</v>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>-0.6056468486785889</v>
+        <v>-0.6177094944873254</v>
       </c>
       <c r="D120" t="n">
-        <v>7.800220012664795</v>
+        <v>7.839794168105493</v>
       </c>
       <c r="E120" t="n">
-        <v>11.04868225249516</v>
+        <v>11.09010707712444</v>
       </c>
       <c r="F120" t="n">
-        <v>72.33969879150391</v>
+        <v>70.91383632558312</v>
       </c>
       <c r="G120" t="n">
         <v>78</v>
@@ -3678,16 +3678,16 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>-7.604530334472656</v>
+        <v>-7.384327229932808</v>
       </c>
       <c r="D121" t="n">
-        <v>261.8820495605469</v>
+        <v>258.0022038353814</v>
       </c>
       <c r="E121" t="n">
-        <v>278.1852603257405</v>
+        <v>274.6026152869421</v>
       </c>
       <c r="F121" t="n">
-        <v>95.7147216796875</v>
+        <v>93.69373231624496</v>
       </c>
       <c r="G121" t="n">
         <v>18</v>
@@ -3705,16 +3705,16 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>-1.244672298431396</v>
+        <v>-0.6426696930593916</v>
       </c>
       <c r="D122" t="n">
-        <v>26.62206268310547</v>
+        <v>21.0709600341454</v>
       </c>
       <c r="E122" t="n">
-        <v>34.32790808420315</v>
+        <v>29.36608133275152</v>
       </c>
       <c r="F122" t="n">
-        <v>32.12125015258789</v>
+        <v>25.51765861188652</v>
       </c>
       <c r="G122" t="n">
         <v>89</v>
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>-0.5867393016815186</v>
+        <v>-0.4758156893571013</v>
       </c>
       <c r="D123" t="n">
-        <v>303.9259033203125</v>
+        <v>310.1381560046264</v>
       </c>
       <c r="E123" t="n">
-        <v>377.4855129670541</v>
+        <v>364.0521174608331</v>
       </c>
       <c r="F123" t="n">
-        <v>36.10033798217773</v>
+        <v>37.8809626057779</v>
       </c>
       <c r="G123" t="n">
         <v>99</v>
@@ -3759,16 +3759,16 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>-0.5687593221664429</v>
+        <v>0.1546033447136805</v>
       </c>
       <c r="D124" t="n">
-        <v>294.8345642089844</v>
+        <v>235.8716220650622</v>
       </c>
       <c r="E124" t="n">
-        <v>401.6576978597572</v>
+        <v>294.8547942725172</v>
       </c>
       <c r="F124" t="n">
-        <v>35.54714202880859</v>
+        <v>28.46303727975533</v>
       </c>
       <c r="G124" t="n">
         <v>93</v>
@@ -3786,16 +3786,16 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>-0.3127110004425049</v>
+        <v>-0.1891456869603207</v>
       </c>
       <c r="D125" t="n">
-        <v>6.770957946777344</v>
+        <v>6.30647473457532</v>
       </c>
       <c r="E125" t="n">
-        <v>9.990104356741913</v>
+        <v>9.508302820024827</v>
       </c>
       <c r="F125" t="n">
-        <v>66.72954559326172</v>
+        <v>62.88331648526187</v>
       </c>
       <c r="G125" t="n">
         <v>78</v>
@@ -3813,16 +3813,16 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>-5.846511363983154</v>
+        <v>-4.107933692025503</v>
       </c>
       <c r="D126" t="n">
-        <v>230.1893157958984</v>
+        <v>193.0384131537543</v>
       </c>
       <c r="E126" t="n">
-        <v>248.1448118664785</v>
+        <v>214.3350440623541</v>
       </c>
       <c r="F126" t="n">
-        <v>83.47871398925781</v>
+        <v>66.48883644569348</v>
       </c>
       <c r="G126" t="n">
         <v>18</v>
@@ -3840,16 +3840,16 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>-1.828530311584473</v>
+        <v>-0.8784148776652518</v>
       </c>
       <c r="D127" t="n">
-        <v>32.10225296020508</v>
+        <v>23.207842966144</v>
       </c>
       <c r="E127" t="n">
-        <v>38.53463811898248</v>
+        <v>31.40267428823843</v>
       </c>
       <c r="F127" t="n">
-        <v>39.23245620727539</v>
+        <v>28.15287314442276</v>
       </c>
       <c r="G127" t="n">
         <v>89</v>
@@ -3867,16 +3867,16 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>-0.5459935665130615</v>
+        <v>-0.5143034495340262</v>
       </c>
       <c r="D128" t="n">
-        <v>307.5283813476562</v>
+        <v>298.6366632634943</v>
       </c>
       <c r="E128" t="n">
-        <v>372.6072832084741</v>
+        <v>368.7686179975199</v>
       </c>
       <c r="F128" t="n">
-        <v>37.05251693725586</v>
+        <v>35.58874054837776</v>
       </c>
       <c r="G128" t="n">
         <v>99</v>
@@ -3894,16 +3894,16 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>-0.559317946434021</v>
+        <v>0.3701708315630077</v>
       </c>
       <c r="D129" t="n">
-        <v>267.8292236328125</v>
+        <v>192.2043929561492</v>
       </c>
       <c r="E129" t="n">
-        <v>400.4472304499059</v>
+        <v>254.5008961434855</v>
       </c>
       <c r="F129" t="n">
-        <v>29.59712409973145</v>
+        <v>22.1071419730485</v>
       </c>
       <c r="G129" t="n">
         <v>93</v>
@@ -3921,16 +3921,16 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>-0.5614244937896729</v>
+        <v>-0.4788117845396138</v>
       </c>
       <c r="D130" t="n">
-        <v>7.725775241851807</v>
+        <v>7.25343761077294</v>
       </c>
       <c r="E130" t="n">
-        <v>10.89546995608564</v>
+        <v>10.60332134940495</v>
       </c>
       <c r="F130" t="n">
-        <v>83.74607849121094</v>
+        <v>68.30533928703247</v>
       </c>
       <c r="G130" t="n">
         <v>78</v>
@@ -3948,16 +3948,16 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>-4.319964408874512</v>
+        <v>-4.269457860744517</v>
       </c>
       <c r="D131" t="n">
-        <v>196.3743286132812</v>
+        <v>198.982385635376</v>
       </c>
       <c r="E131" t="n">
-        <v>218.7383300458564</v>
+        <v>217.6975427799285</v>
       </c>
       <c r="F131" t="n">
-        <v>68.81191253662109</v>
+        <v>69.14402441647786</v>
       </c>
       <c r="G131" t="n">
         <v>18</v>
@@ -3975,16 +3975,16 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>-1.419761657714844</v>
+        <v>-0.8170929692845217</v>
       </c>
       <c r="D132" t="n">
-        <v>26.55002975463867</v>
+        <v>23.18268990248777</v>
       </c>
       <c r="E132" t="n">
-        <v>35.64159769606471</v>
+        <v>30.8858422541879</v>
       </c>
       <c r="F132" t="n">
-        <v>30.37685775756836</v>
+        <v>27.17063512277303</v>
       </c>
       <c r="G132" t="n">
         <v>89</v>
@@ -4002,16 +4002,16 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>-0.2214040756225586</v>
+        <v>0.2906467272793288</v>
       </c>
       <c r="D133" t="n">
-        <v>263.1568298339844</v>
+        <v>192.0155835392499</v>
       </c>
       <c r="E133" t="n">
-        <v>331.1899709758736</v>
+        <v>252.3938615676528</v>
       </c>
       <c r="F133" t="n">
-        <v>38.32844543457031</v>
+        <v>30.26120161240219</v>
       </c>
       <c r="G133" t="n">
         <v>99</v>
@@ -4029,16 +4029,16 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>-1.39612340927124</v>
+        <v>-7.778785152978932</v>
       </c>
       <c r="D134" t="n">
-        <v>417.8755798339844</v>
+        <v>908.4598283665155</v>
       </c>
       <c r="E134" t="n">
-        <v>496.4008744200598</v>
+        <v>950.1564947757618</v>
       </c>
       <c r="F134" t="n">
-        <v>55.5401496887207</v>
+        <v>109.8214920131008</v>
       </c>
       <c r="G134" t="n">
         <v>93</v>
@@ -4056,16 +4056,16 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>-0.4721436500549316</v>
+        <v>-0.7085817619994403</v>
       </c>
       <c r="D135" t="n">
-        <v>7.441687107086182</v>
+        <v>8.220913208447969</v>
       </c>
       <c r="E135" t="n">
-        <v>10.57938818101822</v>
+        <v>11.39733609356648</v>
       </c>
       <c r="F135" t="n">
-        <v>65.43144989013672</v>
+        <v>75.11044094170445</v>
       </c>
       <c r="G135" t="n">
         <v>78</v>
@@ -4083,16 +4083,16 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>-4.587074756622314</v>
+        <v>-2.287796817830702</v>
       </c>
       <c r="D136" t="n">
-        <v>207.5157470703125</v>
+        <v>147.4629486931695</v>
       </c>
       <c r="E136" t="n">
-        <v>224.162399277845</v>
+        <v>171.9582610127163</v>
       </c>
       <c r="F136" t="n">
-        <v>74.51040649414062</v>
+        <v>52.38661347199183</v>
       </c>
       <c r="G136" t="n">
         <v>18</v>
@@ -4110,16 +4110,16 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>-0.6704286336898804</v>
+        <v>-0.8531635263972166</v>
       </c>
       <c r="D137" t="n">
-        <v>22.22757148742676</v>
+        <v>22.97960030630733</v>
       </c>
       <c r="E137" t="n">
-        <v>29.61316454146966</v>
+        <v>31.19088855497812</v>
       </c>
       <c r="F137" t="n">
-        <v>26.97259712219238</v>
+        <v>27.27495947709004</v>
       </c>
       <c r="G137" t="n">
         <v>89</v>
@@ -4137,16 +4137,16 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>-1.594769954681396</v>
+        <v>-0.5045333253473865</v>
       </c>
       <c r="D138" t="n">
-        <v>389.5184631347656</v>
+        <v>307.8393522320372</v>
       </c>
       <c r="E138" t="n">
-        <v>482.7218078251696</v>
+        <v>367.5770650679033</v>
       </c>
       <c r="F138" t="n">
-        <v>45.48021697998047</v>
+        <v>36.59159108424544</v>
       </c>
       <c r="G138" t="n">
         <v>99</v>
@@ -4164,16 +4164,16 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>-2.011883974075317</v>
+        <v>0.3075144052823965</v>
       </c>
       <c r="D139" t="n">
-        <v>431.79150390625</v>
+        <v>202.5840349094842</v>
       </c>
       <c r="E139" t="n">
-        <v>556.5408790017136</v>
+        <v>266.8598900957132</v>
       </c>
       <c r="F139" t="n">
-        <v>54.32023239135742</v>
+        <v>22.36433626196781</v>
       </c>
       <c r="G139" t="n">
         <v>93</v>
@@ -4191,16 +4191,16 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>-0.4593362808227539</v>
+        <v>-0.3703133102812413</v>
       </c>
       <c r="D140" t="n">
-        <v>7.409061431884766</v>
+        <v>6.824401552860554</v>
       </c>
       <c r="E140" t="n">
-        <v>10.5332684945473</v>
+        <v>10.20693643726401</v>
       </c>
       <c r="F140" t="n">
-        <v>82.42741394042969</v>
+        <v>59.28397505340374</v>
       </c>
       <c r="G140" t="n">
         <v>78</v>
@@ -4218,16 +4218,16 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>-4.418069362640381</v>
+        <v>-3.284866441649849</v>
       </c>
       <c r="D141" t="n">
-        <v>201.0440368652344</v>
+        <v>179.1670479244656</v>
       </c>
       <c r="E141" t="n">
-        <v>220.7459831174737</v>
+        <v>196.3085448929817</v>
       </c>
       <c r="F141" t="n">
-        <v>71.77607727050781</v>
+        <v>66.55249286052131</v>
       </c>
       <c r="G141" t="n">
         <v>18</v>
@@ -4245,16 +4245,16 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>-0.7828526496887207</v>
+        <v>-1.345273440891891</v>
       </c>
       <c r="D142" t="n">
-        <v>22.07625961303711</v>
+        <v>27.79285992397351</v>
       </c>
       <c r="E142" t="n">
-        <v>30.59345972315049</v>
+        <v>35.08872741802877</v>
       </c>
       <c r="F142" t="n">
-        <v>25.61226463317871</v>
+        <v>32.75507705737736</v>
       </c>
       <c r="G142" t="n">
         <v>89</v>
@@ -4272,16 +4272,16 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>-1.489524364471436</v>
+        <v>-0.7574707718889857</v>
       </c>
       <c r="D143" t="n">
-        <v>391.0841674804688</v>
+        <v>333.5364376800229</v>
       </c>
       <c r="E143" t="n">
-        <v>472.8307208980821</v>
+        <v>397.2752919258938</v>
       </c>
       <c r="F143" t="n">
-        <v>51.20028686523438</v>
+        <v>40.19958461288206</v>
       </c>
       <c r="G143" t="n">
         <v>99</v>
@@ -4299,16 +4299,16 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>-2.431859254837036</v>
+        <v>-0.06918532449495607</v>
       </c>
       <c r="D144" t="n">
-        <v>373.7655944824219</v>
+        <v>249.8326429141465</v>
       </c>
       <c r="E144" t="n">
-        <v>594.0769100040835</v>
+        <v>331.5922912038361</v>
       </c>
       <c r="F144" t="n">
-        <v>45.71588897705078</v>
+        <v>31.23092711144416</v>
       </c>
       <c r="G144" t="n">
         <v>93</v>
@@ -4326,16 +4326,16 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>-0.6769697666168213</v>
+        <v>-0.5536352137501517</v>
       </c>
       <c r="D145" t="n">
-        <v>8.663174629211426</v>
+        <v>7.606344626500056</v>
       </c>
       <c r="E145" t="n">
-        <v>11.29140735811764</v>
+        <v>10.86825951906584</v>
       </c>
       <c r="F145" t="n">
-        <v>83.65188598632812</v>
+        <v>69.97156774596495</v>
       </c>
       <c r="G145" t="n">
         <v>78</v>
@@ -4353,16 +4353,16 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>-3.24021577835083</v>
+        <v>-2.559879497521367</v>
       </c>
       <c r="D146" t="n">
-        <v>164.5927886962891</v>
+        <v>161.5123566521539</v>
       </c>
       <c r="E146" t="n">
-        <v>195.2830277763534</v>
+        <v>178.9320789030973</v>
       </c>
       <c r="F146" t="n">
-        <v>56.28565979003906</v>
+        <v>56.75649690036172</v>
       </c>
       <c r="G146" t="n">
         <v>18</v>
@@ -4380,16 +4380,16 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>-0.7050124406814575</v>
+        <v>-0.9634038307887671</v>
       </c>
       <c r="D147" t="n">
-        <v>21.15182495117188</v>
+        <v>24.07616315263041</v>
       </c>
       <c r="E147" t="n">
-        <v>29.91814394166293</v>
+        <v>32.10522308677784</v>
       </c>
       <c r="F147" t="n">
-        <v>25.36919403076172</v>
+        <v>28.41969330531283</v>
       </c>
       <c r="G147" t="n">
         <v>89</v>
@@ -4407,16 +4407,16 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>-1.294517755508423</v>
+        <v>-1.355430153346738</v>
       </c>
       <c r="D148" t="n">
-        <v>377.6261291503906</v>
+        <v>388.8000415840534</v>
       </c>
       <c r="E148" t="n">
-        <v>453.9345182677783</v>
+        <v>459.920338337004</v>
       </c>
       <c r="F148" t="n">
-        <v>43.58556365966797</v>
+        <v>44.90932256553143</v>
       </c>
       <c r="G148" t="n">
         <v>99</v>
@@ -4434,16 +4434,16 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>-0.4078384637832642</v>
+        <v>0.3216246240532205</v>
       </c>
       <c r="D149" t="n">
-        <v>297.9008483886719</v>
+        <v>211.6726645192792</v>
       </c>
       <c r="E149" t="n">
-        <v>380.4997330813781</v>
+        <v>264.1271034534338</v>
       </c>
       <c r="F149" t="n">
-        <v>39.27916717529297</v>
+        <v>23.83462466994156</v>
       </c>
       <c r="G149" t="n">
         <v>93</v>
@@ -4461,16 +4461,16 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>-0.4369560480117798</v>
+        <v>-0.487875622923567</v>
       </c>
       <c r="D150" t="n">
-        <v>7.417525291442871</v>
+        <v>7.483346865727351</v>
       </c>
       <c r="E150" t="n">
-        <v>10.45218817329</v>
+        <v>10.63576630917857</v>
       </c>
       <c r="F150" t="n">
-        <v>78.09659576416016</v>
+        <v>72.09116570713144</v>
       </c>
       <c r="G150" t="n">
         <v>78</v>
@@ -4488,16 +4488,16 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>-3.122767448425293</v>
+        <v>-1.272556570194562</v>
       </c>
       <c r="D151" t="n">
-        <v>172.0092010498047</v>
+        <v>125.3054402669271</v>
       </c>
       <c r="E151" t="n">
-        <v>192.5594977046056</v>
+        <v>142.9644015116088</v>
       </c>
       <c r="F151" t="n">
-        <v>61.6312370300293</v>
+        <v>47.36993041364592</v>
       </c>
       <c r="G151" t="n">
         <v>18</v>
@@ -4515,16 +4515,16 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>-0.5053284168243408</v>
+        <v>-1.095590839417806</v>
       </c>
       <c r="D152" t="n">
-        <v>20.16596412658691</v>
+        <v>25.2393757252211</v>
       </c>
       <c r="E152" t="n">
-        <v>28.11166024792081</v>
+        <v>33.1683693311759</v>
       </c>
       <c r="F152" t="n">
-        <v>24.46437835693359</v>
+        <v>29.7866658678733</v>
       </c>
       <c r="G152" t="n">
         <v>89</v>
@@ -4542,16 +4542,16 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>-1.710526943206787</v>
+        <v>-1.028085373933347</v>
       </c>
       <c r="D153" t="n">
-        <v>417.5588989257812</v>
+        <v>348.3906895801275</v>
       </c>
       <c r="E153" t="n">
-        <v>493.3718488624984</v>
+        <v>426.7667901416077</v>
       </c>
       <c r="F153" t="n">
-        <v>48.75337219238281</v>
+        <v>40.2000140876372</v>
       </c>
       <c r="G153" t="n">
         <v>99</v>
@@ -4569,16 +4569,16 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>-0.2200586795806885</v>
+        <v>-2.177581826703654</v>
       </c>
       <c r="D154" t="n">
-        <v>284.7681579589844</v>
+        <v>516.490470640121</v>
       </c>
       <c r="E154" t="n">
-        <v>354.216112969893</v>
+        <v>571.6448596374726</v>
       </c>
       <c r="F154" t="n">
-        <v>30.98860740661621</v>
+        <v>61.28718895743469</v>
       </c>
       <c r="G154" t="n">
         <v>93</v>
@@ -4596,16 +4596,16 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>-0.4332907199859619</v>
+        <v>-0.4115316204798642</v>
       </c>
       <c r="D155" t="n">
-        <v>6.960641860961914</v>
+        <v>7.025651763647031</v>
       </c>
       <c r="E155" t="n">
-        <v>10.43884889943402</v>
+        <v>10.3593087705962</v>
       </c>
       <c r="F155" t="n">
-        <v>63.46746826171875</v>
+        <v>67.82388180037563</v>
       </c>
       <c r="G155" t="n">
         <v>78</v>
@@ -4623,16 +4623,16 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>-3.372340202331543</v>
+        <v>-1.936940944446074</v>
       </c>
       <c r="D156" t="n">
-        <v>176.1928100585938</v>
+        <v>141.7605573866102</v>
       </c>
       <c r="E156" t="n">
-        <v>198.3021881182858</v>
+        <v>162.5242483105625</v>
       </c>
       <c r="F156" t="n">
-        <v>63.12104415893555</v>
+        <v>53.56320760337226</v>
       </c>
       <c r="G156" t="n">
         <v>18</v>
@@ -4650,16 +4650,16 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>-0.8762103319168091</v>
+        <v>-1.48100746612016</v>
       </c>
       <c r="D157" t="n">
-        <v>23.54755783081055</v>
+        <v>28.93659242351404</v>
       </c>
       <c r="E157" t="n">
-        <v>31.38424096668084</v>
+        <v>36.08983617175682</v>
       </c>
       <c r="F157" t="n">
-        <v>27.69512748718262</v>
+        <v>34.40960298823308</v>
       </c>
       <c r="G157" t="n">
         <v>89</v>
@@ -4677,16 +4677,16 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>-2.138822078704834</v>
+        <v>-1.640644065585972</v>
       </c>
       <c r="D158" t="n">
-        <v>452.5007629394531</v>
+        <v>417.1304762098524</v>
       </c>
       <c r="E158" t="n">
-        <v>530.9221635513063</v>
+        <v>486.9702533058045</v>
       </c>
       <c r="F158" t="n">
-        <v>54.26241683959961</v>
+        <v>48.64340495597759</v>
       </c>
       <c r="G158" t="n">
         <v>99</v>
@@ -4704,16 +4704,16 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>-0.741801381111145</v>
+        <v>-0.809835937473756</v>
       </c>
       <c r="D159" t="n">
-        <v>301.8694458007812</v>
+        <v>325.8220516738071</v>
       </c>
       <c r="E159" t="n">
-        <v>423.2307844131851</v>
+        <v>431.4172785441124</v>
       </c>
       <c r="F159" t="n">
-        <v>31.60564613342285</v>
+        <v>40.70779913013961</v>
       </c>
       <c r="G159" t="n">
         <v>93</v>
@@ -4731,16 +4731,16 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>-0.6554282903671265</v>
+        <v>-0.6246180896953344</v>
       </c>
       <c r="D160" t="n">
-        <v>7.885402679443359</v>
+        <v>7.931690772374471</v>
       </c>
       <c r="E160" t="n">
-        <v>11.2186513912362</v>
+        <v>11.11376257114519</v>
       </c>
       <c r="F160" t="n">
-        <v>69.83684539794922</v>
+        <v>68.83928089466973</v>
       </c>
       <c r="G160" t="n">
         <v>78</v>
@@ -4758,16 +4758,16 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>-3.03293514251709</v>
+        <v>-2.885583923169835</v>
       </c>
       <c r="D161" t="n">
-        <v>163.6283264160156</v>
+        <v>168.4930956098768</v>
       </c>
       <c r="E161" t="n">
-        <v>190.4500836833631</v>
+        <v>186.9384794771434</v>
       </c>
       <c r="F161" t="n">
-        <v>54.27779006958008</v>
+        <v>60.77423701855869</v>
       </c>
       <c r="G161" t="n">
         <v>18</v>
@@ -4785,16 +4785,16 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>-0.5882285833358765</v>
+        <v>-0.8189559065681395</v>
       </c>
       <c r="D162" t="n">
-        <v>20.70325469970703</v>
+        <v>22.64288844419329</v>
       </c>
       <c r="E162" t="n">
-        <v>28.87535722519831</v>
+        <v>30.90167073629803</v>
       </c>
       <c r="F162" t="n">
-        <v>24.98853302001953</v>
+        <v>26.87957276265286</v>
       </c>
       <c r="G162" t="n">
         <v>89</v>
@@ -4812,16 +4812,16 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>-2.13313889503479</v>
+        <v>-1.129452536381352</v>
       </c>
       <c r="D163" t="n">
-        <v>448.6455078125</v>
+        <v>360.2670426802202</v>
       </c>
       <c r="E163" t="n">
-        <v>530.4412962336172</v>
+        <v>437.3020186802627</v>
       </c>
       <c r="F163" t="n">
-        <v>51.80421447753906</v>
+        <v>41.68706439333613</v>
       </c>
       <c r="G163" t="n">
         <v>99</v>
@@ -4839,16 +4839,16 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>-0.05384910106658936</v>
+        <v>0.08318476610296421</v>
       </c>
       <c r="D164" t="n">
-        <v>240.8295593261719</v>
+        <v>241.4593479607695</v>
       </c>
       <c r="E164" t="n">
-        <v>329.2055660032194</v>
+        <v>307.0568862263958</v>
       </c>
       <c r="F164" t="n">
-        <v>29.26752471923828</v>
+        <v>27.01222847366</v>
       </c>
       <c r="G164" t="n">
         <v>93</v>
@@ -4866,16 +4866,16 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>-0.527639627456665</v>
+        <v>-0.4486146321315188</v>
       </c>
       <c r="D165" t="n">
-        <v>7.682138442993164</v>
+        <v>7.459526294317001</v>
       </c>
       <c r="E165" t="n">
-        <v>10.77695120649291</v>
+        <v>10.49450372312883</v>
       </c>
       <c r="F165" t="n">
-        <v>72.72779083251953</v>
+        <v>74.22349258325052</v>
       </c>
       <c r="G165" t="n">
         <v>78</v>
@@ -4893,16 +4893,16 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>-3.041323661804199</v>
+        <v>-3.44898333738496</v>
       </c>
       <c r="D166" t="n">
-        <v>171.2068481445312</v>
+        <v>181.6192251841227</v>
       </c>
       <c r="E166" t="n">
-        <v>190.6480416402172</v>
+        <v>200.0326777611348</v>
       </c>
       <c r="F166" t="n">
-        <v>61.39746475219727</v>
+        <v>63.45750666217295</v>
       </c>
       <c r="G166" t="n">
         <v>18</v>
@@ -4920,16 +4920,16 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>-1.500434160232544</v>
+        <v>-1.57102663979183</v>
       </c>
       <c r="D167" t="n">
-        <v>28.57511520385742</v>
+        <v>28.72835465763392</v>
       </c>
       <c r="E167" t="n">
-        <v>36.23085431904001</v>
+        <v>36.73873202702739</v>
       </c>
       <c r="F167" t="n">
-        <v>34.70959091186523</v>
+        <v>34.0664934614391</v>
       </c>
       <c r="G167" t="n">
         <v>89</v>
@@ -4947,16 +4947,16 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>-1.691301822662354</v>
+        <v>-1.051965526072566</v>
       </c>
       <c r="D168" t="n">
-        <v>388.3124084472656</v>
+        <v>357.8331617875533</v>
       </c>
       <c r="E168" t="n">
-        <v>491.6190566637953</v>
+        <v>429.271968553525</v>
       </c>
       <c r="F168" t="n">
-        <v>47.00406646728516</v>
+        <v>41.68425796419069</v>
       </c>
       <c r="G168" t="n">
         <v>99</v>
@@ -4974,16 +4974,16 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>-6.793727874755859</v>
+        <v>0.3106887355032416</v>
       </c>
       <c r="D169" t="n">
-        <v>349.1061401367188</v>
+        <v>195.3682388797883</v>
       </c>
       <c r="E169" t="n">
-        <v>895.2628454817054</v>
+        <v>266.247549259546</v>
       </c>
       <c r="F169" t="n">
-        <v>44.89113235473633</v>
+        <v>19.86175408144076</v>
       </c>
       <c r="G169" t="n">
         <v>93</v>
@@ -5001,16 +5001,16 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>-0.669105052947998</v>
+        <v>-0.484445551697869</v>
       </c>
       <c r="D170" t="n">
-        <v>8.187958717346191</v>
+        <v>7.412311914639595</v>
       </c>
       <c r="E170" t="n">
-        <v>11.26489898839532</v>
+        <v>10.62349966360322</v>
       </c>
       <c r="F170" t="n">
-        <v>70.44698333740234</v>
+        <v>72.04370279000301</v>
       </c>
       <c r="G170" t="n">
         <v>78</v>
@@ -5028,16 +5028,16 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>-4.522716999053955</v>
+        <v>-4.842999472487429</v>
       </c>
       <c r="D171" t="n">
-        <v>199.8318023681641</v>
+        <v>208.0137557983398</v>
       </c>
       <c r="E171" t="n">
-        <v>222.867594871372</v>
+        <v>229.238988064794</v>
       </c>
       <c r="F171" t="n">
-        <v>69.36630249023438</v>
+        <v>71.75721288077494</v>
       </c>
       <c r="G171" t="n">
         <v>18</v>
@@ -5055,16 +5055,16 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>-1.385589361190796</v>
+        <v>-1.193412146943791</v>
       </c>
       <c r="D172" t="n">
-        <v>27.47403907775879</v>
+        <v>26.14771973684933</v>
       </c>
       <c r="E172" t="n">
-        <v>35.38903487045811</v>
+        <v>33.93368289558074</v>
       </c>
       <c r="F172" t="n">
-        <v>33.29476165771484</v>
+        <v>31.62254244447875</v>
       </c>
       <c r="G172" t="n">
         <v>89</v>
@@ -5082,16 +5082,16 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>-1.297470092773438</v>
+        <v>-1.401639604513679</v>
       </c>
       <c r="D173" t="n">
-        <v>362.0537414550781</v>
+        <v>388.0246346213601</v>
       </c>
       <c r="E173" t="n">
-        <v>454.2264543980238</v>
+        <v>464.4098455651067</v>
       </c>
       <c r="F173" t="n">
-        <v>43.25692749023438</v>
+        <v>44.88269622960549</v>
       </c>
       <c r="G173" t="n">
         <v>99</v>
@@ -5109,16 +5109,16 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>-1.514548540115356</v>
+        <v>-0.1496749313768149</v>
       </c>
       <c r="D174" t="n">
-        <v>293.6647033691406</v>
+        <v>221.446033108619</v>
       </c>
       <c r="E174" t="n">
-        <v>508.5199111145993</v>
+        <v>343.8471760488247</v>
       </c>
       <c r="F174" t="n">
-        <v>38.49166488647461</v>
+        <v>22.40465068644746</v>
       </c>
       <c r="G174" t="n">
         <v>93</v>
@@ -5136,16 +5136,16 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>-0.4793814420700073</v>
+        <v>-0.6739863618483759</v>
       </c>
       <c r="D175" t="n">
-        <v>7.855620384216309</v>
+        <v>8.363069601548023</v>
       </c>
       <c r="E175" t="n">
-        <v>10.60536335985849</v>
+        <v>11.28135926318062</v>
       </c>
       <c r="F175" t="n">
-        <v>81.51303100585938</v>
+        <v>75.05730168451808</v>
       </c>
       <c r="G175" t="n">
         <v>78</v>
@@ -5163,16 +5163,16 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>-4.996468544006348</v>
+        <v>-5.434134252739033</v>
       </c>
       <c r="D176" t="n">
-        <v>209.9504547119141</v>
+        <v>222.8589004940457</v>
       </c>
       <c r="E176" t="n">
-        <v>232.2299927469533</v>
+        <v>240.5556813642854</v>
       </c>
       <c r="F176" t="n">
-        <v>72.30362701416016</v>
+        <v>78.29940345170795</v>
       </c>
       <c r="G176" t="n">
         <v>18</v>
@@ -5190,16 +5190,16 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>-1.026478290557861</v>
+        <v>-1.181931489314813</v>
       </c>
       <c r="D177" t="n">
-        <v>24.33605194091797</v>
+        <v>26.44576790627469</v>
       </c>
       <c r="E177" t="n">
-        <v>32.61683663733444</v>
+        <v>33.84475931680016</v>
       </c>
       <c r="F177" t="n">
-        <v>28.94099426269531</v>
+        <v>32.27434650102909</v>
       </c>
       <c r="G177" t="n">
         <v>89</v>
@@ -5217,16 +5217,16 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>-1.645445823669434</v>
+        <v>-0.5399217693191263</v>
       </c>
       <c r="D178" t="n">
-        <v>343.4540710449219</v>
+        <v>289.5303808655402</v>
       </c>
       <c r="E178" t="n">
-        <v>487.4127966877767</v>
+        <v>371.8748682019462</v>
       </c>
       <c r="F178" t="n">
-        <v>44.2984733581543</v>
+        <v>33.61116496967822</v>
       </c>
       <c r="G178" t="n">
         <v>99</v>
@@ -5244,16 +5244,16 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>-4.078596115112305</v>
+        <v>0.10476510191847</v>
       </c>
       <c r="D179" t="n">
-        <v>327.514892578125</v>
+        <v>229.6904132801999</v>
       </c>
       <c r="E179" t="n">
-        <v>722.6862432964945</v>
+        <v>303.4215571715994</v>
       </c>
       <c r="F179" t="n">
-        <v>41.29995346069336</v>
+        <v>21.92118036691907</v>
       </c>
       <c r="G179" t="n">
         <v>93</v>
@@ -5271,16 +5271,16 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>-0.4946976900100708</v>
+        <v>-0.5016879169221551</v>
       </c>
       <c r="D180" t="n">
-        <v>6.949336051940918</v>
+        <v>7.009259538772779</v>
       </c>
       <c r="E180" t="n">
-        <v>10.66012118100681</v>
+        <v>10.68501940720207</v>
       </c>
       <c r="F180" t="n">
-        <v>66.17501831054688</v>
+        <v>68.60414344019313</v>
       </c>
       <c r="G180" t="n">
         <v>78</v>
@@ -5298,16 +5298,16 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>-4.155950546264648</v>
+        <v>-5.704957952355044</v>
       </c>
       <c r="D181" t="n">
-        <v>189.2391967773438</v>
+        <v>227.1795060899523</v>
       </c>
       <c r="E181" t="n">
-        <v>215.3401016415661</v>
+        <v>245.5661992348554</v>
       </c>
       <c r="F181" t="n">
-        <v>66.09856414794922</v>
+        <v>80.18053091940195</v>
       </c>
       <c r="G181" t="n">
         <v>18</v>
@@ -5325,16 +5325,16 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>-0.8293888568878174</v>
+        <v>-0.7737153157260259</v>
       </c>
       <c r="D182" t="n">
-        <v>21.05764961242676</v>
+        <v>20.59147341867511</v>
       </c>
       <c r="E182" t="n">
-        <v>30.99016390387541</v>
+        <v>30.51496197061769</v>
       </c>
       <c r="F182" t="n">
-        <v>25.27356719970703</v>
+        <v>25.19127483114824</v>
       </c>
       <c r="G182" t="n">
         <v>89</v>
@@ -5352,16 +5352,16 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>-1.133171081542969</v>
+        <v>-0.5980159636764126</v>
       </c>
       <c r="D183" t="n">
-        <v>350.672119140625</v>
+        <v>300.747309366862</v>
       </c>
       <c r="E183" t="n">
-        <v>437.6836578797522</v>
+        <v>378.8244982111472</v>
       </c>
       <c r="F183" t="n">
-        <v>40.77842712402344</v>
+        <v>34.9584511159384</v>
       </c>
       <c r="G183" t="n">
         <v>99</v>
@@ -5379,16 +5379,16 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>-1.139641523361206</v>
+        <v>-0.4192392899065511</v>
       </c>
       <c r="D184" t="n">
-        <v>374.1591186523438</v>
+        <v>283.83887210969</v>
       </c>
       <c r="E184" t="n">
-        <v>469.0816659975105</v>
+        <v>382.0372795667112</v>
       </c>
       <c r="F184" t="n">
-        <v>33.17684555053711</v>
+        <v>27.12598296813371</v>
       </c>
       <c r="G184" t="n">
         <v>93</v>
@@ -5406,16 +5406,16 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>-0.3495240211486816</v>
+        <v>-0.3209425473466254</v>
       </c>
       <c r="D185" t="n">
-        <v>7.228414058685303</v>
+        <v>6.762462295018709</v>
       </c>
       <c r="E185" t="n">
-        <v>10.1292146929271</v>
+        <v>10.02137783586598</v>
       </c>
       <c r="F185" t="n">
-        <v>69.87036895751953</v>
+        <v>63.46487177085781</v>
       </c>
       <c r="G185" t="n">
         <v>78</v>
@@ -5433,16 +5433,16 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>-7.296979904174805</v>
+        <v>-6.612655673670171</v>
       </c>
       <c r="D186" t="n">
-        <v>256.3479309082031</v>
+        <v>244.3405620786879</v>
       </c>
       <c r="E186" t="n">
-        <v>273.1684605010249</v>
+        <v>261.6607925499394</v>
       </c>
       <c r="F186" t="n">
-        <v>93.13971710205078</v>
+        <v>87.21091131533932</v>
       </c>
       <c r="G186" t="n">
         <v>18</v>
@@ -5460,16 +5460,16 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>-0.7906651496887207</v>
+        <v>-0.6859531200312967</v>
       </c>
       <c r="D187" t="n">
-        <v>20.93840980529785</v>
+        <v>20.90576585491052</v>
       </c>
       <c r="E187" t="n">
-        <v>30.66041678168388</v>
+        <v>29.75045568668752</v>
       </c>
       <c r="F187" t="n">
-        <v>25.41339683532715</v>
+        <v>24.8303162198921</v>
       </c>
       <c r="G187" t="n">
         <v>89</v>
@@ -5487,16 +5487,16 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>-0.9503151178359985</v>
+        <v>-1.595193658382587</v>
       </c>
       <c r="D188" t="n">
-        <v>331.0310668945312</v>
+        <v>397.7707363860775</v>
       </c>
       <c r="E188" t="n">
-        <v>418.5042562507579</v>
+        <v>482.7612304650125</v>
       </c>
       <c r="F188" t="n">
-        <v>38.33175277709961</v>
+        <v>45.27820645319858</v>
       </c>
       <c r="G188" t="n">
         <v>99</v>
@@ -5514,16 +5514,16 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>-1.411351680755615</v>
+        <v>-0.5281032095883167</v>
       </c>
       <c r="D189" t="n">
-        <v>404.5006713867188</v>
+        <v>303.2670196205057</v>
       </c>
       <c r="E189" t="n">
-        <v>497.9757932118789</v>
+        <v>396.4188296505387</v>
       </c>
       <c r="F189" t="n">
-        <v>36.01168823242188</v>
+        <v>27.40728501865978</v>
       </c>
       <c r="G189" t="n">
         <v>93</v>
@@ -5541,16 +5541,16 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>-0.3084936141967773</v>
+        <v>-0.3055540835975885</v>
       </c>
       <c r="D190" t="n">
-        <v>6.6982102394104</v>
+        <v>6.777614067762326</v>
       </c>
       <c r="E190" t="n">
-        <v>9.974043920297495</v>
+        <v>9.962834268920245</v>
       </c>
       <c r="F190" t="n">
-        <v>64.61605072021484</v>
+        <v>67.02995813785493</v>
       </c>
       <c r="G190" t="n">
         <v>78</v>
@@ -5568,16 +5568,16 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>-7.654361724853516</v>
+        <v>-6.592115820727323</v>
       </c>
       <c r="D191" t="n">
-        <v>262.2432556152344</v>
+        <v>243.5471409691705</v>
       </c>
       <c r="E191" t="n">
-        <v>278.9896251431225</v>
+        <v>261.3075581089995</v>
       </c>
       <c r="F191" t="n">
-        <v>95.55823516845703</v>
+        <v>86.9311771965266</v>
       </c>
       <c r="G191" t="n">
         <v>18</v>
@@ -5595,16 +5595,16 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>-0.4916516542434692</v>
+        <v>-0.5730754107223257</v>
       </c>
       <c r="D192" t="n">
-        <v>20.20565414428711</v>
+        <v>20.83181387654851</v>
       </c>
       <c r="E192" t="n">
-        <v>27.98366288003759</v>
+        <v>28.73727912215473</v>
       </c>
       <c r="F192" t="n">
-        <v>25.26352310180664</v>
+        <v>25.77138753467707</v>
       </c>
       <c r="G192" t="n">
         <v>89</v>
@@ -5622,16 +5622,16 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>-0.3916287422180176</v>
+        <v>-0.3673279360154236</v>
       </c>
       <c r="D193" t="n">
-        <v>290.5246887207031</v>
+        <v>284.9367307412504</v>
       </c>
       <c r="E193" t="n">
-        <v>353.5160887427897</v>
+        <v>350.4159318756999</v>
       </c>
       <c r="F193" t="n">
-        <v>38.79452133178711</v>
+        <v>36.88292960719551</v>
       </c>
       <c r="G193" t="n">
         <v>99</v>
@@ -5649,16 +5649,16 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>-0.280098557472229</v>
+        <v>-0.3657510048857195</v>
       </c>
       <c r="D194" t="n">
-        <v>286.1315612792969</v>
+        <v>294.7666409400202</v>
       </c>
       <c r="E194" t="n">
-        <v>362.8270507418101</v>
+        <v>374.7690306696877</v>
       </c>
       <c r="F194" t="n">
-        <v>29.4891414642334</v>
+        <v>29.99658580731779</v>
       </c>
       <c r="G194" t="n">
         <v>93</v>
@@ -5676,16 +5676,16 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>-0.5774438381195068</v>
+        <v>-0.5832204284844578</v>
       </c>
       <c r="D195" t="n">
-        <v>7.284372329711914</v>
+        <v>7.323860425215501</v>
       </c>
       <c r="E195" t="n">
-        <v>10.95121802954203</v>
+        <v>10.97125134618378</v>
       </c>
       <c r="F195" t="n">
-        <v>68.80508422851562</v>
+        <v>71.07536894882848</v>
       </c>
       <c r="G195" t="n">
         <v>78</v>
@@ -5703,16 +5703,16 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>-6.854687690734863</v>
+        <v>-6.581562341933037</v>
       </c>
       <c r="D196" t="n">
-        <v>250.5045623779297</v>
+        <v>246.5816640853882</v>
       </c>
       <c r="E196" t="n">
-        <v>265.7877736559754</v>
+        <v>261.1258786637104</v>
       </c>
       <c r="F196" t="n">
-        <v>91.73206329345703</v>
+        <v>90.86408683880106</v>
       </c>
       <c r="G196" t="n">
         <v>18</v>
@@ -5730,16 +5730,16 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>-0.6139136552810669</v>
+        <v>-0.4892588499959918</v>
       </c>
       <c r="D197" t="n">
-        <v>20.77426719665527</v>
+        <v>19.91595911176017</v>
       </c>
       <c r="E197" t="n">
-        <v>29.10790933306938</v>
+        <v>27.96121055100132</v>
       </c>
       <c r="F197" t="n">
-        <v>25.36038398742676</v>
+        <v>24.97735664056718</v>
       </c>
       <c r="G197" t="n">
         <v>89</v>
@@ -5757,16 +5757,16 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>-0.5022553205490112</v>
+        <v>-0.3025128698533766</v>
       </c>
       <c r="D198" t="n">
-        <v>302.6532287597656</v>
+        <v>279.6751269716205</v>
       </c>
       <c r="E198" t="n">
-        <v>367.2986906116057</v>
+        <v>342.0097692215887</v>
       </c>
       <c r="F198" t="n">
-        <v>39.59960556030273</v>
+        <v>36.44694688524324</v>
       </c>
       <c r="G198" t="n">
         <v>99</v>
@@ -5784,16 +5784,16 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>-0.362338662147522</v>
+        <v>-0.431842331712204</v>
       </c>
       <c r="D199" t="n">
-        <v>293.5261840820312</v>
+        <v>295.5335913217196</v>
       </c>
       <c r="E199" t="n">
-        <v>374.3005560375245</v>
+        <v>383.7298024361041</v>
       </c>
       <c r="F199" t="n">
-        <v>30.14885711669922</v>
+        <v>29.73390583123148</v>
       </c>
       <c r="G199" t="n">
         <v>93</v>
@@ -5811,16 +5811,16 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>-0.6727986335754395</v>
+        <v>-0.5156291550783556</v>
       </c>
       <c r="D200" t="n">
-        <v>7.609975337982178</v>
+        <v>7.098525579159077</v>
       </c>
       <c r="E200" t="n">
-        <v>11.27735626568841</v>
+        <v>10.73450314585387</v>
       </c>
       <c r="F200" t="n">
-        <v>73.42767333984375</v>
+        <v>69.92411300769544</v>
       </c>
       <c r="G200" t="n">
         <v>78</v>
@@ -5838,16 +5838,16 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>-6.564089298248291</v>
+        <v>-6.532803423001697</v>
       </c>
       <c r="D201" t="n">
-        <v>245.63671875</v>
+        <v>246.615955458747</v>
       </c>
       <c r="E201" t="n">
-        <v>260.8247885314968</v>
+        <v>260.2848414157096</v>
       </c>
       <c r="F201" t="n">
-        <v>90.32256317138672</v>
+        <v>91.3835243013549</v>
       </c>
       <c r="G201" t="n">
         <v>18</v>
@@ -5865,16 +5865,16 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>-0.913367748260498</v>
+        <v>-0.6894163457939881</v>
       </c>
       <c r="D202" t="n">
-        <v>21.86464691162109</v>
+        <v>20.89076710818859</v>
       </c>
       <c r="E202" t="n">
-        <v>31.69349171347625</v>
+        <v>29.78099618220231</v>
       </c>
       <c r="F202" t="n">
-        <v>26.37405014038086</v>
+        <v>25.28582178639046</v>
       </c>
       <c r="G202" t="n">
         <v>89</v>
@@ -5892,16 +5892,16 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>-1.094445466995239</v>
+        <v>-1.091980348144591</v>
       </c>
       <c r="D203" t="n">
-        <v>350.2470092773438</v>
+        <v>356.6549895315459</v>
       </c>
       <c r="E203" t="n">
-        <v>433.69262949121</v>
+        <v>433.4373177625236</v>
       </c>
       <c r="F203" t="n">
-        <v>40.4015007019043</v>
+        <v>41.31209520960022</v>
       </c>
       <c r="G203" t="n">
         <v>99</v>
@@ -5919,16 +5919,16 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>-1.149841070175171</v>
+        <v>-0.2048844240993919</v>
       </c>
       <c r="D204" t="n">
-        <v>378.75</v>
+        <v>262.9507485666583</v>
       </c>
       <c r="E204" t="n">
-        <v>470.1983790114551</v>
+        <v>352.0064538855678</v>
       </c>
       <c r="F204" t="n">
-        <v>34.24449157714844</v>
+        <v>24.80638876358671</v>
       </c>
       <c r="G204" t="n">
         <v>93</v>
@@ -5946,16 +5946,16 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>-0.4685951471328735</v>
+        <v>-0.3816154222879873</v>
       </c>
       <c r="D205" t="n">
-        <v>7.609954833984375</v>
+        <v>7.202038340079478</v>
       </c>
       <c r="E205" t="n">
-        <v>10.56663008080857</v>
+        <v>10.24894254149048</v>
       </c>
       <c r="F205" t="n">
-        <v>74.52328491210938</v>
+        <v>70.72209514067517</v>
       </c>
       <c r="G205" t="n">
         <v>78</v>
@@ -5973,16 +5973,16 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>-7.463031768798828</v>
+        <v>-6.587957741996147</v>
       </c>
       <c r="D206" t="n">
-        <v>258.5137939453125</v>
+        <v>243.619836807251</v>
       </c>
       <c r="E206" t="n">
-        <v>275.8884511899691</v>
+        <v>261.2359913523923</v>
       </c>
       <c r="F206" t="n">
-        <v>93.88908386230469</v>
+        <v>87.67816704038522</v>
       </c>
       <c r="G206" t="n">
         <v>18</v>
@@ -6000,16 +6000,16 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>-0.8142803907394409</v>
+        <v>-1.062062837643853</v>
       </c>
       <c r="D207" t="n">
-        <v>20.89133453369141</v>
+        <v>23.57145352310009</v>
       </c>
       <c r="E207" t="n">
-        <v>30.86192928511143</v>
+        <v>32.90196399294186</v>
       </c>
       <c r="F207" t="n">
-        <v>25.64138412475586</v>
+        <v>27.60189178024334</v>
       </c>
       <c r="G207" t="n">
         <v>89</v>
@@ -6027,16 +6027,16 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>-1.282088994979858</v>
+        <v>-1.674010595069319</v>
       </c>
       <c r="D208" t="n">
-        <v>367.3950500488281</v>
+        <v>407.2497720429392</v>
       </c>
       <c r="E208" t="n">
-        <v>452.7034418358226</v>
+        <v>490.0372136044042</v>
       </c>
       <c r="F208" t="n">
-        <v>42.37786865234375</v>
+        <v>46.72951577019354</v>
       </c>
       <c r="G208" t="n">
         <v>99</v>
@@ -6054,16 +6054,16 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>-1.643673896789551</v>
+        <v>-0.8402140015070059</v>
       </c>
       <c r="D209" t="n">
-        <v>432.5223999023438</v>
+        <v>345.7704343077957</v>
       </c>
       <c r="E209" t="n">
-        <v>521.4130440447381</v>
+        <v>435.0228772036336</v>
       </c>
       <c r="F209" t="n">
-        <v>39.35187149047852</v>
+        <v>32.74211013665547</v>
       </c>
       <c r="G209" t="n">
         <v>93</v>
@@ -6081,16 +6081,16 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>-0.4100571870803833</v>
+        <v>-0.5122694057041417</v>
       </c>
       <c r="D210" t="n">
-        <v>7.1044921875</v>
+        <v>7.882095055702405</v>
       </c>
       <c r="E210" t="n">
-        <v>10.35389677395722</v>
+        <v>10.72259876638663</v>
       </c>
       <c r="F210" t="n">
-        <v>67.41546630859375</v>
+        <v>73.31591806993941</v>
       </c>
       <c r="G210" t="n">
         <v>78</v>
@@ -6108,16 +6108,16 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>-7.488269805908203</v>
+        <v>-7.125325280372541</v>
       </c>
       <c r="D211" t="n">
-        <v>259.5577392578125</v>
+        <v>253.1430814531114</v>
       </c>
       <c r="E211" t="n">
-        <v>276.2995006555386</v>
+        <v>270.3279413825449</v>
       </c>
       <c r="F211" t="n">
-        <v>94.43543243408203</v>
+        <v>91.58458027849473</v>
       </c>
       <c r="G211" t="n">
         <v>18</v>
@@ -6135,16 +6135,16 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>-1.112508535385132</v>
+        <v>-0.7994784254817366</v>
       </c>
       <c r="D212" t="n">
-        <v>25.61381340026855</v>
+        <v>22.51927671539649</v>
       </c>
       <c r="E212" t="n">
-        <v>33.3019833452388</v>
+        <v>30.73577703620542</v>
       </c>
       <c r="F212" t="n">
-        <v>30.11552047729492</v>
+        <v>26.7567194023869</v>
       </c>
       <c r="G212" t="n">
         <v>89</v>
@@ -6162,16 +6162,16 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>-1.23527717590332</v>
+        <v>-0.5572567249668956</v>
       </c>
       <c r="D213" t="n">
-        <v>361.4527587890625</v>
+        <v>305.0465078642874</v>
       </c>
       <c r="E213" t="n">
-        <v>448.0363057275604</v>
+        <v>373.9621150795205</v>
       </c>
       <c r="F213" t="n">
-        <v>42.64250564575195</v>
+        <v>35.59023074015288</v>
       </c>
       <c r="G213" t="n">
         <v>99</v>
@@ -6189,16 +6189,16 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>-0.2700563669204712</v>
+        <v>0.1955065357424646</v>
       </c>
       <c r="D214" t="n">
-        <v>280.8243713378906</v>
+        <v>216.1748414398521</v>
       </c>
       <c r="E214" t="n">
-        <v>361.4010821614955</v>
+        <v>287.6333180422494</v>
       </c>
       <c r="F214" t="n">
-        <v>34.80622100830078</v>
+        <v>24.23268547353963</v>
       </c>
       <c r="G214" t="n">
         <v>93</v>
@@ -6216,16 +6216,16 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>-0.3852256536483765</v>
+        <v>-0.3592979944907633</v>
       </c>
       <c r="D215" t="n">
-        <v>7.545986175537109</v>
+        <v>7.327245311859326</v>
       </c>
       <c r="E215" t="n">
-        <v>10.26232392581712</v>
+        <v>10.16582923627111</v>
       </c>
       <c r="F215" t="n">
-        <v>72.89524841308594</v>
+        <v>70.08052025963994</v>
       </c>
       <c r="G215" t="n">
         <v>78</v>
@@ -6243,16 +6243,16 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>-4.453226089477539</v>
+        <v>-3.780402228171743</v>
       </c>
       <c r="D216" t="n">
-        <v>202.8054504394531</v>
+        <v>182.9107750786675</v>
       </c>
       <c r="E216" t="n">
-        <v>221.4610134284362</v>
+        <v>207.3493981859992</v>
       </c>
       <c r="F216" t="n">
-        <v>71.04513549804688</v>
+        <v>67.37526607115588</v>
       </c>
       <c r="G216" t="n">
         <v>18</v>
@@ -6270,16 +6270,16 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>-0.9336998462677002</v>
+        <v>-0.7926602087688566</v>
       </c>
       <c r="D217" t="n">
-        <v>23.57936859130859</v>
+        <v>21.60004212883081</v>
       </c>
       <c r="E217" t="n">
-        <v>31.86143917264793</v>
+        <v>30.67749290476109</v>
       </c>
       <c r="F217" t="n">
-        <v>28.92194747924805</v>
+        <v>25.53319352989697</v>
       </c>
       <c r="G217" t="n">
         <v>89</v>
@@ -6297,16 +6297,16 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>-0.7327380180358887</v>
+        <v>-0.7551060916349333</v>
       </c>
       <c r="D218" t="n">
-        <v>320.4478149414062</v>
+        <v>322.4973210806799</v>
       </c>
       <c r="E218" t="n">
-        <v>394.4699766775667</v>
+        <v>397.0079346341175</v>
       </c>
       <c r="F218" t="n">
-        <v>37.18215560913086</v>
+        <v>37.22662924128691</v>
       </c>
       <c r="G218" t="n">
         <v>99</v>
@@ -6324,16 +6324,16 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>-0.7657793760299683</v>
+        <v>0.1039951740504761</v>
       </c>
       <c r="D219" t="n">
-        <v>268.5079956054688</v>
+        <v>220.9435149162046</v>
       </c>
       <c r="E219" t="n">
-        <v>426.1339834782013</v>
+        <v>303.5520047816537</v>
       </c>
       <c r="F219" t="n">
-        <v>34.10477066040039</v>
+        <v>24.97887596248838</v>
       </c>
       <c r="G219" t="n">
         <v>93</v>
@@ -6351,16 +6351,16 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>-0.4367632865905762</v>
+        <v>-0.4120759205546436</v>
       </c>
       <c r="D220" t="n">
-        <v>7.67913293838501</v>
+        <v>7.731944206433418</v>
       </c>
       <c r="E220" t="n">
-        <v>10.45148668437052</v>
+        <v>10.36130590228976</v>
       </c>
       <c r="F220" t="n">
-        <v>75.91935729980469</v>
+        <v>71.50425659560501</v>
       </c>
       <c r="G220" t="n">
         <v>78</v>
@@ -6378,16 +6378,16 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>-4.981131553649902</v>
+        <v>-4.145029791686168</v>
       </c>
       <c r="D221" t="n">
-        <v>208.871826171875</v>
+        <v>193.5725123087565</v>
       </c>
       <c r="E221" t="n">
-        <v>231.932817926334</v>
+        <v>215.1119345720969</v>
       </c>
       <c r="F221" t="n">
-        <v>71.32169342041016</v>
+        <v>67.33205023706013</v>
       </c>
       <c r="G221" t="n">
         <v>18</v>
@@ -6405,16 +6405,16 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>-2.845862150192261</v>
+        <v>-1.052595338091129</v>
       </c>
       <c r="D222" t="n">
-        <v>38.36745834350586</v>
+        <v>24.22258966424492</v>
       </c>
       <c r="E222" t="n">
-        <v>44.93323905172748</v>
+        <v>32.82634609912782</v>
       </c>
       <c r="F222" t="n">
-        <v>46.76688003540039</v>
+        <v>28.09372704472366</v>
       </c>
       <c r="G222" t="n">
         <v>89</v>
@@ -6432,16 +6432,16 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>-2.387351274490356</v>
+        <v>-0.2425737507283601</v>
       </c>
       <c r="D223" t="n">
-        <v>478.8817138671875</v>
+        <v>263.1671116376164</v>
       </c>
       <c r="E223" t="n">
-        <v>551.5407679854682</v>
+        <v>334.047778071336</v>
       </c>
       <c r="F223" t="n">
-        <v>56.97918701171875</v>
+        <v>33.73596570894822</v>
       </c>
       <c r="G223" t="n">
         <v>99</v>
@@ -6459,16 +6459,16 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>-0.3578135967254639</v>
+        <v>-5.539740751006747</v>
       </c>
       <c r="D224" t="n">
-        <v>296.5106811523438</v>
+        <v>775.6306401734711</v>
       </c>
       <c r="E224" t="n">
-        <v>373.6784212394395</v>
+        <v>820.0837326626873</v>
       </c>
       <c r="F224" t="n">
-        <v>30.41553115844727</v>
+        <v>95.0971748154959</v>
       </c>
       <c r="G224" t="n">
         <v>93</v>
@@ -6486,16 +6486,16 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>-0.4278008937835693</v>
+        <v>-0.4362719441407512</v>
       </c>
       <c r="D225" t="n">
-        <v>8.026216506958008</v>
+        <v>7.828089900505849</v>
       </c>
       <c r="E225" t="n">
-        <v>10.4188379898429</v>
+        <v>10.44969971707367</v>
       </c>
       <c r="F225" t="n">
-        <v>81.19218444824219</v>
+        <v>73.19365522966437</v>
       </c>
       <c r="G225" t="n">
         <v>78</v>
@@ -6513,16 +6513,16 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>-5.676581859588623</v>
+        <v>-2.533740001791604</v>
       </c>
       <c r="D226" t="n">
-        <v>225.8882141113281</v>
+        <v>158.6405137379964</v>
       </c>
       <c r="E226" t="n">
-        <v>245.0460017399794</v>
+        <v>178.2739369753718</v>
       </c>
       <c r="F226" t="n">
-        <v>80.35462951660156</v>
+        <v>58.02696935954541</v>
       </c>
       <c r="G226" t="n">
         <v>18</v>
@@ -6540,16 +6540,16 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>-1.049450159072876</v>
+        <v>-1.191672223389605</v>
       </c>
       <c r="D227" t="n">
-        <v>24.17374229431152</v>
+        <v>25.9192422373911</v>
       </c>
       <c r="E227" t="n">
-        <v>32.80118666572427</v>
+        <v>33.92022128335159</v>
       </c>
       <c r="F227" t="n">
-        <v>28.7475757598877</v>
+        <v>30.19523765760052</v>
       </c>
       <c r="G227" t="n">
         <v>89</v>
@@ -6567,16 +6567,16 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>-1.523493528366089</v>
+        <v>-1.276675991461411</v>
       </c>
       <c r="D228" t="n">
-        <v>386.1473388671875</v>
+        <v>371.6499135951803</v>
       </c>
       <c r="E228" t="n">
-        <v>476.0456418506528</v>
+        <v>452.1662193910212</v>
       </c>
       <c r="F228" t="n">
-        <v>43.69943237304688</v>
+        <v>42.72082331701036</v>
       </c>
       <c r="G228" t="n">
         <v>99</v>
@@ -6594,16 +6594,16 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>-0.2333300113677979</v>
+        <v>-1.81406841637482</v>
       </c>
       <c r="D229" t="n">
-        <v>257.48486328125</v>
+        <v>441.3036295572917</v>
       </c>
       <c r="E229" t="n">
-        <v>356.1374164209652</v>
+        <v>537.9541436039012</v>
       </c>
       <c r="F229" t="n">
-        <v>27.16765403747559</v>
+        <v>55.22462924979848</v>
       </c>
       <c r="G229" t="n">
         <v>93</v>
@@ -6621,16 +6621,16 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>-0.4814140796661377</v>
+        <v>-0.4407127650863576</v>
       </c>
       <c r="D230" t="n">
-        <v>8.130165100097656</v>
+        <v>7.817050343904739</v>
       </c>
       <c r="E230" t="n">
-        <v>10.61264648336405</v>
+        <v>10.46584200500373</v>
       </c>
       <c r="F230" t="n">
-        <v>76.17813873291016</v>
+        <v>75.21630955683494</v>
       </c>
       <c r="G230" t="n">
         <v>78</v>
@@ -6648,16 +6648,16 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>-3.33339786529541</v>
+        <v>-2.530163285637005</v>
       </c>
       <c r="D231" t="n">
-        <v>176.5150451660156</v>
+        <v>155.0740051269531</v>
       </c>
       <c r="E231" t="n">
-        <v>197.4171206639637</v>
+        <v>178.1836931120428</v>
       </c>
       <c r="F231" t="n">
-        <v>65.69640350341797</v>
+        <v>57.29309683734176</v>
       </c>
       <c r="G231" t="n">
         <v>18</v>
@@ -6675,16 +6675,16 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>-1.13573431968689</v>
+        <v>-1.046951504858986</v>
       </c>
       <c r="D232" t="n">
-        <v>23.64959144592285</v>
+        <v>24.32488557194056</v>
       </c>
       <c r="E232" t="n">
-        <v>33.48455181066245</v>
+        <v>32.78118523681007</v>
       </c>
       <c r="F232" t="n">
-        <v>27.7942008972168</v>
+        <v>28.18260740122056</v>
       </c>
       <c r="G232" t="n">
         <v>89</v>
@@ -6702,16 +6702,16 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>-1.063735961914062</v>
+        <v>-0.468513501546187</v>
       </c>
       <c r="D233" t="n">
-        <v>343.3301696777344</v>
+        <v>293.9969490128334</v>
       </c>
       <c r="E233" t="n">
-        <v>430.5013973554558</v>
+        <v>363.1503539615618</v>
       </c>
       <c r="F233" t="n">
-        <v>39.58252716064453</v>
+        <v>35.53732984986364</v>
       </c>
       <c r="G233" t="n">
         <v>99</v>
@@ -6729,16 +6729,16 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>-0.5916843414306641</v>
+        <v>-1.981488320853019</v>
       </c>
       <c r="D234" t="n">
-        <v>308.1426086425781</v>
+        <v>483.0365318380377</v>
       </c>
       <c r="E234" t="n">
-        <v>404.5818829359516</v>
+        <v>553.7254532445368</v>
       </c>
       <c r="F234" t="n">
-        <v>33.75617980957031</v>
+        <v>58.48720441061869</v>
       </c>
       <c r="G234" t="n">
         <v>93</v>
@@ -6756,16 +6756,16 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>-0.33746337890625</v>
+        <v>-0.4431307103967701</v>
       </c>
       <c r="D235" t="n">
-        <v>7.806882381439209</v>
+        <v>7.887305006002769</v>
       </c>
       <c r="E235" t="n">
-        <v>10.08385064765823</v>
+        <v>10.47462072392214</v>
       </c>
       <c r="F235" t="n">
-        <v>84.64964294433594</v>
+        <v>73.11201627282291</v>
       </c>
       <c r="G235" t="n">
         <v>78</v>
@@ -6783,16 +6783,16 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>-4.128103733062744</v>
+        <v>-2.603777992348424</v>
       </c>
       <c r="D236" t="n">
-        <v>194.67822265625</v>
+        <v>160.1927151150174</v>
       </c>
       <c r="E236" t="n">
-        <v>214.7577941688031</v>
+        <v>180.0319450194683</v>
       </c>
       <c r="F236" t="n">
-        <v>66.90456390380859</v>
+        <v>60.3896719532663</v>
       </c>
       <c r="G236" t="n">
         <v>18</v>
@@ -6810,16 +6810,16 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>-0.6544630527496338</v>
+        <v>-0.5320147270303941</v>
       </c>
       <c r="D237" t="n">
-        <v>20.95588111877441</v>
+        <v>20.63823183466879</v>
       </c>
       <c r="E237" t="n">
-        <v>29.47130676375381</v>
+        <v>28.35974653762207</v>
       </c>
       <c r="F237" t="n">
-        <v>24.82281684875488</v>
+        <v>24.19747195988141</v>
       </c>
       <c r="G237" t="n">
         <v>89</v>
@@ -6837,16 +6837,16 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>-1.851409196853638</v>
+        <v>-0.4166426441284452</v>
       </c>
       <c r="D238" t="n">
-        <v>422.0851135253906</v>
+        <v>290.5145525691485</v>
       </c>
       <c r="E238" t="n">
-        <v>506.0311872799936</v>
+        <v>356.6790944411501</v>
       </c>
       <c r="F238" t="n">
-        <v>48.06918334960938</v>
+        <v>34.38159603118228</v>
       </c>
       <c r="G238" t="n">
         <v>99</v>
@@ -6864,16 +6864,16 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>-0.7383323907852173</v>
+        <v>0.2116704463940676</v>
       </c>
       <c r="D239" t="n">
-        <v>321.8226623535156</v>
+        <v>218.8970888199345</v>
       </c>
       <c r="E239" t="n">
-        <v>422.8091324699598</v>
+        <v>284.7290867293206</v>
       </c>
       <c r="F239" t="n">
-        <v>39.41382598876953</v>
+        <v>25.153768383693</v>
       </c>
       <c r="G239" t="n">
         <v>93</v>
@@ -6891,16 +6891,16 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>-0.4608381986618042</v>
+        <v>-0.4882212133282782</v>
       </c>
       <c r="D240" t="n">
-        <v>8.010960578918457</v>
+        <v>7.853038494403545</v>
       </c>
       <c r="E240" t="n">
-        <v>10.5386871429404</v>
+        <v>10.63700142766442</v>
       </c>
       <c r="F240" t="n">
-        <v>87.09407806396484</v>
+        <v>76.65046102244824</v>
       </c>
       <c r="G240" t="n">
         <v>78</v>
@@ -6918,16 +6918,16 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>-3.320566177368164</v>
+        <v>-2.469019899246356</v>
       </c>
       <c r="D241" t="n">
-        <v>177.4082641601562</v>
+        <v>150.1096110873752</v>
       </c>
       <c r="E241" t="n">
-        <v>197.1246135855439</v>
+        <v>176.6338579406965</v>
       </c>
       <c r="F241" t="n">
-        <v>63.84624862670898</v>
+        <v>57.2695210618277</v>
       </c>
       <c r="G241" t="n">
         <v>18</v>
@@ -6945,16 +6945,16 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>-0.9921504259109497</v>
+        <v>-1.116890733857974</v>
       </c>
       <c r="D242" t="n">
-        <v>22.79814338684082</v>
+        <v>24.99528094088094</v>
       </c>
       <c r="E242" t="n">
-        <v>32.33939810698206</v>
+        <v>33.33650726613759</v>
       </c>
       <c r="F242" t="n">
-        <v>26.80211067199707</v>
+        <v>28.92634321411477</v>
       </c>
       <c r="G242" t="n">
         <v>89</v>
@@ -6972,16 +6972,16 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>-2.474125623703003</v>
+        <v>-1.257643196657656</v>
       </c>
       <c r="D243" t="n">
-        <v>457.9946594238281</v>
+        <v>361.2899593777126</v>
       </c>
       <c r="E243" t="n">
-        <v>558.5605383483513</v>
+        <v>450.2722193690092</v>
       </c>
       <c r="F243" t="n">
-        <v>51.42304992675781</v>
+        <v>42.16717138721328</v>
       </c>
       <c r="G243" t="n">
         <v>99</v>
@@ -6999,16 +6999,16 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>-0.5765595436096191</v>
+        <v>-0.3659555184316123</v>
       </c>
       <c r="D244" t="n">
-        <v>303.5155944824219</v>
+        <v>321.0971285912298</v>
       </c>
       <c r="E244" t="n">
-        <v>402.6550361351513</v>
+        <v>374.7970893985449</v>
       </c>
       <c r="F244" t="n">
-        <v>35.5786018371582</v>
+        <v>41.94172999284585</v>
       </c>
       <c r="G244" t="n">
         <v>93</v>
@@ -7026,16 +7026,16 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>-0.4092632532119751</v>
+        <v>-0.4240804294778029</v>
       </c>
       <c r="D245" t="n">
-        <v>7.596645355224609</v>
+        <v>7.805462941145286</v>
       </c>
       <c r="E245" t="n">
-        <v>10.35098133686997</v>
+        <v>10.40525508075793</v>
       </c>
       <c r="F245" t="n">
-        <v>71.67426300048828</v>
+        <v>71.5284613955365</v>
       </c>
       <c r="G245" t="n">
         <v>78</v>
@@ -7053,16 +7053,16 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>-3.683977127075195</v>
+        <v>-1.10567956110332</v>
       </c>
       <c r="D246" t="n">
-        <v>186.3503875732422</v>
+        <v>108.8524432712131</v>
       </c>
       <c r="E246" t="n">
-        <v>205.2475163522083</v>
+        <v>137.6152932571081</v>
       </c>
       <c r="F246" t="n">
-        <v>65.95228576660156</v>
+        <v>49.86665615737952</v>
       </c>
       <c r="G246" t="n">
         <v>18</v>
@@ -7080,16 +7080,16 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>-1.082615613937378</v>
+        <v>-0.9944926704878307</v>
       </c>
       <c r="D247" t="n">
-        <v>23.77409934997559</v>
+        <v>23.97780722714542</v>
       </c>
       <c r="E247" t="n">
-        <v>33.06552554386801</v>
+        <v>32.35840432740449</v>
       </c>
       <c r="F247" t="n">
-        <v>27.83277893066406</v>
+        <v>28.41517969029998</v>
       </c>
       <c r="G247" t="n">
         <v>89</v>
@@ -7107,16 +7107,16 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>-2.932629823684692</v>
+        <v>-0.8461347973221263</v>
       </c>
       <c r="D248" t="n">
-        <v>511.881103515625</v>
+        <v>343.8564339069405</v>
       </c>
       <c r="E248" t="n">
-        <v>594.2771607171186</v>
+        <v>407.1732177123494</v>
       </c>
       <c r="F248" t="n">
-        <v>60.33992767333984</v>
+        <v>40.47680822037624</v>
       </c>
       <c r="G248" t="n">
         <v>99</v>
@@ -7134,16 +7134,16 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>-0.6056426763534546</v>
+        <v>0.1241995418458515</v>
       </c>
       <c r="D249" t="n">
-        <v>286.0107421875</v>
+        <v>224.1393800140709</v>
       </c>
       <c r="E249" t="n">
-        <v>406.3520064242331</v>
+        <v>300.1100333436594</v>
       </c>
       <c r="F249" t="n">
-        <v>32.1140251159668</v>
+        <v>23.73855180606838</v>
       </c>
       <c r="G249" t="n">
         <v>93</v>
@@ -7161,16 +7161,16 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>-0.4448953866958618</v>
+        <v>-0.4601680876955685</v>
       </c>
       <c r="D250" t="n">
-        <v>7.687781810760498</v>
+        <v>7.754510610531538</v>
       </c>
       <c r="E250" t="n">
-        <v>10.48102271527942</v>
+        <v>10.53627017553216</v>
       </c>
       <c r="F250" t="n">
-        <v>71.82942199707031</v>
+        <v>71.42636776609274</v>
       </c>
       <c r="G250" t="n">
         <v>78</v>
@@ -7188,16 +7188,16 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>-4.226077556610107</v>
+        <v>-2.993411534796583</v>
       </c>
       <c r="D251" t="n">
-        <v>194.7242736816406</v>
+        <v>167.2479252285428</v>
       </c>
       <c r="E251" t="n">
-        <v>216.7995906361449</v>
+        <v>189.5145650781025</v>
       </c>
       <c r="F251" t="n">
-        <v>66.66062164306641</v>
+        <v>60.01930491810776</v>
       </c>
       <c r="G251" t="n">
         <v>18</v>
@@ -7215,16 +7215,16 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>-0.6599210500717163</v>
+        <v>-0.5756619345472715</v>
       </c>
       <c r="D252" t="n">
-        <v>21.27164840698242</v>
+        <v>21.20046679893236</v>
       </c>
       <c r="E252" t="n">
-        <v>29.51987938336798</v>
+        <v>28.76089500465785</v>
       </c>
       <c r="F252" t="n">
-        <v>25.10060691833496</v>
+        <v>24.9184933972329</v>
       </c>
       <c r="G252" t="n">
         <v>89</v>
@@ -7242,16 +7242,16 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>-3.263728141784668</v>
+        <v>-0.9527955821386083</v>
       </c>
       <c r="D253" t="n">
-        <v>533.9349975585938</v>
+        <v>341.1968485514323</v>
       </c>
       <c r="E253" t="n">
-        <v>618.7885089026784</v>
+        <v>418.7703180904882</v>
       </c>
       <c r="F253" t="n">
-        <v>64.68948364257812</v>
+        <v>39.34696040147879</v>
       </c>
       <c r="G253" t="n">
         <v>99</v>
@@ -7269,16 +7269,16 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>-4.217411041259766</v>
+        <v>0.2454368049754027</v>
       </c>
       <c r="D254" t="n">
-        <v>540.5457153320312</v>
+        <v>191.0465875441028</v>
       </c>
       <c r="E254" t="n">
-        <v>732.4963737111605</v>
+        <v>278.5644811052236</v>
       </c>
       <c r="F254" t="n">
-        <v>63.29471969604492</v>
+        <v>20.5249961395885</v>
       </c>
       <c r="G254" t="n">
         <v>93</v>
@@ -7296,16 +7296,16 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>-0.4215292930603027</v>
+        <v>-0.3962070731308458</v>
       </c>
       <c r="D255" t="n">
-        <v>7.362564563751221</v>
+        <v>7.184881476255564</v>
       </c>
       <c r="E255" t="n">
-        <v>10.39593049171522</v>
+        <v>10.30292145714324</v>
       </c>
       <c r="F255" t="n">
-        <v>73.91253662109375</v>
+        <v>73.18370513871072</v>
       </c>
       <c r="G255" t="n">
         <v>78</v>
@@ -7323,16 +7323,16 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>-2.407104730606079</v>
+        <v>-2.544499039991656</v>
       </c>
       <c r="D256" t="n">
-        <v>156.5856628417969</v>
+        <v>154.864742702908</v>
       </c>
       <c r="E256" t="n">
-        <v>175.0504670534329</v>
+        <v>178.5451225122226</v>
       </c>
       <c r="F256" t="n">
-        <v>55.91886138916016</v>
+        <v>59.01242832046258</v>
       </c>
       <c r="G256" t="n">
         <v>18</v>
@@ -7350,16 +7350,16 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>-1.097411394119263</v>
+        <v>-1.546113838407473</v>
       </c>
       <c r="D257" t="n">
-        <v>24.63192367553711</v>
+        <v>27.25316639160842</v>
       </c>
       <c r="E257" t="n">
-        <v>33.18277317444814</v>
+        <v>36.56030277301873</v>
       </c>
       <c r="F257" t="n">
-        <v>29.16412353515625</v>
+        <v>31.98620910990679</v>
       </c>
       <c r="G257" t="n">
         <v>89</v>
@@ -7377,16 +7377,16 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>-0.652186393737793</v>
+        <v>-1.066444515529898</v>
       </c>
       <c r="D258" t="n">
-        <v>319.2099304199219</v>
+        <v>364.3880952777284</v>
       </c>
       <c r="E258" t="n">
-        <v>385.1917947594419</v>
+        <v>430.7838113427497</v>
       </c>
       <c r="F258" t="n">
-        <v>38.15027618408203</v>
+        <v>42.5565617309613</v>
       </c>
       <c r="G258" t="n">
         <v>99</v>
@@ -7404,16 +7404,16 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>-0.8184747695922852</v>
+        <v>-0.4512318692432173</v>
       </c>
       <c r="D259" t="n">
-        <v>269.366455078125</v>
+        <v>293.5815672515541</v>
       </c>
       <c r="E259" t="n">
-        <v>432.4457155239256</v>
+        <v>386.3192369324878</v>
       </c>
       <c r="F259" t="n">
-        <v>37.13764572143555</v>
+        <v>31.06487361597929</v>
       </c>
       <c r="G259" t="n">
         <v>93</v>
@@ -7431,16 +7431,16 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>-0.4389194250106812</v>
+        <v>-0.3904205201193249</v>
       </c>
       <c r="D260" t="n">
-        <v>7.914105415344238</v>
+        <v>7.566052586604387</v>
       </c>
       <c r="E260" t="n">
-        <v>10.45932593834195</v>
+        <v>10.28154916126466</v>
       </c>
       <c r="F260" t="n">
-        <v>75.23017883300781</v>
+        <v>70.52758884046135</v>
       </c>
       <c r="G260" t="n">
         <v>78</v>
@@ -7458,16 +7458,16 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>-4.327867031097412</v>
+        <v>-4.881480331302187</v>
       </c>
       <c r="D261" t="n">
-        <v>196.4458923339844</v>
+        <v>209.8775520324707</v>
       </c>
       <c r="E261" t="n">
-        <v>218.9007337813192</v>
+        <v>229.9926110064288</v>
       </c>
       <c r="F261" t="n">
-        <v>68.29132080078125</v>
+        <v>73.31169548587606</v>
       </c>
       <c r="G261" t="n">
         <v>18</v>
@@ -7485,16 +7485,16 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>-1.303085327148438</v>
+        <v>-1.811620809150287</v>
       </c>
       <c r="D262" t="n">
-        <v>25.07853126525879</v>
+        <v>28.68460466620627</v>
       </c>
       <c r="E262" t="n">
-        <v>34.77169715230423</v>
+        <v>38.41928245906006</v>
       </c>
       <c r="F262" t="n">
-        <v>29.67264938354492</v>
+        <v>33.57867809784063</v>
       </c>
       <c r="G262" t="n">
         <v>89</v>
@@ -7512,16 +7512,16 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>-1.014536142349243</v>
+        <v>-1.136401551030715</v>
       </c>
       <c r="D263" t="n">
-        <v>354.9026184082031</v>
+        <v>372.923748748471</v>
       </c>
       <c r="E263" t="n">
-        <v>425.3388171505159</v>
+        <v>438.0149585051894</v>
       </c>
       <c r="F263" t="n">
-        <v>41.90744400024414</v>
+        <v>44.21335803843869</v>
       </c>
       <c r="G263" t="n">
         <v>99</v>
@@ -7539,16 +7539,16 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>-2.09305739402771</v>
+        <v>-0.1610467976049847</v>
       </c>
       <c r="D264" t="n">
-        <v>388.0029907226562</v>
+        <v>263.604492843792</v>
       </c>
       <c r="E264" t="n">
-        <v>563.9906914125445</v>
+        <v>345.5435522311388</v>
       </c>
       <c r="F264" t="n">
-        <v>50.30712890625</v>
+        <v>27.10989966365229</v>
       </c>
       <c r="G264" t="n">
         <v>93</v>
@@ -7566,16 +7566,16 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>-0.4870314598083496</v>
+        <v>-0.3893056071107894</v>
       </c>
       <c r="D265" t="n">
-        <v>8.097893714904785</v>
+        <v>7.571754553379157</v>
       </c>
       <c r="E265" t="n">
-        <v>10.63274828059684</v>
+        <v>10.27742618854498</v>
       </c>
       <c r="F265" t="n">
-        <v>77.53297424316406</v>
+        <v>70.96723895373285</v>
       </c>
       <c r="G265" t="n">
         <v>78</v>
@@ -7593,16 +7593,16 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>-4.436274528503418</v>
+        <v>-6.01993820448623</v>
       </c>
       <c r="D266" t="n">
-        <v>199.7730407714844</v>
+        <v>233.5326068666246</v>
       </c>
       <c r="E266" t="n">
-        <v>221.1165381365672</v>
+        <v>251.2680119942676</v>
       </c>
       <c r="F266" t="n">
-        <v>69.00889587402344</v>
+        <v>83.32980415823155</v>
       </c>
       <c r="G266" t="n">
         <v>18</v>
@@ -7620,16 +7620,16 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>-1.546246290206909</v>
+        <v>-1.614327561525045</v>
       </c>
       <c r="D267" t="n">
-        <v>26.92910003662109</v>
+        <v>27.92833079648821</v>
       </c>
       <c r="E267" t="n">
-        <v>36.56125131414747</v>
+        <v>37.04681492457851</v>
       </c>
       <c r="F267" t="n">
-        <v>31.94832229614258</v>
+        <v>33.40563701161418</v>
       </c>
       <c r="G267" t="n">
         <v>89</v>
@@ -7647,16 +7647,16 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>-0.9407534599304199</v>
+        <v>-1.250241794976319</v>
       </c>
       <c r="D268" t="n">
-        <v>334.8219299316406</v>
+        <v>385.1331483474885</v>
       </c>
       <c r="E268" t="n">
-        <v>417.4771326072843</v>
+        <v>449.5335327889837</v>
       </c>
       <c r="F268" t="n">
-        <v>39.23305130004883</v>
+        <v>45.45839542866296</v>
       </c>
       <c r="G268" t="n">
         <v>99</v>
@@ -7674,16 +7674,16 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>-3.070669651031494</v>
+        <v>0.002451931589871892</v>
       </c>
       <c r="D269" t="n">
-        <v>407.3607482910156</v>
+        <v>250.4412979618195</v>
       </c>
       <c r="E269" t="n">
-        <v>647.0098289438886</v>
+        <v>320.2910823644029</v>
       </c>
       <c r="F269" t="n">
-        <v>52.04536819458008</v>
+        <v>25.26336708901933</v>
       </c>
       <c r="G269" t="n">
         <v>93</v>
@@ -7701,16 +7701,16 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>-0.3355721235275269</v>
+        <v>-0.3517134720077819</v>
       </c>
       <c r="D270" t="n">
-        <v>7.082448482513428</v>
+        <v>7.158053089410831</v>
       </c>
       <c r="E270" t="n">
-        <v>10.07671872758893</v>
+        <v>10.13742824717811</v>
       </c>
       <c r="F270" t="n">
-        <v>72.40744018554688</v>
+        <v>73.76433889709148</v>
       </c>
       <c r="G270" t="n">
         <v>78</v>
@@ -7728,16 +7728,16 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>-3.551579475402832</v>
+        <v>-5.58022254252251</v>
       </c>
       <c r="D271" t="n">
-        <v>179.2604217529297</v>
+        <v>224.7889120313856</v>
       </c>
       <c r="E271" t="n">
-        <v>202.3259572292937</v>
+        <v>243.2712854439308</v>
       </c>
       <c r="F271" t="n">
-        <v>63.2346076965332</v>
+        <v>79.38481548723965</v>
       </c>
       <c r="G271" t="n">
         <v>18</v>
@@ -7755,16 +7755,16 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>-0.6525487899780273</v>
+        <v>-0.6978165904788969</v>
       </c>
       <c r="D272" t="n">
-        <v>20.66713905334473</v>
+        <v>20.19339023547226</v>
       </c>
       <c r="E272" t="n">
-        <v>29.45425333548249</v>
+        <v>29.85494404312423</v>
       </c>
       <c r="F272" t="n">
-        <v>25.82494926452637</v>
+        <v>24.57428322174631</v>
       </c>
       <c r="G272" t="n">
         <v>89</v>
@@ -7782,16 +7782,16 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>-0.6832640171051025</v>
+        <v>-0.5901883381512407</v>
       </c>
       <c r="D273" t="n">
-        <v>301.7088928222656</v>
+        <v>295.1535807908184</v>
       </c>
       <c r="E273" t="n">
-        <v>388.7976457940557</v>
+        <v>377.8955536456612</v>
       </c>
       <c r="F273" t="n">
-        <v>36.50547027587891</v>
+        <v>35.89158180155784</v>
       </c>
       <c r="G273" t="n">
         <v>99</v>
@@ -7809,16 +7809,16 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>-0.3388099670410156</v>
+        <v>-0.5067553165957035</v>
       </c>
       <c r="D274" t="n">
-        <v>264.2990112304688</v>
+        <v>279.5849012149278</v>
       </c>
       <c r="E274" t="n">
-        <v>371.0542623727694</v>
+        <v>393.6400672660482</v>
       </c>
       <c r="F274" t="n">
-        <v>25.35978889465332</v>
+        <v>27.25282243791903</v>
       </c>
       <c r="G274" t="n">
         <v>93</v>
@@ -7836,16 +7836,16 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>-0.3381558656692505</v>
+        <v>-0.4521020916746499</v>
       </c>
       <c r="D275" t="n">
-        <v>6.738833904266357</v>
+        <v>7.068349321683248</v>
       </c>
       <c r="E275" t="n">
-        <v>10.08646094207168</v>
+        <v>10.50712859768566</v>
       </c>
       <c r="F275" t="n">
-        <v>64.0223388671875</v>
+        <v>67.42944773093799</v>
       </c>
       <c r="G275" t="n">
         <v>78</v>
@@ -7863,16 +7863,16 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>-6.907746315002441</v>
+        <v>-6.879054722515255</v>
       </c>
       <c r="D276" t="n">
-        <v>250.0215454101562</v>
+        <v>250.6251353157891</v>
       </c>
       <c r="E276" t="n">
-        <v>266.6839626552373</v>
+        <v>266.1997342163991</v>
       </c>
       <c r="F276" t="n">
-        <v>91.054931640625</v>
+        <v>91.73624560122585</v>
       </c>
       <c r="G276" t="n">
         <v>18</v>
@@ -7890,16 +7890,16 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>-1.019572019577026</v>
+        <v>-0.6833477861098347</v>
       </c>
       <c r="D277" t="n">
-        <v>22.86163139343262</v>
+        <v>20.29329604245304</v>
       </c>
       <c r="E277" t="n">
-        <v>32.5612085126564</v>
+        <v>29.72745984001488</v>
       </c>
       <c r="F277" t="n">
-        <v>27.61337089538574</v>
+        <v>25.03062096284989</v>
       </c>
       <c r="G277" t="n">
         <v>89</v>
@@ -7917,16 +7917,16 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>-0.4543187618255615</v>
+        <v>-0.7773229613792982</v>
       </c>
       <c r="D278" t="n">
-        <v>282.9900512695312</v>
+        <v>320.7682078968395</v>
       </c>
       <c r="E278" t="n">
-        <v>361.3909759526377</v>
+        <v>399.5127792732802</v>
       </c>
       <c r="F278" t="n">
-        <v>34.61687088012695</v>
+        <v>38.71089221142047</v>
       </c>
       <c r="G278" t="n">
         <v>99</v>
@@ -7944,16 +7944,16 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>-0.08735454082489014</v>
+        <v>-0.5415570061269463</v>
       </c>
       <c r="D279" t="n">
-        <v>241.6903533935547</v>
+        <v>277.2802183089718</v>
       </c>
       <c r="E279" t="n">
-        <v>334.3978847308996</v>
+        <v>398.1600898721044</v>
       </c>
       <c r="F279" t="n">
-        <v>23.3603515625</v>
+        <v>26.97212292129539</v>
       </c>
       <c r="G279" t="n">
         <v>93</v>
@@ -7971,16 +7971,16 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>-0.292959451675415</v>
+        <v>-0.4095727776080509</v>
       </c>
       <c r="D280" t="n">
-        <v>6.733515739440918</v>
+        <v>6.834444868258941</v>
       </c>
       <c r="E280" t="n">
-        <v>9.914661963505662</v>
+        <v>10.35211824689637</v>
       </c>
       <c r="F280" t="n">
-        <v>67.79158020019531</v>
+        <v>68.82040150034437</v>
       </c>
       <c r="G280" t="n">
         <v>78</v>
@@ -7998,16 +7998,16 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>-7.077383995056152</v>
+        <v>-7.017389125041287</v>
       </c>
       <c r="D281" t="n">
-        <v>252.1455688476562</v>
+        <v>251.7242404090034</v>
       </c>
       <c r="E281" t="n">
-        <v>269.529248180972</v>
+        <v>268.5264314904143</v>
       </c>
       <c r="F281" t="n">
-        <v>91.74074554443359</v>
+        <v>91.519061178432</v>
       </c>
       <c r="G281" t="n">
         <v>18</v>
@@ -8025,16 +8025,16 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>-0.5009293556213379</v>
+        <v>-0.4762245283331823</v>
       </c>
       <c r="D282" t="n">
-        <v>20.03783988952637</v>
+        <v>20.14552566442597</v>
       </c>
       <c r="E282" t="n">
-        <v>28.0705538536799</v>
+        <v>27.83858030111018</v>
       </c>
       <c r="F282" t="n">
-        <v>25.003173828125</v>
+        <v>25.49209178948691</v>
       </c>
       <c r="G282" t="n">
         <v>89</v>
@@ -8052,16 +8052,16 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>-0.7988922595977783</v>
+        <v>-0.320313917867973</v>
       </c>
       <c r="D283" t="n">
-        <v>335.0534973144531</v>
+        <v>279.6460113525391</v>
       </c>
       <c r="E283" t="n">
-        <v>401.92968134986</v>
+        <v>344.3389101608722</v>
       </c>
       <c r="F283" t="n">
-        <v>44.61103439331055</v>
+        <v>36.35966993886088</v>
       </c>
       <c r="G283" t="n">
         <v>99</v>
@@ -8079,16 +8079,16 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>-0.2150856256484985</v>
+        <v>-0.3780099409643636</v>
       </c>
       <c r="D284" t="n">
-        <v>277.99853515625</v>
+        <v>295.0229846585182</v>
       </c>
       <c r="E284" t="n">
-        <v>353.4934582138685</v>
+        <v>376.4472304596206</v>
       </c>
       <c r="F284" t="n">
-        <v>28.1470890045166</v>
+        <v>29.89739900766882</v>
       </c>
       <c r="G284" t="n">
         <v>93</v>
@@ -8106,16 +8106,16 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>-0.5924992561340332</v>
+        <v>-0.5678760891054653</v>
       </c>
       <c r="D285" t="n">
-        <v>7.348139762878418</v>
+        <v>7.323732859049088</v>
       </c>
       <c r="E285" t="n">
-        <v>11.00335364804323</v>
+        <v>10.91795602250162</v>
       </c>
       <c r="F285" t="n">
-        <v>70.09101104736328</v>
+        <v>72.50955254076969</v>
       </c>
       <c r="G285" t="n">
         <v>78</v>
@@ -8133,16 +8133,16 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>-6.798649787902832</v>
+        <v>-6.613427158340776</v>
       </c>
       <c r="D286" t="n">
-        <v>249.2642211914062</v>
+        <v>246.8864279852973</v>
       </c>
       <c r="E286" t="n">
-        <v>264.8379663822768</v>
+        <v>261.6740508782308</v>
       </c>
       <c r="F286" t="n">
-        <v>91.24649810791016</v>
+        <v>90.82907286545959</v>
       </c>
       <c r="G286" t="n">
         <v>18</v>
@@ -8160,16 +8160,16 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>-0.5580943822860718</v>
+        <v>-0.5809219222440289</v>
       </c>
       <c r="D287" t="n">
-        <v>20.4738883972168</v>
+        <v>20.99253474460559</v>
       </c>
       <c r="E287" t="n">
-        <v>28.6001134910199</v>
+        <v>28.80886084865924</v>
       </c>
       <c r="F287" t="n">
-        <v>25.14516448974609</v>
+        <v>26.15618995801447</v>
       </c>
       <c r="G287" t="n">
         <v>89</v>
@@ -8187,16 +8187,16 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>-0.6240415573120117</v>
+        <v>-0.3272407578500083</v>
       </c>
       <c r="D288" t="n">
-        <v>307.0920104980469</v>
+        <v>280.4221709280303</v>
       </c>
       <c r="E288" t="n">
-        <v>381.896848802134</v>
+        <v>345.2409912112795</v>
       </c>
       <c r="F288" t="n">
-        <v>39.81062316894531</v>
+        <v>36.50249454269719</v>
       </c>
       <c r="G288" t="n">
         <v>99</v>
@@ -8214,16 +8214,16 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>-0.4352117776870728</v>
+        <v>-0.3690693258325817</v>
       </c>
       <c r="D289" t="n">
-        <v>299.0475158691406</v>
+        <v>293.4228128412718</v>
       </c>
       <c r="E289" t="n">
-        <v>384.1810486281175</v>
+        <v>375.2240365420982</v>
       </c>
       <c r="F289" t="n">
-        <v>29.93879318237305</v>
+        <v>29.84675666642331</v>
       </c>
       <c r="G289" t="n">
         <v>93</v>
@@ -8241,16 +8241,16 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>-0.6216089725494385</v>
+        <v>-0.5918725327318344</v>
       </c>
       <c r="D290" t="n">
-        <v>7.420212268829346</v>
+        <v>7.364927398852813</v>
       </c>
       <c r="E290" t="n">
-        <v>11.10346495013722</v>
+        <v>11.00118876812341</v>
       </c>
       <c r="F290" t="n">
-        <v>70.51368713378906</v>
+        <v>71.70997838903642</v>
       </c>
       <c r="G290" t="n">
         <v>78</v>
@@ -8268,16 +8268,16 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>-6.927266120910645</v>
+        <v>-6.71349170903616</v>
       </c>
       <c r="D291" t="n">
-        <v>251.205810546875</v>
+        <v>248.3103527492947</v>
       </c>
       <c r="E291" t="n">
-        <v>267.0129034803375</v>
+        <v>263.3880503970113</v>
       </c>
       <c r="F291" t="n">
-        <v>91.88066101074219</v>
+        <v>90.98328656762362</v>
       </c>
       <c r="G291" t="n">
         <v>18</v>
@@ -8295,16 +8295,16 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>-1.898525238037109</v>
+        <v>-0.5587826993497995</v>
       </c>
       <c r="D292" t="n">
-        <v>32.1710205078125</v>
+        <v>20.81559528393692</v>
       </c>
       <c r="E292" t="n">
-        <v>39.00851425740684</v>
+        <v>28.6064300665583</v>
       </c>
       <c r="F292" t="n">
-        <v>39.94146347045898</v>
+        <v>26.16487934741536</v>
       </c>
       <c r="G292" t="n">
         <v>89</v>
@@ -8322,16 +8322,16 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>-0.4313303232192993</v>
+        <v>-0.4270298069084506</v>
       </c>
       <c r="D293" t="n">
-        <v>260.1125183105469</v>
+        <v>283.5729092684659</v>
       </c>
       <c r="E293" t="n">
-        <v>358.5233495708474</v>
+        <v>357.9843344535138</v>
       </c>
       <c r="F293" t="n">
-        <v>31.0853099822998</v>
+        <v>34.09127799725024</v>
       </c>
       <c r="G293" t="n">
         <v>99</v>
@@ -8349,16 +8349,16 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>-0.2483690977096558</v>
+        <v>-0.293677849349645</v>
       </c>
       <c r="D294" t="n">
-        <v>243.1741790771484</v>
+        <v>263.2908223470052</v>
       </c>
       <c r="E294" t="n">
-        <v>358.3021813009237</v>
+        <v>364.7463899018653</v>
       </c>
       <c r="F294" t="n">
-        <v>24.15104293823242</v>
+        <v>25.63279552883719</v>
       </c>
       <c r="G294" t="n">
         <v>93</v>
@@ -8376,16 +8376,16 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>-0.4360780715942383</v>
+        <v>-0.4523569703823236</v>
       </c>
       <c r="D295" t="n">
-        <v>7.406351566314697</v>
+        <v>6.990892061820397</v>
       </c>
       <c r="E295" t="n">
-        <v>10.44899422948041</v>
+        <v>10.5080506836288</v>
       </c>
       <c r="F295" t="n">
-        <v>84.18775939941406</v>
+        <v>63.88364267749424</v>
       </c>
       <c r="G295" t="n">
         <v>78</v>
@@ -8403,16 +8403,16 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>-5.598790645599365</v>
+        <v>-6.931726760930554</v>
       </c>
       <c r="D296" t="n">
-        <v>224.1001586914062</v>
+        <v>250.9922940995958</v>
       </c>
       <c r="E296" t="n">
-        <v>243.6142650918661</v>
+        <v>267.0880341333346</v>
       </c>
       <c r="F296" t="n">
-        <v>79.25181579589844</v>
+        <v>91.27475923462049</v>
       </c>
       <c r="G296" t="n">
         <v>18</v>
@@ -8430,16 +8430,16 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>-2.208689212799072</v>
+        <v>-1.131068228164587</v>
       </c>
       <c r="D297" t="n">
-        <v>31.80771827697754</v>
+        <v>24.48109262445</v>
       </c>
       <c r="E297" t="n">
-        <v>41.04258340240963</v>
+        <v>33.44795360529827</v>
       </c>
       <c r="F297" t="n">
-        <v>37.43040084838867</v>
+        <v>29.30966611255386</v>
       </c>
       <c r="G297" t="n">
         <v>89</v>
@@ -8457,16 +8457,16 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>-1.025795221328735</v>
+        <v>-1.666140128363025</v>
       </c>
       <c r="D298" t="n">
-        <v>347.7959594726562</v>
+        <v>406.1776294130268</v>
       </c>
       <c r="E298" t="n">
-        <v>426.5257539117655</v>
+        <v>489.315514197137</v>
       </c>
       <c r="F298" t="n">
-        <v>40.00230026245117</v>
+        <v>46.42830657359046</v>
       </c>
       <c r="G298" t="n">
         <v>99</v>
@@ -8484,16 +8484,16 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>-0.7505500316619873</v>
+        <v>-0.03659489916680614</v>
       </c>
       <c r="D299" t="n">
-        <v>326.0927429199219</v>
+        <v>218.2092114520329</v>
       </c>
       <c r="E299" t="n">
-        <v>424.2923520404298</v>
+        <v>326.4994580963705</v>
       </c>
       <c r="F299" t="n">
-        <v>29.72326278686523</v>
+        <v>20.11624695882148</v>
       </c>
       <c r="G299" t="n">
         <v>93</v>
@@ -8511,16 +8511,16 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>-0.6287134885787964</v>
+        <v>-0.5942694301826654</v>
       </c>
       <c r="D300" t="n">
-        <v>8.184557914733887</v>
+        <v>7.87262369119204</v>
       </c>
       <c r="E300" t="n">
-        <v>11.12776132667998</v>
+        <v>11.00946794950579</v>
       </c>
       <c r="F300" t="n">
-        <v>83.38270568847656</v>
+        <v>71.2883139840193</v>
       </c>
       <c r="G300" t="n">
         <v>78</v>
@@ -8538,16 +8538,16 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>-7.218284606933594</v>
+        <v>-7.442564495645307</v>
       </c>
       <c r="D301" t="n">
-        <v>255.4673461914062</v>
+        <v>258.8731240166558</v>
       </c>
       <c r="E301" t="n">
-        <v>271.8698850093552</v>
+        <v>275.5546553791785</v>
       </c>
       <c r="F301" t="n">
-        <v>93.00672912597656</v>
+        <v>94.3238724370124</v>
       </c>
       <c r="G301" t="n">
         <v>18</v>
@@ -8565,16 +8565,16 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>-2.998255729675293</v>
+        <v>-0.5997879075117767</v>
       </c>
       <c r="D302" t="n">
-        <v>37.84020233154297</v>
+        <v>22.64814145377513</v>
       </c>
       <c r="E302" t="n">
-        <v>45.81483676253933</v>
+        <v>28.98024681301506</v>
       </c>
       <c r="F302" t="n">
-        <v>49.96093368530273</v>
+        <v>29.5082680546673</v>
       </c>
       <c r="G302" t="n">
         <v>89</v>
@@ -8592,16 +8592,16 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>-0.9903426170349121</v>
+        <v>-1.669153869157633</v>
       </c>
       <c r="D303" t="n">
-        <v>336.4241638183594</v>
+        <v>429.1417524549696</v>
       </c>
       <c r="E303" t="n">
-        <v>422.7770541313707</v>
+        <v>489.5919913435041</v>
       </c>
       <c r="F303" t="n">
-        <v>51.20483016967773</v>
+        <v>54.13277982531183</v>
       </c>
       <c r="G303" t="n">
         <v>99</v>
@@ -8619,16 +8619,16 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>-14.47664356231689</v>
+        <v>-5.682720788752633</v>
       </c>
       <c r="D304" t="n">
-        <v>1066.81103515625</v>
+        <v>747.3819606329805</v>
       </c>
       <c r="E304" t="n">
-        <v>1261.584470021726</v>
+        <v>829.0001119108841</v>
       </c>
       <c r="F304" t="n">
-        <v>135.9222106933594</v>
+        <v>94.27195730647131</v>
       </c>
       <c r="G304" t="n">
         <v>93</v>
@@ -8646,16 +8646,16 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>-0.5181906223297119</v>
+        <v>-0.2021112338991005</v>
       </c>
       <c r="D305" t="n">
-        <v>8.051947593688965</v>
+        <v>7.224334343885764</v>
       </c>
       <c r="E305" t="n">
-        <v>10.74356986844068</v>
+        <v>9.559997969104355</v>
       </c>
       <c r="F305" t="n">
-        <v>121.2475891113281</v>
+        <v>69.95402119960252</v>
       </c>
       <c r="G305" t="n">
         <v>78</v>
@@ -8673,16 +8673,16 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>-3.675182819366455</v>
+        <v>-3.30922749313712</v>
       </c>
       <c r="D306" t="n">
-        <v>187.7877197265625</v>
+        <v>179.7172414991591</v>
       </c>
       <c r="E306" t="n">
-        <v>205.0547468817779</v>
+        <v>196.8657973332948</v>
       </c>
       <c r="F306" t="n">
-        <v>72.96741485595703</v>
+        <v>67.15584474977908</v>
       </c>
       <c r="G306" t="n">
         <v>18</v>
@@ -8700,16 +8700,16 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>-1.234483957290649</v>
+        <v>-0.91369586832426</v>
       </c>
       <c r="D307" t="n">
-        <v>26.18498229980469</v>
+        <v>24.30345473128758</v>
       </c>
       <c r="E307" t="n">
-        <v>34.24991446157202</v>
+        <v>31.69620992985441</v>
       </c>
       <c r="F307" t="n">
-        <v>32.16163635253906</v>
+        <v>29.67675216076159</v>
       </c>
       <c r="G307" t="n">
         <v>89</v>
@@ -8727,16 +8727,16 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>-0.137373685836792</v>
+        <v>-0.7745543445182861</v>
       </c>
       <c r="D308" t="n">
-        <v>261.045654296875</v>
+        <v>331.6836480034722</v>
       </c>
       <c r="E308" t="n">
-        <v>319.5943473764829</v>
+        <v>399.2014883791976</v>
       </c>
       <c r="F308" t="n">
-        <v>39.87717056274414</v>
+        <v>38.75648826123103</v>
       </c>
       <c r="G308" t="n">
         <v>99</v>
@@ -8754,16 +8754,16 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>-8.462636947631836</v>
+        <v>0.05014812635868082</v>
       </c>
       <c r="D309" t="n">
-        <v>713.588623046875</v>
+        <v>252.8082728232107</v>
       </c>
       <c r="E309" t="n">
-        <v>986.4703175970375</v>
+        <v>312.5401907954745</v>
       </c>
       <c r="F309" t="n">
-        <v>89.80455780029297</v>
+        <v>32.65299319056529</v>
       </c>
       <c r="G309" t="n">
         <v>93</v>
@@ -8781,16 +8781,16 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>-0.4290462732315063</v>
+        <v>-0.559846550020821</v>
       </c>
       <c r="D310" t="n">
-        <v>7.534183502197266</v>
+        <v>7.520713002253801</v>
       </c>
       <c r="E310" t="n">
-        <v>10.42338109608015</v>
+        <v>10.88996315866099</v>
       </c>
       <c r="F310" t="n">
-        <v>103.8501968383789</v>
+        <v>68.21156528311364</v>
       </c>
       <c r="G310" t="n">
         <v>78</v>
@@ -8808,16 +8808,16 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>-3.278170585632324</v>
+        <v>-3.257454049614479</v>
       </c>
       <c r="D311" t="n">
-        <v>176.5291595458984</v>
+        <v>176.9429846869575</v>
       </c>
       <c r="E311" t="n">
-        <v>196.1550924969831</v>
+        <v>195.6795963376719</v>
       </c>
       <c r="F311" t="n">
-        <v>64.48259735107422</v>
+        <v>61.41739536846465</v>
       </c>
       <c r="G311" t="n">
         <v>18</v>
@@ -8835,16 +8835,16 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>-0.9513394832611084</v>
+        <v>-1.239868651384722</v>
       </c>
       <c r="D312" t="n">
-        <v>24.93626594543457</v>
+        <v>26.62653284394339</v>
       </c>
       <c r="E312" t="n">
-        <v>32.00643284035355</v>
+        <v>34.29115795541059</v>
       </c>
       <c r="F312" t="n">
-        <v>34.88427352905273</v>
+        <v>31.63041585932758</v>
       </c>
       <c r="G312" t="n">
         <v>89</v>
@@ -8862,16 +8862,16 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>-1.067177057266235</v>
+        <v>-1.504163146261459</v>
       </c>
       <c r="D313" t="n">
-        <v>353.5836486816406</v>
+        <v>400.6291553227588</v>
       </c>
       <c r="E313" t="n">
-        <v>430.8601680069765</v>
+        <v>474.218846478684</v>
       </c>
       <c r="F313" t="n">
-        <v>47.60379028320312</v>
+        <v>46.78518437236985</v>
       </c>
       <c r="G313" t="n">
         <v>99</v>
@@ -8889,16 +8889,16 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>-4.715171337127686</v>
+        <v>-1.139196257550506</v>
       </c>
       <c r="D314" t="n">
-        <v>651.1296997070312</v>
+        <v>410.156015047463</v>
       </c>
       <c r="E314" t="n">
-        <v>766.6419470652515</v>
+        <v>469.0328341840745</v>
       </c>
       <c r="F314" t="n">
-        <v>86.79528045654297</v>
+        <v>53.20235739249814</v>
       </c>
       <c r="G314" t="n">
         <v>93</v>
@@ -8916,16 +8916,16 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>-0.1380665302276611</v>
+        <v>-0.4898519360947875</v>
       </c>
       <c r="D315" t="n">
-        <v>6.779623031616211</v>
+        <v>7.376897243353037</v>
       </c>
       <c r="E315" t="n">
-        <v>9.30184921419988</v>
+        <v>10.64282759487298</v>
       </c>
       <c r="F315" t="n">
-        <v>94.49237823486328</v>
+        <v>67.69173912738438</v>
       </c>
       <c r="G315" t="n">
         <v>78</v>
@@ -8943,16 +8943,16 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>-1.335033416748047</v>
+        <v>-2.188310132886189</v>
       </c>
       <c r="D316" t="n">
-        <v>124.7925109863281</v>
+        <v>146.3561871846517</v>
       </c>
       <c r="E316" t="n">
-        <v>144.9162473637791</v>
+        <v>169.3366012572951</v>
       </c>
       <c r="F316" t="n">
-        <v>45.76003265380859</v>
+        <v>51.7490773608361</v>
       </c>
       <c r="G316" t="n">
         <v>18</v>
@@ -8970,16 +8970,16 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>-1.680652618408203</v>
+        <v>-1.920610602419873</v>
       </c>
       <c r="D317" t="n">
-        <v>29.25917053222656</v>
+        <v>31.89668389652552</v>
       </c>
       <c r="E317" t="n">
-        <v>37.51380767932739</v>
+        <v>39.1568460612888</v>
       </c>
       <c r="F317" t="n">
-        <v>37.17203140258789</v>
+        <v>38.6078617247083</v>
       </c>
       <c r="G317" t="n">
         <v>89</v>
@@ -8997,16 +8997,16 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>-3.512007713317871</v>
+        <v>-1.189173660839657</v>
       </c>
       <c r="D318" t="n">
-        <v>533.5320434570312</v>
+        <v>378.6781536063763</v>
       </c>
       <c r="E318" t="n">
-        <v>636.5498556672525</v>
+        <v>443.391748894932</v>
       </c>
       <c r="F318" t="n">
-        <v>96.03681945800781</v>
+        <v>45.17657939218682</v>
       </c>
       <c r="G318" t="n">
         <v>99</v>
@@ -9024,16 +9024,16 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>-15.75869369506836</v>
+        <v>-0.007213139628941212</v>
       </c>
       <c r="D319" t="n">
-        <v>1168.333618164062</v>
+        <v>269.4705672725555</v>
       </c>
       <c r="E319" t="n">
-        <v>1312.798347043444</v>
+        <v>321.8389646443138</v>
       </c>
       <c r="F319" t="n">
-        <v>137.8984375</v>
+        <v>30.98411710368008</v>
       </c>
       <c r="G319" t="n">
         <v>93</v>
@@ -9051,16 +9051,16 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>-0.3909399509429932</v>
+        <v>-0.3276131207120623</v>
       </c>
       <c r="D320" t="n">
-        <v>7.733711242675781</v>
+        <v>7.029819580224844</v>
       </c>
       <c r="E320" t="n">
-        <v>10.28346928816272</v>
+        <v>10.04664924337879</v>
       </c>
       <c r="F320" t="n">
-        <v>116.1726379394531</v>
+        <v>69.64909026834609</v>
       </c>
       <c r="G320" t="n">
         <v>78</v>
@@ -9078,16 +9078,16 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>-2.389865636825562</v>
+        <v>-1.806102004229778</v>
       </c>
       <c r="D321" t="n">
-        <v>149.1025238037109</v>
+        <v>129.8733020358615</v>
       </c>
       <c r="E321" t="n">
-        <v>174.6070476634606</v>
+        <v>158.8628267991436</v>
       </c>
       <c r="F321" t="n">
-        <v>51.5123291015625</v>
+        <v>45.98890361237795</v>
       </c>
       <c r="G321" t="n">
         <v>18</v>
@@ -9105,16 +9105,16 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>-0.1847410202026367</v>
+        <v>-1.650291919911844</v>
       </c>
       <c r="D322" t="n">
-        <v>19.6728401184082</v>
+        <v>30.58229604999671</v>
       </c>
       <c r="E322" t="n">
-        <v>24.93920341926542</v>
+        <v>37.30076434976645</v>
       </c>
       <c r="F322" t="n">
-        <v>26.70952606201172</v>
+        <v>36.98362419983516</v>
       </c>
       <c r="G322" t="n">
         <v>89</v>
@@ -9132,16 +9132,16 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>-1.919324398040771</v>
+        <v>-1.201433793133569</v>
       </c>
       <c r="D323" t="n">
-        <v>417.0028076171875</v>
+        <v>367.0531861276338</v>
       </c>
       <c r="E323" t="n">
-        <v>512.0220637335856</v>
+        <v>444.6315892749886</v>
       </c>
       <c r="F323" t="n">
-        <v>80.36500549316406</v>
+        <v>42.39254867572663</v>
       </c>
       <c r="G323" t="n">
         <v>99</v>
@@ -9159,16 +9159,16 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>-10.81807804107666</v>
+        <v>-0.1654214623506094</v>
       </c>
       <c r="D324" t="n">
-        <v>917.7921142578125</v>
+        <v>265.8633783812164</v>
       </c>
       <c r="E324" t="n">
-        <v>1102.430893525757</v>
+        <v>346.1939204872216</v>
       </c>
       <c r="F324" t="n">
-        <v>115.0577392578125</v>
+        <v>32.2829003732928</v>
       </c>
       <c r="G324" t="n">
         <v>93</v>
@@ -9186,16 +9186,16 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>-1.821172475814819</v>
+        <v>-0.6711072610774125</v>
       </c>
       <c r="D325" t="n">
-        <v>11.40359687805176</v>
+        <v>8.257120175239367</v>
       </c>
       <c r="E325" t="n">
-        <v>14.64536790754882</v>
+        <v>11.27165364411673</v>
       </c>
       <c r="F325" t="n">
-        <v>90.960693359375</v>
+        <v>75.28851017964084</v>
       </c>
       <c r="G325" t="n">
         <v>78</v>
@@ -9213,16 +9213,16 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>-0.4378335475921631</v>
+        <v>-3.008615174371539</v>
       </c>
       <c r="D326" t="n">
-        <v>90.71733856201172</v>
+        <v>159.8629586961534</v>
       </c>
       <c r="E326" t="n">
-        <v>113.7168521413493</v>
+        <v>189.8749804656143</v>
       </c>
       <c r="F326" t="n">
-        <v>44.04671859741211</v>
+        <v>54.21421023235199</v>
       </c>
       <c r="G326" t="n">
         <v>18</v>
@@ -9240,16 +9240,16 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>-1.575698852539062</v>
+        <v>-0.8706842047778061</v>
       </c>
       <c r="D327" t="n">
-        <v>27.80570983886719</v>
+        <v>23.50251607144817</v>
       </c>
       <c r="E327" t="n">
-        <v>36.77209721771472</v>
+        <v>31.33798834043756</v>
       </c>
       <c r="F327" t="n">
-        <v>33.87638473510742</v>
+        <v>28.29469554484053</v>
       </c>
       <c r="G327" t="n">
         <v>89</v>
@@ -9267,16 +9267,16 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>-0.5223877429962158</v>
+        <v>-1.851201626413469</v>
       </c>
       <c r="D328" t="n">
-        <v>292.5158081054688</v>
+        <v>456.498829080601</v>
       </c>
       <c r="E328" t="n">
-        <v>369.7516691983959</v>
+        <v>506.0127558966839</v>
       </c>
       <c r="F328" t="n">
-        <v>35.91228103637695</v>
+        <v>58.67322018991333</v>
       </c>
       <c r="G328" t="n">
         <v>99</v>
@@ -9294,16 +9294,16 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>-0.2437885999679565</v>
+        <v>0.2762976324074323</v>
       </c>
       <c r="D329" t="n">
-        <v>293.057373046875</v>
+        <v>205.7702984553511</v>
       </c>
       <c r="E329" t="n">
-        <v>357.6442344530386</v>
+        <v>272.8085189117106</v>
       </c>
       <c r="F329" t="n">
-        <v>36.21072769165039</v>
+        <v>22.48314579514147</v>
       </c>
       <c r="G329" t="n">
         <v>93</v>
@@ -9321,16 +9321,16 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>-0.8042106628417969</v>
+        <v>-0.8670005735936976</v>
       </c>
       <c r="D330" t="n">
-        <v>8.620769500732422</v>
+        <v>8.706022244233351</v>
       </c>
       <c r="E330" t="n">
-        <v>11.7119465928241</v>
+        <v>11.91400280047058</v>
       </c>
       <c r="F330" t="n">
-        <v>100.758171081543</v>
+        <v>70.18927667796706</v>
       </c>
       <c r="G330" t="n">
         <v>78</v>
@@ -9348,16 +9348,16 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>-1.51707124710083</v>
+        <v>-1.817267427128847</v>
       </c>
       <c r="D331" t="n">
-        <v>131.8396606445312</v>
+        <v>139.4182607862684</v>
       </c>
       <c r="E331" t="n">
-        <v>150.4590436900521</v>
+        <v>159.178569009118</v>
       </c>
       <c r="F331" t="n">
-        <v>49.63168334960938</v>
+        <v>50.93734090512908</v>
       </c>
       <c r="G331" t="n">
         <v>18</v>
@@ -9375,16 +9375,16 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>-1.054601669311523</v>
+        <v>-0.2595336982005263</v>
       </c>
       <c r="D332" t="n">
-        <v>25.01724433898926</v>
+        <v>19.11488331569715</v>
       </c>
       <c r="E332" t="n">
-        <v>32.84238594336783</v>
+        <v>25.71436301664186</v>
       </c>
       <c r="F332" t="n">
-        <v>31.9730339050293</v>
+        <v>23.23338115641026</v>
       </c>
       <c r="G332" t="n">
         <v>89</v>
@@ -9402,16 +9402,16 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>-1.195911169052124</v>
+        <v>0.3327188750166445</v>
       </c>
       <c r="D333" t="n">
-        <v>356.6697692871094</v>
+        <v>198.5659982700541</v>
       </c>
       <c r="E333" t="n">
-        <v>444.0735264289012</v>
+        <v>244.7946488988397</v>
       </c>
       <c r="F333" t="n">
-        <v>55.09633255004883</v>
+        <v>34.54183968373295</v>
       </c>
       <c r="G333" t="n">
         <v>99</v>
@@ -9429,16 +9429,16 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>-22.36465644836426</v>
+        <v>-3.591956911221319</v>
       </c>
       <c r="D334" t="n">
-        <v>1241.005493164062</v>
+        <v>647.9411187941029</v>
       </c>
       <c r="E334" t="n">
-        <v>1550.092577880431</v>
+        <v>687.190003415733</v>
       </c>
       <c r="F334" t="n">
-        <v>162.3095092773438</v>
+        <v>78.68591969617424</v>
       </c>
       <c r="G334" t="n">
         <v>93</v>
@@ -9456,16 +9456,16 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>-0.4559409618377686</v>
+        <v>-0.3805902962991961</v>
       </c>
       <c r="D335" t="n">
-        <v>7.483597755432129</v>
+        <v>6.927816042533288</v>
       </c>
       <c r="E335" t="n">
-        <v>10.52100777560105</v>
+        <v>10.24513959937052</v>
       </c>
       <c r="F335" t="n">
-        <v>95.6510009765625</v>
+        <v>62.55656554820599</v>
       </c>
       <c r="G335" t="n">
         <v>78</v>
@@ -9483,16 +9483,16 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>-0.3623441457748413</v>
+        <v>-3.640330753320186</v>
       </c>
       <c r="D336" t="n">
-        <v>70.45464324951172</v>
+        <v>185.587043232388</v>
       </c>
       <c r="E336" t="n">
-        <v>110.6914172090592</v>
+        <v>204.28902126823</v>
       </c>
       <c r="F336" t="n">
-        <v>37.72591018676758</v>
+        <v>67.68697487512222</v>
       </c>
       <c r="G336" t="n">
         <v>18</v>
@@ -9510,16 +9510,16 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>-0.7915885448455811</v>
+        <v>-0.6211944980864532</v>
       </c>
       <c r="D337" t="n">
-        <v>23.29141616821289</v>
+        <v>21.06725969207421</v>
       </c>
       <c r="E337" t="n">
-        <v>30.66832076324852</v>
+        <v>29.17349329726974</v>
       </c>
       <c r="F337" t="n">
-        <v>29.8873462677002</v>
+        <v>25.26513353677961</v>
       </c>
       <c r="G337" t="n">
         <v>89</v>
@@ -9537,16 +9537,16 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>-2.062113285064697</v>
+        <v>-1.582220366494431</v>
       </c>
       <c r="D338" t="n">
-        <v>431.0391845703125</v>
+        <v>425.2112873732441</v>
       </c>
       <c r="E338" t="n">
-        <v>524.3945020211406</v>
+        <v>481.5530645352371</v>
       </c>
       <c r="F338" t="n">
-        <v>49.99063491821289</v>
+        <v>53.10070558606584</v>
       </c>
       <c r="G338" t="n">
         <v>99</v>
@@ -9564,16 +9564,16 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>-6.228216171264648</v>
+        <v>0.1468691898451178</v>
       </c>
       <c r="D339" t="n">
-        <v>711.1844482421875</v>
+        <v>223.303222328104</v>
       </c>
       <c r="E339" t="n">
-        <v>862.171205445879</v>
+        <v>296.2004706726592</v>
       </c>
       <c r="F339" t="n">
-        <v>87.11696624755859</v>
+        <v>21.1202806365057</v>
       </c>
       <c r="G339" t="n">
         <v>93</v>
@@ -9591,16 +9591,16 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>-0.7980953454971313</v>
+        <v>-0.8274173919965884</v>
       </c>
       <c r="D340" t="n">
-        <v>8.441810607910156</v>
+        <v>8.799399846639389</v>
       </c>
       <c r="E340" t="n">
-        <v>11.69208098203351</v>
+        <v>11.78702892022724</v>
       </c>
       <c r="F340" t="n">
-        <v>76.80641174316406</v>
+        <v>70.54556976266959</v>
       </c>
       <c r="G340" t="n">
         <v>78</v>
@@ -9618,16 +9618,16 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>-2.321736574172974</v>
+        <v>-2.255029344254267</v>
       </c>
       <c r="D341" t="n">
-        <v>153.1052856445312</v>
+        <v>148.9760305616591</v>
       </c>
       <c r="E341" t="n">
-        <v>172.8435268259271</v>
+        <v>171.0992134895432</v>
       </c>
       <c r="F341" t="n">
-        <v>60.80830001831055</v>
+        <v>51.35998742832402</v>
       </c>
       <c r="G341" t="n">
         <v>18</v>
@@ -9645,16 +9645,16 @@
         </is>
       </c>
       <c r="C342" t="n">
-        <v>-1.736569404602051</v>
+        <v>-1.329766573013788</v>
       </c>
       <c r="D342" t="n">
-        <v>28.98009490966797</v>
+        <v>27.04563603776225</v>
       </c>
       <c r="E342" t="n">
-        <v>37.90304403435577</v>
+        <v>34.97253229640221</v>
       </c>
       <c r="F342" t="n">
-        <v>34.50964736938477</v>
+        <v>32.41120722707624</v>
       </c>
       <c r="G342" t="n">
         <v>89</v>
@@ -9672,16 +9672,16 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>-2.399471282958984</v>
+        <v>-2.025832978512701</v>
       </c>
       <c r="D343" t="n">
-        <v>477.0024719238281</v>
+        <v>451.7551032172309</v>
       </c>
       <c r="E343" t="n">
-        <v>552.5265830708962</v>
+        <v>521.2786955831672</v>
       </c>
       <c r="F343" t="n">
-        <v>56.61016082763672</v>
+        <v>52.9253043066959</v>
       </c>
       <c r="G343" t="n">
         <v>99</v>
@@ -9699,16 +9699,16 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>-0.9952120780944824</v>
+        <v>0.3048343892830856</v>
       </c>
       <c r="D344" t="n">
-        <v>373.5649719238281</v>
+        <v>188.7695916288642</v>
       </c>
       <c r="E344" t="n">
-        <v>452.9731642161597</v>
+        <v>267.3757839613343</v>
       </c>
       <c r="F344" t="n">
-        <v>35.86848449707031</v>
+        <v>19.68207213622275</v>
       </c>
       <c r="G344" t="n">
         <v>93</v>
@@ -9726,16 +9726,16 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>-0.511305570602417</v>
+        <v>-0.690433530211507</v>
       </c>
       <c r="D345" t="n">
-        <v>7.609275817871094</v>
+        <v>7.986524667495337</v>
       </c>
       <c r="E345" t="n">
-        <v>10.71918097427585</v>
+        <v>11.33664432681304</v>
       </c>
       <c r="F345" t="n">
-        <v>93.77949523925781</v>
+        <v>69.23630247100746</v>
       </c>
       <c r="G345" t="n">
         <v>78</v>
@@ -9753,16 +9753,16 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>-6.643017768859863</v>
+        <v>-1.148603729412702</v>
       </c>
       <c r="D346" t="n">
-        <v>241.1653900146484</v>
+        <v>121.7617179022895</v>
       </c>
       <c r="E346" t="n">
-        <v>262.1820544726507</v>
+        <v>139.0108573091917</v>
       </c>
       <c r="F346" t="n">
-        <v>89.04609680175781</v>
+        <v>46.06669943738122</v>
       </c>
       <c r="G346" t="n">
         <v>18</v>
@@ -9780,16 +9780,16 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>-1.491742134094238</v>
+        <v>-0.9899056607388947</v>
       </c>
       <c r="D347" t="n">
-        <v>28.45255470275879</v>
+        <v>25.81671661205506</v>
       </c>
       <c r="E347" t="n">
-        <v>36.16782678480887</v>
+        <v>32.32117336715877</v>
       </c>
       <c r="F347" t="n">
-        <v>37.31308364868164</v>
+        <v>31.54035819435562</v>
       </c>
       <c r="G347" t="n">
         <v>89</v>
@@ -9807,16 +9807,16 @@
         </is>
       </c>
       <c r="C348" t="n">
-        <v>-0.9448227882385254</v>
+        <v>-1.513615198685391</v>
       </c>
       <c r="D348" t="n">
-        <v>303.2421569824219</v>
+        <v>409.0977675312697</v>
       </c>
       <c r="E348" t="n">
-        <v>417.9145584027912</v>
+        <v>475.1129814472325</v>
       </c>
       <c r="F348" t="n">
-        <v>56.96482849121094</v>
+        <v>48.64557361472649</v>
       </c>
       <c r="G348" t="n">
         <v>99</v>
@@ -9834,16 +9834,16 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>-43.04380798339844</v>
+        <v>-0.234761335714065</v>
       </c>
       <c r="D349" t="n">
-        <v>1794.178588867188</v>
+        <v>254.8629294774865</v>
       </c>
       <c r="E349" t="n">
-        <v>2128.238943351991</v>
+        <v>356.3439928817897</v>
       </c>
       <c r="F349" t="n">
-        <v>217.6033935546875</v>
+        <v>25.00243865508996</v>
       </c>
       <c r="G349" t="n">
         <v>93</v>
@@ -9861,16 +9861,16 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>-0.5618739128112793</v>
+        <v>-0.5683341047567587</v>
       </c>
       <c r="D350" t="n">
-        <v>8.482063293457031</v>
+        <v>7.892050449664776</v>
       </c>
       <c r="E350" t="n">
-        <v>10.89703767051742</v>
+        <v>10.91955060948045</v>
       </c>
       <c r="F350" t="n">
-        <v>122.7432861328125</v>
+        <v>70.75963382632858</v>
       </c>
       <c r="G350" t="n">
         <v>78</v>
@@ -9888,16 +9888,16 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>-2.443097352981567</v>
+        <v>-4.95877170240426</v>
       </c>
       <c r="D351" t="n">
-        <v>156.2286834716797</v>
+        <v>212.4010583029853</v>
       </c>
       <c r="E351" t="n">
-        <v>175.9726541255771</v>
+        <v>231.498900381268</v>
       </c>
       <c r="F351" t="n">
-        <v>54.67598342895508</v>
+        <v>73.82663364322497</v>
       </c>
       <c r="G351" t="n">
         <v>18</v>
@@ -9915,16 +9915,16 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>-0.8710343837738037</v>
+        <v>-1.308143573480528</v>
       </c>
       <c r="D352" t="n">
-        <v>23.94600296020508</v>
+        <v>27.10971065049761</v>
       </c>
       <c r="E352" t="n">
-        <v>31.34092144359501</v>
+        <v>34.80986066173026</v>
       </c>
       <c r="F352" t="n">
-        <v>32.24449920654297</v>
+        <v>32.57592099859848</v>
       </c>
       <c r="G352" t="n">
         <v>89</v>
@@ -9942,16 +9942,16 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>-2.802462816238403</v>
+        <v>-1.084982252946701</v>
       </c>
       <c r="D353" t="n">
-        <v>440.3907775878906</v>
+        <v>365.6785592743845</v>
       </c>
       <c r="E353" t="n">
-        <v>584.359344710085</v>
+        <v>432.7117429352205</v>
       </c>
       <c r="F353" t="n">
-        <v>55.01591110229492</v>
+        <v>43.51659666668592</v>
       </c>
       <c r="G353" t="n">
         <v>99</v>
@@ -9969,16 +9969,16 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>-21.43607902526855</v>
+        <v>0.0725100918722873</v>
       </c>
       <c r="D354" t="n">
-        <v>1298.206176757812</v>
+        <v>247.9214461131762</v>
       </c>
       <c r="E354" t="n">
-        <v>1518.977781272656</v>
+        <v>308.8392772791778</v>
       </c>
       <c r="F354" t="n">
-        <v>157.0455932617188</v>
+        <v>23.85765572343767</v>
       </c>
       <c r="G354" t="n">
         <v>93</v>
@@ -9996,16 +9996,16 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>-1.087658166885376</v>
+        <v>-0.7664328271026193</v>
       </c>
       <c r="D355" t="n">
-        <v>9.748940467834473</v>
+        <v>8.346399946090502</v>
       </c>
       <c r="E355" t="n">
-        <v>12.59839326816928</v>
+        <v>11.58868173072428</v>
       </c>
       <c r="F355" t="n">
-        <v>207.0217437744141</v>
+        <v>66.62471677545282</v>
       </c>
       <c r="G355" t="n">
         <v>78</v>
@@ -10023,16 +10023,16 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>-0.4987068176269531</v>
+        <v>-5.987513609633422</v>
       </c>
       <c r="D356" t="n">
-        <v>91.9281005859375</v>
+        <v>233.0180833604601</v>
       </c>
       <c r="E356" t="n">
-        <v>116.0991040151689</v>
+        <v>250.6870458270122</v>
       </c>
       <c r="F356" t="n">
-        <v>32.81344604492188</v>
+        <v>83.46020609734597</v>
       </c>
       <c r="G356" t="n">
         <v>18</v>
@@ -10050,16 +10050,16 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>-2.079301595687866</v>
+        <v>-1.727839525004533</v>
       </c>
       <c r="D357" t="n">
-        <v>32.64619445800781</v>
+        <v>29.61311843957794</v>
       </c>
       <c r="E357" t="n">
-        <v>40.20656654284301</v>
+        <v>37.84254045724339</v>
       </c>
       <c r="F357" t="n">
-        <v>47.37935256958008</v>
+        <v>35.17999516175077</v>
       </c>
       <c r="G357" t="n">
         <v>89</v>
@@ -10077,16 +10077,16 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>-4.665843963623047</v>
+        <v>-0.9131428347860147</v>
       </c>
       <c r="D358" t="n">
-        <v>586.7703857421875</v>
+        <v>351.9384744046914</v>
       </c>
       <c r="E358" t="n">
-        <v>713.3124534522021</v>
+        <v>414.4968149182145</v>
       </c>
       <c r="F358" t="n">
-        <v>101.6365737915039</v>
+        <v>41.40681901451624</v>
       </c>
       <c r="G358" t="n">
         <v>99</v>
@@ -10104,16 +10104,16 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>-36.15894317626953</v>
+        <v>0.4097551746595348</v>
       </c>
       <c r="D359" t="n">
-        <v>1705.903442382812</v>
+        <v>171.7165284515709</v>
       </c>
       <c r="E359" t="n">
-        <v>1954.83279336111</v>
+        <v>246.3735181865684</v>
       </c>
       <c r="F359" t="n">
-        <v>202.0977783203125</v>
+        <v>17.71766636630671</v>
       </c>
       <c r="G359" t="n">
         <v>93</v>
@@ -10131,16 +10131,16 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>-0.3158504962921143</v>
+        <v>-0.5469671857471528</v>
       </c>
       <c r="D360" t="n">
-        <v>7.268117904663086</v>
+        <v>7.516001255084307</v>
       </c>
       <c r="E360" t="n">
-        <v>10.00204332456643</v>
+        <v>10.84491176548315</v>
       </c>
       <c r="F360" t="n">
-        <v>138.5851440429688</v>
+        <v>61.04793215990928</v>
       </c>
       <c r="G360" t="n">
         <v>78</v>
@@ -10158,16 +10158,16 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>-11.08670997619629</v>
+        <v>-5.910342147736023</v>
       </c>
       <c r="D361" t="n">
-        <v>307.8316650390625</v>
+        <v>231.9035588370429</v>
       </c>
       <c r="E361" t="n">
-        <v>329.704270900454</v>
+        <v>249.2988841119521</v>
       </c>
       <c r="F361" t="n">
-        <v>117.8665161132812</v>
+        <v>82.52159143028436</v>
       </c>
       <c r="G361" t="n">
         <v>18</v>

--- a/results/surrogate_comparison.xlsx
+++ b/results/surrogate_comparison.xlsx
@@ -465,16 +465,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.3072641484405483</v>
+        <v>-0.4433546853638226</v>
       </c>
       <c r="D2" t="n">
-        <v>17.78658916173356</v>
+        <v>18.52742726615306</v>
       </c>
       <c r="E2" t="n">
-        <v>26.19705973824611</v>
+        <v>27.52690652964422</v>
       </c>
       <c r="F2" t="n">
-        <v>22.65103009560166</v>
+        <v>23.21959805540183</v>
       </c>
       <c r="G2" t="n">
         <v>89</v>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.3465122657973161</v>
+        <v>-0.2166850844939658</v>
       </c>
       <c r="D3" t="n">
-        <v>284.0645796650588</v>
+        <v>259.892372054283</v>
       </c>
       <c r="E3" t="n">
-        <v>347.7384042594837</v>
+        <v>330.5495664791308</v>
       </c>
       <c r="F3" t="n">
-        <v>36.55196720430772</v>
+        <v>31.7579700030932</v>
       </c>
       <c r="G3" t="n">
         <v>99</v>
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.0843912241645246</v>
+        <v>-0.1244208886001663</v>
       </c>
       <c r="D4" t="n">
-        <v>240.8351089313466</v>
+        <v>243.1851038778982</v>
       </c>
       <c r="E4" t="n">
-        <v>333.9419110601584</v>
+        <v>340.0496902348658</v>
       </c>
       <c r="F4" t="n">
-        <v>22.84011131083356</v>
+        <v>23.72542402097881</v>
       </c>
       <c r="G4" t="n">
         <v>93</v>
@@ -546,16 +546,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.156898204465231</v>
+        <v>-0.1912434446916196</v>
       </c>
       <c r="D5" t="n">
-        <v>6.001259186328986</v>
+        <v>6.194101015726726</v>
       </c>
       <c r="E5" t="n">
-        <v>9.378492721033419</v>
+        <v>9.516685866376974</v>
       </c>
       <c r="F5" t="n">
-        <v>53.39400253438625</v>
+        <v>55.62269361421956</v>
       </c>
       <c r="G5" t="n">
         <v>78</v>
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-5.953406757707963</v>
+        <v>-6.319836021418417</v>
       </c>
       <c r="D6" t="n">
-        <v>233.2503853903876</v>
+        <v>240.297711054484</v>
       </c>
       <c r="E6" t="n">
-        <v>250.074481363366</v>
+        <v>256.5790750412079</v>
       </c>
       <c r="F6" t="n">
-        <v>84.17094205932058</v>
+        <v>87.31599924242198</v>
       </c>
       <c r="G6" t="n">
         <v>18</v>
@@ -600,16 +600,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.3562135824898545</v>
+        <v>-0.5232482234761384</v>
       </c>
       <c r="D7" t="n">
-        <v>18.05010769876202</v>
+        <v>19.30319916800167</v>
       </c>
       <c r="E7" t="n">
-        <v>26.6830161927196</v>
+        <v>28.27848997612359</v>
       </c>
       <c r="F7" t="n">
-        <v>22.61665948545714</v>
+        <v>24.06901622479159</v>
       </c>
       <c r="G7" t="n">
         <v>89</v>
@@ -627,16 +627,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.2126494740735947</v>
+        <v>-0.2640173976847997</v>
       </c>
       <c r="D8" t="n">
-        <v>259.2783704044843</v>
+        <v>263.0321055710918</v>
       </c>
       <c r="E8" t="n">
-        <v>330.000912892615</v>
+        <v>336.9178539114663</v>
       </c>
       <c r="F8" t="n">
-        <v>31.59391640024469</v>
+        <v>31.80603782982222</v>
       </c>
       <c r="G8" t="n">
         <v>99</v>
@@ -654,16 +654,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.1674362721357603</v>
+        <v>-0.2052623940811666</v>
       </c>
       <c r="D9" t="n">
-        <v>246.2278455508653</v>
+        <v>252.144030827348</v>
       </c>
       <c r="E9" t="n">
-        <v>346.49304561538</v>
+        <v>352.0616614381422</v>
       </c>
       <c r="F9" t="n">
-        <v>24.09703788464843</v>
+        <v>24.73195082895289</v>
       </c>
       <c r="G9" t="n">
         <v>93</v>
@@ -681,16 +681,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.2190301553017804</v>
+        <v>-0.2240688107134829</v>
       </c>
       <c r="D10" t="n">
-        <v>6.271222952084663</v>
+        <v>6.325749195539034</v>
       </c>
       <c r="E10" t="n">
-        <v>9.627038234086605</v>
+        <v>9.646913586306365</v>
       </c>
       <c r="F10" t="n">
-        <v>57.98680114990958</v>
+        <v>57.97777326957719</v>
       </c>
       <c r="G10" t="n">
         <v>78</v>
@@ -708,16 +708,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-6.130273246065486</v>
+        <v>-6.516382907779738</v>
       </c>
       <c r="D11" t="n">
-        <v>237.3195865419176</v>
+        <v>243.7098619672987</v>
       </c>
       <c r="E11" t="n">
-        <v>253.2349508522515</v>
+        <v>260.0009933781797</v>
       </c>
       <c r="F11" t="n">
-        <v>85.9969832682841</v>
+        <v>88.47717702966729</v>
       </c>
       <c r="G11" t="n">
         <v>18</v>
@@ -735,16 +735,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.4936522320197756</v>
+        <v>-0.6105230048210351</v>
       </c>
       <c r="D12" t="n">
-        <v>20.07610929682014</v>
+        <v>21.23204966341511</v>
       </c>
       <c r="E12" t="n">
-        <v>28.00242360611291</v>
+        <v>29.07731768305414</v>
       </c>
       <c r="F12" t="n">
-        <v>25.18497008971853</v>
+        <v>26.20545300843988</v>
       </c>
       <c r="G12" t="n">
         <v>89</v>
@@ -762,16 +762,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.5703311507458499</v>
+        <v>-0.6305797074873616</v>
       </c>
       <c r="D13" t="n">
-        <v>311.3123267587989</v>
+        <v>304.3984029750631</v>
       </c>
       <c r="E13" t="n">
-        <v>375.5286905220995</v>
+        <v>382.6648014986005</v>
       </c>
       <c r="F13" t="n">
-        <v>40.26112515905412</v>
+        <v>38.61739532235065</v>
       </c>
       <c r="G13" t="n">
         <v>99</v>
@@ -789,16 +789,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.3023972443355452</v>
+        <v>-0.4723667180206208</v>
       </c>
       <c r="D14" t="n">
-        <v>288.2823033486643</v>
+        <v>300.060799547421</v>
       </c>
       <c r="E14" t="n">
-        <v>365.9735218748763</v>
+        <v>389.1221268629725</v>
       </c>
       <c r="F14" t="n">
-        <v>29.50074257876374</v>
+        <v>29.86602709319129</v>
       </c>
       <c r="G14" t="n">
         <v>93</v>
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.5625398920205991</v>
+        <v>-0.6054362147766987</v>
       </c>
       <c r="D15" t="n">
-        <v>7.291862845420837</v>
+        <v>7.390923634553567</v>
       </c>
       <c r="E15" t="n">
-        <v>10.8993607962309</v>
+        <v>11.04795762596857</v>
       </c>
       <c r="F15" t="n">
-        <v>70.49442013191025</v>
+        <v>71.46432785134684</v>
       </c>
       <c r="G15" t="n">
         <v>78</v>
@@ -843,16 +843,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-6.514974862399907</v>
+        <v>-6.877170957055541</v>
       </c>
       <c r="D16" t="n">
-        <v>245.0524733861288</v>
+        <v>250.2345217598809</v>
       </c>
       <c r="E16" t="n">
-        <v>259.9766392208243</v>
+        <v>266.1679101043237</v>
       </c>
       <c r="F16" t="n">
-        <v>90.02255155222686</v>
+        <v>91.2008337242217</v>
       </c>
       <c r="G16" t="n">
         <v>18</v>
@@ -870,16 +870,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.592261629853911</v>
+        <v>-0.6405610935862798</v>
       </c>
       <c r="D17" t="n">
-        <v>21.14445360590902</v>
+        <v>21.36564614799585</v>
       </c>
       <c r="E17" t="n">
-        <v>28.91199697831197</v>
+        <v>29.34722751574721</v>
       </c>
       <c r="F17" t="n">
-        <v>26.17478300571639</v>
+        <v>26.16281808231566</v>
       </c>
       <c r="G17" t="n">
         <v>89</v>
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.5250174577575086</v>
+        <v>-0.4226068654313968</v>
       </c>
       <c r="D18" t="n">
-        <v>299.6331321639244</v>
+        <v>292.7752334132339</v>
       </c>
       <c r="E18" t="n">
-        <v>370.0708755153819</v>
+        <v>357.4291349357281</v>
       </c>
       <c r="F18" t="n">
-        <v>38.5736470498556</v>
+        <v>37.41024216704611</v>
       </c>
       <c r="G18" t="n">
         <v>99</v>
@@ -924,16 +924,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.3043011636924173</v>
+        <v>-0.5043186532267536</v>
       </c>
       <c r="D19" t="n">
-        <v>290.0358476536248</v>
+        <v>303.0115182527932</v>
       </c>
       <c r="E19" t="n">
-        <v>366.2409247781038</v>
+        <v>393.3216491334703</v>
       </c>
       <c r="F19" t="n">
-        <v>29.33559820892856</v>
+        <v>30.56847213527716</v>
       </c>
       <c r="G19" t="n">
         <v>93</v>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.6011122095914649</v>
+        <v>-0.6592724614386916</v>
       </c>
       <c r="D20" t="n">
-        <v>7.31931205590566</v>
+        <v>7.585002672977937</v>
       </c>
       <c r="E20" t="n">
-        <v>11.03306957394549</v>
+        <v>11.23166974041273</v>
       </c>
       <c r="F20" t="n">
-        <v>69.90194024014485</v>
+        <v>72.12605330803041</v>
       </c>
       <c r="G20" t="n">
         <v>78</v>
@@ -978,16 +978,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-6.639855798617955</v>
+        <v>-6.637238973400845</v>
       </c>
       <c r="D21" t="n">
-        <v>246.6724683973524</v>
+        <v>247.0020982954237</v>
       </c>
       <c r="E21" t="n">
-        <v>262.1278345664948</v>
+        <v>262.0829383345823</v>
       </c>
       <c r="F21" t="n">
-        <v>90.31635146045154</v>
+        <v>90.60451631097899</v>
       </c>
       <c r="G21" t="n">
         <v>18</v>
@@ -1005,16 +1005,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.3190428523755027</v>
+        <v>-0.4249748090074423</v>
       </c>
       <c r="D22" t="n">
-        <v>17.56953151574296</v>
+        <v>18.79910912674465</v>
       </c>
       <c r="E22" t="n">
-        <v>26.31481538147835</v>
+        <v>27.35107928418134</v>
       </c>
       <c r="F22" t="n">
-        <v>22.28724507592869</v>
+        <v>23.59621548316874</v>
       </c>
       <c r="G22" t="n">
         <v>89</v>
@@ -1032,16 +1032,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.3325667461566131</v>
+        <v>-0.4876250568993015</v>
       </c>
       <c r="D23" t="n">
-        <v>281.4172358657374</v>
+        <v>290.441417193172</v>
       </c>
       <c r="E23" t="n">
-        <v>345.9329939685035</v>
+        <v>365.5057742451698</v>
       </c>
       <c r="F23" t="n">
-        <v>35.62225782888974</v>
+        <v>36.16119228882673</v>
       </c>
       <c r="G23" t="n">
         <v>99</v>
@@ -1059,16 +1059,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.2772937491028276</v>
+        <v>-0.3971082230854419</v>
       </c>
       <c r="D24" t="n">
-        <v>267.9284963300151</v>
+        <v>266.4825101462744</v>
       </c>
       <c r="E24" t="n">
-        <v>362.4293202181124</v>
+        <v>379.0469055259701</v>
       </c>
       <c r="F24" t="n">
-        <v>26.56927439142802</v>
+        <v>25.9184284788149</v>
       </c>
       <c r="G24" t="n">
         <v>93</v>
@@ -1086,16 +1086,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.2332150604697607</v>
+        <v>-0.2408372801356713</v>
       </c>
       <c r="D25" t="n">
-        <v>6.410100288880177</v>
+        <v>6.468798671013269</v>
       </c>
       <c r="E25" t="n">
-        <v>9.682887411323394</v>
+        <v>9.712765169550172</v>
       </c>
       <c r="F25" t="n">
-        <v>63.88330338888119</v>
+        <v>62.68603953344653</v>
       </c>
       <c r="G25" t="n">
         <v>78</v>
@@ -1113,16 +1113,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-6.755483744892608</v>
+        <v>-6.304824360913674</v>
       </c>
       <c r="D26" t="n">
-        <v>246.2555590735541</v>
+        <v>238.3590316772461</v>
       </c>
       <c r="E26" t="n">
-        <v>264.1040159319073</v>
+        <v>256.3158413596589</v>
       </c>
       <c r="F26" t="n">
-        <v>87.84528889508135</v>
+        <v>84.9251357609479</v>
       </c>
       <c r="G26" t="n">
         <v>18</v>
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-1.040303095091922</v>
+        <v>-0.9800782623423003</v>
       </c>
       <c r="D27" t="n">
-        <v>23.98492455214597</v>
+        <v>22.63779498753923</v>
       </c>
       <c r="E27" t="n">
-        <v>32.72790600505611</v>
+        <v>32.24126350192439</v>
       </c>
       <c r="F27" t="n">
-        <v>28.30041748576344</v>
+        <v>27.39435587908935</v>
       </c>
       <c r="G27" t="n">
         <v>89</v>
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-1.072889654062955</v>
+        <v>-0.7521031502067419</v>
       </c>
       <c r="D28" t="n">
-        <v>353.6823023015803</v>
+        <v>314.9342027143999</v>
       </c>
       <c r="E28" t="n">
-        <v>431.4550850641374</v>
+        <v>396.6681540450891</v>
       </c>
       <c r="F28" t="n">
-        <v>40.58623559583062</v>
+        <v>36.35278355372198</v>
       </c>
       <c r="G28" t="n">
         <v>99</v>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.7903189867696965</v>
+        <v>-0.5493961242081549</v>
       </c>
       <c r="D29" t="n">
-        <v>341.4309525028352</v>
+        <v>282.5962074854041</v>
       </c>
       <c r="E29" t="n">
-        <v>429.0848094450324</v>
+        <v>399.1711669831904</v>
       </c>
       <c r="F29" t="n">
-        <v>30.9397860855669</v>
+        <v>26.6363052858097</v>
       </c>
       <c r="G29" t="n">
         <v>93</v>
@@ -1221,16 +1221,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.5866542723655261</v>
+        <v>-0.4885319173975196</v>
       </c>
       <c r="D30" t="n">
-        <v>7.690622659829947</v>
+        <v>7.388545815761272</v>
       </c>
       <c r="E30" t="n">
-        <v>10.98314266536361</v>
+        <v>10.63811174215191</v>
       </c>
       <c r="F30" t="n">
-        <v>72.22647384751426</v>
+        <v>68.78475193875919</v>
       </c>
       <c r="G30" t="n">
         <v>78</v>
@@ -1248,16 +1248,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-7.078967031045412</v>
+        <v>-7.153564558770304</v>
       </c>
       <c r="D31" t="n">
-        <v>252.7446058061388</v>
+        <v>254.5191548665365</v>
       </c>
       <c r="E31" t="n">
-        <v>269.5556734564208</v>
+        <v>270.7972914962932</v>
       </c>
       <c r="F31" t="n">
-        <v>91.72107226166149</v>
+        <v>92.80769973090747</v>
       </c>
       <c r="G31" t="n">
         <v>18</v>
@@ -1275,16 +1275,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.6887375210439668</v>
+        <v>-0.6301918766991375</v>
       </c>
       <c r="D32" t="n">
-        <v>20.73987802226892</v>
+        <v>20.65723897098156</v>
       </c>
       <c r="E32" t="n">
-        <v>29.77501242677582</v>
+        <v>29.25433547392583</v>
       </c>
       <c r="F32" t="n">
-        <v>24.4808748485773</v>
+        <v>24.54569476521053</v>
       </c>
       <c r="G32" t="n">
         <v>89</v>
@@ -1302,16 +1302,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.3686207661977268</v>
+        <v>-0.559606235202782</v>
       </c>
       <c r="D33" t="n">
-        <v>285.1443421334931</v>
+        <v>306.4565072107796</v>
       </c>
       <c r="E33" t="n">
-        <v>350.5815546372194</v>
+        <v>374.2441163210599</v>
       </c>
       <c r="F33" t="n">
-        <v>33.77669032280083</v>
+        <v>35.97961031263934</v>
       </c>
       <c r="G33" t="n">
         <v>99</v>
@@ -1329,16 +1329,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-8.290178894312195</v>
+        <v>-4.424537872601253</v>
       </c>
       <c r="D34" t="n">
-        <v>829.401377688172</v>
+        <v>683.2225722446236</v>
       </c>
       <c r="E34" t="n">
-        <v>977.4396888922822</v>
+        <v>746.8945731303328</v>
       </c>
       <c r="F34" t="n">
-        <v>98.99495757703627</v>
+        <v>78.97954476047772</v>
       </c>
       <c r="G34" t="n">
         <v>93</v>
@@ -1356,16 +1356,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-0.2546967979455157</v>
+        <v>-0.2582835908418688</v>
       </c>
       <c r="D35" t="n">
-        <v>6.708555606695322</v>
+        <v>6.542941010915316</v>
       </c>
       <c r="E35" t="n">
-        <v>9.766857851832505</v>
+        <v>9.780808112933709</v>
       </c>
       <c r="F35" t="n">
-        <v>67.40555461532048</v>
+        <v>66.10203741123985</v>
       </c>
       <c r="G35" t="n">
         <v>78</v>
@@ -1383,16 +1383,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-2.520468750780295</v>
+        <v>-5.083551361093961</v>
       </c>
       <c r="D36" t="n">
-        <v>157.5548351075914</v>
+        <v>213.3989946577284</v>
       </c>
       <c r="E36" t="n">
-        <v>177.9388608667372</v>
+        <v>233.9101937203399</v>
       </c>
       <c r="F36" t="n">
-        <v>57.76817954644618</v>
+        <v>73.92508420757373</v>
       </c>
       <c r="G36" t="n">
         <v>18</v>
@@ -1410,16 +1410,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-0.9031867519468004</v>
+        <v>-1.040096239523901</v>
       </c>
       <c r="D37" t="n">
-        <v>23.76065354936578</v>
+        <v>23.96677246522368</v>
       </c>
       <c r="E37" t="n">
-        <v>31.60905979009016</v>
+        <v>32.72624690812973</v>
       </c>
       <c r="F37" t="n">
-        <v>28.60230451716832</v>
+        <v>27.81308560980368</v>
       </c>
       <c r="G37" t="n">
         <v>89</v>
@@ -1437,16 +1437,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-0.3996542227901694</v>
+        <v>-0.4405001882345934</v>
       </c>
       <c r="D38" t="n">
-        <v>292.9044896906072</v>
+        <v>281.6791707048512</v>
       </c>
       <c r="E38" t="n">
-        <v>354.5339907753966</v>
+        <v>359.669954181316</v>
       </c>
       <c r="F38" t="n">
-        <v>35.34564287841501</v>
+        <v>32.8337685200995</v>
       </c>
       <c r="G38" t="n">
         <v>99</v>
@@ -1464,16 +1464,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.4769441903239487</v>
+        <v>-3.231218131027331</v>
       </c>
       <c r="D39" t="n">
-        <v>184.8829713226646</v>
+        <v>528.3580801358787</v>
       </c>
       <c r="E39" t="n">
-        <v>231.9273395442031</v>
+        <v>659.6455523619329</v>
       </c>
       <c r="F39" t="n">
-        <v>20.67754337034225</v>
+        <v>65.57364961492338</v>
       </c>
       <c r="G39" t="n">
         <v>93</v>
@@ -1491,16 +1491,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-0.5016864578997249</v>
+        <v>-0.6335745728939657</v>
       </c>
       <c r="D40" t="n">
-        <v>7.260508194947854</v>
+        <v>7.947351529048039</v>
       </c>
       <c r="E40" t="n">
-        <v>10.68501421648082</v>
+        <v>11.14435542692986</v>
       </c>
       <c r="F40" t="n">
-        <v>64.16286033762766</v>
+        <v>74.73986168719836</v>
       </c>
       <c r="G40" t="n">
         <v>78</v>
@@ -1518,16 +1518,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-4.126228556117708</v>
+        <v>-3.60101911693528</v>
       </c>
       <c r="D41" t="n">
-        <v>195.7884472741021</v>
+        <v>186.5478943718804</v>
       </c>
       <c r="E41" t="n">
-        <v>214.7185382388743</v>
+        <v>203.4218398577079</v>
       </c>
       <c r="F41" t="n">
-        <v>67.92346195398073</v>
+        <v>66.33093644657495</v>
       </c>
       <c r="G41" t="n">
         <v>18</v>
@@ -1545,16 +1545,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-0.6073658732630696</v>
+        <v>-0.2658648719891576</v>
       </c>
       <c r="D42" t="n">
-        <v>22.22232687875126</v>
+        <v>20.63560127944089</v>
       </c>
       <c r="E42" t="n">
-        <v>29.04880335857041</v>
+        <v>25.77890993135084</v>
       </c>
       <c r="F42" t="n">
-        <v>26.97099939307425</v>
+        <v>30.75009940994461</v>
       </c>
       <c r="G42" t="n">
         <v>89</v>
@@ -1572,16 +1572,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.09592182583488251</v>
+        <v>0.07815204987977165</v>
       </c>
       <c r="D43" t="n">
-        <v>222.1371254969125</v>
+        <v>226.6489379574554</v>
       </c>
       <c r="E43" t="n">
-        <v>284.9380791856747</v>
+        <v>287.724700757809</v>
       </c>
       <c r="F43" t="n">
-        <v>36.9338021111279</v>
+        <v>42.53183377070678</v>
       </c>
       <c r="G43" t="n">
         <v>99</v>
@@ -1599,16 +1599,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-3.865217447812372</v>
+        <v>-11.9185278430578</v>
       </c>
       <c r="D44" t="n">
-        <v>657.1819871471774</v>
+        <v>1113.83639952957</v>
       </c>
       <c r="E44" t="n">
-        <v>707.3413693661138</v>
+        <v>1152.615469006447</v>
       </c>
       <c r="F44" t="n">
-        <v>80.56230023227077</v>
+        <v>133.7612397023653</v>
       </c>
       <c r="G44" t="n">
         <v>93</v>
@@ -1626,16 +1626,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.4137607763614504</v>
+        <v>-0.3199648689231966</v>
       </c>
       <c r="D45" t="n">
-        <v>7.590343395868937</v>
+        <v>7.304104377061893</v>
       </c>
       <c r="E45" t="n">
-        <v>10.3674854928677</v>
+        <v>10.01766855324757</v>
       </c>
       <c r="F45" t="n">
-        <v>84.06196489090652</v>
+        <v>84.35395208960151</v>
       </c>
       <c r="G45" t="n">
         <v>78</v>
@@ -1653,16 +1653,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-1.964722082961699</v>
+        <v>-1.417639971518604</v>
       </c>
       <c r="D46" t="n">
-        <v>140.0951025221083</v>
+        <v>122.194995880127</v>
       </c>
       <c r="E46" t="n">
-        <v>163.2911145164973</v>
+        <v>147.4573323456971</v>
       </c>
       <c r="F46" t="n">
-        <v>52.11919073258375</v>
+        <v>46.95617916840063</v>
       </c>
       <c r="G46" t="n">
         <v>18</v>
@@ -1680,16 +1680,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.8029031812242198</v>
+        <v>-0.9633827075801049</v>
       </c>
       <c r="D47" t="n">
-        <v>22.94288939572452</v>
+        <v>23.87727806005585</v>
       </c>
       <c r="E47" t="n">
-        <v>30.7650111996374</v>
+        <v>32.10505038487623</v>
       </c>
       <c r="F47" t="n">
-        <v>27.58231326003771</v>
+        <v>28.77333807697932</v>
       </c>
       <c r="G47" t="n">
         <v>89</v>
@@ -1707,16 +1707,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-0.6901756179470575</v>
+        <v>-0.5198701518104034</v>
       </c>
       <c r="D48" t="n">
-        <v>325.1736567333491</v>
+        <v>309.4393964054609</v>
       </c>
       <c r="E48" t="n">
-        <v>389.5950372527197</v>
+        <v>369.4458078889135</v>
       </c>
       <c r="F48" t="n">
-        <v>40.00038952705444</v>
+        <v>36.44466740909726</v>
       </c>
       <c r="G48" t="n">
         <v>99</v>
@@ -1734,16 +1734,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-1.13309948485514</v>
+        <v>0.3390836855064515</v>
       </c>
       <c r="D49" t="n">
-        <v>406.5952410954301</v>
+        <v>200.6278017105595</v>
       </c>
       <c r="E49" t="n">
-        <v>468.3639785445299</v>
+        <v>260.7060846148894</v>
       </c>
       <c r="F49" t="n">
-        <v>52.6464160461428</v>
+        <v>21.94836482608741</v>
       </c>
       <c r="G49" t="n">
         <v>93</v>
@@ -1761,16 +1761,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.3530611250626676</v>
+        <v>-0.2731679496765009</v>
       </c>
       <c r="D50" t="n">
-        <v>7.129007944693933</v>
+        <v>6.76723143687615</v>
       </c>
       <c r="E50" t="n">
-        <v>10.14248047642301</v>
+        <v>9.838487106469985</v>
       </c>
       <c r="F50" t="n">
-        <v>66.25284197338944</v>
+        <v>68.10539294986468</v>
       </c>
       <c r="G50" t="n">
         <v>78</v>
@@ -1788,16 +1788,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-1.507637289072617</v>
+        <v>-2.468788189854897</v>
       </c>
       <c r="D51" t="n">
-        <v>129.7535845438639</v>
+        <v>157.3167576260037</v>
       </c>
       <c r="E51" t="n">
-        <v>150.1768251407771</v>
+        <v>176.6279588094755</v>
       </c>
       <c r="F51" t="n">
-        <v>47.25746321548785</v>
+        <v>56.52108204672276</v>
       </c>
       <c r="G51" t="n">
         <v>18</v>
@@ -1815,16 +1815,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-1.388696760533941</v>
+        <v>-1.343752314074517</v>
       </c>
       <c r="D52" t="n">
-        <v>28.15463207544905</v>
+        <v>28.00341584709253</v>
       </c>
       <c r="E52" t="n">
-        <v>35.41207581071647</v>
+        <v>35.07734642920675</v>
       </c>
       <c r="F52" t="n">
-        <v>33.42160971997356</v>
+        <v>33.2580733030431</v>
       </c>
       <c r="G52" t="n">
         <v>89</v>
@@ -1842,16 +1842,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.5785131323079133</v>
+        <v>-1.092614072956793</v>
       </c>
       <c r="D53" t="n">
-        <v>316.1964240796638</v>
+        <v>360.5005725899128</v>
       </c>
       <c r="E53" t="n">
-        <v>376.5057382359775</v>
+        <v>433.5029634995768</v>
       </c>
       <c r="F53" t="n">
-        <v>38.39208546384418</v>
+        <v>42.75689942619029</v>
       </c>
       <c r="G53" t="n">
         <v>99</v>
@@ -1869,16 +1869,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.2889272756895652</v>
+        <v>-0.06406541735680049</v>
       </c>
       <c r="D54" t="n">
-        <v>190.2254067697833</v>
+        <v>237.9108066353747</v>
       </c>
       <c r="E54" t="n">
-        <v>270.4175919483293</v>
+        <v>330.7974060652663</v>
       </c>
       <c r="F54" t="n">
-        <v>20.07786198347624</v>
+        <v>29.43323190791053</v>
       </c>
       <c r="G54" t="n">
         <v>93</v>
@@ -1896,16 +1896,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-0.5398361406289216</v>
+        <v>-0.7493661117904729</v>
       </c>
       <c r="D55" t="n">
-        <v>7.547737048222468</v>
+        <v>8.272061564983465</v>
       </c>
       <c r="E55" t="n">
-        <v>10.81988703156064</v>
+        <v>11.53256276190246</v>
       </c>
       <c r="F55" t="n">
-        <v>69.29105275692513</v>
+        <v>69.02721341830558</v>
       </c>
       <c r="G55" t="n">
         <v>78</v>
@@ -1923,16 +1923,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-2.667159129964999</v>
+        <v>-3.071168959770504</v>
       </c>
       <c r="D56" t="n">
-        <v>160.3341348436144</v>
+        <v>171.3428501553006</v>
       </c>
       <c r="E56" t="n">
-        <v>181.6081929232232</v>
+        <v>191.3507295828701</v>
       </c>
       <c r="F56" t="n">
-        <v>57.72136479545487</v>
+        <v>60.01040507045793</v>
       </c>
       <c r="G56" t="n">
         <v>18</v>
@@ -1950,16 +1950,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-0.712612010935548</v>
+        <v>-0.9474637921688138</v>
       </c>
       <c r="D57" t="n">
-        <v>22.15713590986273</v>
+        <v>24.47720774104086</v>
       </c>
       <c r="E57" t="n">
-        <v>29.98474554856081</v>
+        <v>31.97463318648046</v>
       </c>
       <c r="F57" t="n">
-        <v>26.46629967631079</v>
+        <v>29.54778872735012</v>
       </c>
       <c r="G57" t="n">
         <v>89</v>
@@ -1977,16 +1977,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-0.6784445221405448</v>
+        <v>-0.83914022949874</v>
       </c>
       <c r="D58" t="n">
-        <v>322.9315535420119</v>
+        <v>339.9813905966402</v>
       </c>
       <c r="E58" t="n">
-        <v>388.2406410681739</v>
+        <v>406.401144239207</v>
       </c>
       <c r="F58" t="n">
-        <v>37.79107198383351</v>
+        <v>39.42977219262929</v>
       </c>
       <c r="G58" t="n">
         <v>99</v>
@@ -2004,16 +2004,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-0.02217820535706827</v>
+        <v>0.001413163636892922</v>
       </c>
       <c r="D59" t="n">
-        <v>269.418691983787</v>
+        <v>260.9485611454133</v>
       </c>
       <c r="E59" t="n">
-        <v>324.2210735461169</v>
+        <v>320.4578019208748</v>
       </c>
       <c r="F59" t="n">
-        <v>34.17419424001673</v>
+        <v>30.09114131111776</v>
       </c>
       <c r="G59" t="n">
         <v>93</v>
@@ -2031,16 +2031,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-0.5098301449884124</v>
+        <v>-0.573500482287117</v>
       </c>
       <c r="D60" t="n">
-        <v>7.598719009986291</v>
+        <v>7.748043277324775</v>
       </c>
       <c r="E60" t="n">
-        <v>10.7139476063095</v>
+        <v>10.93752131393213</v>
       </c>
       <c r="F60" t="n">
-        <v>73.06407608655935</v>
+        <v>68.50092680356649</v>
       </c>
       <c r="G60" t="n">
         <v>78</v>
@@ -2058,16 +2058,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-1.562177349127126</v>
+        <v>-2.849318707839123</v>
       </c>
       <c r="D61" t="n">
-        <v>131.2283100552029</v>
+        <v>164.9558842976888</v>
       </c>
       <c r="E61" t="n">
-        <v>151.8011818833562</v>
+        <v>186.0640604692693</v>
       </c>
       <c r="F61" t="n">
-        <v>48.19410375702947</v>
+        <v>57.88403599077412</v>
       </c>
       <c r="G61" t="n">
         <v>18</v>
@@ -2085,16 +2085,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-0.9561016447504809</v>
+        <v>-0.8605010070335575</v>
       </c>
       <c r="D62" t="n">
-        <v>24.59569491697161</v>
+        <v>23.13001392664534</v>
       </c>
       <c r="E62" t="n">
-        <v>32.0454654628026</v>
+        <v>31.25257670158128</v>
       </c>
       <c r="F62" t="n">
-        <v>29.65577881898939</v>
+        <v>27.55316720415363</v>
       </c>
       <c r="G62" t="n">
         <v>89</v>
@@ -2112,16 +2112,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-1.010680123885915</v>
+        <v>-0.3936570380115552</v>
       </c>
       <c r="D63" t="n">
-        <v>359.9001786973741</v>
+        <v>288.6277724757339</v>
       </c>
       <c r="E63" t="n">
-        <v>424.9315645428971</v>
+        <v>353.7736285794363</v>
       </c>
       <c r="F63" t="n">
-        <v>42.70344374607338</v>
+        <v>33.98067408835536</v>
       </c>
       <c r="G63" t="n">
         <v>99</v>
@@ -2139,16 +2139,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.2191522760674934</v>
+        <v>0.4785468939898412</v>
       </c>
       <c r="D64" t="n">
-        <v>201.5814359931535</v>
+        <v>177.1591442477319</v>
       </c>
       <c r="E64" t="n">
-        <v>283.3747209275528</v>
+        <v>231.5717408023934</v>
       </c>
       <c r="F64" t="n">
-        <v>21.81242916628523</v>
+        <v>20.45740992457245</v>
       </c>
       <c r="G64" t="n">
         <v>93</v>
@@ -2166,16 +2166,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-0.2766191155782776</v>
+        <v>-0.2350427910799582</v>
       </c>
       <c r="D65" t="n">
-        <v>6.542743912109962</v>
+        <v>6.518052960053469</v>
       </c>
       <c r="E65" t="n">
-        <v>9.851812635317803</v>
+        <v>9.690060189923535</v>
       </c>
       <c r="F65" t="n">
-        <v>65.00816710839401</v>
+        <v>60.21703257484342</v>
       </c>
       <c r="G65" t="n">
         <v>78</v>
@@ -2193,16 +2193,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-2.494549600966554</v>
+        <v>-2.801511457300116</v>
       </c>
       <c r="D66" t="n">
-        <v>161.992542690701</v>
+        <v>168.096151775784</v>
       </c>
       <c r="E66" t="n">
-        <v>177.282620942239</v>
+        <v>184.905023822695</v>
       </c>
       <c r="F66" t="n">
-        <v>60.22770724432731</v>
+        <v>58.49444609923873</v>
       </c>
       <c r="G66" t="n">
         <v>18</v>
@@ -2220,16 +2220,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-1.23412200952765</v>
+        <v>-1.167520736037395</v>
       </c>
       <c r="D67" t="n">
-        <v>26.76355713404966</v>
+        <v>26.69052359763156</v>
       </c>
       <c r="E67" t="n">
-        <v>34.24714074031103</v>
+        <v>33.73280885910732</v>
       </c>
       <c r="F67" t="n">
-        <v>31.84071388607514</v>
+        <v>32.09591980773539</v>
       </c>
       <c r="G67" t="n">
         <v>89</v>
@@ -2247,16 +2247,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-0.8744280587701148</v>
+        <v>-0.7723288446861207</v>
       </c>
       <c r="D68" t="n">
-        <v>337.7421407988577</v>
+        <v>333.8967593414615</v>
       </c>
       <c r="E68" t="n">
-        <v>410.2814561820248</v>
+        <v>398.9510870405131</v>
       </c>
       <c r="F68" t="n">
-        <v>39.96154195121211</v>
+        <v>39.46590773230047</v>
       </c>
       <c r="G68" t="n">
         <v>99</v>
@@ -2274,16 +2274,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.3574849420823776</v>
+        <v>0.2808628218168763</v>
       </c>
       <c r="D69" t="n">
-        <v>182.488272061912</v>
+        <v>191.603522844212</v>
       </c>
       <c r="E69" t="n">
-        <v>257.0511707226869</v>
+        <v>271.9467054783973</v>
       </c>
       <c r="F69" t="n">
-        <v>18.66330340161542</v>
+        <v>20.57708351345929</v>
       </c>
       <c r="G69" t="n">
         <v>93</v>
@@ -2301,16 +2301,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-0.4978579724313059</v>
+        <v>-0.4064651239950932</v>
       </c>
       <c r="D70" t="n">
-        <v>7.474532414705325</v>
+        <v>7.028409157043848</v>
       </c>
       <c r="E70" t="n">
-        <v>10.67138503055381</v>
+        <v>10.34070040834416</v>
       </c>
       <c r="F70" t="n">
-        <v>66.20355771670083</v>
+        <v>63.30353320998159</v>
       </c>
       <c r="G70" t="n">
         <v>78</v>
@@ -2328,16 +2328,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-3.974120065601638</v>
+        <v>-4.066040080556198</v>
       </c>
       <c r="D71" t="n">
-        <v>191.9554409450955</v>
+        <v>191.7731191847059</v>
       </c>
       <c r="E71" t="n">
-        <v>211.5089217029002</v>
+        <v>213.454281237801</v>
       </c>
       <c r="F71" t="n">
-        <v>67.1966081191585</v>
+        <v>66.6712322884306</v>
       </c>
       <c r="G71" t="n">
         <v>18</v>
@@ -2355,16 +2355,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-0.8969940112900641</v>
+        <v>-1.048136907536882</v>
       </c>
       <c r="D72" t="n">
-        <v>23.40047116226025</v>
+        <v>24.66014853488193</v>
       </c>
       <c r="E72" t="n">
-        <v>31.55759185003268</v>
+        <v>32.7906757597757</v>
       </c>
       <c r="F72" t="n">
-        <v>27.87750812937442</v>
+        <v>29.16944956313586</v>
       </c>
       <c r="G72" t="n">
         <v>89</v>
@@ -2382,16 +2382,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-1.884606654742357</v>
+        <v>-1.03208565930142</v>
       </c>
       <c r="D73" t="n">
-        <v>430.098183371804</v>
+        <v>349.7959106137054</v>
       </c>
       <c r="E73" t="n">
-        <v>508.9683777873696</v>
+        <v>427.1874696562783</v>
       </c>
       <c r="F73" t="n">
-        <v>49.3924755656981</v>
+        <v>40.38978798635378</v>
       </c>
       <c r="G73" t="n">
         <v>99</v>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-0.1630218632553682</v>
+        <v>-1.478232226446296</v>
       </c>
       <c r="D74" t="n">
-        <v>282.3343322097614</v>
+        <v>440.1566792149698</v>
       </c>
       <c r="E74" t="n">
-        <v>345.83733074613</v>
+        <v>504.8343890476452</v>
       </c>
       <c r="F74" t="n">
-        <v>37.06336303538314</v>
+        <v>56.79077265826082</v>
       </c>
       <c r="G74" t="n">
         <v>93</v>
@@ -2436,16 +2436,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-0.4115700939486044</v>
+        <v>-0.3788650775383002</v>
       </c>
       <c r="D75" t="n">
-        <v>7.335883748837007</v>
+        <v>7.24635429871388</v>
       </c>
       <c r="E75" t="n">
-        <v>10.35944994909358</v>
+        <v>10.23873631218442</v>
       </c>
       <c r="F75" t="n">
-        <v>74.9187239520605</v>
+        <v>73.66590980386488</v>
       </c>
       <c r="G75" t="n">
         <v>78</v>
@@ -2463,16 +2463,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-3.500269670717614</v>
+        <v>-4.376380190224774</v>
       </c>
       <c r="D76" t="n">
-        <v>182.3565283881293</v>
+        <v>200.6302083333333</v>
       </c>
       <c r="E76" t="n">
-        <v>201.1823276501243</v>
+        <v>219.8950966094401</v>
       </c>
       <c r="F76" t="n">
-        <v>64.43595583752786</v>
+        <v>69.87589010279434</v>
       </c>
       <c r="G76" t="n">
         <v>18</v>
@@ -2490,16 +2490,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-1.549231633359118</v>
+        <v>-1.771036505002272</v>
       </c>
       <c r="D77" t="n">
-        <v>29.12890151377474</v>
+        <v>30.2435010202815</v>
       </c>
       <c r="E77" t="n">
-        <v>36.58268053392933</v>
+        <v>38.14099325076334</v>
       </c>
       <c r="F77" t="n">
-        <v>35.33817030687494</v>
+        <v>35.90433907444319</v>
       </c>
       <c r="G77" t="n">
         <v>89</v>
@@ -2517,16 +2517,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-0.6432047888541312</v>
+        <v>-0.9357644660010294</v>
       </c>
       <c r="D78" t="n">
-        <v>316.7615882025825</v>
+        <v>351.3308834499783</v>
       </c>
       <c r="E78" t="n">
-        <v>384.1433734091705</v>
+        <v>416.9401867889899</v>
       </c>
       <c r="F78" t="n">
-        <v>37.57718408147151</v>
+        <v>41.27883777410714</v>
       </c>
       <c r="G78" t="n">
         <v>99</v>
@@ -2544,16 +2544,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-0.007173693541636217</v>
+        <v>0.1494137014362729</v>
       </c>
       <c r="D79" t="n">
-        <v>245.9248729418683</v>
+        <v>202.9841525170111</v>
       </c>
       <c r="E79" t="n">
-        <v>321.8326623972031</v>
+        <v>295.7584233692621</v>
       </c>
       <c r="F79" t="n">
-        <v>23.12370983633483</v>
+        <v>20.79119934264222</v>
       </c>
       <c r="G79" t="n">
         <v>93</v>
@@ -2571,16 +2571,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-0.4894839003153706</v>
+        <v>-0.6180625931120993</v>
       </c>
       <c r="D80" t="n">
-        <v>7.324220250814389</v>
+        <v>7.831171023540008</v>
       </c>
       <c r="E80" t="n">
-        <v>10.64151297320386</v>
+        <v>11.09131733394513</v>
       </c>
       <c r="F80" t="n">
-        <v>67.37045194568285</v>
+        <v>71.06094113183956</v>
       </c>
       <c r="G80" t="n">
         <v>78</v>
@@ -2598,16 +2598,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-5.296140249254645</v>
+        <v>-5.273265177489796</v>
       </c>
       <c r="D81" t="n">
-        <v>215.7366598976983</v>
+        <v>218.3342639075385</v>
       </c>
       <c r="E81" t="n">
-        <v>237.9620797324347</v>
+        <v>237.5294056921927</v>
       </c>
       <c r="F81" t="n">
-        <v>73.95924010762748</v>
+        <v>76.10598613053413</v>
       </c>
       <c r="G81" t="n">
         <v>18</v>
@@ -2625,16 +2625,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-1.471639320853854</v>
+        <v>-1.331671462446003</v>
       </c>
       <c r="D82" t="n">
-        <v>27.51576805114746</v>
+        <v>28.34089964963077</v>
       </c>
       <c r="E82" t="n">
-        <v>36.02163512978397</v>
+        <v>34.98682668883706</v>
       </c>
       <c r="F82" t="n">
-        <v>32.34854275170433</v>
+        <v>34.35009675367393</v>
       </c>
       <c r="G82" t="n">
         <v>89</v>
@@ -2652,16 +2652,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-1.215198924684078</v>
+        <v>-1.131691870508748</v>
       </c>
       <c r="D83" t="n">
-        <v>369.7394799126519</v>
+        <v>358.907000146731</v>
       </c>
       <c r="E83" t="n">
-        <v>446.0195198816821</v>
+        <v>437.5318918528021</v>
       </c>
       <c r="F83" t="n">
-        <v>43.27805505367751</v>
+        <v>41.74828712977906</v>
       </c>
       <c r="G83" t="n">
         <v>99</v>
@@ -2679,16 +2679,16 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.1224780929247532</v>
+        <v>0.08282013273278843</v>
       </c>
       <c r="D84" t="n">
-        <v>231.7278691773774</v>
+        <v>213.4938459498908</v>
       </c>
       <c r="E84" t="n">
-        <v>300.4048325025429</v>
+        <v>307.1179410894192</v>
       </c>
       <c r="F84" t="n">
-        <v>25.56728717971516</v>
+        <v>21.32619540162688</v>
       </c>
       <c r="G84" t="n">
         <v>93</v>
@@ -2706,16 +2706,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-0.6352777245902743</v>
+        <v>-0.532219666862956</v>
       </c>
       <c r="D85" t="n">
-        <v>7.975412708062392</v>
+        <v>7.365130418386215</v>
       </c>
       <c r="E85" t="n">
-        <v>11.15016342109965</v>
+        <v>10.79309471856502</v>
       </c>
       <c r="F85" t="n">
-        <v>73.7908922035902</v>
+        <v>68.03604520476495</v>
       </c>
       <c r="G85" t="n">
         <v>78</v>
@@ -2733,16 +2733,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-5.283701956703678</v>
+        <v>-5.718140023321393</v>
       </c>
       <c r="D86" t="n">
-        <v>218.0422744750977</v>
+        <v>226.9578906165229</v>
       </c>
       <c r="E86" t="n">
-        <v>237.7269114296623</v>
+        <v>245.8074745429912</v>
       </c>
       <c r="F86" t="n">
-        <v>76.06983393658727</v>
+        <v>80.53521177779301</v>
       </c>
       <c r="G86" t="n">
         <v>18</v>
@@ -2760,16 +2760,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-1.389030043204086</v>
+        <v>-1.661976362016268</v>
       </c>
       <c r="D87" t="n">
-        <v>26.91502095340343</v>
+        <v>29.10442543029785</v>
       </c>
       <c r="E87" t="n">
-        <v>35.41454615767072</v>
+        <v>37.3828985666974</v>
       </c>
       <c r="F87" t="n">
-        <v>32.38512177211038</v>
+        <v>34.79943290552116</v>
       </c>
       <c r="G87" t="n">
         <v>89</v>
@@ -2787,16 +2787,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-1.002709445526146</v>
+        <v>-1.202413871108631</v>
       </c>
       <c r="D88" t="n">
-        <v>357.4730622262666</v>
+        <v>376.0615269824712</v>
       </c>
       <c r="E88" t="n">
-        <v>424.0884776417598</v>
+        <v>444.7305532179948</v>
       </c>
       <c r="F88" t="n">
-        <v>42.72816845696019</v>
+        <v>44.36969329582796</v>
       </c>
       <c r="G88" t="n">
         <v>99</v>
@@ -2814,16 +2814,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>0.1974920760436352</v>
+        <v>0.1841206177070547</v>
       </c>
       <c r="D89" t="n">
-        <v>211.1936317361811</v>
+        <v>193.6379781743532</v>
       </c>
       <c r="E89" t="n">
-        <v>287.2781502328453</v>
+        <v>289.6615900097273</v>
       </c>
       <c r="F89" t="n">
-        <v>20.43244152786891</v>
+        <v>20.86475764425462</v>
       </c>
       <c r="G89" t="n">
         <v>93</v>
@@ -2841,16 +2841,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-0.5033404311527419</v>
+        <v>-0.5031583192291444</v>
       </c>
       <c r="D90" t="n">
-        <v>7.2030723461738</v>
+        <v>7.010259964527228</v>
       </c>
       <c r="E90" t="n">
-        <v>10.69089689061536</v>
+        <v>10.69024933310838</v>
       </c>
       <c r="F90" t="n">
-        <v>66.85184262361365</v>
+        <v>63.3746028623483</v>
       </c>
       <c r="G90" t="n">
         <v>78</v>
@@ -2868,16 +2868,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-5.442559650857128</v>
+        <v>-4.753168489673673</v>
       </c>
       <c r="D91" t="n">
-        <v>220.1774340735541</v>
+        <v>208.1590353647868</v>
       </c>
       <c r="E91" t="n">
-        <v>240.7131317866134</v>
+        <v>227.4699885177035</v>
       </c>
       <c r="F91" t="n">
-        <v>76.34565548902457</v>
+        <v>72.20801249518254</v>
       </c>
       <c r="G91" t="n">
         <v>18</v>
@@ -2895,16 +2895,16 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-0.2570850724143601</v>
+        <v>-0.3680810879712231</v>
       </c>
       <c r="D92" t="n">
-        <v>17.61364126741216</v>
+        <v>18.47897122415264</v>
       </c>
       <c r="E92" t="n">
-        <v>25.68935555383979</v>
+        <v>26.79950637046448</v>
       </c>
       <c r="F92" t="n">
-        <v>22.48992653425854</v>
+        <v>23.26730313964255</v>
       </c>
       <c r="G92" t="n">
         <v>89</v>
@@ -2922,16 +2922,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-0.2026257004567971</v>
+        <v>-0.2090163509592375</v>
       </c>
       <c r="D93" t="n">
-        <v>258.7381479282572</v>
+        <v>261.1705067952474</v>
       </c>
       <c r="E93" t="n">
-        <v>328.6341871388381</v>
+        <v>329.5061972614428</v>
       </c>
       <c r="F93" t="n">
-        <v>32.07150539183605</v>
+        <v>31.92903829052065</v>
       </c>
       <c r="G93" t="n">
         <v>99</v>
@@ -2949,16 +2949,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-0.1498895716296738</v>
+        <v>-0.1923919067754845</v>
       </c>
       <c r="D94" t="n">
-        <v>250.7450659967238</v>
+        <v>253.1833991594212</v>
       </c>
       <c r="E94" t="n">
-        <v>343.8792720780625</v>
+        <v>350.1768573927458</v>
       </c>
       <c r="F94" t="n">
-        <v>24.81727555162303</v>
+        <v>25.72794160950618</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
@@ -2976,16 +2976,16 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-0.1830178658587442</v>
+        <v>-0.2051268473983452</v>
       </c>
       <c r="D95" t="n">
-        <v>6.258523351106888</v>
+        <v>6.17689197185712</v>
       </c>
       <c r="E95" t="n">
-        <v>9.483772421721717</v>
+        <v>9.57198155286315</v>
       </c>
       <c r="F95" t="n">
-        <v>59.67610140848139</v>
+        <v>54.78162893268976</v>
       </c>
       <c r="G95" t="n">
         <v>78</v>
@@ -3003,16 +3003,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-6.151845667325443</v>
+        <v>-6.403128501409416</v>
       </c>
       <c r="D96" t="n">
-        <v>237.4648608101739</v>
+        <v>242.4200292163425</v>
       </c>
       <c r="E96" t="n">
-        <v>253.617738799916</v>
+        <v>258.0347535127812</v>
       </c>
       <c r="F96" t="n">
-        <v>85.94680093957292</v>
+        <v>88.25368616458532</v>
       </c>
       <c r="G96" t="n">
         <v>18</v>
@@ -3030,16 +3030,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-0.3530784381472216</v>
+        <v>-0.5396678551145384</v>
       </c>
       <c r="D97" t="n">
-        <v>18.11343638816576</v>
+        <v>19.22976733861345</v>
       </c>
       <c r="E97" t="n">
-        <v>26.65215692746227</v>
+        <v>28.43049337471401</v>
       </c>
       <c r="F97" t="n">
-        <v>22.85026761363112</v>
+        <v>23.93276935152997</v>
       </c>
       <c r="G97" t="n">
         <v>89</v>
@@ -3057,16 +3057,16 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-0.1396847239236756</v>
+        <v>-0.465898680829816</v>
       </c>
       <c r="D98" t="n">
-        <v>250.9837720466383</v>
+        <v>284.1608225504557</v>
       </c>
       <c r="E98" t="n">
-        <v>319.918874666805</v>
+        <v>362.8268989355907</v>
       </c>
       <c r="F98" t="n">
-        <v>30.53908230884521</v>
+        <v>34.17726241087783</v>
       </c>
       <c r="G98" t="n">
         <v>99</v>
@@ -3084,16 +3084,16 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-0.1705221817995277</v>
+        <v>-0.262779500238401</v>
       </c>
       <c r="D99" t="n">
-        <v>256.3892359579763</v>
+        <v>252.0371661442582</v>
       </c>
       <c r="E99" t="n">
-        <v>346.9506896878131</v>
+        <v>360.3642436888967</v>
       </c>
       <c r="F99" t="n">
-        <v>25.87939729728357</v>
+        <v>24.83133565360496</v>
       </c>
       <c r="G99" t="n">
         <v>93</v>
@@ -3111,16 +3111,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-0.169926881412269</v>
+        <v>-0.1328304262626649</v>
       </c>
       <c r="D100" t="n">
-        <v>6.199532252091628</v>
+        <v>6.096722061817463</v>
       </c>
       <c r="E100" t="n">
-        <v>9.431153905528097</v>
+        <v>9.28042626841312</v>
       </c>
       <c r="F100" t="n">
-        <v>56.78333217753499</v>
+        <v>55.0044433349492</v>
       </c>
       <c r="G100" t="n">
         <v>78</v>
@@ -3138,16 +3138,16 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-6.122575966890341</v>
+        <v>-6.65250124129068</v>
       </c>
       <c r="D101" t="n">
-        <v>237.1753910912408</v>
+        <v>245.2689612706502</v>
       </c>
       <c r="E101" t="n">
-        <v>253.0982277291369</v>
+        <v>262.3446810685194</v>
       </c>
       <c r="F101" t="n">
-        <v>86.1801103321517</v>
+        <v>88.30813673595239</v>
       </c>
       <c r="G101" t="n">
         <v>18</v>
@@ -3165,16 +3165,16 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-0.6767156101956449</v>
+        <v>-0.6105230048210351</v>
       </c>
       <c r="D102" t="n">
-        <v>21.87050054314431</v>
+        <v>21.23204966341511</v>
       </c>
       <c r="E102" t="n">
-        <v>29.66884084209764</v>
+        <v>29.07731768305414</v>
       </c>
       <c r="F102" t="n">
-        <v>26.82193788604062</v>
+        <v>26.20545300843988</v>
       </c>
       <c r="G102" t="n">
         <v>89</v>
@@ -3192,16 +3192,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-0.4115967816098458</v>
+        <v>-0.6305797074873616</v>
       </c>
       <c r="D103" t="n">
-        <v>288.1707820699672</v>
+        <v>304.3984029750631</v>
       </c>
       <c r="E103" t="n">
-        <v>356.0433098440271</v>
+        <v>382.6648014986005</v>
       </c>
       <c r="F103" t="n">
-        <v>37.15099874364159</v>
+        <v>38.61739532235065</v>
       </c>
       <c r="G103" t="n">
         <v>99</v>
@@ -3219,16 +3219,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-0.4544465018555139</v>
+        <v>-0.4723667180206208</v>
       </c>
       <c r="D104" t="n">
-        <v>301.2230365712156</v>
+        <v>300.060799547421</v>
       </c>
       <c r="E104" t="n">
-        <v>386.7468693060013</v>
+        <v>389.1221268629725</v>
       </c>
       <c r="F104" t="n">
-        <v>30.50805931037572</v>
+        <v>29.86602709319129</v>
       </c>
       <c r="G104" t="n">
         <v>93</v>
@@ -3246,16 +3246,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-0.6276911289332823</v>
+        <v>-0.6054362147766987</v>
       </c>
       <c r="D105" t="n">
-        <v>7.517317194205064</v>
+        <v>7.390923634553567</v>
       </c>
       <c r="E105" t="n">
-        <v>11.12426869976479</v>
+        <v>11.04795762596857</v>
       </c>
       <c r="F105" t="n">
-        <v>72.90617490816005</v>
+        <v>71.46432785134684</v>
       </c>
       <c r="G105" t="n">
         <v>78</v>
@@ -3273,16 +3273,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>-6.666026803164889</v>
+        <v>-6.877170957055541</v>
       </c>
       <c r="D106" t="n">
-        <v>245.7406954235501</v>
+        <v>250.2345217598809</v>
       </c>
       <c r="E106" t="n">
-        <v>262.5764218147352</v>
+        <v>266.1679101043237</v>
       </c>
       <c r="F106" t="n">
-        <v>89.26161711708028</v>
+        <v>91.2008337242217</v>
       </c>
       <c r="G106" t="n">
         <v>18</v>
@@ -3300,16 +3300,16 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>-0.5052568231541132</v>
+        <v>-0.6405610935862798</v>
       </c>
       <c r="D107" t="n">
-        <v>20.00652131069912</v>
+        <v>21.36564614799585</v>
       </c>
       <c r="E107" t="n">
-        <v>28.1109923681545</v>
+        <v>29.34722751574721</v>
       </c>
       <c r="F107" t="n">
-        <v>24.70006248289159</v>
+        <v>26.16281808231566</v>
       </c>
       <c r="G107" t="n">
         <v>89</v>
@@ -3327,16 +3327,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>-0.3580515197443044</v>
+        <v>-0.4226068654313968</v>
       </c>
       <c r="D108" t="n">
-        <v>286.2276651401713</v>
+        <v>292.7752334132339</v>
       </c>
       <c r="E108" t="n">
-        <v>349.2252386820446</v>
+        <v>357.4291349357281</v>
       </c>
       <c r="F108" t="n">
-        <v>37.23221173650085</v>
+        <v>37.41024216704611</v>
       </c>
       <c r="G108" t="n">
         <v>99</v>
@@ -3354,16 +3354,16 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>-0.4248261172339993</v>
+        <v>-0.5043186532267536</v>
       </c>
       <c r="D109" t="n">
-        <v>297.9818732148858</v>
+        <v>303.0115182527932</v>
       </c>
       <c r="E109" t="n">
-        <v>382.7884847943502</v>
+        <v>393.3216491334703</v>
       </c>
       <c r="F109" t="n">
-        <v>30.07757604301327</v>
+        <v>30.56847213527716</v>
       </c>
       <c r="G109" t="n">
         <v>93</v>
@@ -3381,16 +3381,16 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>-0.6010503843694646</v>
+        <v>-0.6592724614386916</v>
       </c>
       <c r="D110" t="n">
-        <v>7.354301969210307</v>
+        <v>7.585002672977937</v>
       </c>
       <c r="E110" t="n">
-        <v>11.03285655684505</v>
+        <v>11.23166974041273</v>
       </c>
       <c r="F110" t="n">
-        <v>71.76877658501866</v>
+        <v>72.12605330803041</v>
       </c>
       <c r="G110" t="n">
         <v>78</v>
@@ -3408,16 +3408,16 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>-6.666264216543272</v>
+        <v>-6.637238973400845</v>
       </c>
       <c r="D111" t="n">
-        <v>247.5233608881632</v>
+        <v>247.0020982954237</v>
       </c>
       <c r="E111" t="n">
-        <v>262.5804877196911</v>
+        <v>262.0829383345823</v>
       </c>
       <c r="F111" t="n">
-        <v>91.0171921089588</v>
+        <v>90.60451631097899</v>
       </c>
       <c r="G111" t="n">
         <v>18</v>
@@ -3435,16 +3435,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>-0.5348925668426003</v>
+        <v>-0.4968916869364484</v>
       </c>
       <c r="D112" t="n">
-        <v>19.68904253070274</v>
+        <v>19.42545254310865</v>
       </c>
       <c r="E112" t="n">
-        <v>28.38637047095544</v>
+        <v>28.03277319333644</v>
       </c>
       <c r="F112" t="n">
-        <v>24.37800941468251</v>
+        <v>24.32207865199499</v>
       </c>
       <c r="G112" t="n">
         <v>89</v>
@@ -3462,16 +3462,16 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>-0.7235706407040736</v>
+        <v>-0.3207458834598917</v>
       </c>
       <c r="D113" t="n">
-        <v>309.7161211726641</v>
+        <v>273.1559184681286</v>
       </c>
       <c r="E113" t="n">
-        <v>393.425081775846</v>
+        <v>344.3952340377706</v>
       </c>
       <c r="F113" t="n">
-        <v>38.37262486416343</v>
+        <v>32.98985811930012</v>
       </c>
       <c r="G113" t="n">
         <v>99</v>
@@ -3489,16 +3489,16 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>-0.5569021384023682</v>
+        <v>-0.3798871699013817</v>
       </c>
       <c r="D114" t="n">
-        <v>273.784171811996</v>
+        <v>270.4888190812962</v>
       </c>
       <c r="E114" t="n">
-        <v>400.1368866028785</v>
+        <v>376.7035555791625</v>
       </c>
       <c r="F114" t="n">
-        <v>28.0110378861938</v>
+        <v>26.51740610933909</v>
       </c>
       <c r="G114" t="n">
         <v>93</v>
@@ -3516,16 +3516,16 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>-0.3396354277203011</v>
+        <v>-0.3395805452418252</v>
       </c>
       <c r="D115" t="n">
-        <v>6.679340824102744</v>
+        <v>6.604273903064239</v>
       </c>
       <c r="E115" t="n">
-        <v>10.09203584312609</v>
+        <v>10.09182911463809</v>
       </c>
       <c r="F115" t="n">
-        <v>62.03568320833757</v>
+        <v>64.17045003936779</v>
       </c>
       <c r="G115" t="n">
         <v>78</v>
@@ -3543,16 +3543,16 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>-6.533716841068441</v>
+        <v>-6.724553195188505</v>
       </c>
       <c r="D116" t="n">
-        <v>242.6494998931885</v>
+        <v>245.6571519639757</v>
       </c>
       <c r="E116" t="n">
-        <v>260.3006218401051</v>
+        <v>263.576837759576</v>
       </c>
       <c r="F116" t="n">
-        <v>86.80668227194305</v>
+        <v>87.65566083590554</v>
       </c>
       <c r="G116" t="n">
         <v>18</v>
@@ -3570,16 +3570,16 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>-1.172412305400828</v>
+        <v>-0.7640848863776069</v>
       </c>
       <c r="D117" t="n">
-        <v>24.22419187995825</v>
+        <v>21.86369081561485</v>
       </c>
       <c r="E117" t="n">
-        <v>33.77085079837414</v>
+        <v>30.43200836306427</v>
       </c>
       <c r="F117" t="n">
-        <v>28.49451651217407</v>
+        <v>25.90117134530095</v>
       </c>
       <c r="G117" t="n">
         <v>89</v>
@@ -3597,16 +3597,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>-1.745034850826802</v>
+        <v>-1.111224517516397</v>
       </c>
       <c r="D118" t="n">
-        <v>421.0036970966994</v>
+        <v>356.3497436215179</v>
       </c>
       <c r="E118" t="n">
-        <v>496.5024904006485</v>
+        <v>435.4263532492881</v>
       </c>
       <c r="F118" t="n">
-        <v>48.96888752957938</v>
+        <v>41.03150816647485</v>
       </c>
       <c r="G118" t="n">
         <v>99</v>
@@ -3624,16 +3624,16 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>-0.4502566788311921</v>
+        <v>-0.6321118830122627</v>
       </c>
       <c r="D119" t="n">
-        <v>272.0021171980007</v>
+        <v>312.6606757051201</v>
       </c>
       <c r="E119" t="n">
-        <v>386.1894168347771</v>
+        <v>409.6876708347244</v>
       </c>
       <c r="F119" t="n">
-        <v>24.55857392532573</v>
+        <v>28.332791683221</v>
       </c>
       <c r="G119" t="n">
         <v>93</v>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>-0.6177094944873254</v>
+        <v>-0.5802128288885171</v>
       </c>
       <c r="D120" t="n">
-        <v>7.839794168105493</v>
+        <v>7.659635287064773</v>
       </c>
       <c r="E120" t="n">
-        <v>11.09010707712444</v>
+        <v>10.96082550264481</v>
       </c>
       <c r="F120" t="n">
-        <v>70.91383632558312</v>
+        <v>69.59439923098216</v>
       </c>
       <c r="G120" t="n">
         <v>78</v>
@@ -3678,16 +3678,16 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>-7.384327229932808</v>
+        <v>-5.810030066047833</v>
       </c>
       <c r="D121" t="n">
-        <v>258.0022038353814</v>
+        <v>228.6884284549289</v>
       </c>
       <c r="E121" t="n">
-        <v>274.6026152869421</v>
+        <v>247.4828301056637</v>
       </c>
       <c r="F121" t="n">
-        <v>93.69373231624496</v>
+        <v>80.49451020914391</v>
       </c>
       <c r="G121" t="n">
         <v>18</v>
@@ -3705,16 +3705,16 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>-0.6426696930593916</v>
+        <v>-0.7929285258524696</v>
       </c>
       <c r="D122" t="n">
-        <v>21.0709600341454</v>
+        <v>22.48738595341029</v>
       </c>
       <c r="E122" t="n">
-        <v>29.36608133275152</v>
+        <v>30.67978865144136</v>
       </c>
       <c r="F122" t="n">
-        <v>25.51765861188652</v>
+        <v>27.44536352285757</v>
       </c>
       <c r="G122" t="n">
         <v>89</v>
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>-0.4758156893571013</v>
+        <v>-0.2157605336262309</v>
       </c>
       <c r="D123" t="n">
-        <v>310.1381560046264</v>
+        <v>269.2971911189532</v>
       </c>
       <c r="E123" t="n">
-        <v>364.0521174608331</v>
+        <v>330.423951407404</v>
       </c>
       <c r="F123" t="n">
-        <v>37.8809626057779</v>
+        <v>34.9290583297329</v>
       </c>
       <c r="G123" t="n">
         <v>99</v>
@@ -3759,16 +3759,16 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>0.1546033447136805</v>
+        <v>-5.621455468903743</v>
       </c>
       <c r="D124" t="n">
-        <v>235.8716220650622</v>
+        <v>732.9597909578713</v>
       </c>
       <c r="E124" t="n">
-        <v>294.8547942725172</v>
+        <v>825.1913414992816</v>
       </c>
       <c r="F124" t="n">
-        <v>28.46303727975533</v>
+        <v>88.85349637498675</v>
       </c>
       <c r="G124" t="n">
         <v>93</v>
@@ -3786,16 +3786,16 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>-0.1891456869603207</v>
+        <v>-0.3998725522180948</v>
       </c>
       <c r="D125" t="n">
-        <v>6.30647473457532</v>
+        <v>7.04068355071239</v>
       </c>
       <c r="E125" t="n">
-        <v>9.508302820024827</v>
+        <v>10.31643678378333</v>
       </c>
       <c r="F125" t="n">
-        <v>62.88331648526187</v>
+        <v>62.75296199357226</v>
       </c>
       <c r="G125" t="n">
         <v>78</v>
@@ -3813,16 +3813,16 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>-4.107933692025503</v>
+        <v>-4.051612108349482</v>
       </c>
       <c r="D126" t="n">
-        <v>193.0384131537543</v>
+        <v>193.7168742285834</v>
       </c>
       <c r="E126" t="n">
-        <v>214.3350440623541</v>
+        <v>213.1501079333415</v>
       </c>
       <c r="F126" t="n">
-        <v>66.48883644569348</v>
+        <v>67.76856678471694</v>
       </c>
       <c r="G126" t="n">
         <v>18</v>
@@ -3840,16 +3840,16 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>-0.8784148776652518</v>
+        <v>-0.9547916558402294</v>
       </c>
       <c r="D127" t="n">
-        <v>23.207842966144</v>
+        <v>23.67369086019109</v>
       </c>
       <c r="E127" t="n">
-        <v>31.40267428823843</v>
+        <v>32.03473334283605</v>
       </c>
       <c r="F127" t="n">
-        <v>28.15287314442276</v>
+        <v>27.76904022693836</v>
       </c>
       <c r="G127" t="n">
         <v>89</v>
@@ -3867,16 +3867,16 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>-0.5143034495340262</v>
+        <v>-0.7162640963836804</v>
       </c>
       <c r="D128" t="n">
-        <v>298.6366632634943</v>
+        <v>319.4340892753216</v>
       </c>
       <c r="E128" t="n">
-        <v>368.7686179975199</v>
+        <v>392.5902941918702</v>
       </c>
       <c r="F128" t="n">
-        <v>35.58874054837776</v>
+        <v>39.32166216424348</v>
       </c>
       <c r="G128" t="n">
         <v>99</v>
@@ -3894,16 +3894,16 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>0.3701708315630077</v>
+        <v>-3.126422551974676</v>
       </c>
       <c r="D129" t="n">
-        <v>192.2043929561492</v>
+        <v>493.3934372112315</v>
       </c>
       <c r="E129" t="n">
-        <v>254.5008961434855</v>
+        <v>651.4255378782099</v>
       </c>
       <c r="F129" t="n">
-        <v>22.1071419730485</v>
+        <v>63.31144084209374</v>
       </c>
       <c r="G129" t="n">
         <v>93</v>
@@ -3921,16 +3921,16 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>-0.4788117845396138</v>
+        <v>-0.6005965692179651</v>
       </c>
       <c r="D130" t="n">
-        <v>7.25343761077294</v>
+        <v>7.92194258249723</v>
       </c>
       <c r="E130" t="n">
-        <v>10.60332134940495</v>
+        <v>11.03129282332148</v>
       </c>
       <c r="F130" t="n">
-        <v>68.30533928703247</v>
+        <v>75.86222281903726</v>
       </c>
       <c r="G130" t="n">
         <v>78</v>
@@ -3948,16 +3948,16 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>-4.269457860744517</v>
+        <v>-4.114889802433125</v>
       </c>
       <c r="D131" t="n">
-        <v>198.982385635376</v>
+        <v>189.5305701361762</v>
       </c>
       <c r="E131" t="n">
-        <v>217.6975427799285</v>
+        <v>214.4809377903058</v>
       </c>
       <c r="F131" t="n">
-        <v>69.14402441647786</v>
+        <v>64.40307485060785</v>
       </c>
       <c r="G131" t="n">
         <v>18</v>
@@ -3975,16 +3975,16 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>-0.8170929692845217</v>
+        <v>-0.1850723432893764</v>
       </c>
       <c r="D132" t="n">
-        <v>23.18268990248777</v>
+        <v>19.6083290228683</v>
       </c>
       <c r="E132" t="n">
-        <v>30.8858422541879</v>
+        <v>24.94269099411932</v>
       </c>
       <c r="F132" t="n">
-        <v>27.17063512277303</v>
+        <v>28.90965427563238</v>
       </c>
       <c r="G132" t="n">
         <v>89</v>
@@ -4002,16 +4002,16 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>0.2906467272793288</v>
+        <v>-0.04240186913696875</v>
       </c>
       <c r="D133" t="n">
-        <v>192.0155835392499</v>
+        <v>242.2717172641947</v>
       </c>
       <c r="E133" t="n">
-        <v>252.3938615676528</v>
+        <v>305.9603088372051</v>
       </c>
       <c r="F133" t="n">
-        <v>30.26120161240219</v>
+        <v>42.7193598365474</v>
       </c>
       <c r="G133" t="n">
         <v>99</v>
@@ -4029,16 +4029,16 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>-7.778785152978932</v>
+        <v>-13.0312519738583</v>
       </c>
       <c r="D134" t="n">
-        <v>908.4598283665155</v>
+        <v>1156.430094401042</v>
       </c>
       <c r="E134" t="n">
-        <v>950.1564947757618</v>
+        <v>1201.229925467327</v>
       </c>
       <c r="F134" t="n">
-        <v>109.8214920131008</v>
+        <v>139.6627127713542</v>
       </c>
       <c r="G134" t="n">
         <v>93</v>
@@ -4056,16 +4056,16 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>-0.7085817619994403</v>
+        <v>-0.395943847276002</v>
       </c>
       <c r="D135" t="n">
-        <v>8.220913208447969</v>
+        <v>7.281949122746785</v>
       </c>
       <c r="E135" t="n">
-        <v>11.39733609356648</v>
+        <v>10.30195021040098</v>
       </c>
       <c r="F135" t="n">
-        <v>75.11044094170445</v>
+        <v>73.9955495354035</v>
       </c>
       <c r="G135" t="n">
         <v>78</v>
@@ -4083,16 +4083,16 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>-2.287796817830702</v>
+        <v>-1.189841408131175</v>
       </c>
       <c r="D136" t="n">
-        <v>147.4629486931695</v>
+        <v>116.0142220391168</v>
       </c>
       <c r="E136" t="n">
-        <v>171.9582610127163</v>
+        <v>140.3385196051105</v>
       </c>
       <c r="F136" t="n">
-        <v>52.38661347199183</v>
+        <v>44.27039522958592</v>
       </c>
       <c r="G136" t="n">
         <v>18</v>
@@ -4110,16 +4110,16 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>-0.8531635263972166</v>
+        <v>-0.8921087159721524</v>
       </c>
       <c r="D137" t="n">
-        <v>22.97960030630733</v>
+        <v>23.99865214744311</v>
       </c>
       <c r="E137" t="n">
-        <v>31.19088855497812</v>
+        <v>31.51693079906481</v>
       </c>
       <c r="F137" t="n">
-        <v>27.27495947709004</v>
+        <v>28.87970069666251</v>
       </c>
       <c r="G137" t="n">
         <v>89</v>
@@ -4137,16 +4137,16 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>-0.5045333253473865</v>
+        <v>-0.8186471422007457</v>
       </c>
       <c r="D138" t="n">
-        <v>307.8393522320372</v>
+        <v>337.0378348610618</v>
       </c>
       <c r="E138" t="n">
-        <v>367.5770650679033</v>
+        <v>404.1305874524475</v>
       </c>
       <c r="F138" t="n">
-        <v>36.59159108424544</v>
+        <v>40.01558567093836</v>
       </c>
       <c r="G138" t="n">
         <v>99</v>
@@ -4164,16 +4164,16 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>0.3075144052823965</v>
+        <v>0.4468806452318094</v>
       </c>
       <c r="D139" t="n">
-        <v>202.5840349094842</v>
+        <v>197.7466535670783</v>
       </c>
       <c r="E139" t="n">
-        <v>266.8598900957132</v>
+        <v>238.4994373713666</v>
       </c>
       <c r="F139" t="n">
-        <v>22.36433626196781</v>
+        <v>24.01573487367146</v>
       </c>
       <c r="G139" t="n">
         <v>93</v>
@@ -4191,16 +4191,16 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>-0.3703133102812413</v>
+        <v>-0.3861896699118585</v>
       </c>
       <c r="D140" t="n">
-        <v>6.824401552860554</v>
+        <v>7.122512514774616</v>
       </c>
       <c r="E140" t="n">
-        <v>10.20693643726401</v>
+        <v>10.2658946038678</v>
       </c>
       <c r="F140" t="n">
-        <v>59.28397505340374</v>
+        <v>68.26947567827493</v>
       </c>
       <c r="G140" t="n">
         <v>78</v>
@@ -4218,16 +4218,16 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>-3.284866441649849</v>
+        <v>-2.684432482159305</v>
       </c>
       <c r="D141" t="n">
-        <v>179.1670479244656</v>
+        <v>162.8340509202745</v>
       </c>
       <c r="E141" t="n">
-        <v>196.3085448929817</v>
+        <v>182.035403309194</v>
       </c>
       <c r="F141" t="n">
-        <v>66.55249286052131</v>
+        <v>60.78582093467506</v>
       </c>
       <c r="G141" t="n">
         <v>18</v>
@@ -4245,16 +4245,16 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>-1.345273440891891</v>
+        <v>-1.375110159658862</v>
       </c>
       <c r="D142" t="n">
-        <v>27.79285992397351</v>
+        <v>29.06336885087946</v>
       </c>
       <c r="E142" t="n">
-        <v>35.08872741802877</v>
+        <v>35.31122252287937</v>
       </c>
       <c r="F142" t="n">
-        <v>32.75507705737736</v>
+        <v>35.27891556358686</v>
       </c>
       <c r="G142" t="n">
         <v>89</v>
@@ -4272,16 +4272,16 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>-0.7574707718889857</v>
+        <v>-0.5773681166649531</v>
       </c>
       <c r="D143" t="n">
-        <v>333.5364376800229</v>
+        <v>311.6756346731475</v>
       </c>
       <c r="E143" t="n">
-        <v>397.2752919258938</v>
+        <v>376.3691593384723</v>
       </c>
       <c r="F143" t="n">
-        <v>40.19958461288206</v>
+        <v>37.95270631772003</v>
       </c>
       <c r="G143" t="n">
         <v>99</v>
@@ -4299,16 +4299,16 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>-0.06918532449495607</v>
+        <v>0.490650735272455</v>
       </c>
       <c r="D144" t="n">
-        <v>249.8326429141465</v>
+        <v>176.8882636613743</v>
       </c>
       <c r="E144" t="n">
-        <v>331.5922912038361</v>
+        <v>228.8683680361679</v>
       </c>
       <c r="F144" t="n">
-        <v>31.23092711144416</v>
+        <v>19.53229463979732</v>
       </c>
       <c r="G144" t="n">
         <v>93</v>
@@ -4326,16 +4326,16 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>-0.5536352137501517</v>
+        <v>-0.5572284863737518</v>
       </c>
       <c r="D145" t="n">
-        <v>7.606344626500056</v>
+        <v>7.711874729547745</v>
       </c>
       <c r="E145" t="n">
-        <v>10.86825951906584</v>
+        <v>10.88082040361029</v>
       </c>
       <c r="F145" t="n">
-        <v>69.97156774596495</v>
+        <v>71.30788989082897</v>
       </c>
       <c r="G145" t="n">
         <v>78</v>
@@ -4353,16 +4353,16 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>-2.559879497521367</v>
+        <v>-3.944672139307774</v>
       </c>
       <c r="D146" t="n">
-        <v>161.5123566521539</v>
+        <v>190.8397095998128</v>
       </c>
       <c r="E146" t="n">
-        <v>178.9320789030973</v>
+        <v>210.8819017498205</v>
       </c>
       <c r="F146" t="n">
-        <v>56.75649690036172</v>
+        <v>66.12566498991531</v>
       </c>
       <c r="G146" t="n">
         <v>18</v>
@@ -4380,16 +4380,16 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>-0.9634038307887671</v>
+        <v>-0.962292991103153</v>
       </c>
       <c r="D147" t="n">
-        <v>24.07616315263041</v>
+        <v>24.62734177407254</v>
       </c>
       <c r="E147" t="n">
-        <v>32.10522308677784</v>
+        <v>32.09613967734862</v>
       </c>
       <c r="F147" t="n">
-        <v>28.41969330531283</v>
+        <v>29.39829538600128</v>
       </c>
       <c r="G147" t="n">
         <v>89</v>
@@ -4407,16 +4407,16 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>-1.355430153346738</v>
+        <v>-1.082816543098563</v>
       </c>
       <c r="D148" t="n">
-        <v>388.8000415840534</v>
+        <v>362.0314745662188</v>
       </c>
       <c r="E148" t="n">
-        <v>459.920338337004</v>
+        <v>432.4869516782883</v>
       </c>
       <c r="F148" t="n">
-        <v>44.90932256553143</v>
+        <v>41.80937108132183</v>
       </c>
       <c r="G148" t="n">
         <v>99</v>
@@ -4434,16 +4434,16 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>0.3216246240532205</v>
+        <v>0.1912224425551839</v>
       </c>
       <c r="D149" t="n">
-        <v>211.6726645192792</v>
+        <v>226.5905938917591</v>
       </c>
       <c r="E149" t="n">
-        <v>264.1271034534338</v>
+        <v>288.3981544598179</v>
       </c>
       <c r="F149" t="n">
-        <v>23.83462466994156</v>
+        <v>26.7243620989343</v>
       </c>
       <c r="G149" t="n">
         <v>93</v>
@@ -4461,16 +4461,16 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>-0.487875622923567</v>
+        <v>-0.6025571598298576</v>
       </c>
       <c r="D150" t="n">
-        <v>7.483346865727351</v>
+        <v>7.943279963273269</v>
       </c>
       <c r="E150" t="n">
-        <v>10.63576630917857</v>
+        <v>11.03804693943051</v>
       </c>
       <c r="F150" t="n">
-        <v>72.09116570713144</v>
+        <v>71.79234169214446</v>
       </c>
       <c r="G150" t="n">
         <v>78</v>
@@ -4488,16 +4488,16 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>-1.272556570194562</v>
+        <v>-2.630121872904626</v>
       </c>
       <c r="D151" t="n">
-        <v>125.3054402669271</v>
+        <v>163.4619856940375</v>
       </c>
       <c r="E151" t="n">
-        <v>142.9644015116088</v>
+        <v>180.6887701842875</v>
       </c>
       <c r="F151" t="n">
-        <v>47.36993041364592</v>
+        <v>59.50961899156562</v>
       </c>
       <c r="G151" t="n">
         <v>18</v>
@@ -4515,16 +4515,16 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>-1.095590839417806</v>
+        <v>-1.131373334674514</v>
       </c>
       <c r="D152" t="n">
-        <v>25.2393757252211</v>
+        <v>24.86636138230227</v>
       </c>
       <c r="E152" t="n">
-        <v>33.1683693311759</v>
+        <v>33.45034790291132</v>
       </c>
       <c r="F152" t="n">
-        <v>29.7866658678733</v>
+        <v>29.3827322938527</v>
       </c>
       <c r="G152" t="n">
         <v>89</v>
@@ -4542,16 +4542,16 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>-1.028085373933347</v>
+        <v>-0.5826176239187095</v>
       </c>
       <c r="D153" t="n">
-        <v>348.3906895801275</v>
+        <v>314.5085759018407</v>
       </c>
       <c r="E153" t="n">
-        <v>426.7667901416077</v>
+        <v>376.9949205372935</v>
       </c>
       <c r="F153" t="n">
-        <v>40.2000140876372</v>
+        <v>37.21698386488082</v>
       </c>
       <c r="G153" t="n">
         <v>99</v>
@@ -4569,16 +4569,16 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>-2.177581826703654</v>
+        <v>0.349499475750688</v>
       </c>
       <c r="D154" t="n">
-        <v>516.490470640121</v>
+        <v>191.1952074932796</v>
       </c>
       <c r="E154" t="n">
-        <v>571.6448596374726</v>
+        <v>258.6436119309387</v>
       </c>
       <c r="F154" t="n">
-        <v>61.28718895743469</v>
+        <v>21.76120792155023</v>
       </c>
       <c r="G154" t="n">
         <v>93</v>
@@ -4596,16 +4596,16 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>-0.4115316204798642</v>
+        <v>-0.3794389395169082</v>
       </c>
       <c r="D155" t="n">
-        <v>7.025651763647031</v>
+        <v>7.04024443259606</v>
       </c>
       <c r="E155" t="n">
-        <v>10.3593087705962</v>
+        <v>10.24086669113379</v>
       </c>
       <c r="F155" t="n">
-        <v>67.82388180037563</v>
+        <v>61.96886912339831</v>
       </c>
       <c r="G155" t="n">
         <v>78</v>
@@ -4623,16 +4623,16 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>-1.936940944446074</v>
+        <v>-2.648735166623892</v>
       </c>
       <c r="D156" t="n">
-        <v>141.7605573866102</v>
+        <v>163.630611843533</v>
       </c>
       <c r="E156" t="n">
-        <v>162.5242483105625</v>
+        <v>181.1514148424475</v>
       </c>
       <c r="F156" t="n">
-        <v>53.56320760337226</v>
+        <v>58.78690886752577</v>
       </c>
       <c r="G156" t="n">
         <v>18</v>
@@ -4650,16 +4650,16 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>-1.48100746612016</v>
+        <v>-1.403168434485263</v>
       </c>
       <c r="D157" t="n">
-        <v>28.93659242351404</v>
+        <v>28.17141895079881</v>
       </c>
       <c r="E157" t="n">
-        <v>36.08983617175682</v>
+        <v>35.51918404147411</v>
       </c>
       <c r="F157" t="n">
-        <v>34.40960298823308</v>
+        <v>34.18426412791427</v>
       </c>
       <c r="G157" t="n">
         <v>89</v>
@@ -4677,16 +4677,16 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>-1.640644065585972</v>
+        <v>-0.7508773294774611</v>
       </c>
       <c r="D158" t="n">
-        <v>417.1304762098524</v>
+        <v>327.4013237230706</v>
       </c>
       <c r="E158" t="n">
-        <v>486.9702533058045</v>
+        <v>396.5293696581398</v>
       </c>
       <c r="F158" t="n">
-        <v>48.64340495597759</v>
+        <v>38.49670213075475</v>
       </c>
       <c r="G158" t="n">
         <v>99</v>
@@ -4704,16 +4704,16 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>-0.809835937473756</v>
+        <v>0.2630877182184792</v>
       </c>
       <c r="D159" t="n">
-        <v>325.8220516738071</v>
+        <v>199.4486418693296</v>
       </c>
       <c r="E159" t="n">
-        <v>431.4172785441124</v>
+        <v>275.2870795257362</v>
       </c>
       <c r="F159" t="n">
-        <v>40.70779913013961</v>
+        <v>22.57385888508666</v>
       </c>
       <c r="G159" t="n">
         <v>93</v>
@@ -4731,16 +4731,16 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>-0.6246180896953344</v>
+        <v>-0.4849637884661606</v>
       </c>
       <c r="D160" t="n">
-        <v>7.931690772374471</v>
+        <v>7.290579349566729</v>
       </c>
       <c r="E160" t="n">
-        <v>11.11376257114519</v>
+        <v>10.62535389385913</v>
       </c>
       <c r="F160" t="n">
-        <v>68.83928089466973</v>
+        <v>64.6302077288388</v>
       </c>
       <c r="G160" t="n">
         <v>78</v>
@@ -4758,16 +4758,16 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>-2.885583923169835</v>
+        <v>-3.184125382756486</v>
       </c>
       <c r="D161" t="n">
-        <v>168.4930956098768</v>
+        <v>171.2091181013319</v>
       </c>
       <c r="E161" t="n">
-        <v>186.9384794771434</v>
+        <v>193.9871239520244</v>
       </c>
       <c r="F161" t="n">
-        <v>60.77423701855869</v>
+        <v>60.02441873166796</v>
       </c>
       <c r="G161" t="n">
         <v>18</v>
@@ -4785,16 +4785,16 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>-0.8189559065681395</v>
+        <v>-0.9642709241582585</v>
       </c>
       <c r="D162" t="n">
-        <v>22.64288844419329</v>
+        <v>23.90034840615948</v>
       </c>
       <c r="E162" t="n">
-        <v>30.90167073629803</v>
+        <v>32.11231158094653</v>
       </c>
       <c r="F162" t="n">
-        <v>26.87957276265286</v>
+        <v>28.11780138393544</v>
       </c>
       <c r="G162" t="n">
         <v>89</v>
@@ -4812,16 +4812,16 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>-1.129452536381352</v>
+        <v>-1.554117729642243</v>
       </c>
       <c r="D163" t="n">
-        <v>360.2670426802202</v>
+        <v>399.6270463731554</v>
       </c>
       <c r="E163" t="n">
-        <v>437.3020186802627</v>
+        <v>478.9254939163361</v>
       </c>
       <c r="F163" t="n">
-        <v>41.68706439333613</v>
+        <v>45.87206138181642</v>
       </c>
       <c r="G163" t="n">
         <v>99</v>
@@ -4839,16 +4839,16 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>0.08318476610296421</v>
+        <v>0.07242579792643189</v>
       </c>
       <c r="D164" t="n">
-        <v>241.4593479607695</v>
+        <v>256.270751953125</v>
       </c>
       <c r="E164" t="n">
-        <v>307.0568862263958</v>
+        <v>308.8533112269405</v>
       </c>
       <c r="F164" t="n">
-        <v>27.01222847366</v>
+        <v>31.61860511773386</v>
       </c>
       <c r="G164" t="n">
         <v>93</v>
@@ -4866,16 +4866,16 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>-0.4486146321315188</v>
+        <v>-0.4364502872544169</v>
       </c>
       <c r="D165" t="n">
-        <v>7.459526294317001</v>
+        <v>7.377525149247585</v>
       </c>
       <c r="E165" t="n">
-        <v>10.49450372312883</v>
+        <v>10.45034847100338</v>
       </c>
       <c r="F165" t="n">
-        <v>74.22349258325052</v>
+        <v>73.2163505245863</v>
       </c>
       <c r="G165" t="n">
         <v>78</v>
@@ -4893,16 +4893,16 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>-3.44898333738496</v>
+        <v>-3.738717499012719</v>
       </c>
       <c r="D166" t="n">
-        <v>181.6192251841227</v>
+        <v>188.0579630533854</v>
       </c>
       <c r="E166" t="n">
-        <v>200.0326777611348</v>
+        <v>206.443383595205</v>
       </c>
       <c r="F166" t="n">
-        <v>63.45750666217295</v>
+        <v>66.23039657251874</v>
       </c>
       <c r="G166" t="n">
         <v>18</v>
@@ -4920,16 +4920,16 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>-1.57102663979183</v>
+        <v>-1.808246009661858</v>
       </c>
       <c r="D167" t="n">
-        <v>28.72835465763392</v>
+        <v>30.76434574770124</v>
       </c>
       <c r="E167" t="n">
-        <v>36.73873202702739</v>
+        <v>38.39621812819471</v>
       </c>
       <c r="F167" t="n">
-        <v>34.0664934614391</v>
+        <v>37.12236465218499</v>
       </c>
       <c r="G167" t="n">
         <v>89</v>
@@ -4947,16 +4947,16 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>-1.051965526072566</v>
+        <v>-1.344260543997093</v>
       </c>
       <c r="D168" t="n">
-        <v>357.8331617875533</v>
+        <v>384.6456366644965</v>
       </c>
       <c r="E168" t="n">
-        <v>429.271968553525</v>
+        <v>458.8285557719386</v>
       </c>
       <c r="F168" t="n">
-        <v>41.68425796419069</v>
+        <v>45.66125805593316</v>
       </c>
       <c r="G168" t="n">
         <v>99</v>
@@ -4974,16 +4974,16 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>0.3106887355032416</v>
+        <v>-0.6635700294284386</v>
       </c>
       <c r="D169" t="n">
-        <v>195.3682388797883</v>
+        <v>215.4946860036542</v>
       </c>
       <c r="E169" t="n">
-        <v>266.247549259546</v>
+        <v>413.6170900520944</v>
       </c>
       <c r="F169" t="n">
-        <v>19.86175408144076</v>
+        <v>24.67543044814636</v>
       </c>
       <c r="G169" t="n">
         <v>93</v>
@@ -5001,16 +5001,16 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>-0.484445551697869</v>
+        <v>-0.6520014077398946</v>
       </c>
       <c r="D170" t="n">
-        <v>7.412311914639595</v>
+        <v>8.068228220328306</v>
       </c>
       <c r="E170" t="n">
-        <v>10.62349966360322</v>
+        <v>11.20703372102616</v>
       </c>
       <c r="F170" t="n">
-        <v>72.04370279000301</v>
+        <v>71.52336694688746</v>
       </c>
       <c r="G170" t="n">
         <v>78</v>
@@ -5028,16 +5028,16 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>-4.842999472487429</v>
+        <v>-4.756439140300148</v>
       </c>
       <c r="D171" t="n">
-        <v>208.0137557983398</v>
+        <v>208.2415495978461</v>
       </c>
       <c r="E171" t="n">
-        <v>229.238988064794</v>
+        <v>227.5346371678544</v>
       </c>
       <c r="F171" t="n">
-        <v>71.75721288077494</v>
+        <v>72.85515619415014</v>
       </c>
       <c r="G171" t="n">
         <v>18</v>
@@ -5055,16 +5055,16 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>-1.193412146943791</v>
+        <v>-1.23128304448906</v>
       </c>
       <c r="D172" t="n">
-        <v>26.14771973684933</v>
+        <v>25.69733934723929</v>
       </c>
       <c r="E172" t="n">
-        <v>33.93368289558074</v>
+        <v>34.22537439505618</v>
       </c>
       <c r="F172" t="n">
-        <v>31.62254244447875</v>
+        <v>30.44916708121425</v>
       </c>
       <c r="G172" t="n">
         <v>89</v>
@@ -5082,16 +5082,16 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>-1.401639604513679</v>
+        <v>-1.002107037739293</v>
       </c>
       <c r="D173" t="n">
-        <v>388.0246346213601</v>
+        <v>346.3102814645478</v>
       </c>
       <c r="E173" t="n">
-        <v>464.4098455651067</v>
+        <v>424.0246907014883</v>
       </c>
       <c r="F173" t="n">
-        <v>44.88269622960549</v>
+        <v>40.75636003653282</v>
       </c>
       <c r="G173" t="n">
         <v>99</v>
@@ -5109,16 +5109,16 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>-0.1496749313768149</v>
+        <v>-0.08365767759925946</v>
       </c>
       <c r="D174" t="n">
-        <v>221.446033108619</v>
+        <v>239.2281172557544</v>
       </c>
       <c r="E174" t="n">
-        <v>343.8471760488247</v>
+        <v>333.8289428909625</v>
       </c>
       <c r="F174" t="n">
-        <v>22.40465068644746</v>
+        <v>25.30975160680656</v>
       </c>
       <c r="G174" t="n">
         <v>93</v>
@@ -5136,16 +5136,16 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>-0.6739863618483759</v>
+        <v>-0.6086355708727904</v>
       </c>
       <c r="D175" t="n">
-        <v>8.363069601548023</v>
+        <v>7.564220605752407</v>
       </c>
       <c r="E175" t="n">
-        <v>11.28135926318062</v>
+        <v>11.05896047927166</v>
       </c>
       <c r="F175" t="n">
-        <v>75.05730168451808</v>
+        <v>66.56303616514776</v>
       </c>
       <c r="G175" t="n">
         <v>78</v>
@@ -5163,16 +5163,16 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>-5.434134252739033</v>
+        <v>-5.676736146511002</v>
       </c>
       <c r="D176" t="n">
-        <v>222.8589004940457</v>
+        <v>224.6036987304688</v>
       </c>
       <c r="E176" t="n">
-        <v>240.5556813642854</v>
+        <v>245.0488485199228</v>
       </c>
       <c r="F176" t="n">
-        <v>78.29940345170795</v>
+        <v>78.64438860009913</v>
       </c>
       <c r="G176" t="n">
         <v>18</v>
@@ -5190,16 +5190,16 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>-1.181931489314813</v>
+        <v>-1.554216314797547</v>
       </c>
       <c r="D177" t="n">
-        <v>26.44576790627469</v>
+        <v>28.49674977077527</v>
       </c>
       <c r="E177" t="n">
-        <v>33.84475931680016</v>
+        <v>36.61842933595221</v>
       </c>
       <c r="F177" t="n">
-        <v>32.27434650102909</v>
+        <v>34.2245118185568</v>
       </c>
       <c r="G177" t="n">
         <v>89</v>
@@ -5217,16 +5217,16 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>-0.5399217693191263</v>
+        <v>-1.095668615860515</v>
       </c>
       <c r="D178" t="n">
-        <v>289.5303808655402</v>
+        <v>363.2102843005248</v>
       </c>
       <c r="E178" t="n">
-        <v>371.8748682019462</v>
+        <v>433.8192355157416</v>
       </c>
       <c r="F178" t="n">
-        <v>33.61116496967822</v>
+        <v>42.5412598525265</v>
       </c>
       <c r="G178" t="n">
         <v>99</v>
@@ -5244,16 +5244,16 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>0.10476510191847</v>
+        <v>0.3280042580188944</v>
       </c>
       <c r="D179" t="n">
-        <v>229.6904132801999</v>
+        <v>191.1724459740423</v>
       </c>
       <c r="E179" t="n">
-        <v>303.4215571715994</v>
+        <v>262.8822066946469</v>
       </c>
       <c r="F179" t="n">
-        <v>21.92118036691907</v>
+        <v>19.10963056046448</v>
       </c>
       <c r="G179" t="n">
         <v>93</v>
@@ -5271,16 +5271,16 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>-0.5016879169221551</v>
+        <v>-0.5277804452861246</v>
       </c>
       <c r="D180" t="n">
-        <v>7.009259538772779</v>
+        <v>7.236536325552525</v>
       </c>
       <c r="E180" t="n">
-        <v>10.68501940720207</v>
+        <v>10.77744823709677</v>
       </c>
       <c r="F180" t="n">
-        <v>68.60414344019313</v>
+        <v>63.78658730660312</v>
       </c>
       <c r="G180" t="n">
         <v>78</v>
@@ -5298,16 +5298,16 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>-5.704957952355044</v>
+        <v>-5.543793658126716</v>
       </c>
       <c r="D181" t="n">
-        <v>227.1795060899523</v>
+        <v>221.8251321580675</v>
       </c>
       <c r="E181" t="n">
-        <v>245.5661992348554</v>
+        <v>242.5969616688006</v>
       </c>
       <c r="F181" t="n">
-        <v>80.18053091940195</v>
+        <v>76.95330360213083</v>
       </c>
       <c r="G181" t="n">
         <v>18</v>
@@ -5325,16 +5325,16 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>-0.7737153157260259</v>
+        <v>-0.9567829923740074</v>
       </c>
       <c r="D182" t="n">
-        <v>20.59147341867511</v>
+        <v>24.0301908857367</v>
       </c>
       <c r="E182" t="n">
-        <v>30.51496197061769</v>
+        <v>32.05104600122164</v>
       </c>
       <c r="F182" t="n">
-        <v>25.19127483114824</v>
+        <v>29.17037763268223</v>
       </c>
       <c r="G182" t="n">
         <v>89</v>
@@ -5352,16 +5352,16 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>-0.5980159636764126</v>
+        <v>-1.144540955552919</v>
       </c>
       <c r="D183" t="n">
-        <v>300.747309366862</v>
+        <v>335.6232236611723</v>
       </c>
       <c r="E183" t="n">
-        <v>378.8244982111472</v>
+        <v>438.8485545278575</v>
       </c>
       <c r="F183" t="n">
-        <v>34.9584511159384</v>
+        <v>39.51165217846295</v>
       </c>
       <c r="G183" t="n">
         <v>99</v>
@@ -5379,16 +5379,16 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>-0.4192392899065511</v>
+        <v>-1.069264752318956</v>
       </c>
       <c r="D184" t="n">
-        <v>283.83887210969</v>
+        <v>339.781239499328</v>
       </c>
       <c r="E184" t="n">
-        <v>382.0372795667112</v>
+        <v>461.3026623706165</v>
       </c>
       <c r="F184" t="n">
-        <v>27.12598296813371</v>
+        <v>31.85554177764128</v>
       </c>
       <c r="G184" t="n">
         <v>93</v>
@@ -5406,16 +5406,16 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>-0.3209425473466254</v>
+        <v>-0.3868805157608257</v>
       </c>
       <c r="D185" t="n">
-        <v>6.762462295018709</v>
+        <v>7.266551476258498</v>
       </c>
       <c r="E185" t="n">
-        <v>10.02137783586598</v>
+        <v>10.26845243105583</v>
       </c>
       <c r="F185" t="n">
-        <v>63.46487177085781</v>
+        <v>67.44526002145847</v>
       </c>
       <c r="G185" t="n">
         <v>78</v>
@@ -5433,16 +5433,16 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>-6.612655673670171</v>
+        <v>-6.981191962300877</v>
       </c>
       <c r="D186" t="n">
-        <v>244.3405620786879</v>
+        <v>251.1597185134888</v>
       </c>
       <c r="E186" t="n">
-        <v>261.6607925499394</v>
+        <v>267.9195699206729</v>
       </c>
       <c r="F186" t="n">
-        <v>87.21091131533932</v>
+        <v>91.68272496493555</v>
       </c>
       <c r="G186" t="n">
         <v>18</v>
@@ -5460,16 +5460,16 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>-0.6859531200312967</v>
+        <v>-1.071548307740349</v>
       </c>
       <c r="D187" t="n">
-        <v>20.90576585491052</v>
+        <v>25.34139770336365</v>
       </c>
       <c r="E187" t="n">
-        <v>29.75045568668752</v>
+        <v>32.97755153312815</v>
       </c>
       <c r="F187" t="n">
-        <v>24.8303162198921</v>
+        <v>30.71210703927289</v>
       </c>
       <c r="G187" t="n">
         <v>89</v>
@@ -5487,16 +5487,16 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>-1.595193658382587</v>
+        <v>-2.569357144328271</v>
       </c>
       <c r="D188" t="n">
-        <v>397.7707363860775</v>
+        <v>475.5268368191189</v>
       </c>
       <c r="E188" t="n">
-        <v>482.7612304650125</v>
+        <v>566.1643278010233</v>
       </c>
       <c r="F188" t="n">
-        <v>45.27820645319858</v>
+        <v>56.0352465945308</v>
       </c>
       <c r="G188" t="n">
         <v>99</v>
@@ -5514,16 +5514,16 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>-0.5281032095883167</v>
+        <v>-0.513995514978012</v>
       </c>
       <c r="D189" t="n">
-        <v>303.2670196205057</v>
+        <v>287.0438645885837</v>
       </c>
       <c r="E189" t="n">
-        <v>396.4188296505387</v>
+        <v>394.5846853582461</v>
       </c>
       <c r="F189" t="n">
-        <v>27.40728501865978</v>
+        <v>26.28627375425111</v>
       </c>
       <c r="G189" t="n">
         <v>93</v>
@@ -5541,16 +5541,16 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>-0.3055540835975885</v>
+        <v>-0.5330300819968492</v>
       </c>
       <c r="D190" t="n">
-        <v>6.777614067762326</v>
+        <v>7.859258370521741</v>
       </c>
       <c r="E190" t="n">
-        <v>9.962834268920245</v>
+        <v>10.79594866020431</v>
       </c>
       <c r="F190" t="n">
-        <v>67.02995813785493</v>
+        <v>73.82712597311072</v>
       </c>
       <c r="G190" t="n">
         <v>78</v>
@@ -5568,16 +5568,16 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>-6.592115820727323</v>
+        <v>-6.147065152363887</v>
       </c>
       <c r="D191" t="n">
-        <v>243.5471409691705</v>
+        <v>235.894521607293</v>
       </c>
       <c r="E191" t="n">
-        <v>261.3075581089995</v>
+        <v>253.5329616581594</v>
       </c>
       <c r="F191" t="n">
-        <v>86.9311771965266</v>
+        <v>85.8818935779037</v>
       </c>
       <c r="G191" t="n">
         <v>18</v>
@@ -5595,16 +5595,16 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>-0.5730754107223257</v>
+        <v>-0.7005850885877072</v>
       </c>
       <c r="D192" t="n">
-        <v>20.83181387654851</v>
+        <v>21.65801185436463</v>
       </c>
       <c r="E192" t="n">
-        <v>28.73727912215473</v>
+        <v>29.8792752017196</v>
       </c>
       <c r="F192" t="n">
-        <v>25.77138753467707</v>
+        <v>26.3185306796528</v>
       </c>
       <c r="G192" t="n">
         <v>89</v>
@@ -5622,16 +5622,16 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>-0.3673279360154236</v>
+        <v>-0.4281337039008297</v>
       </c>
       <c r="D193" t="n">
-        <v>284.9367307412504</v>
+        <v>285.8900340687145</v>
       </c>
       <c r="E193" t="n">
-        <v>350.4159318756999</v>
+        <v>358.1227693460611</v>
       </c>
       <c r="F193" t="n">
-        <v>36.88292960719551</v>
+        <v>36.97158614476397</v>
       </c>
       <c r="G193" t="n">
         <v>99</v>
@@ -5649,16 +5649,16 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>-0.3657510048857195</v>
+        <v>-0.3729437671958662</v>
       </c>
       <c r="D194" t="n">
-        <v>294.7666409400202</v>
+        <v>290.959464124454</v>
       </c>
       <c r="E194" t="n">
-        <v>374.7690306696877</v>
+        <v>375.754600045284</v>
       </c>
       <c r="F194" t="n">
-        <v>29.99658580731779</v>
+        <v>28.85961511191012</v>
       </c>
       <c r="G194" t="n">
         <v>93</v>
@@ -5676,16 +5676,16 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>-0.5832204284844578</v>
+        <v>-0.610028951744888</v>
       </c>
       <c r="D195" t="n">
-        <v>7.323860425215501</v>
+        <v>7.470342232630803</v>
       </c>
       <c r="E195" t="n">
-        <v>10.97125134618378</v>
+        <v>11.06374901213551</v>
       </c>
       <c r="F195" t="n">
-        <v>71.07536894882848</v>
+        <v>72.02130406700253</v>
       </c>
       <c r="G195" t="n">
         <v>78</v>
@@ -5703,16 +5703,16 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>-6.581562341933037</v>
+        <v>-6.659874574685139</v>
       </c>
       <c r="D196" t="n">
-        <v>246.5816640853882</v>
+        <v>246.0634887483385</v>
       </c>
       <c r="E196" t="n">
-        <v>261.1258786637104</v>
+        <v>262.4710377337489</v>
       </c>
       <c r="F196" t="n">
-        <v>90.86408683880106</v>
+        <v>89.68479143870699</v>
       </c>
       <c r="G196" t="n">
         <v>18</v>
@@ -5730,16 +5730,16 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>-0.4892588499959918</v>
+        <v>-0.5652410780403949</v>
       </c>
       <c r="D197" t="n">
-        <v>19.91595911176017</v>
+        <v>20.65105251783735</v>
       </c>
       <c r="E197" t="n">
-        <v>27.96121055100132</v>
+        <v>28.66563016792593</v>
       </c>
       <c r="F197" t="n">
-        <v>24.97735664056718</v>
+        <v>25.35411617961116</v>
       </c>
       <c r="G197" t="n">
         <v>89</v>
@@ -5757,16 +5757,16 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>-0.3025128698533766</v>
+        <v>-0.4111868560011318</v>
       </c>
       <c r="D198" t="n">
-        <v>279.6751269716205</v>
+        <v>289.7379363088897</v>
       </c>
       <c r="E198" t="n">
-        <v>342.0097692215887</v>
+        <v>355.9916088661117</v>
       </c>
       <c r="F198" t="n">
-        <v>36.44694688524324</v>
+        <v>37.58249884579269</v>
       </c>
       <c r="G198" t="n">
         <v>99</v>
@@ -5784,16 +5784,16 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>-0.431842331712204</v>
+        <v>-0.406039266282556</v>
       </c>
       <c r="D199" t="n">
-        <v>295.5335913217196</v>
+        <v>291.0369466145833</v>
       </c>
       <c r="E199" t="n">
-        <v>383.7298024361041</v>
+        <v>380.2565080927498</v>
       </c>
       <c r="F199" t="n">
-        <v>29.73390583123148</v>
+        <v>29.17161741904529</v>
       </c>
       <c r="G199" t="n">
         <v>93</v>
@@ -5811,16 +5811,16 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>-0.5156291550783556</v>
+        <v>-0.5911238732536308</v>
       </c>
       <c r="D200" t="n">
-        <v>7.098525579159077</v>
+        <v>7.41372959736066</v>
       </c>
       <c r="E200" t="n">
-        <v>10.73450314585387</v>
+        <v>10.99860152804351</v>
       </c>
       <c r="F200" t="n">
-        <v>69.92411300769544</v>
+        <v>73.08279798282696</v>
       </c>
       <c r="G200" t="n">
         <v>78</v>
@@ -5838,16 +5838,16 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>-6.532803423001697</v>
+        <v>-6.611487219575932</v>
       </c>
       <c r="D201" t="n">
-        <v>246.615955458747</v>
+        <v>246.3150435553657</v>
       </c>
       <c r="E201" t="n">
-        <v>260.2848414157096</v>
+        <v>261.640710835345</v>
       </c>
       <c r="F201" t="n">
-        <v>91.3835243013549</v>
+        <v>90.16338637919158</v>
       </c>
       <c r="G201" t="n">
         <v>18</v>
@@ -5865,16 +5865,16 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>-0.6894163457939881</v>
+        <v>-0.9297799852223465</v>
       </c>
       <c r="D202" t="n">
-        <v>20.89076710818859</v>
+        <v>23.06489961602715</v>
       </c>
       <c r="E202" t="n">
-        <v>29.78099618220231</v>
+        <v>31.82913043106898</v>
       </c>
       <c r="F202" t="n">
-        <v>25.28582178639046</v>
+        <v>27.67861779135395</v>
       </c>
       <c r="G202" t="n">
         <v>89</v>
@@ -5892,16 +5892,16 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>-1.091980348144591</v>
+        <v>-1.003639258083384</v>
       </c>
       <c r="D203" t="n">
-        <v>356.6549895315459</v>
+        <v>327.2754273077454</v>
       </c>
       <c r="E203" t="n">
-        <v>433.4373177625236</v>
+        <v>424.1869135468312</v>
       </c>
       <c r="F203" t="n">
-        <v>41.31209520960022</v>
+        <v>38.88475467575985</v>
       </c>
       <c r="G203" t="n">
         <v>99</v>
@@ -5919,16 +5919,16 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>-0.2048844240993919</v>
+        <v>-0.9204751170383259</v>
       </c>
       <c r="D204" t="n">
-        <v>262.9507485666583</v>
+        <v>326.9422768213416</v>
       </c>
       <c r="E204" t="n">
-        <v>352.0064538855678</v>
+        <v>444.4084144868905</v>
       </c>
       <c r="F204" t="n">
-        <v>24.80638876358671</v>
+        <v>30.79597491585612</v>
       </c>
       <c r="G204" t="n">
         <v>93</v>
@@ -5946,16 +5946,16 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>-0.3816154222879873</v>
+        <v>-0.3683104486906692</v>
       </c>
       <c r="D205" t="n">
-        <v>7.202038340079478</v>
+        <v>7.122487930151133</v>
       </c>
       <c r="E205" t="n">
-        <v>10.24894254149048</v>
+        <v>10.19947443707636</v>
       </c>
       <c r="F205" t="n">
-        <v>70.72209514067517</v>
+        <v>65.97500139015068</v>
       </c>
       <c r="G205" t="n">
         <v>78</v>
@@ -5973,16 +5973,16 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>-6.587957741996147</v>
+        <v>-6.920189049311627</v>
       </c>
       <c r="D206" t="n">
-        <v>243.619836807251</v>
+        <v>250.2318079206678</v>
       </c>
       <c r="E206" t="n">
-        <v>261.2359913523923</v>
+        <v>266.8937065762186</v>
       </c>
       <c r="F206" t="n">
-        <v>87.67816704038522</v>
+        <v>90.99599981539926</v>
       </c>
       <c r="G206" t="n">
         <v>18</v>
@@ -6000,16 +6000,16 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>-1.062062837643853</v>
+        <v>-1.048459019927811</v>
       </c>
       <c r="D207" t="n">
-        <v>23.57145352310009</v>
+        <v>24.5370500971762</v>
       </c>
       <c r="E207" t="n">
-        <v>32.90196399294186</v>
+        <v>32.79325416839622</v>
       </c>
       <c r="F207" t="n">
-        <v>27.60189178024334</v>
+        <v>29.80465414215448</v>
       </c>
       <c r="G207" t="n">
         <v>89</v>
@@ -6027,16 +6027,16 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>-1.674010595069319</v>
+        <v>-1.262176429740922</v>
       </c>
       <c r="D208" t="n">
-        <v>407.2497720429392</v>
+        <v>351.5985985958215</v>
       </c>
       <c r="E208" t="n">
-        <v>490.0372136044042</v>
+        <v>450.7240545617461</v>
       </c>
       <c r="F208" t="n">
-        <v>46.72951577019354</v>
+        <v>41.26149761313641</v>
       </c>
       <c r="G208" t="n">
         <v>99</v>
@@ -6054,16 +6054,16 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>-0.8402140015070059</v>
+        <v>-0.7237950125970711</v>
       </c>
       <c r="D209" t="n">
-        <v>345.7704343077957</v>
+        <v>293.9646905058174</v>
       </c>
       <c r="E209" t="n">
-        <v>435.0228772036336</v>
+        <v>421.0374638326508</v>
       </c>
       <c r="F209" t="n">
-        <v>32.74211013665547</v>
+        <v>28.32377353708036</v>
       </c>
       <c r="G209" t="n">
         <v>93</v>
@@ -6081,16 +6081,16 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>-0.5122694057041417</v>
+        <v>-0.3676325792873372</v>
       </c>
       <c r="D210" t="n">
-        <v>7.882095055702405</v>
+        <v>7.225676243121807</v>
       </c>
       <c r="E210" t="n">
-        <v>10.72259876638663</v>
+        <v>10.1969476829438</v>
       </c>
       <c r="F210" t="n">
-        <v>73.31591806993941</v>
+        <v>68.52784033526767</v>
       </c>
       <c r="G210" t="n">
         <v>78</v>
@@ -6108,16 +6108,16 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>-7.125325280372541</v>
+        <v>-7.119786567593868</v>
       </c>
       <c r="D211" t="n">
-        <v>253.1430814531114</v>
+        <v>253.7697585423788</v>
       </c>
       <c r="E211" t="n">
-        <v>270.3279413825449</v>
+        <v>270.2357897445533</v>
       </c>
       <c r="F211" t="n">
-        <v>91.58458027849473</v>
+        <v>93.01248027478512</v>
       </c>
       <c r="G211" t="n">
         <v>18</v>
@@ -6135,16 +6135,16 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>-0.7994784254817366</v>
+        <v>-1.578714712341688</v>
       </c>
       <c r="D212" t="n">
-        <v>22.51927671539649</v>
+        <v>29.03671650404341</v>
       </c>
       <c r="E212" t="n">
-        <v>30.73577703620542</v>
+        <v>36.79362045121718</v>
       </c>
       <c r="F212" t="n">
-        <v>26.7567194023869</v>
+        <v>34.88002060285481</v>
       </c>
       <c r="G212" t="n">
         <v>89</v>
@@ -6162,16 +6162,16 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>-0.5572567249668956</v>
+        <v>-1.105233790245549</v>
       </c>
       <c r="D213" t="n">
-        <v>305.0465078642874</v>
+        <v>344.4116365066682</v>
       </c>
       <c r="E213" t="n">
-        <v>373.9621150795205</v>
+        <v>434.8081400758538</v>
       </c>
       <c r="F213" t="n">
-        <v>35.59023074015288</v>
+        <v>40.75560819988232</v>
       </c>
       <c r="G213" t="n">
         <v>99</v>
@@ -6189,16 +6189,16 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>0.1955065357424646</v>
+        <v>-1.464866775022096</v>
       </c>
       <c r="D214" t="n">
-        <v>216.1748414398521</v>
+        <v>429.1354442309308</v>
       </c>
       <c r="E214" t="n">
-        <v>287.6333180422494</v>
+        <v>503.4712275606155</v>
       </c>
       <c r="F214" t="n">
-        <v>24.23268547353963</v>
+        <v>54.8862952731662</v>
       </c>
       <c r="G214" t="n">
         <v>93</v>
@@ -6216,16 +6216,16 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>-0.3592979944907633</v>
+        <v>-0.4486128184669118</v>
       </c>
       <c r="D215" t="n">
-        <v>7.327245311859326</v>
+        <v>7.761005478027539</v>
       </c>
       <c r="E215" t="n">
-        <v>10.16582923627111</v>
+        <v>10.49449715357075</v>
       </c>
       <c r="F215" t="n">
-        <v>70.08052025963994</v>
+        <v>76.69915421796489</v>
       </c>
       <c r="G215" t="n">
         <v>78</v>
@@ -6243,16 +6243,16 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>-3.780402228171743</v>
+        <v>-3.808299579498858</v>
       </c>
       <c r="D216" t="n">
-        <v>182.9107750786675</v>
+        <v>187.3452983432346</v>
       </c>
       <c r="E216" t="n">
-        <v>207.3493981859992</v>
+        <v>207.9535402654511</v>
       </c>
       <c r="F216" t="n">
-        <v>67.37526607115588</v>
+        <v>65.22074466248371</v>
       </c>
       <c r="G216" t="n">
         <v>18</v>
@@ -6270,16 +6270,16 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>-0.7926602087688566</v>
+        <v>-1.242243029174666</v>
       </c>
       <c r="D217" t="n">
-        <v>21.60004212883081</v>
+        <v>25.6353933998708</v>
       </c>
       <c r="E217" t="n">
-        <v>30.67749290476109</v>
+        <v>34.30932835076226</v>
       </c>
       <c r="F217" t="n">
-        <v>25.53319352989697</v>
+        <v>30.61616609289538</v>
       </c>
       <c r="G217" t="n">
         <v>89</v>
@@ -6297,16 +6297,16 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>-0.7551060916349333</v>
+        <v>-1.222145742822378</v>
       </c>
       <c r="D218" t="n">
-        <v>322.4973210806799</v>
+        <v>351.5927025380761</v>
       </c>
       <c r="E218" t="n">
-        <v>397.0079346341175</v>
+        <v>446.7183264572723</v>
       </c>
       <c r="F218" t="n">
-        <v>37.22662924128691</v>
+        <v>40.18193434219356</v>
       </c>
       <c r="G218" t="n">
         <v>99</v>
@@ -6324,16 +6324,16 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>0.1039951740504761</v>
+        <v>-0.1532222179430998</v>
       </c>
       <c r="D219" t="n">
-        <v>220.9435149162046</v>
+        <v>246.5956243699597</v>
       </c>
       <c r="E219" t="n">
-        <v>303.5520047816537</v>
+        <v>344.3772324275123</v>
       </c>
       <c r="F219" t="n">
-        <v>24.97887596248838</v>
+        <v>28.60568940282134</v>
       </c>
       <c r="G219" t="n">
         <v>93</v>
@@ -6351,16 +6351,16 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>-0.4120759205546436</v>
+        <v>-0.3384844871483301</v>
       </c>
       <c r="D220" t="n">
-        <v>7.731944206433418</v>
+        <v>7.33597607490344</v>
       </c>
       <c r="E220" t="n">
-        <v>10.36130590228976</v>
+        <v>10.0876996524169</v>
       </c>
       <c r="F220" t="n">
-        <v>71.50425659560501</v>
+        <v>71.74945453715689</v>
       </c>
       <c r="G220" t="n">
         <v>78</v>
@@ -6378,16 +6378,16 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>-4.145029791686168</v>
+        <v>-4.525771807776323</v>
       </c>
       <c r="D221" t="n">
-        <v>193.5725123087565</v>
+        <v>201.7013651529948</v>
       </c>
       <c r="E221" t="n">
-        <v>215.1119345720969</v>
+        <v>222.9292383759808</v>
       </c>
       <c r="F221" t="n">
-        <v>67.33205023706013</v>
+        <v>69.72329645463743</v>
       </c>
       <c r="G221" t="n">
         <v>18</v>
@@ -6405,16 +6405,16 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>-1.052595338091129</v>
+        <v>-1.143861527531052</v>
       </c>
       <c r="D222" t="n">
-        <v>24.22258966424492</v>
+        <v>24.80255193388864</v>
       </c>
       <c r="E222" t="n">
-        <v>32.82634609912782</v>
+        <v>33.54820130926478</v>
       </c>
       <c r="F222" t="n">
-        <v>28.09372704472366</v>
+        <v>29.58477292218192</v>
       </c>
       <c r="G222" t="n">
         <v>89</v>
@@ -6432,16 +6432,16 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>-0.2425737507283601</v>
+        <v>-0.8997392130427762</v>
       </c>
       <c r="D223" t="n">
-        <v>263.1671116376164</v>
+        <v>334.8096358174025</v>
       </c>
       <c r="E223" t="n">
-        <v>334.047778071336</v>
+        <v>413.0422649304267</v>
       </c>
       <c r="F223" t="n">
-        <v>33.73596570894822</v>
+        <v>38.70490072911844</v>
       </c>
       <c r="G223" t="n">
         <v>99</v>
@@ -6459,16 +6459,16 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>-5.539740751006747</v>
+        <v>-0.07810377768282017</v>
       </c>
       <c r="D224" t="n">
-        <v>775.6306401734711</v>
+        <v>216.0594265845514</v>
       </c>
       <c r="E224" t="n">
-        <v>820.0837326626873</v>
+        <v>332.9723835483017</v>
       </c>
       <c r="F224" t="n">
-        <v>95.0971748154959</v>
+        <v>23.20786304887792</v>
       </c>
       <c r="G224" t="n">
         <v>93</v>
@@ -6486,16 +6486,16 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>-0.4362719441407512</v>
+        <v>-0.343222521455828</v>
       </c>
       <c r="D225" t="n">
-        <v>7.828089900505849</v>
+        <v>7.027547081311543</v>
       </c>
       <c r="E225" t="n">
-        <v>10.44969971707367</v>
+        <v>10.10553835157395</v>
       </c>
       <c r="F225" t="n">
-        <v>73.19365522966437</v>
+        <v>66.83294565592442</v>
       </c>
       <c r="G225" t="n">
         <v>78</v>
@@ -6513,16 +6513,16 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>-2.533740001791604</v>
+        <v>-5.590708650260099</v>
       </c>
       <c r="D226" t="n">
-        <v>158.6405137379964</v>
+        <v>225.5250918070475</v>
       </c>
       <c r="E226" t="n">
-        <v>178.2739369753718</v>
+        <v>243.4650443486013</v>
       </c>
       <c r="F226" t="n">
-        <v>58.02696935954541</v>
+        <v>80.2015426879982</v>
       </c>
       <c r="G226" t="n">
         <v>18</v>
@@ -6540,16 +6540,16 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>-1.191672223389605</v>
+        <v>-1.563762571343993</v>
       </c>
       <c r="D227" t="n">
-        <v>25.9192422373911</v>
+        <v>29.43810797273443</v>
       </c>
       <c r="E227" t="n">
-        <v>33.92022128335159</v>
+        <v>36.68679529688841</v>
       </c>
       <c r="F227" t="n">
-        <v>30.19523765760052</v>
+        <v>35.79751854123915</v>
       </c>
       <c r="G227" t="n">
         <v>89</v>
@@ -6567,16 +6567,16 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>-1.276675991461411</v>
+        <v>-0.7091749315527529</v>
       </c>
       <c r="D228" t="n">
-        <v>371.6499135951803</v>
+        <v>309.0006471884371</v>
       </c>
       <c r="E228" t="n">
-        <v>452.1662193910212</v>
+        <v>391.7786425190006</v>
       </c>
       <c r="F228" t="n">
-        <v>42.72082331701036</v>
+        <v>38.82754392572371</v>
       </c>
       <c r="G228" t="n">
         <v>99</v>
@@ -6594,16 +6594,16 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>-1.81406841637482</v>
+        <v>-0.3195010115443957</v>
       </c>
       <c r="D229" t="n">
-        <v>441.3036295572917</v>
+        <v>260.3425955823673</v>
       </c>
       <c r="E229" t="n">
-        <v>537.9541436039012</v>
+        <v>368.368762246467</v>
       </c>
       <c r="F229" t="n">
-        <v>55.22462924979848</v>
+        <v>30.29910190050172</v>
       </c>
       <c r="G229" t="n">
         <v>93</v>
@@ -6621,16 +6621,16 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>-0.4407127650863576</v>
+        <v>-0.4187613532104031</v>
       </c>
       <c r="D230" t="n">
-        <v>7.817050343904739</v>
+        <v>7.6347722304173</v>
       </c>
       <c r="E230" t="n">
-        <v>10.46584200500373</v>
+        <v>10.3858045911921</v>
       </c>
       <c r="F230" t="n">
-        <v>75.21630955683494</v>
+        <v>76.52840752185163</v>
       </c>
       <c r="G230" t="n">
         <v>78</v>
@@ -6648,16 +6648,16 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>-2.530163285637005</v>
+        <v>-3.084189079687083</v>
       </c>
       <c r="D231" t="n">
-        <v>155.0740051269531</v>
+        <v>167.6963365342882</v>
       </c>
       <c r="E231" t="n">
-        <v>178.1836931120428</v>
+        <v>191.6564674050001</v>
       </c>
       <c r="F231" t="n">
-        <v>57.29309683734176</v>
+        <v>56.44275941431381</v>
       </c>
       <c r="G231" t="n">
         <v>18</v>
@@ -6675,16 +6675,16 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>-1.046951504858986</v>
+        <v>-1.517079766282079</v>
       </c>
       <c r="D232" t="n">
-        <v>24.32488557194056</v>
+        <v>29.18809502848079</v>
       </c>
       <c r="E232" t="n">
-        <v>32.78118523681007</v>
+        <v>36.35125124485523</v>
       </c>
       <c r="F232" t="n">
-        <v>28.18260740122056</v>
+        <v>35.58848033376072</v>
       </c>
       <c r="G232" t="n">
         <v>89</v>
@@ -6702,16 +6702,16 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>-0.468513501546187</v>
+        <v>-1.328481311170317</v>
       </c>
       <c r="D233" t="n">
-        <v>293.9969490128334</v>
+        <v>365.2929291388001</v>
       </c>
       <c r="E233" t="n">
-        <v>363.1503539615618</v>
+        <v>457.281759520591</v>
       </c>
       <c r="F233" t="n">
-        <v>35.53732984986364</v>
+        <v>42.27792343613099</v>
       </c>
       <c r="G233" t="n">
         <v>99</v>
@@ -6729,16 +6729,16 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>-1.981488320853019</v>
+        <v>-0.3227868501894418</v>
       </c>
       <c r="D234" t="n">
-        <v>483.0365318380377</v>
+        <v>270.1337516538558</v>
       </c>
       <c r="E234" t="n">
-        <v>553.7254532445368</v>
+        <v>368.8271354125904</v>
       </c>
       <c r="F234" t="n">
-        <v>58.48720441061869</v>
+        <v>31.61347102686888</v>
       </c>
       <c r="G234" t="n">
         <v>93</v>
@@ -6756,16 +6756,16 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>-0.4431307103967701</v>
+        <v>-0.4646485341148578</v>
       </c>
       <c r="D235" t="n">
-        <v>7.887305006002769</v>
+        <v>7.989189322178181</v>
       </c>
       <c r="E235" t="n">
-        <v>10.47462072392214</v>
+        <v>10.55242278037732</v>
       </c>
       <c r="F235" t="n">
-        <v>73.11201627282291</v>
+        <v>78.55246237512917</v>
       </c>
       <c r="G235" t="n">
         <v>78</v>
@@ -6783,16 +6783,16 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>-2.603777992348424</v>
+        <v>-3.067774562377379</v>
       </c>
       <c r="D236" t="n">
-        <v>160.1927151150174</v>
+        <v>165.7994151645237</v>
       </c>
       <c r="E236" t="n">
-        <v>180.0319450194683</v>
+        <v>191.2709421965723</v>
       </c>
       <c r="F236" t="n">
-        <v>60.3896719532663</v>
+        <v>56.18888275562121</v>
       </c>
       <c r="G236" t="n">
         <v>18</v>
@@ -6810,16 +6810,16 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>-0.5320147270303941</v>
+        <v>-1.116040638941978</v>
       </c>
       <c r="D237" t="n">
-        <v>20.63823183466879</v>
+        <v>25.14804565772582</v>
       </c>
       <c r="E237" t="n">
-        <v>28.35974653762207</v>
+        <v>33.3298130044652</v>
       </c>
       <c r="F237" t="n">
-        <v>24.19747195988141</v>
+        <v>29.41088780149945</v>
       </c>
       <c r="G237" t="n">
         <v>89</v>
@@ -6837,16 +6837,16 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>-0.4166426441284452</v>
+        <v>-1.163581488255079</v>
       </c>
       <c r="D238" t="n">
-        <v>290.5145525691485</v>
+        <v>352.3660748414319</v>
       </c>
       <c r="E238" t="n">
-        <v>356.6790944411501</v>
+        <v>440.7924308869243</v>
       </c>
       <c r="F238" t="n">
-        <v>34.38159603118228</v>
+        <v>40.39150255767689</v>
       </c>
       <c r="G238" t="n">
         <v>99</v>
@@ -6864,16 +6864,16 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>0.2116704463940676</v>
+        <v>-0.2028708392898653</v>
       </c>
       <c r="D239" t="n">
-        <v>218.8970888199345</v>
+        <v>260.2488094863071</v>
       </c>
       <c r="E239" t="n">
-        <v>284.7290867293206</v>
+        <v>351.7121969370359</v>
       </c>
       <c r="F239" t="n">
-        <v>25.153768383693</v>
+        <v>29.77827268294045</v>
       </c>
       <c r="G239" t="n">
         <v>93</v>
@@ -6891,16 +6891,16 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>-0.4882212133282782</v>
+        <v>-0.5935314968919334</v>
       </c>
       <c r="D240" t="n">
-        <v>7.853038494403545</v>
+        <v>8.34694834244557</v>
       </c>
       <c r="E240" t="n">
-        <v>10.63700142766442</v>
+        <v>11.00691969979111</v>
       </c>
       <c r="F240" t="n">
-        <v>76.65046102244824</v>
+        <v>79.9917425833081</v>
       </c>
       <c r="G240" t="n">
         <v>78</v>
@@ -6918,16 +6918,16 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>-2.469019899246356</v>
+        <v>-4.703116895302848</v>
       </c>
       <c r="D241" t="n">
-        <v>150.1096110873752</v>
+        <v>208.5744520823161</v>
       </c>
       <c r="E241" t="n">
-        <v>176.6338579406965</v>
+        <v>226.4783517937183</v>
       </c>
       <c r="F241" t="n">
-        <v>57.2695210618277</v>
+        <v>74.28881252809532</v>
       </c>
       <c r="G241" t="n">
         <v>18</v>
@@ -6945,16 +6945,16 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>-1.116890733857974</v>
+        <v>-1.400697113493282</v>
       </c>
       <c r="D242" t="n">
-        <v>24.99528094088094</v>
+        <v>28.26845582683435</v>
       </c>
       <c r="E242" t="n">
-        <v>33.33650726613759</v>
+        <v>35.50091609931479</v>
       </c>
       <c r="F242" t="n">
-        <v>28.92634321411477</v>
+        <v>34.09986073887558</v>
       </c>
       <c r="G242" t="n">
         <v>89</v>
@@ -6972,16 +6972,16 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>-1.257643196657656</v>
+        <v>-0.9834193464557068</v>
       </c>
       <c r="D243" t="n">
-        <v>361.2899593777126</v>
+        <v>331.9423015864209</v>
       </c>
       <c r="E243" t="n">
-        <v>450.2722193690092</v>
+        <v>422.0411254007336</v>
       </c>
       <c r="F243" t="n">
-        <v>42.16717138721328</v>
+        <v>39.46471041454099</v>
       </c>
       <c r="G243" t="n">
         <v>99</v>
@@ -6999,16 +6999,16 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>-0.3659555184316123</v>
+        <v>-0.05138345829608815</v>
       </c>
       <c r="D244" t="n">
-        <v>321.0971285912298</v>
+        <v>244.0733931346606</v>
       </c>
       <c r="E244" t="n">
-        <v>374.7970893985449</v>
+        <v>328.8202089684428</v>
       </c>
       <c r="F244" t="n">
-        <v>41.94172999284585</v>
+        <v>29.03451019985249</v>
       </c>
       <c r="G244" t="n">
         <v>93</v>
@@ -7026,16 +7026,16 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>-0.4240804294778029</v>
+        <v>-0.4090822653902857</v>
       </c>
       <c r="D245" t="n">
-        <v>7.805462941145286</v>
+        <v>7.663222960936717</v>
       </c>
       <c r="E245" t="n">
-        <v>10.40525508075793</v>
+        <v>10.35031689176511</v>
       </c>
       <c r="F245" t="n">
-        <v>71.5284613955365</v>
+        <v>75.10522544166326</v>
       </c>
       <c r="G245" t="n">
         <v>78</v>
@@ -7053,16 +7053,16 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>-1.10567956110332</v>
+        <v>-4.231282638029538</v>
       </c>
       <c r="D246" t="n">
-        <v>108.8524432712131</v>
+        <v>196.9236878289117</v>
       </c>
       <c r="E246" t="n">
-        <v>137.6152932571081</v>
+        <v>216.9075413176093</v>
       </c>
       <c r="F246" t="n">
-        <v>49.86665615737952</v>
+        <v>68.14082618474259</v>
       </c>
       <c r="G246" t="n">
         <v>18</v>
@@ -7080,16 +7080,16 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>-0.9944926704878307</v>
+        <v>-1.479274618399249</v>
       </c>
       <c r="D247" t="n">
-        <v>23.97780722714542</v>
+        <v>29.10081685526987</v>
       </c>
       <c r="E247" t="n">
-        <v>32.35840432740449</v>
+        <v>36.07723058412719</v>
       </c>
       <c r="F247" t="n">
-        <v>28.41517969029998</v>
+        <v>35.94429326865054</v>
       </c>
       <c r="G247" t="n">
         <v>89</v>
@@ -7107,16 +7107,16 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>-0.8461347973221263</v>
+        <v>-1.004918632069878</v>
       </c>
       <c r="D248" t="n">
-        <v>343.8564339069405</v>
+        <v>338.2327854657414</v>
       </c>
       <c r="E248" t="n">
-        <v>407.1732177123494</v>
+        <v>424.3223189340962</v>
       </c>
       <c r="F248" t="n">
-        <v>40.47680822037624</v>
+        <v>39.29693038920577</v>
       </c>
       <c r="G248" t="n">
         <v>99</v>
@@ -7134,16 +7134,16 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>0.1241995418458515</v>
+        <v>-0.3767138742861016</v>
       </c>
       <c r="D249" t="n">
-        <v>224.1393800140709</v>
+        <v>284.3496920677923</v>
       </c>
       <c r="E249" t="n">
-        <v>300.1100333436594</v>
+        <v>376.2701579026928</v>
       </c>
       <c r="F249" t="n">
-        <v>23.73855180606838</v>
+        <v>34.24229163326509</v>
       </c>
       <c r="G249" t="n">
         <v>93</v>
@@ -7161,16 +7161,16 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>-0.4601680876955685</v>
+        <v>-0.4373457706152415</v>
       </c>
       <c r="D250" t="n">
-        <v>7.754510610531538</v>
+        <v>7.824152821149582</v>
       </c>
       <c r="E250" t="n">
-        <v>10.53627017553216</v>
+        <v>10.45360533803377</v>
       </c>
       <c r="F250" t="n">
-        <v>71.42636776609274</v>
+        <v>75.47591483218629</v>
       </c>
       <c r="G250" t="n">
         <v>78</v>
@@ -7188,16 +7188,16 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>-2.993411534796583</v>
+        <v>-4.531400612859817</v>
       </c>
       <c r="D251" t="n">
-        <v>167.2479252285428</v>
+        <v>202.1124119228787</v>
       </c>
       <c r="E251" t="n">
-        <v>189.5145650781025</v>
+        <v>223.0427524587971</v>
       </c>
       <c r="F251" t="n">
-        <v>60.01930491810776</v>
+        <v>69.27364297296037</v>
       </c>
       <c r="G251" t="n">
         <v>18</v>
@@ -7215,16 +7215,16 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>-0.5756619345472715</v>
+        <v>-1.173840277578173</v>
       </c>
       <c r="D252" t="n">
-        <v>21.20046679893236</v>
+        <v>25.91668673311726</v>
       </c>
       <c r="E252" t="n">
-        <v>28.76089500465785</v>
+        <v>33.78194811935559</v>
       </c>
       <c r="F252" t="n">
-        <v>24.9184933972329</v>
+        <v>30.49651858711043</v>
       </c>
       <c r="G252" t="n">
         <v>89</v>
@@ -7242,16 +7242,16 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>-0.9527955821386083</v>
+        <v>-1.749194586162721</v>
       </c>
       <c r="D253" t="n">
-        <v>341.1968485514323</v>
+        <v>406.3593816275549</v>
       </c>
       <c r="E253" t="n">
-        <v>418.7703180904882</v>
+        <v>496.8785397459374</v>
       </c>
       <c r="F253" t="n">
-        <v>39.34696040147879</v>
+        <v>46.56763087733673</v>
       </c>
       <c r="G253" t="n">
         <v>99</v>
@@ -7269,16 +7269,16 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>0.2454368049754027</v>
+        <v>-1.060630369911157</v>
       </c>
       <c r="D254" t="n">
-        <v>191.0465875441028</v>
+        <v>402.7707847677252</v>
       </c>
       <c r="E254" t="n">
-        <v>278.5644811052236</v>
+        <v>460.3392217829875</v>
       </c>
       <c r="F254" t="n">
-        <v>20.5249961395885</v>
+        <v>50.49369202727573</v>
       </c>
       <c r="G254" t="n">
         <v>93</v>
@@ -7296,16 +7296,16 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>-0.3962070731308458</v>
+        <v>-0.5548105305339013</v>
       </c>
       <c r="D255" t="n">
-        <v>7.184881476255564</v>
+        <v>8.039755115142235</v>
       </c>
       <c r="E255" t="n">
-        <v>10.30292145714324</v>
+        <v>10.87236963218121</v>
       </c>
       <c r="F255" t="n">
-        <v>73.18370513871072</v>
+        <v>77.37490893288351</v>
       </c>
       <c r="G255" t="n">
         <v>78</v>
@@ -7323,16 +7323,16 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>-2.544499039991656</v>
+        <v>-2.578201656744629</v>
       </c>
       <c r="D256" t="n">
-        <v>154.864742702908</v>
+        <v>155.4479149712457</v>
       </c>
       <c r="E256" t="n">
-        <v>178.5451225122226</v>
+        <v>179.3919560531362</v>
       </c>
       <c r="F256" t="n">
-        <v>59.01242832046258</v>
+        <v>51.41695903766923</v>
       </c>
       <c r="G256" t="n">
         <v>18</v>
@@ -7350,16 +7350,16 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>-1.546113838407473</v>
+        <v>-1.404866518601901</v>
       </c>
       <c r="D257" t="n">
-        <v>27.25316639160842</v>
+        <v>27.42600213811639</v>
       </c>
       <c r="E257" t="n">
-        <v>36.56030277301873</v>
+        <v>35.53173079237041</v>
       </c>
       <c r="F257" t="n">
-        <v>31.98620910990679</v>
+        <v>32.79801818335552</v>
       </c>
       <c r="G257" t="n">
         <v>89</v>
@@ -7377,16 +7377,16 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>-1.066444515529898</v>
+        <v>-1.305782444316173</v>
       </c>
       <c r="D258" t="n">
-        <v>364.3880952777284</v>
+        <v>371.2568966643979</v>
       </c>
       <c r="E258" t="n">
-        <v>430.7838113427497</v>
+        <v>455.0474280220695</v>
       </c>
       <c r="F258" t="n">
-        <v>42.5565617309613</v>
+        <v>42.44698660470722</v>
       </c>
       <c r="G258" t="n">
         <v>99</v>
@@ -7404,16 +7404,16 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>-0.4512318692432173</v>
+        <v>0.1329542598896151</v>
       </c>
       <c r="D259" t="n">
-        <v>293.5815672515541</v>
+        <v>208.3983521820396</v>
       </c>
       <c r="E259" t="n">
-        <v>386.3192369324878</v>
+        <v>298.6062788608312</v>
       </c>
       <c r="F259" t="n">
-        <v>31.06487361597929</v>
+        <v>20.58203139151582</v>
       </c>
       <c r="G259" t="n">
         <v>93</v>
@@ -7431,16 +7431,16 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>-0.3904205201193249</v>
+        <v>-0.4999673209292852</v>
       </c>
       <c r="D260" t="n">
-        <v>7.566052586604387</v>
+        <v>8.011011469058502</v>
       </c>
       <c r="E260" t="n">
-        <v>10.28154916126466</v>
+        <v>10.67889634043821</v>
       </c>
       <c r="F260" t="n">
-        <v>70.52758884046135</v>
+        <v>75.97610601853879</v>
       </c>
       <c r="G260" t="n">
         <v>78</v>
@@ -7458,16 +7458,16 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>-4.881480331302187</v>
+        <v>-5.166385571269354</v>
       </c>
       <c r="D261" t="n">
-        <v>209.8775520324707</v>
+        <v>215.6625985039605</v>
       </c>
       <c r="E261" t="n">
-        <v>229.9926110064288</v>
+        <v>235.4972811533491</v>
       </c>
       <c r="F261" t="n">
-        <v>73.31169548587606</v>
+        <v>74.71851153913242</v>
       </c>
       <c r="G261" t="n">
         <v>18</v>
@@ -7485,16 +7485,16 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>-1.811620809150287</v>
+        <v>-1.348833618479677</v>
       </c>
       <c r="D262" t="n">
-        <v>28.68460466620627</v>
+        <v>26.85797747065512</v>
       </c>
       <c r="E262" t="n">
-        <v>38.41928245906006</v>
+        <v>35.11535005530283</v>
       </c>
       <c r="F262" t="n">
-        <v>33.57867809784063</v>
+        <v>32.39378287967574</v>
       </c>
       <c r="G262" t="n">
         <v>89</v>
@@ -7512,16 +7512,16 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>-1.136401551030715</v>
+        <v>-0.9609618524672632</v>
       </c>
       <c r="D263" t="n">
-        <v>372.923748748471</v>
+        <v>336.9483107749862</v>
       </c>
       <c r="E263" t="n">
-        <v>438.0149585051894</v>
+        <v>419.6450189190776</v>
       </c>
       <c r="F263" t="n">
-        <v>44.21335803843869</v>
+        <v>38.55156848568426</v>
       </c>
       <c r="G263" t="n">
         <v>99</v>
@@ -7539,16 +7539,16 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>-0.1610467976049847</v>
+        <v>-0.0437347742342824</v>
       </c>
       <c r="D264" t="n">
-        <v>263.604492843792</v>
+        <v>225.4765401860719</v>
       </c>
       <c r="E264" t="n">
-        <v>345.5435522311388</v>
+        <v>327.6219626291866</v>
       </c>
       <c r="F264" t="n">
-        <v>27.10989966365229</v>
+        <v>23.56923552516053</v>
       </c>
       <c r="G264" t="n">
         <v>93</v>
@@ -7566,16 +7566,16 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>-0.3893056071107894</v>
+        <v>-0.4258005892926617</v>
       </c>
       <c r="D265" t="n">
-        <v>7.571754553379157</v>
+        <v>7.908362345817761</v>
       </c>
       <c r="E265" t="n">
-        <v>10.27742618854498</v>
+        <v>10.41153748572022</v>
       </c>
       <c r="F265" t="n">
-        <v>70.96723895373285</v>
+        <v>77.6668832992615</v>
       </c>
       <c r="G265" t="n">
         <v>78</v>
@@ -7593,16 +7593,16 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>-6.01993820448623</v>
+        <v>-5.477058782013901</v>
       </c>
       <c r="D266" t="n">
-        <v>233.5326068666246</v>
+        <v>222.1002368927002</v>
       </c>
       <c r="E266" t="n">
-        <v>251.2680119942676</v>
+        <v>241.3567662085897</v>
       </c>
       <c r="F266" t="n">
-        <v>83.32980415823155</v>
+        <v>78.19560741140185</v>
       </c>
       <c r="G266" t="n">
         <v>18</v>
@@ -7620,16 +7620,16 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>-1.614327561525045</v>
+        <v>-1.062538822243805</v>
       </c>
       <c r="D267" t="n">
-        <v>27.92833079648821</v>
+        <v>25.29296358515707</v>
       </c>
       <c r="E267" t="n">
-        <v>37.04681492457851</v>
+        <v>32.90576114311657</v>
       </c>
       <c r="F267" t="n">
-        <v>33.40563701161418</v>
+        <v>30.87127650149488</v>
       </c>
       <c r="G267" t="n">
         <v>89</v>
@@ -7647,16 +7647,16 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>-1.250241794976319</v>
+        <v>-0.8417049521010016</v>
       </c>
       <c r="D268" t="n">
-        <v>385.1331483474885</v>
+        <v>321.1523892181088</v>
       </c>
       <c r="E268" t="n">
-        <v>449.5335327889837</v>
+        <v>406.6844133061239</v>
       </c>
       <c r="F268" t="n">
-        <v>45.45839542866296</v>
+        <v>38.30790183700496</v>
       </c>
       <c r="G268" t="n">
         <v>99</v>
@@ -7674,16 +7674,16 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>0.002451931589871892</v>
+        <v>-0.1330689767557518</v>
       </c>
       <c r="D269" t="n">
-        <v>250.4412979618195</v>
+        <v>248.528324250252</v>
       </c>
       <c r="E269" t="n">
-        <v>320.2910823644029</v>
+        <v>341.3548718068078</v>
       </c>
       <c r="F269" t="n">
-        <v>25.26336708901933</v>
+        <v>29.45168967684375</v>
       </c>
       <c r="G269" t="n">
         <v>93</v>
@@ -7701,16 +7701,16 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>-0.3517134720077819</v>
+        <v>-0.3549022635977639</v>
       </c>
       <c r="D270" t="n">
-        <v>7.158053089410831</v>
+        <v>7.284344086280236</v>
       </c>
       <c r="E270" t="n">
-        <v>10.13742824717811</v>
+        <v>10.14937867310893</v>
       </c>
       <c r="F270" t="n">
-        <v>73.76433889709148</v>
+        <v>71.79342031297065</v>
       </c>
       <c r="G270" t="n">
         <v>78</v>
@@ -7728,16 +7728,16 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>-5.58022254252251</v>
+        <v>-5.046203355513168</v>
       </c>
       <c r="D271" t="n">
-        <v>224.7889120313856</v>
+        <v>214.2656497955322</v>
       </c>
       <c r="E271" t="n">
-        <v>243.2712854439308</v>
+        <v>233.1910801546183</v>
       </c>
       <c r="F271" t="n">
-        <v>79.38481548723965</v>
+        <v>75.24543279446294</v>
       </c>
       <c r="G271" t="n">
         <v>18</v>
@@ -7755,16 +7755,16 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>-0.6978165904788969</v>
+        <v>-0.7245668318634335</v>
       </c>
       <c r="D272" t="n">
-        <v>20.19339023547226</v>
+        <v>21.71481483973814</v>
       </c>
       <c r="E272" t="n">
-        <v>29.85494404312423</v>
+        <v>30.089217220264</v>
       </c>
       <c r="F272" t="n">
-        <v>24.57428322174631</v>
+        <v>26.39620429645159</v>
       </c>
       <c r="G272" t="n">
         <v>89</v>
@@ -7782,16 +7782,16 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>-0.5901883381512407</v>
+        <v>-0.5670799915687996</v>
       </c>
       <c r="D273" t="n">
-        <v>295.1535807908184</v>
+        <v>287.2273448597301</v>
       </c>
       <c r="E273" t="n">
-        <v>377.8955536456612</v>
+        <v>375.1397483133298</v>
       </c>
       <c r="F273" t="n">
-        <v>35.89158180155784</v>
+        <v>33.94208988173621</v>
       </c>
       <c r="G273" t="n">
         <v>99</v>
@@ -7809,16 +7809,16 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>-0.5067553165957035</v>
+        <v>-0.5598129197997315</v>
       </c>
       <c r="D274" t="n">
-        <v>279.5849012149278</v>
+        <v>278.8616838352655</v>
       </c>
       <c r="E274" t="n">
-        <v>393.6400672660482</v>
+        <v>400.5107595330105</v>
       </c>
       <c r="F274" t="n">
-        <v>27.25282243791903</v>
+        <v>26.66119750166183</v>
       </c>
       <c r="G274" t="n">
         <v>93</v>
@@ -7836,16 +7836,16 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>-0.4521020916746499</v>
+        <v>-0.4526558816222486</v>
       </c>
       <c r="D275" t="n">
-        <v>7.068349321683248</v>
+        <v>7.05973923817659</v>
       </c>
       <c r="E275" t="n">
-        <v>10.50712859768566</v>
+        <v>10.50913196492804</v>
       </c>
       <c r="F275" t="n">
-        <v>67.42944773093799</v>
+        <v>65.03655407177452</v>
       </c>
       <c r="G275" t="n">
         <v>78</v>
@@ -7863,16 +7863,16 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>-6.879054722515255</v>
+        <v>-7.094142708071995</v>
       </c>
       <c r="D276" t="n">
-        <v>250.6251353157891</v>
+        <v>253.3656511306763</v>
       </c>
       <c r="E276" t="n">
-        <v>266.1997342163991</v>
+        <v>269.8087237920088</v>
       </c>
       <c r="F276" t="n">
-        <v>91.73624560122585</v>
+        <v>92.11425295984293</v>
       </c>
       <c r="G276" t="n">
         <v>18</v>
@@ -7890,16 +7890,16 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>-0.6833477861098347</v>
+        <v>-0.9801371403985848</v>
       </c>
       <c r="D277" t="n">
-        <v>20.29329604245304</v>
+        <v>23.33493787786934</v>
       </c>
       <c r="E277" t="n">
-        <v>29.72745984001488</v>
+        <v>32.24174284884008</v>
       </c>
       <c r="F277" t="n">
-        <v>25.03062096284989</v>
+        <v>28.29100660461934</v>
       </c>
       <c r="G277" t="n">
         <v>89</v>
@@ -7917,16 +7917,16 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>-0.7773229613792982</v>
+        <v>-0.8003722133600231</v>
       </c>
       <c r="D278" t="n">
-        <v>320.7682078968395</v>
+        <v>316.2520563915522</v>
       </c>
       <c r="E278" t="n">
-        <v>399.5127792732802</v>
+        <v>402.0949795507859</v>
       </c>
       <c r="F278" t="n">
-        <v>38.71089221142047</v>
+        <v>37.18786403466713</v>
       </c>
       <c r="G278" t="n">
         <v>99</v>
@@ -7944,16 +7944,16 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>-0.5415570061269463</v>
+        <v>-0.6565230967997862</v>
       </c>
       <c r="D279" t="n">
-        <v>277.2802183089718</v>
+        <v>276.8389679283224</v>
       </c>
       <c r="E279" t="n">
-        <v>398.1600898721044</v>
+        <v>412.740113130786</v>
       </c>
       <c r="F279" t="n">
-        <v>26.97212292129539</v>
+        <v>26.09825698389173</v>
       </c>
       <c r="G279" t="n">
         <v>93</v>
@@ -7971,16 +7971,16 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>-0.4095727776080509</v>
+        <v>-0.4381901748074502</v>
       </c>
       <c r="D280" t="n">
-        <v>6.834444868258941</v>
+        <v>7.007214537033668</v>
       </c>
       <c r="E280" t="n">
-        <v>10.35211824689637</v>
+        <v>10.45667550121668</v>
       </c>
       <c r="F280" t="n">
-        <v>68.82040150034437</v>
+        <v>64.64948528203615</v>
       </c>
       <c r="G280" t="n">
         <v>78</v>
@@ -7998,16 +7998,16 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>-7.017389125041287</v>
+        <v>-7.133027768163172</v>
       </c>
       <c r="D281" t="n">
-        <v>251.7242404090034</v>
+        <v>253.5720478693644</v>
       </c>
       <c r="E281" t="n">
-        <v>268.5264314904143</v>
+        <v>270.456041142836</v>
       </c>
       <c r="F281" t="n">
-        <v>91.519061178432</v>
+        <v>91.98980734803227</v>
       </c>
       <c r="G281" t="n">
         <v>18</v>
@@ -8025,16 +8025,16 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>-0.4762245283331823</v>
+        <v>-0.5537336176365171</v>
       </c>
       <c r="D282" t="n">
-        <v>20.14552566442597</v>
+        <v>20.54246163100339</v>
       </c>
       <c r="E282" t="n">
-        <v>27.83858030111018</v>
+        <v>28.56006268183801</v>
       </c>
       <c r="F282" t="n">
-        <v>25.49209178948691</v>
+        <v>25.6883907140482</v>
       </c>
       <c r="G282" t="n">
         <v>89</v>
@@ -8052,16 +8052,16 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>-0.320313917867973</v>
+        <v>-0.366173748294119</v>
       </c>
       <c r="D283" t="n">
-        <v>279.6460113525391</v>
+        <v>286.5529214878275</v>
       </c>
       <c r="E283" t="n">
-        <v>344.3389101608722</v>
+        <v>350.2680042493372</v>
       </c>
       <c r="F283" t="n">
-        <v>36.35966993886088</v>
+        <v>37.62905778532713</v>
       </c>
       <c r="G283" t="n">
         <v>99</v>
@@ -8079,16 +8079,16 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>-0.3780099409643636</v>
+        <v>-0.3805394272062506</v>
       </c>
       <c r="D284" t="n">
-        <v>295.0229846585182</v>
+        <v>291.7579037245883</v>
       </c>
       <c r="E284" t="n">
-        <v>376.4472304596206</v>
+        <v>376.7925768492702</v>
       </c>
       <c r="F284" t="n">
-        <v>29.89739900766882</v>
+        <v>29.39104227193242</v>
       </c>
       <c r="G284" t="n">
         <v>93</v>
@@ -8106,16 +8106,16 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>-0.5678760891054653</v>
+        <v>-0.5623737711560339</v>
       </c>
       <c r="D285" t="n">
-        <v>7.323732859049088</v>
+        <v>7.313107010645744</v>
       </c>
       <c r="E285" t="n">
-        <v>10.91795602250162</v>
+        <v>10.89878140002665</v>
       </c>
       <c r="F285" t="n">
-        <v>72.50955254076969</v>
+        <v>71.11649069091051</v>
       </c>
       <c r="G285" t="n">
         <v>78</v>
@@ -8133,16 +8133,16 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>-6.613427158340776</v>
+        <v>-6.659385147218567</v>
       </c>
       <c r="D286" t="n">
-        <v>246.8864279852973</v>
+        <v>247.1716629664103</v>
       </c>
       <c r="E286" t="n">
-        <v>261.6740508782308</v>
+        <v>262.4626523100807</v>
       </c>
       <c r="F286" t="n">
-        <v>90.82907286545959</v>
+        <v>90.56991846591377</v>
       </c>
       <c r="G286" t="n">
         <v>18</v>
@@ -8160,16 +8160,16 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>-0.5809219222440289</v>
+        <v>-0.5021535455839283</v>
       </c>
       <c r="D287" t="n">
-        <v>20.99253474460559</v>
+        <v>20.47346194406574</v>
       </c>
       <c r="E287" t="n">
-        <v>28.80886084865924</v>
+        <v>28.08200023230058</v>
       </c>
       <c r="F287" t="n">
-        <v>26.15618995801447</v>
+        <v>25.59239223333319</v>
       </c>
       <c r="G287" t="n">
         <v>89</v>
@@ -8187,16 +8187,16 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>-0.3272407578500083</v>
+        <v>-0.5474763420117186</v>
       </c>
       <c r="D288" t="n">
-        <v>280.4221709280303</v>
+        <v>306.0283013546106</v>
       </c>
       <c r="E288" t="n">
-        <v>345.2409912112795</v>
+        <v>372.785927016937</v>
       </c>
       <c r="F288" t="n">
-        <v>36.50249454269719</v>
+        <v>39.6915077959551</v>
       </c>
       <c r="G288" t="n">
         <v>99</v>
@@ -8214,16 +8214,16 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>-0.3690693258325817</v>
+        <v>-0.2657205061686603</v>
       </c>
       <c r="D289" t="n">
-        <v>293.4228128412718</v>
+        <v>283.3550526608703</v>
       </c>
       <c r="E289" t="n">
-        <v>375.2240365420982</v>
+        <v>360.7836427243927</v>
       </c>
       <c r="F289" t="n">
-        <v>29.84675666642331</v>
+        <v>28.4610359065537</v>
       </c>
       <c r="G289" t="n">
         <v>93</v>
@@ -8241,16 +8241,16 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>-0.5918725327318344</v>
+        <v>-0.5555531363265231</v>
       </c>
       <c r="D290" t="n">
-        <v>7.364927398852813</v>
+        <v>7.253400833178789</v>
       </c>
       <c r="E290" t="n">
-        <v>11.00118876812341</v>
+        <v>10.87496574298746</v>
       </c>
       <c r="F290" t="n">
-        <v>71.70997838903642</v>
+        <v>70.94009619255611</v>
       </c>
       <c r="G290" t="n">
         <v>78</v>
@@ -8268,16 +8268,16 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>-6.71349170903616</v>
+        <v>-6.636358663693772</v>
       </c>
       <c r="D291" t="n">
-        <v>248.3103527492947</v>
+        <v>247.0018249087863</v>
       </c>
       <c r="E291" t="n">
-        <v>263.3880503970113</v>
+        <v>262.0678333467586</v>
       </c>
       <c r="F291" t="n">
-        <v>90.98328656762362</v>
+        <v>90.60150222516583</v>
       </c>
       <c r="G291" t="n">
         <v>18</v>
@@ -8295,16 +8295,16 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>-0.5587826993497995</v>
+        <v>-0.5994280143709345</v>
       </c>
       <c r="D292" t="n">
-        <v>20.81559528393692</v>
+        <v>20.92498337820675</v>
       </c>
       <c r="E292" t="n">
-        <v>28.6064300665583</v>
+        <v>28.97698688754483</v>
       </c>
       <c r="F292" t="n">
-        <v>26.16487934741536</v>
+        <v>25.78201965039486</v>
       </c>
       <c r="G292" t="n">
         <v>89</v>
@@ -8322,16 +8322,16 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>-0.4270298069084506</v>
+        <v>-0.5498977791477555</v>
       </c>
       <c r="D293" t="n">
-        <v>283.5729092684659</v>
+        <v>301.0952962239583</v>
       </c>
       <c r="E293" t="n">
-        <v>357.9843344535138</v>
+        <v>373.077474234597</v>
       </c>
       <c r="F293" t="n">
-        <v>34.09127799725024</v>
+        <v>36.21184919178158</v>
       </c>
       <c r="G293" t="n">
         <v>99</v>
@@ -8349,16 +8349,16 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>-0.293677849349645</v>
+        <v>0.101215820068993</v>
       </c>
       <c r="D294" t="n">
-        <v>263.2908223470052</v>
+        <v>237.4432665096816</v>
       </c>
       <c r="E294" t="n">
-        <v>364.7463899018653</v>
+        <v>304.0224404318058</v>
       </c>
       <c r="F294" t="n">
-        <v>25.63279552883719</v>
+        <v>23.26905503759552</v>
       </c>
       <c r="G294" t="n">
         <v>93</v>
@@ -8376,16 +8376,16 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>-0.4523569703823236</v>
+        <v>-0.5381244266172787</v>
       </c>
       <c r="D295" t="n">
-        <v>6.990892061820397</v>
+        <v>7.347975199039166</v>
       </c>
       <c r="E295" t="n">
-        <v>10.5080506836288</v>
+        <v>10.81387155317032</v>
       </c>
       <c r="F295" t="n">
-        <v>63.88364267749424</v>
+        <v>68.87216671172773</v>
       </c>
       <c r="G295" t="n">
         <v>78</v>
@@ -8403,16 +8403,16 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>-6.931726760930554</v>
+        <v>-6.73166429383926</v>
       </c>
       <c r="D296" t="n">
-        <v>250.9922940995958</v>
+        <v>246.7997284995185</v>
       </c>
       <c r="E296" t="n">
-        <v>267.0880341333346</v>
+        <v>263.6981321360326</v>
       </c>
       <c r="F296" t="n">
-        <v>91.27475923462049</v>
+        <v>89.41077061534482</v>
       </c>
       <c r="G296" t="n">
         <v>18</v>
@@ -8430,16 +8430,16 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>-1.131068228164587</v>
+        <v>-1.59136912401529</v>
       </c>
       <c r="D297" t="n">
-        <v>24.48109262445</v>
+        <v>27.45272002059422</v>
       </c>
       <c r="E297" t="n">
-        <v>33.44795360529827</v>
+        <v>36.88378781417818</v>
       </c>
       <c r="F297" t="n">
-        <v>29.30966611255386</v>
+        <v>31.96424414078532</v>
       </c>
       <c r="G297" t="n">
         <v>89</v>
@@ -8457,16 +8457,16 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>-1.666140128363025</v>
+        <v>-3.355810503376864</v>
       </c>
       <c r="D298" t="n">
-        <v>406.1776294130268</v>
+        <v>555.8388237230705</v>
       </c>
       <c r="E298" t="n">
-        <v>489.315514197137</v>
+        <v>625.4347229893536</v>
       </c>
       <c r="F298" t="n">
-        <v>46.42830657359046</v>
+        <v>67.38667982635826</v>
       </c>
       <c r="G298" t="n">
         <v>99</v>
@@ -8484,16 +8484,16 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>-0.03659489916680614</v>
+        <v>0.06644789258549544</v>
       </c>
       <c r="D299" t="n">
-        <v>218.2092114520329</v>
+        <v>246.1549833564348</v>
       </c>
       <c r="E299" t="n">
-        <v>326.4994580963705</v>
+        <v>309.8469410152019</v>
       </c>
       <c r="F299" t="n">
-        <v>20.11624695882148</v>
+        <v>29.98598722150887</v>
       </c>
       <c r="G299" t="n">
         <v>93</v>
@@ -8511,16 +8511,16 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>-0.5942694301826654</v>
+        <v>-0.8028907166689636</v>
       </c>
       <c r="D300" t="n">
-        <v>7.87262369119204</v>
+        <v>8.4611819371199</v>
       </c>
       <c r="E300" t="n">
-        <v>11.00946794950579</v>
+        <v>11.70766193359035</v>
       </c>
       <c r="F300" t="n">
-        <v>71.2883139840193</v>
+        <v>73.06062065356915</v>
       </c>
       <c r="G300" t="n">
         <v>78</v>
@@ -8538,16 +8538,16 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>-7.442564495645307</v>
+        <v>-7.318117901366197</v>
       </c>
       <c r="D301" t="n">
-        <v>258.8731240166558</v>
+        <v>257.1924441655477</v>
       </c>
       <c r="E301" t="n">
-        <v>275.5546553791785</v>
+        <v>273.5162257577184</v>
       </c>
       <c r="F301" t="n">
-        <v>94.3238724370124</v>
+        <v>93.69754619242075</v>
       </c>
       <c r="G301" t="n">
         <v>18</v>
@@ -8565,16 +8565,16 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>-0.5997879075117767</v>
+        <v>-1.922464412147399</v>
       </c>
       <c r="D302" t="n">
-        <v>22.64814145377513</v>
+        <v>31.39157830999139</v>
       </c>
       <c r="E302" t="n">
-        <v>28.98024681301506</v>
+        <v>39.16927117318113</v>
       </c>
       <c r="F302" t="n">
-        <v>29.5082680546673</v>
+        <v>47.31085597302599</v>
       </c>
       <c r="G302" t="n">
         <v>89</v>
@@ -8592,16 +8592,16 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>-1.669153869157633</v>
+        <v>-0.2887877266101353</v>
       </c>
       <c r="D303" t="n">
-        <v>429.1417524549696</v>
+        <v>276.543114093819</v>
       </c>
       <c r="E303" t="n">
-        <v>489.5919913435041</v>
+        <v>340.2030443911871</v>
       </c>
       <c r="F303" t="n">
-        <v>54.13277982531183</v>
+        <v>53.97241403636693</v>
       </c>
       <c r="G303" t="n">
         <v>99</v>
@@ -8619,16 +8619,16 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>-5.682720788752633</v>
+        <v>-1.664768729589909</v>
       </c>
       <c r="D304" t="n">
-        <v>747.3819606329805</v>
+        <v>441.2389900453629</v>
       </c>
       <c r="E304" t="n">
-        <v>829.0001119108841</v>
+        <v>523.4891596107491</v>
       </c>
       <c r="F304" t="n">
-        <v>94.27195730647131</v>
+        <v>54.78038751335404</v>
       </c>
       <c r="G304" t="n">
         <v>93</v>
@@ -8646,16 +8646,16 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>-0.2021112338991005</v>
+        <v>-0.8355010264646996</v>
       </c>
       <c r="D305" t="n">
-        <v>7.224334343885764</v>
+        <v>8.658914080032936</v>
       </c>
       <c r="E305" t="n">
-        <v>9.559997969104355</v>
+        <v>11.81307028750553</v>
       </c>
       <c r="F305" t="n">
-        <v>69.95402119960252</v>
+        <v>72.621963315814</v>
       </c>
       <c r="G305" t="n">
         <v>78</v>
@@ -8673,16 +8673,16 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>-3.30922749313712</v>
+        <v>-9.739168381038176</v>
       </c>
       <c r="D306" t="n">
-        <v>179.7172414991591</v>
+        <v>292.464227464464</v>
       </c>
       <c r="E306" t="n">
-        <v>196.8657973332948</v>
+        <v>310.7820199024409</v>
       </c>
       <c r="F306" t="n">
-        <v>67.15584474977908</v>
+        <v>106.3310556974009</v>
       </c>
       <c r="G306" t="n">
         <v>18</v>
@@ -8700,16 +8700,16 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>-0.91369586832426</v>
+        <v>-0.9399259287378792</v>
       </c>
       <c r="D307" t="n">
-        <v>24.30345473128758</v>
+        <v>23.86611730596992</v>
       </c>
       <c r="E307" t="n">
-        <v>31.69620992985441</v>
+        <v>31.91269260115178</v>
       </c>
       <c r="F307" t="n">
-        <v>29.67675216076159</v>
+        <v>29.32095747406085</v>
       </c>
       <c r="G307" t="n">
         <v>89</v>
@@ -8727,16 +8727,16 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>-0.7745543445182861</v>
+        <v>0.2023859790171801</v>
       </c>
       <c r="D308" t="n">
-        <v>331.6836480034722</v>
+        <v>197.7307555844085</v>
       </c>
       <c r="E308" t="n">
-        <v>399.2014883791976</v>
+        <v>267.6356051765399</v>
       </c>
       <c r="F308" t="n">
-        <v>38.75648826123103</v>
+        <v>25.68009528229366</v>
       </c>
       <c r="G308" t="n">
         <v>99</v>
@@ -8754,16 +8754,16 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>0.05014812635868082</v>
+        <v>-4.401752733710092</v>
       </c>
       <c r="D309" t="n">
-        <v>252.8082728232107</v>
+        <v>702.5317724084341</v>
       </c>
       <c r="E309" t="n">
-        <v>312.5401907954745</v>
+        <v>745.3243006712632</v>
       </c>
       <c r="F309" t="n">
-        <v>32.65299319056529</v>
+        <v>83.68737632035212</v>
       </c>
       <c r="G309" t="n">
         <v>93</v>
@@ -8781,16 +8781,16 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>-0.559846550020821</v>
+        <v>-0.4610347634041423</v>
       </c>
       <c r="D310" t="n">
-        <v>7.520713002253801</v>
+        <v>7.583043923744788</v>
       </c>
       <c r="E310" t="n">
-        <v>10.88996315866099</v>
+        <v>10.5393965877943</v>
       </c>
       <c r="F310" t="n">
-        <v>68.21156528311364</v>
+        <v>75.77768586905057</v>
       </c>
       <c r="G310" t="n">
         <v>78</v>
@@ -8808,16 +8808,16 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>-3.257454049614479</v>
+        <v>-3.538574539670187</v>
       </c>
       <c r="D311" t="n">
-        <v>176.9429846869575</v>
+        <v>178.408040576511</v>
       </c>
       <c r="E311" t="n">
-        <v>195.6795963376719</v>
+        <v>202.0367135383169</v>
       </c>
       <c r="F311" t="n">
-        <v>61.41739536846465</v>
+        <v>60.64952819477565</v>
       </c>
       <c r="G311" t="n">
         <v>18</v>
@@ -8835,16 +8835,16 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>-1.239868651384722</v>
+        <v>-1.179520416874973</v>
       </c>
       <c r="D312" t="n">
-        <v>26.62653284394339</v>
+        <v>25.34562149476469</v>
       </c>
       <c r="E312" t="n">
-        <v>34.29115795541059</v>
+        <v>33.82605462276179</v>
       </c>
       <c r="F312" t="n">
-        <v>31.63041585932758</v>
+        <v>29.66046468510928</v>
       </c>
       <c r="G312" t="n">
         <v>89</v>
@@ -8862,16 +8862,16 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>-1.504163146261459</v>
+        <v>-0.3303834791521283</v>
       </c>
       <c r="D313" t="n">
-        <v>400.6291553227588</v>
+        <v>281.4249429413767</v>
       </c>
       <c r="E313" t="n">
-        <v>474.218846478684</v>
+        <v>345.6494908336472</v>
       </c>
       <c r="F313" t="n">
-        <v>46.78518437236985</v>
+        <v>33.93588561825722</v>
       </c>
       <c r="G313" t="n">
         <v>99</v>
@@ -8889,16 +8889,16 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>-1.139196257550506</v>
+        <v>-12.44161726375941</v>
       </c>
       <c r="D314" t="n">
-        <v>410.156015047463</v>
+        <v>1118.126281081989</v>
       </c>
       <c r="E314" t="n">
-        <v>469.0328341840745</v>
+        <v>1175.71942517315</v>
       </c>
       <c r="F314" t="n">
-        <v>53.20235739249814</v>
+        <v>137.5466167814023</v>
       </c>
       <c r="G314" t="n">
         <v>93</v>
@@ -8916,16 +8916,16 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>-0.4898519360947875</v>
+        <v>-1.2950474824231</v>
       </c>
       <c r="D315" t="n">
-        <v>7.376897243353037</v>
+        <v>10.01498823899489</v>
       </c>
       <c r="E315" t="n">
-        <v>10.64282759487298</v>
+        <v>13.20934580732404</v>
       </c>
       <c r="F315" t="n">
-        <v>67.69173912738438</v>
+        <v>68.89307518112932</v>
       </c>
       <c r="G315" t="n">
         <v>78</v>
@@ -8943,16 +8943,16 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>-2.188310132886189</v>
+        <v>-2.463329760257188</v>
       </c>
       <c r="D316" t="n">
-        <v>146.3561871846517</v>
+        <v>153.2469359503852</v>
       </c>
       <c r="E316" t="n">
-        <v>169.3366012572951</v>
+        <v>176.4889346313495</v>
       </c>
       <c r="F316" t="n">
-        <v>51.7490773608361</v>
+        <v>54.93233431421815</v>
       </c>
       <c r="G316" t="n">
         <v>18</v>
@@ -8970,16 +8970,16 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>-1.920610602419873</v>
+        <v>-0.8006065110842515</v>
       </c>
       <c r="D317" t="n">
-        <v>31.89668389652552</v>
+        <v>22.35375899411319</v>
       </c>
       <c r="E317" t="n">
-        <v>39.1568460612888</v>
+        <v>30.74540959271259</v>
       </c>
       <c r="F317" t="n">
-        <v>38.6078617247083</v>
+        <v>27.72318374425111</v>
       </c>
       <c r="G317" t="n">
         <v>89</v>
@@ -8997,16 +8997,16 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>-1.189173660839657</v>
+        <v>-0.62734849586384</v>
       </c>
       <c r="D318" t="n">
-        <v>378.6781536063763</v>
+        <v>318.1465902617483</v>
       </c>
       <c r="E318" t="n">
-        <v>443.391748894932</v>
+        <v>382.2854627534187</v>
       </c>
       <c r="F318" t="n">
-        <v>45.17657939218682</v>
+        <v>37.78826894988935</v>
       </c>
       <c r="G318" t="n">
         <v>99</v>
@@ -9024,16 +9024,16 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>-0.007213139628941212</v>
+        <v>0.133442862958603</v>
       </c>
       <c r="D319" t="n">
-        <v>269.4705672725555</v>
+        <v>248.9875055128528</v>
       </c>
       <c r="E319" t="n">
-        <v>321.8389646443138</v>
+        <v>298.5221307600291</v>
       </c>
       <c r="F319" t="n">
-        <v>30.98411710368008</v>
+        <v>29.17868147786507</v>
       </c>
       <c r="G319" t="n">
         <v>93</v>
@@ -9051,16 +9051,16 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>-0.3276131207120623</v>
+        <v>-0.3096603029377447</v>
       </c>
       <c r="D320" t="n">
-        <v>7.029819580224844</v>
+        <v>7.787125776975583</v>
       </c>
       <c r="E320" t="n">
-        <v>10.04664924337879</v>
+        <v>9.978489486358765</v>
       </c>
       <c r="F320" t="n">
-        <v>69.64909026834609</v>
+        <v>128.970521400037</v>
       </c>
       <c r="G320" t="n">
         <v>78</v>
@@ -9078,16 +9078,16 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>-1.806102004229778</v>
+        <v>-1.033513064943824</v>
       </c>
       <c r="D321" t="n">
-        <v>129.8733020358615</v>
+        <v>109.1487528483073</v>
       </c>
       <c r="E321" t="n">
-        <v>158.8628267991436</v>
+        <v>135.2365374248067</v>
       </c>
       <c r="F321" t="n">
-        <v>45.98890361237795</v>
+        <v>40.60587721877004</v>
       </c>
       <c r="G321" t="n">
         <v>18</v>
@@ -9105,16 +9105,16 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>-1.650291919911844</v>
+        <v>-0.1312036458147339</v>
       </c>
       <c r="D322" t="n">
-        <v>30.58229604999671</v>
+        <v>18.33314439152064</v>
       </c>
       <c r="E322" t="n">
-        <v>37.30076434976645</v>
+        <v>24.36920004638205</v>
       </c>
       <c r="F322" t="n">
-        <v>36.98362419983516</v>
+        <v>24.90799450779089</v>
       </c>
       <c r="G322" t="n">
         <v>89</v>
@@ -9132,16 +9132,16 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>-1.201433793133569</v>
+        <v>-0.2329392495281248</v>
       </c>
       <c r="D323" t="n">
-        <v>367.0531861276338</v>
+        <v>264.4947949033795</v>
       </c>
       <c r="E323" t="n">
-        <v>444.6315892749886</v>
+        <v>332.7502105875989</v>
       </c>
       <c r="F323" t="n">
-        <v>42.39254867572663</v>
+        <v>31.05719753703102</v>
       </c>
       <c r="G323" t="n">
         <v>99</v>
@@ -9159,16 +9159,16 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>-0.1654214623506094</v>
+        <v>0.2823264276856096</v>
       </c>
       <c r="D324" t="n">
-        <v>265.8633783812164</v>
+        <v>201.425786500336</v>
       </c>
       <c r="E324" t="n">
-        <v>346.1939204872216</v>
+        <v>271.6698281808385</v>
       </c>
       <c r="F324" t="n">
-        <v>32.2829003732928</v>
+        <v>20.57099598191811</v>
       </c>
       <c r="G324" t="n">
         <v>93</v>
@@ -9186,16 +9186,16 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>-0.6711072610774125</v>
+        <v>-1.059407602879726</v>
       </c>
       <c r="D325" t="n">
-        <v>8.257120175239367</v>
+        <v>9.300091911584904</v>
       </c>
       <c r="E325" t="n">
-        <v>11.27165364411673</v>
+        <v>12.51286122535322</v>
       </c>
       <c r="F325" t="n">
-        <v>75.28851017964084</v>
+        <v>67.30082023991049</v>
       </c>
       <c r="G325" t="n">
         <v>78</v>
@@ -9213,16 +9213,16 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>-3.008615174371539</v>
+        <v>-5.221682602982495</v>
       </c>
       <c r="D326" t="n">
-        <v>159.8629586961534</v>
+        <v>215.7528122795953</v>
       </c>
       <c r="E326" t="n">
-        <v>189.8749804656143</v>
+        <v>236.5508348349391</v>
       </c>
       <c r="F326" t="n">
-        <v>54.21421023235199</v>
+        <v>76.17694594764187</v>
       </c>
       <c r="G326" t="n">
         <v>18</v>
@@ -9240,16 +9240,16 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>-0.8706842047778061</v>
+        <v>-1.92451631924865</v>
       </c>
       <c r="D327" t="n">
-        <v>23.50251607144817</v>
+        <v>31.7388562406047</v>
       </c>
       <c r="E327" t="n">
-        <v>31.33798834043756</v>
+        <v>39.1830194335082</v>
       </c>
       <c r="F327" t="n">
-        <v>28.29469554484053</v>
+        <v>38.41612005221312</v>
       </c>
       <c r="G327" t="n">
         <v>89</v>
@@ -9267,16 +9267,16 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>-1.851201626413469</v>
+        <v>-2.452693202936123</v>
       </c>
       <c r="D328" t="n">
-        <v>456.498829080601</v>
+        <v>499.5785149468316</v>
       </c>
       <c r="E328" t="n">
-        <v>506.0127558966839</v>
+        <v>556.834961114428</v>
       </c>
       <c r="F328" t="n">
-        <v>58.67322018991333</v>
+        <v>61.7878578547507</v>
       </c>
       <c r="G328" t="n">
         <v>99</v>
@@ -9294,16 +9294,16 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>0.2762976324074323</v>
+        <v>-0.4273059009333364</v>
       </c>
       <c r="D329" t="n">
-        <v>205.7702984553511</v>
+        <v>321.5246037308888</v>
       </c>
       <c r="E329" t="n">
-        <v>272.8085189117106</v>
+        <v>383.121444717875</v>
       </c>
       <c r="F329" t="n">
-        <v>22.48314579514147</v>
+        <v>40.75876393724337</v>
       </c>
       <c r="G329" t="n">
         <v>93</v>
@@ -9321,16 +9321,16 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>-0.8670005735936976</v>
+        <v>-1.031539495232889</v>
       </c>
       <c r="D330" t="n">
-        <v>8.706022244233351</v>
+        <v>9.200932010626181</v>
       </c>
       <c r="E330" t="n">
-        <v>11.91400280047058</v>
+        <v>12.4279102164095</v>
       </c>
       <c r="F330" t="n">
-        <v>70.18927667796706</v>
+        <v>66.77775222049547</v>
       </c>
       <c r="G330" t="n">
         <v>78</v>
@@ -9348,16 +9348,16 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>-1.817267427128847</v>
+        <v>-0.907023634137788</v>
       </c>
       <c r="D331" t="n">
-        <v>139.4182607862684</v>
+        <v>108.8437983194987</v>
       </c>
       <c r="E331" t="n">
-        <v>159.178569009118</v>
+        <v>130.9629945147114</v>
       </c>
       <c r="F331" t="n">
-        <v>50.93734090512908</v>
+        <v>42.54532955162038</v>
       </c>
       <c r="G331" t="n">
         <v>18</v>
@@ -9375,16 +9375,16 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>-0.2595336982005263</v>
+        <v>-6.531533471162424</v>
       </c>
       <c r="D332" t="n">
-        <v>19.11488331569715</v>
+        <v>58.3555615671565</v>
       </c>
       <c r="E332" t="n">
-        <v>25.71436301664186</v>
+        <v>62.88000683688097</v>
       </c>
       <c r="F332" t="n">
-        <v>23.23338115641026</v>
+        <v>91.13090137824476</v>
       </c>
       <c r="G332" t="n">
         <v>89</v>
@@ -9402,16 +9402,16 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>0.3327188750166445</v>
+        <v>-7.679873862168096</v>
       </c>
       <c r="D333" t="n">
-        <v>198.5659982700541</v>
+        <v>835.679572673759</v>
       </c>
       <c r="E333" t="n">
-        <v>244.7946488988397</v>
+        <v>882.8851393823981</v>
       </c>
       <c r="F333" t="n">
-        <v>34.54183968373295</v>
+        <v>112.9099681956137</v>
       </c>
       <c r="G333" t="n">
         <v>99</v>
@@ -9429,16 +9429,16 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>-3.591956911221319</v>
+        <v>-1.243477471977259</v>
       </c>
       <c r="D334" t="n">
-        <v>647.9411187941029</v>
+        <v>425.6302319598454</v>
       </c>
       <c r="E334" t="n">
-        <v>687.190003415733</v>
+        <v>480.3289772556403</v>
       </c>
       <c r="F334" t="n">
-        <v>78.68591969617424</v>
+        <v>50.84535472789713</v>
       </c>
       <c r="G334" t="n">
         <v>93</v>
@@ -9456,16 +9456,16 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>-0.3805902962991961</v>
+        <v>-0.6272173421650122</v>
       </c>
       <c r="D335" t="n">
-        <v>6.927816042533288</v>
+        <v>7.781140703421372</v>
       </c>
       <c r="E335" t="n">
-        <v>10.24513959937052</v>
+        <v>11.12264956121508</v>
       </c>
       <c r="F335" t="n">
-        <v>62.55656554820599</v>
+        <v>68.82459309650454</v>
       </c>
       <c r="G335" t="n">
         <v>78</v>
@@ -9483,16 +9483,16 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>-3.640330753320186</v>
+        <v>-2.65655425999814</v>
       </c>
       <c r="D336" t="n">
-        <v>185.587043232388</v>
+        <v>156.97107357449</v>
       </c>
       <c r="E336" t="n">
-        <v>204.28902126823</v>
+        <v>181.3454110810644</v>
       </c>
       <c r="F336" t="n">
-        <v>67.68697487512222</v>
+        <v>54.08329544664137</v>
       </c>
       <c r="G336" t="n">
         <v>18</v>
@@ -9510,16 +9510,16 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>-0.6211944980864532</v>
+        <v>-0.1970241779676571</v>
       </c>
       <c r="D337" t="n">
-        <v>21.06725969207421</v>
+        <v>18.93434861001004</v>
       </c>
       <c r="E337" t="n">
-        <v>29.17349329726974</v>
+        <v>25.06815297597209</v>
       </c>
       <c r="F337" t="n">
-        <v>25.26513353677961</v>
+        <v>26.21572051845386</v>
       </c>
       <c r="G337" t="n">
         <v>89</v>
@@ -9537,16 +9537,16 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>-1.582220366494431</v>
+        <v>-1.463354225723834</v>
       </c>
       <c r="D338" t="n">
-        <v>425.2112873732441</v>
+        <v>401.9775549378058</v>
       </c>
       <c r="E338" t="n">
-        <v>481.5530645352371</v>
+        <v>470.3389371564971</v>
       </c>
       <c r="F338" t="n">
-        <v>53.10070558606584</v>
+        <v>47.62128947835865</v>
       </c>
       <c r="G338" t="n">
         <v>99</v>
@@ -9564,16 +9564,16 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>0.1468691898451178</v>
+        <v>-1.810045781060024</v>
       </c>
       <c r="D339" t="n">
-        <v>223.303222328104</v>
+        <v>460.4117090368783</v>
       </c>
       <c r="E339" t="n">
-        <v>296.2004706726592</v>
+        <v>537.5695105901759</v>
       </c>
       <c r="F339" t="n">
-        <v>21.1202806365057</v>
+        <v>59.77988775413727</v>
       </c>
       <c r="G339" t="n">
         <v>93</v>
@@ -9591,16 +9591,16 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>-0.8274173919965884</v>
+        <v>-0.544887068405068</v>
       </c>
       <c r="D340" t="n">
-        <v>8.799399846639389</v>
+        <v>7.586580514907837</v>
       </c>
       <c r="E340" t="n">
-        <v>11.78702892022724</v>
+        <v>10.83761804985406</v>
       </c>
       <c r="F340" t="n">
-        <v>70.54556976266959</v>
+        <v>67.11079914982641</v>
       </c>
       <c r="G340" t="n">
         <v>78</v>
@@ -9618,16 +9618,16 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>-2.255029344254267</v>
+        <v>-2.675412266973527</v>
       </c>
       <c r="D341" t="n">
-        <v>148.9760305616591</v>
+        <v>160.4565823872884</v>
       </c>
       <c r="E341" t="n">
-        <v>171.0992134895432</v>
+        <v>181.8124375291012</v>
       </c>
       <c r="F341" t="n">
-        <v>51.35998742832402</v>
+        <v>57.12220945431442</v>
       </c>
       <c r="G341" t="n">
         <v>18</v>
@@ -9645,16 +9645,16 @@
         </is>
       </c>
       <c r="C342" t="n">
-        <v>-1.329766573013788</v>
+        <v>-0.7574985709306563</v>
       </c>
       <c r="D342" t="n">
-        <v>27.04563603776225</v>
+        <v>22.34377432405279</v>
       </c>
       <c r="E342" t="n">
-        <v>34.97253229640221</v>
+        <v>30.37514538493303</v>
       </c>
       <c r="F342" t="n">
-        <v>32.41120722707624</v>
+        <v>26.54652890103539</v>
       </c>
       <c r="G342" t="n">
         <v>89</v>
@@ -9672,16 +9672,16 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>-2.025832978512701</v>
+        <v>-0.4394401622188595</v>
       </c>
       <c r="D343" t="n">
-        <v>451.7551032172309</v>
+        <v>288.8700649377071</v>
       </c>
       <c r="E343" t="n">
-        <v>521.2786955831672</v>
+        <v>359.537594020192</v>
       </c>
       <c r="F343" t="n">
-        <v>52.9253043066959</v>
+        <v>33.8000482617419</v>
       </c>
       <c r="G343" t="n">
         <v>99</v>
@@ -9699,16 +9699,16 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>0.3048343892830856</v>
+        <v>0.2653372804943984</v>
       </c>
       <c r="D344" t="n">
-        <v>188.7695916288642</v>
+        <v>196.1483600575437</v>
       </c>
       <c r="E344" t="n">
-        <v>267.3757839613343</v>
+        <v>274.8665757692664</v>
       </c>
       <c r="F344" t="n">
-        <v>19.68207213622275</v>
+        <v>21.08905335565285</v>
       </c>
       <c r="G344" t="n">
         <v>93</v>
@@ -9726,16 +9726,16 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>-0.690433530211507</v>
+        <v>-1.518775580397132</v>
       </c>
       <c r="D345" t="n">
-        <v>7.986524667495337</v>
+        <v>10.54307125164912</v>
       </c>
       <c r="E345" t="n">
-        <v>11.33664432681304</v>
+        <v>13.83821931492177</v>
       </c>
       <c r="F345" t="n">
-        <v>69.23630247100746</v>
+        <v>76.22838281024234</v>
       </c>
       <c r="G345" t="n">
         <v>78</v>
@@ -9753,16 +9753,16 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>-1.148603729412702</v>
+        <v>-2.974966838847194</v>
       </c>
       <c r="D346" t="n">
-        <v>121.7617179022895</v>
+        <v>170.339352077908</v>
       </c>
       <c r="E346" t="n">
-        <v>139.0108573091917</v>
+        <v>189.0763953413982</v>
       </c>
       <c r="F346" t="n">
-        <v>46.06669943738122</v>
+        <v>60.48985417137148</v>
       </c>
       <c r="G346" t="n">
         <v>18</v>
@@ -9780,16 +9780,16 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>-0.9899056607388947</v>
+        <v>-1.170363985079215</v>
       </c>
       <c r="D347" t="n">
-        <v>25.81671661205506</v>
+        <v>26.16670822829343</v>
       </c>
       <c r="E347" t="n">
-        <v>32.32117336715877</v>
+        <v>33.75492614331672</v>
       </c>
       <c r="F347" t="n">
-        <v>31.54035819435562</v>
+        <v>31.13225935356248</v>
       </c>
       <c r="G347" t="n">
         <v>89</v>
@@ -9807,16 +9807,16 @@
         </is>
       </c>
       <c r="C348" t="n">
-        <v>-1.513615198685391</v>
+        <v>-2.465714334040271</v>
       </c>
       <c r="D348" t="n">
-        <v>409.0977675312697</v>
+        <v>485.1432430382931</v>
       </c>
       <c r="E348" t="n">
-        <v>475.1129814472325</v>
+        <v>557.8839679918519</v>
       </c>
       <c r="F348" t="n">
-        <v>48.64557361472649</v>
+        <v>57.70115447333048</v>
       </c>
       <c r="G348" t="n">
         <v>99</v>
@@ -9834,16 +9834,16 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>-0.234761335714065</v>
+        <v>-0.3293986540843752</v>
       </c>
       <c r="D349" t="n">
-        <v>254.8629294774865</v>
+        <v>276.8514689783896</v>
       </c>
       <c r="E349" t="n">
-        <v>356.3439928817897</v>
+        <v>369.7477572792819</v>
       </c>
       <c r="F349" t="n">
-        <v>25.00243865508996</v>
+        <v>26.01376763261845</v>
       </c>
       <c r="G349" t="n">
         <v>93</v>
@@ -9861,16 +9861,16 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>-0.5683341047567587</v>
+        <v>-1.267400844568888</v>
       </c>
       <c r="D350" t="n">
-        <v>7.892050449664776</v>
+        <v>10.04170159193186</v>
       </c>
       <c r="E350" t="n">
-        <v>10.91955060948045</v>
+        <v>13.12954343316646</v>
       </c>
       <c r="F350" t="n">
-        <v>70.75963382632858</v>
+        <v>68.09251002321504</v>
       </c>
       <c r="G350" t="n">
         <v>78</v>
@@ -9888,16 +9888,16 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>-4.95877170240426</v>
+        <v>-5.119862829266934</v>
       </c>
       <c r="D351" t="n">
-        <v>212.4010583029853</v>
+        <v>216.2550307379828</v>
       </c>
       <c r="E351" t="n">
-        <v>231.498900381268</v>
+        <v>234.6072360861777</v>
       </c>
       <c r="F351" t="n">
-        <v>73.82663364322497</v>
+        <v>75.99202613438082</v>
       </c>
       <c r="G351" t="n">
         <v>18</v>
@@ -9915,16 +9915,16 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>-1.308143573480528</v>
+        <v>-0.5562582109772414</v>
       </c>
       <c r="D352" t="n">
-        <v>27.10971065049761</v>
+        <v>21.37206703357482</v>
       </c>
       <c r="E352" t="n">
-        <v>34.80986066173026</v>
+        <v>28.58325625824904</v>
       </c>
       <c r="F352" t="n">
-        <v>32.57592099859848</v>
+        <v>26.14848722198703</v>
       </c>
       <c r="G352" t="n">
         <v>89</v>
@@ -9942,16 +9942,16 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>-1.084982252946701</v>
+        <v>-1.961363878045254</v>
       </c>
       <c r="D353" t="n">
-        <v>365.6785592743845</v>
+        <v>437.0993228488499</v>
       </c>
       <c r="E353" t="n">
-        <v>432.7117429352205</v>
+        <v>515.6955540375247</v>
       </c>
       <c r="F353" t="n">
-        <v>43.51659666668592</v>
+        <v>50.75843167437033</v>
       </c>
       <c r="G353" t="n">
         <v>99</v>
@@ -9969,16 +9969,16 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>0.0725100918722873</v>
+        <v>-0.09349184481544137</v>
       </c>
       <c r="D354" t="n">
-        <v>247.9214461131762</v>
+        <v>260.9300038327453</v>
       </c>
       <c r="E354" t="n">
-        <v>308.8392772791778</v>
+        <v>335.3402666199524</v>
       </c>
       <c r="F354" t="n">
-        <v>23.85765572343767</v>
+        <v>27.25203824935338</v>
       </c>
       <c r="G354" t="n">
         <v>93</v>
@@ -9996,16 +9996,16 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>-0.7664328271026193</v>
+        <v>-0.8742361163459411</v>
       </c>
       <c r="D355" t="n">
-        <v>8.346399946090502</v>
+        <v>8.821903693370331</v>
       </c>
       <c r="E355" t="n">
-        <v>11.58868173072428</v>
+        <v>11.93706677761165</v>
       </c>
       <c r="F355" t="n">
-        <v>66.62471677545282</v>
+        <v>68.03064394417191</v>
       </c>
       <c r="G355" t="n">
         <v>78</v>
@@ -10023,16 +10023,16 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>-5.987513609633422</v>
+        <v>-4.766457524699846</v>
       </c>
       <c r="D356" t="n">
-        <v>233.0180833604601</v>
+        <v>208.3832685682509</v>
       </c>
       <c r="E356" t="n">
-        <v>250.6870458270122</v>
+        <v>227.7325493193445</v>
       </c>
       <c r="F356" t="n">
-        <v>83.46020609734597</v>
+        <v>72.14998390685405</v>
       </c>
       <c r="G356" t="n">
         <v>18</v>
@@ -10050,16 +10050,16 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>-1.727839525004533</v>
+        <v>-1.588835747085712</v>
       </c>
       <c r="D357" t="n">
-        <v>29.61311843957794</v>
+        <v>28.98271344217022</v>
       </c>
       <c r="E357" t="n">
-        <v>37.84254045724339</v>
+        <v>36.86575422243974</v>
       </c>
       <c r="F357" t="n">
-        <v>35.17999516175077</v>
+        <v>36.64915180377663</v>
       </c>
       <c r="G357" t="n">
         <v>89</v>
@@ -10077,16 +10077,16 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>-0.9131428347860147</v>
+        <v>-1.345158863882544</v>
       </c>
       <c r="D358" t="n">
-        <v>351.9384744046914</v>
+        <v>388.4749446059718</v>
       </c>
       <c r="E358" t="n">
-        <v>414.4968149182145</v>
+        <v>458.9164588290386</v>
       </c>
       <c r="F358" t="n">
-        <v>41.40681901451624</v>
+        <v>46.30168774396746</v>
       </c>
       <c r="G358" t="n">
         <v>99</v>
@@ -10104,16 +10104,16 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>0.4097551746595348</v>
+        <v>-0.7252051683003251</v>
       </c>
       <c r="D359" t="n">
-        <v>171.7165284515709</v>
+        <v>338.2837898500504</v>
       </c>
       <c r="E359" t="n">
-        <v>246.3735181865684</v>
+        <v>421.2096441095652</v>
       </c>
       <c r="F359" t="n">
-        <v>17.71766636630671</v>
+        <v>32.08605571292005</v>
       </c>
       <c r="G359" t="n">
         <v>93</v>
@@ -10131,16 +10131,16 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>-0.5469671857471528</v>
+        <v>-0.8484091693341975</v>
       </c>
       <c r="D360" t="n">
-        <v>7.516001255084307</v>
+        <v>8.680920417492207</v>
       </c>
       <c r="E360" t="n">
-        <v>10.84491176548315</v>
+        <v>11.85453516504549</v>
       </c>
       <c r="F360" t="n">
-        <v>61.04793215990928</v>
+        <v>71.81077394800639</v>
       </c>
       <c r="G360" t="n">
         <v>78</v>
@@ -10158,16 +10158,16 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>-5.910342147736023</v>
+        <v>-5.120973166142416</v>
       </c>
       <c r="D361" t="n">
-        <v>231.9035588370429</v>
+        <v>214.6291478474935</v>
       </c>
       <c r="E361" t="n">
-        <v>249.2988841119521</v>
+        <v>234.628517711142</v>
       </c>
       <c r="F361" t="n">
-        <v>82.52159143028436</v>
+        <v>75.85463937737394</v>
       </c>
       <c r="G361" t="n">
         <v>18</v>

--- a/results/surrogate_comparison.xlsx
+++ b/results/surrogate_comparison.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G361"/>
+  <dimension ref="A1:G366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,16 +465,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.4433546853638226</v>
+        <v>0.6916798456347149</v>
       </c>
       <c r="D2" t="n">
-        <v>18.52742726615306</v>
+        <v>9.241051234556048</v>
       </c>
       <c r="E2" t="n">
-        <v>27.52690652964422</v>
+        <v>12.72248156529546</v>
       </c>
       <c r="F2" t="n">
-        <v>23.21959805540183</v>
+        <v>13.42327990138537</v>
       </c>
       <c r="G2" t="n">
         <v>89</v>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.2166850844939658</v>
+        <v>0.7289272830950621</v>
       </c>
       <c r="D3" t="n">
-        <v>259.892372054283</v>
+        <v>108.5659130366162</v>
       </c>
       <c r="E3" t="n">
-        <v>330.5495664791308</v>
+        <v>156.0236399023971</v>
       </c>
       <c r="F3" t="n">
-        <v>31.7579700030932</v>
+        <v>17.03467305234554</v>
       </c>
       <c r="G3" t="n">
         <v>99</v>
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.1244208886001663</v>
+        <v>0.7173209358571585</v>
       </c>
       <c r="D4" t="n">
-        <v>243.1851038778982</v>
+        <v>117.0791855678764</v>
       </c>
       <c r="E4" t="n">
-        <v>340.0496902348658</v>
+        <v>170.5001435145123</v>
       </c>
       <c r="F4" t="n">
-        <v>23.72542402097881</v>
+        <v>11.74715412227553</v>
       </c>
       <c r="G4" t="n">
         <v>93</v>
@@ -546,16 +546,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.1912434446916196</v>
+        <v>0.1189974630245483</v>
       </c>
       <c r="D5" t="n">
-        <v>6.194101015726726</v>
+        <v>5.347624466969417</v>
       </c>
       <c r="E5" t="n">
-        <v>9.516685866376974</v>
+        <v>8.184158505552732</v>
       </c>
       <c r="F5" t="n">
-        <v>55.62269361421956</v>
+        <v>54.36726293249973</v>
       </c>
       <c r="G5" t="n">
         <v>78</v>
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-6.319836021418417</v>
+        <v>0.8384405692448381</v>
       </c>
       <c r="D6" t="n">
-        <v>240.297711054484</v>
+        <v>28.50716145833333</v>
       </c>
       <c r="E6" t="n">
-        <v>256.5790750412079</v>
+        <v>38.118579821849</v>
       </c>
       <c r="F6" t="n">
-        <v>87.31599924242198</v>
+        <v>10.05117503985481</v>
       </c>
       <c r="G6" t="n">
         <v>18</v>
@@ -600,16 +600,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.5232482234761384</v>
+        <v>0.6579536090274878</v>
       </c>
       <c r="D7" t="n">
-        <v>19.30319916800167</v>
+        <v>9.492118363969782</v>
       </c>
       <c r="E7" t="n">
-        <v>28.27848997612359</v>
+        <v>13.40026475798775</v>
       </c>
       <c r="F7" t="n">
-        <v>24.06901622479159</v>
+        <v>13.50990240361873</v>
       </c>
       <c r="G7" t="n">
         <v>89</v>
@@ -627,16 +627,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.2640173976847997</v>
+        <v>0.7019326661049463</v>
       </c>
       <c r="D8" t="n">
-        <v>263.0321055710918</v>
+        <v>118.8115733753551</v>
       </c>
       <c r="E8" t="n">
-        <v>336.9178539114663</v>
+        <v>163.6080590995961</v>
       </c>
       <c r="F8" t="n">
-        <v>31.80603782982222</v>
+        <v>18.92576886686039</v>
       </c>
       <c r="G8" t="n">
         <v>99</v>
@@ -654,16 +654,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.2052623940811666</v>
+        <v>0.6618457845507211</v>
       </c>
       <c r="D9" t="n">
-        <v>252.144030827348</v>
+        <v>126.472162718414</v>
       </c>
       <c r="E9" t="n">
-        <v>352.0616614381422</v>
+        <v>186.4813177135977</v>
       </c>
       <c r="F9" t="n">
-        <v>24.73195082895289</v>
+        <v>12.66863356061985</v>
       </c>
       <c r="G9" t="n">
         <v>93</v>
@@ -681,16 +681,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.2240688107134829</v>
+        <v>0.1405791879864404</v>
       </c>
       <c r="D10" t="n">
-        <v>6.325749195539034</v>
+        <v>5.315059973643376</v>
       </c>
       <c r="E10" t="n">
-        <v>9.646913586306365</v>
+        <v>8.083294199334638</v>
       </c>
       <c r="F10" t="n">
-        <v>57.97777326957719</v>
+        <v>58.56306800438038</v>
       </c>
       <c r="G10" t="n">
         <v>78</v>
@@ -708,16 +708,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-6.516382907779738</v>
+        <v>0.774049615249454</v>
       </c>
       <c r="D11" t="n">
-        <v>243.7098619672987</v>
+        <v>34.01454755995009</v>
       </c>
       <c r="E11" t="n">
-        <v>260.0009933781797</v>
+        <v>45.07929311342053</v>
       </c>
       <c r="F11" t="n">
-        <v>88.47717702966729</v>
+        <v>13.14859220795982</v>
       </c>
       <c r="G11" t="n">
         <v>18</v>
@@ -735,16 +735,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.6105230048210351</v>
+        <v>0.6673462615024428</v>
       </c>
       <c r="D12" t="n">
-        <v>21.23204966341511</v>
+        <v>9.880999833010556</v>
       </c>
       <c r="E12" t="n">
-        <v>29.07731768305414</v>
+        <v>13.21499725262077</v>
       </c>
       <c r="F12" t="n">
-        <v>26.20545300843988</v>
+        <v>14.21337140004822</v>
       </c>
       <c r="G12" t="n">
         <v>89</v>
@@ -762,16 +762,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.6305797074873616</v>
+        <v>0.6732482039160284</v>
       </c>
       <c r="D13" t="n">
-        <v>304.3984029750631</v>
+        <v>131.0351852262863</v>
       </c>
       <c r="E13" t="n">
-        <v>382.6648014986005</v>
+        <v>171.2996567925574</v>
       </c>
       <c r="F13" t="n">
-        <v>38.61739532235065</v>
+        <v>20.69265493089212</v>
       </c>
       <c r="G13" t="n">
         <v>99</v>
@@ -789,16 +789,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.4723667180206208</v>
+        <v>0.6652674136915786</v>
       </c>
       <c r="D14" t="n">
-        <v>300.060799547421</v>
+        <v>136.2133076985677</v>
       </c>
       <c r="E14" t="n">
-        <v>389.1221268629725</v>
+        <v>185.5354590124376</v>
       </c>
       <c r="F14" t="n">
-        <v>29.86602709319129</v>
+        <v>14.11356457530503</v>
       </c>
       <c r="G14" t="n">
         <v>93</v>
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.6054362147766987</v>
+        <v>0.2101251365858466</v>
       </c>
       <c r="D15" t="n">
-        <v>7.390923634553567</v>
+        <v>5.55935577245859</v>
       </c>
       <c r="E15" t="n">
-        <v>11.04795762596857</v>
+        <v>7.749337915758235</v>
       </c>
       <c r="F15" t="n">
-        <v>71.46432785134684</v>
+        <v>96.99691296370892</v>
       </c>
       <c r="G15" t="n">
         <v>78</v>
@@ -843,16 +843,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-6.877170957055541</v>
+        <v>0.6520797724064511</v>
       </c>
       <c r="D16" t="n">
-        <v>250.2345217598809</v>
+        <v>33.41465504964193</v>
       </c>
       <c r="E16" t="n">
-        <v>266.1679101043237</v>
+        <v>55.93844558597606</v>
       </c>
       <c r="F16" t="n">
-        <v>91.2008337242217</v>
+        <v>19.13037437808491</v>
       </c>
       <c r="G16" t="n">
         <v>18</v>
@@ -870,16 +870,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.6405610935862798</v>
+        <v>0.6670424700670625</v>
       </c>
       <c r="D17" t="n">
-        <v>21.36564614799585</v>
+        <v>9.900568458471405</v>
       </c>
       <c r="E17" t="n">
-        <v>29.34722751574721</v>
+        <v>13.2210300825089</v>
       </c>
       <c r="F17" t="n">
-        <v>26.16281808231566</v>
+        <v>14.37718154936586</v>
       </c>
       <c r="G17" t="n">
         <v>89</v>
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.4226068654313968</v>
+        <v>0.6844887757201327</v>
       </c>
       <c r="D18" t="n">
-        <v>292.7752334132339</v>
+        <v>127.6147593488597</v>
       </c>
       <c r="E18" t="n">
-        <v>357.4291349357281</v>
+        <v>168.3274359253667</v>
       </c>
       <c r="F18" t="n">
-        <v>37.41024216704611</v>
+        <v>20.27960021249281</v>
       </c>
       <c r="G18" t="n">
         <v>99</v>
@@ -924,16 +924,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.5043186532267536</v>
+        <v>0.6594814701273061</v>
       </c>
       <c r="D19" t="n">
-        <v>303.0115182527932</v>
+        <v>135.7263646279612</v>
       </c>
       <c r="E19" t="n">
-        <v>393.3216491334703</v>
+        <v>187.1321043326049</v>
       </c>
       <c r="F19" t="n">
-        <v>30.56847213527716</v>
+        <v>13.83189324739927</v>
       </c>
       <c r="G19" t="n">
         <v>93</v>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.6592724614386916</v>
+        <v>0.1727583116680828</v>
       </c>
       <c r="D20" t="n">
-        <v>7.585002672977937</v>
+        <v>5.63975863578992</v>
       </c>
       <c r="E20" t="n">
-        <v>11.23166974041273</v>
+        <v>7.930519887698541</v>
       </c>
       <c r="F20" t="n">
-        <v>72.12605330803041</v>
+        <v>100.6478563092873</v>
       </c>
       <c r="G20" t="n">
         <v>78</v>
@@ -978,16 +978,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-6.637238973400845</v>
+        <v>0.6503757883585685</v>
       </c>
       <c r="D21" t="n">
-        <v>247.0020982954237</v>
+        <v>33.82724846733941</v>
       </c>
       <c r="E21" t="n">
-        <v>262.0829383345823</v>
+        <v>56.07526113737028</v>
       </c>
       <c r="F21" t="n">
-        <v>90.60451631097899</v>
+        <v>19.60583834236591</v>
       </c>
       <c r="G21" t="n">
         <v>18</v>
@@ -1005,16 +1005,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.4249748090074423</v>
+        <v>0.7055983066884487</v>
       </c>
       <c r="D22" t="n">
-        <v>18.79910912674465</v>
+        <v>9.178284591503358</v>
       </c>
       <c r="E22" t="n">
-        <v>27.35107928418134</v>
+        <v>12.43200066501365</v>
       </c>
       <c r="F22" t="n">
-        <v>23.59621548316874</v>
+        <v>13.25946612533147</v>
       </c>
       <c r="G22" t="n">
         <v>89</v>
@@ -1032,16 +1032,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.4876250568993015</v>
+        <v>0.6908829188716539</v>
       </c>
       <c r="D23" t="n">
-        <v>290.441417193172</v>
+        <v>122.8905688969776</v>
       </c>
       <c r="E23" t="n">
-        <v>365.5057742451698</v>
+        <v>166.6130455619019</v>
       </c>
       <c r="F23" t="n">
-        <v>36.16119228882673</v>
+        <v>19.17593479608843</v>
       </c>
       <c r="G23" t="n">
         <v>99</v>
@@ -1059,16 +1059,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.3971082230854419</v>
+        <v>0.6916734933734558</v>
       </c>
       <c r="D24" t="n">
-        <v>266.4825101462744</v>
+        <v>125.381592125021</v>
       </c>
       <c r="E24" t="n">
-        <v>379.0469055259701</v>
+        <v>178.0669654321783</v>
       </c>
       <c r="F24" t="n">
-        <v>25.9184284788149</v>
+        <v>12.74701296275286</v>
       </c>
       <c r="G24" t="n">
         <v>93</v>
@@ -1086,16 +1086,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.2408372801356713</v>
+        <v>0.1459165103961165</v>
       </c>
       <c r="D25" t="n">
-        <v>6.468798671013269</v>
+        <v>5.157609010354067</v>
       </c>
       <c r="E25" t="n">
-        <v>9.712765169550172</v>
+        <v>8.0581549781175</v>
       </c>
       <c r="F25" t="n">
-        <v>62.68603953344653</v>
+        <v>62.81900047250664</v>
       </c>
       <c r="G25" t="n">
         <v>78</v>
@@ -1113,16 +1113,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-6.304824360913674</v>
+        <v>0.7282752720996135</v>
       </c>
       <c r="D26" t="n">
-        <v>238.3590316772461</v>
+        <v>37.07543012830946</v>
       </c>
       <c r="E26" t="n">
-        <v>256.3158413596589</v>
+        <v>49.43506800710641</v>
       </c>
       <c r="F26" t="n">
-        <v>84.9251357609479</v>
+        <v>18.21159499931154</v>
       </c>
       <c r="G26" t="n">
         <v>18</v>
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.9800782623423003</v>
+        <v>0.5514799914704986</v>
       </c>
       <c r="D27" t="n">
-        <v>22.63779498753923</v>
+        <v>10.95608919122246</v>
       </c>
       <c r="E27" t="n">
-        <v>32.24126350192439</v>
+        <v>15.34481948344273</v>
       </c>
       <c r="F27" t="n">
-        <v>27.39435587908935</v>
+        <v>14.65939841377681</v>
       </c>
       <c r="G27" t="n">
         <v>89</v>
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.7521031502067419</v>
+        <v>0.6864600648085368</v>
       </c>
       <c r="D28" t="n">
-        <v>314.9342027143999</v>
+        <v>121.3196589922664</v>
       </c>
       <c r="E28" t="n">
-        <v>396.6681540450891</v>
+        <v>167.8007637548065</v>
       </c>
       <c r="F28" t="n">
-        <v>36.35278355372198</v>
+        <v>19.14271908146164</v>
       </c>
       <c r="G28" t="n">
         <v>99</v>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.5493961242081549</v>
+        <v>0.7003766716036786</v>
       </c>
       <c r="D29" t="n">
-        <v>282.5962074854041</v>
+        <v>122.4321476105721</v>
       </c>
       <c r="E29" t="n">
-        <v>399.1711669831904</v>
+        <v>175.5358144011395</v>
       </c>
       <c r="F29" t="n">
-        <v>26.6363052858097</v>
+        <v>12.38659164949818</v>
       </c>
       <c r="G29" t="n">
         <v>93</v>
@@ -1221,16 +1221,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.4885319173975196</v>
+        <v>0.1091969555436096</v>
       </c>
       <c r="D30" t="n">
-        <v>7.388545815761272</v>
+        <v>6.074242188380315</v>
       </c>
       <c r="E30" t="n">
-        <v>10.63811174215191</v>
+        <v>8.229553989187956</v>
       </c>
       <c r="F30" t="n">
-        <v>68.78475193875919</v>
+        <v>96.51305812775189</v>
       </c>
       <c r="G30" t="n">
         <v>78</v>
@@ -1248,16 +1248,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-7.153564558770304</v>
+        <v>0.6959770942010222</v>
       </c>
       <c r="D31" t="n">
-        <v>254.5191548665365</v>
+        <v>39.33022054036459</v>
       </c>
       <c r="E31" t="n">
-        <v>270.7972914962932</v>
+        <v>52.29060991912563</v>
       </c>
       <c r="F31" t="n">
-        <v>92.80769973090747</v>
+        <v>20.13925918553835</v>
       </c>
       <c r="G31" t="n">
         <v>18</v>
@@ -1275,16 +1275,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.6301918766991375</v>
+        <v>0.5294930810670462</v>
       </c>
       <c r="D32" t="n">
-        <v>20.65723897098156</v>
+        <v>11.24342166171985</v>
       </c>
       <c r="E32" t="n">
-        <v>29.25433547392583</v>
+        <v>15.71642918368175</v>
       </c>
       <c r="F32" t="n">
-        <v>24.54569476521053</v>
+        <v>15.30150956340185</v>
       </c>
       <c r="G32" t="n">
         <v>89</v>
@@ -1302,16 +1302,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.559606235202782</v>
+        <v>0.4538626418189228</v>
       </c>
       <c r="D33" t="n">
-        <v>306.4565072107796</v>
+        <v>172.4709454160748</v>
       </c>
       <c r="E33" t="n">
-        <v>374.2441163210599</v>
+        <v>221.4616053236374</v>
       </c>
       <c r="F33" t="n">
-        <v>35.97961031263934</v>
+        <v>23.24954938479708</v>
       </c>
       <c r="G33" t="n">
         <v>99</v>
@@ -1329,16 +1329,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-4.424537872601253</v>
+        <v>0.3899696595588528</v>
       </c>
       <c r="D34" t="n">
-        <v>683.2225722446236</v>
+        <v>204.3117186843708</v>
       </c>
       <c r="E34" t="n">
-        <v>746.8945731303328</v>
+        <v>250.4688053052476</v>
       </c>
       <c r="F34" t="n">
-        <v>78.97954476047772</v>
+        <v>25.07606738230238</v>
       </c>
       <c r="G34" t="n">
         <v>93</v>
@@ -1356,16 +1356,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-0.2582835908418688</v>
+        <v>0.1981066105255346</v>
       </c>
       <c r="D35" t="n">
-        <v>6.542941010915316</v>
+        <v>5.618680923413008</v>
       </c>
       <c r="E35" t="n">
-        <v>9.780808112933709</v>
+        <v>7.808071274827694</v>
       </c>
       <c r="F35" t="n">
-        <v>66.10203741123985</v>
+        <v>83.08705522815603</v>
       </c>
       <c r="G35" t="n">
         <v>78</v>
@@ -1383,16 +1383,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-5.083551361093961</v>
+        <v>0.6413251319032103</v>
       </c>
       <c r="D36" t="n">
-        <v>213.3989946577284</v>
+        <v>43.35861206054688</v>
       </c>
       <c r="E36" t="n">
-        <v>233.9101937203399</v>
+        <v>56.79642866402691</v>
       </c>
       <c r="F36" t="n">
-        <v>73.92508420757373</v>
+        <v>24.80408655543308</v>
       </c>
       <c r="G36" t="n">
         <v>18</v>
@@ -1410,16 +1410,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-1.040096239523901</v>
+        <v>0.4563676691728515</v>
       </c>
       <c r="D37" t="n">
-        <v>23.96677246522368</v>
+        <v>12.00400886107027</v>
       </c>
       <c r="E37" t="n">
-        <v>32.72624690812973</v>
+        <v>16.89365074513139</v>
       </c>
       <c r="F37" t="n">
-        <v>27.81308560980368</v>
+        <v>17.14180583862315</v>
       </c>
       <c r="G37" t="n">
         <v>89</v>
@@ -1437,16 +1437,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-0.4405001882345934</v>
+        <v>0.5869095035151486</v>
       </c>
       <c r="D38" t="n">
-        <v>281.6791707048512</v>
+        <v>148.5584124940814</v>
       </c>
       <c r="E38" t="n">
-        <v>359.669954181316</v>
+        <v>192.6061290444328</v>
       </c>
       <c r="F38" t="n">
-        <v>32.8337685200995</v>
+        <v>24.11200941987056</v>
       </c>
       <c r="G38" t="n">
         <v>99</v>
@@ -1464,16 +1464,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-3.231218131027331</v>
+        <v>0.5745855883320756</v>
       </c>
       <c r="D39" t="n">
-        <v>528.3580801358787</v>
+        <v>177.074704077936</v>
       </c>
       <c r="E39" t="n">
-        <v>659.6455523619329</v>
+        <v>209.162597074001</v>
       </c>
       <c r="F39" t="n">
-        <v>65.57364961492338</v>
+        <v>20.86873347537231</v>
       </c>
       <c r="G39" t="n">
         <v>93</v>
@@ -1491,16 +1491,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-0.6335745728939657</v>
+        <v>0.1592437698897339</v>
       </c>
       <c r="D40" t="n">
-        <v>7.947351529048039</v>
+        <v>5.667006113590339</v>
       </c>
       <c r="E40" t="n">
-        <v>11.14435542692986</v>
+        <v>7.995037396749165</v>
       </c>
       <c r="F40" t="n">
-        <v>74.73986168719836</v>
+        <v>95.13555406815308</v>
       </c>
       <c r="G40" t="n">
         <v>78</v>
@@ -1518,16 +1518,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-3.60101911693528</v>
+        <v>0.5833386021415015</v>
       </c>
       <c r="D41" t="n">
-        <v>186.5478943718804</v>
+        <v>46.82452562120226</v>
       </c>
       <c r="E41" t="n">
-        <v>203.4218398577079</v>
+        <v>61.21561090909579</v>
       </c>
       <c r="F41" t="n">
-        <v>66.33093644657495</v>
+        <v>28.00443277492566</v>
       </c>
       <c r="G41" t="n">
         <v>18</v>
@@ -1545,16 +1545,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-0.2658648719891576</v>
+        <v>0.3050273991366131</v>
       </c>
       <c r="D42" t="n">
-        <v>20.63560127944089</v>
+        <v>13.61437606811523</v>
       </c>
       <c r="E42" t="n">
-        <v>25.77890993135084</v>
+        <v>19.10093885610169</v>
       </c>
       <c r="F42" t="n">
-        <v>30.75009940994461</v>
+        <v>18.30238063370811</v>
       </c>
       <c r="G42" t="n">
         <v>89</v>
@@ -1572,16 +1572,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.07815204987977165</v>
+        <v>0.5133033052270798</v>
       </c>
       <c r="D43" t="n">
-        <v>226.6489379574554</v>
+        <v>172.0685008655895</v>
       </c>
       <c r="E43" t="n">
-        <v>287.724700757809</v>
+        <v>209.0627696212515</v>
       </c>
       <c r="F43" t="n">
-        <v>42.53183377070678</v>
+        <v>29.41900595011272</v>
       </c>
       <c r="G43" t="n">
         <v>99</v>
@@ -1599,16 +1599,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-11.9185278430578</v>
+        <v>-2.265905168940568</v>
       </c>
       <c r="D44" t="n">
-        <v>1113.83639952957</v>
+        <v>498.2940243956863</v>
       </c>
       <c r="E44" t="n">
-        <v>1152.615469006447</v>
+        <v>579.5350560151063</v>
       </c>
       <c r="F44" t="n">
-        <v>133.7612397023653</v>
+        <v>65.68775207253515</v>
       </c>
       <c r="G44" t="n">
         <v>93</v>
@@ -1626,16 +1626,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.3199648689231966</v>
+        <v>0.08290168570051026</v>
       </c>
       <c r="D45" t="n">
-        <v>7.304104377061893</v>
+        <v>6.300214963081555</v>
       </c>
       <c r="E45" t="n">
-        <v>10.01766855324757</v>
+        <v>8.35013313584153</v>
       </c>
       <c r="F45" t="n">
-        <v>84.35395208960151</v>
+        <v>96.70952845199855</v>
       </c>
       <c r="G45" t="n">
         <v>78</v>
@@ -1653,16 +1653,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-1.417639971518604</v>
+        <v>0.5933681732034755</v>
       </c>
       <c r="D46" t="n">
-        <v>122.194995880127</v>
+        <v>43.49881235758463</v>
       </c>
       <c r="E46" t="n">
-        <v>147.4573323456971</v>
+        <v>60.47435408769775</v>
       </c>
       <c r="F46" t="n">
-        <v>46.95617916840063</v>
+        <v>25.97724764888586</v>
       </c>
       <c r="G46" t="n">
         <v>18</v>
@@ -1680,16 +1680,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.9633827075801049</v>
+        <v>0.4134038420293051</v>
       </c>
       <c r="D47" t="n">
-        <v>23.87727806005585</v>
+        <v>12.2217585960131</v>
       </c>
       <c r="E47" t="n">
-        <v>32.10505038487623</v>
+        <v>17.54851939264527</v>
       </c>
       <c r="F47" t="n">
-        <v>28.77333807697932</v>
+        <v>16.80022683102034</v>
       </c>
       <c r="G47" t="n">
         <v>89</v>
@@ -1707,16 +1707,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-0.5198701518104034</v>
+        <v>0.5889107025090721</v>
       </c>
       <c r="D48" t="n">
-        <v>309.4393964054609</v>
+        <v>147.3604119811395</v>
       </c>
       <c r="E48" t="n">
-        <v>369.4458078889135</v>
+        <v>192.1390266239865</v>
       </c>
       <c r="F48" t="n">
-        <v>36.44466740909726</v>
+        <v>21.29853631639075</v>
       </c>
       <c r="G48" t="n">
         <v>99</v>
@@ -1734,16 +1734,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.3390836855064515</v>
+        <v>0.648388334954942</v>
       </c>
       <c r="D49" t="n">
-        <v>200.6278017105595</v>
+        <v>147.8091657084804</v>
       </c>
       <c r="E49" t="n">
-        <v>260.7060846148894</v>
+        <v>190.1557944616443</v>
       </c>
       <c r="F49" t="n">
-        <v>21.94836482608741</v>
+        <v>17.05559866149589</v>
       </c>
       <c r="G49" t="n">
         <v>93</v>
@@ -1761,16 +1761,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.2731679496765009</v>
+        <v>0.2845500613630918</v>
       </c>
       <c r="D50" t="n">
-        <v>6.76723143687615</v>
+        <v>5.198490093915891</v>
       </c>
       <c r="E50" t="n">
-        <v>9.838487106469985</v>
+        <v>7.375221666117175</v>
       </c>
       <c r="F50" t="n">
-        <v>68.10539294986468</v>
+        <v>77.39009756798517</v>
       </c>
       <c r="G50" t="n">
         <v>78</v>
@@ -1788,16 +1788,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-2.468788189854897</v>
+        <v>0.6052215430313441</v>
       </c>
       <c r="D51" t="n">
-        <v>157.3167576260037</v>
+        <v>43.08936140272353</v>
       </c>
       <c r="E51" t="n">
-        <v>176.6279588094755</v>
+        <v>59.58641778346726</v>
       </c>
       <c r="F51" t="n">
-        <v>56.52108204672276</v>
+        <v>26.29673873237448</v>
       </c>
       <c r="G51" t="n">
         <v>18</v>
@@ -1815,16 +1815,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-1.343752314074517</v>
+        <v>0.5442300678446423</v>
       </c>
       <c r="D52" t="n">
-        <v>28.00341584709253</v>
+        <v>11.7271842956543</v>
       </c>
       <c r="E52" t="n">
-        <v>35.07734642920675</v>
+        <v>15.46833995646796</v>
       </c>
       <c r="F52" t="n">
-        <v>33.2580733030431</v>
+        <v>16.43258354074826</v>
       </c>
       <c r="G52" t="n">
         <v>89</v>
@@ -1842,16 +1842,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-1.092614072956793</v>
+        <v>0.6166403279966584</v>
       </c>
       <c r="D53" t="n">
-        <v>360.5005725899128</v>
+        <v>140.1454668141375</v>
       </c>
       <c r="E53" t="n">
-        <v>433.5029634995768</v>
+        <v>185.545622848297</v>
       </c>
       <c r="F53" t="n">
-        <v>42.75689942619029</v>
+        <v>22.05795792961611</v>
       </c>
       <c r="G53" t="n">
         <v>99</v>
@@ -1869,16 +1869,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.06406541735680049</v>
+        <v>0.6016787121430793</v>
       </c>
       <c r="D54" t="n">
-        <v>237.9108066353747</v>
+        <v>162.6171609201739</v>
       </c>
       <c r="E54" t="n">
-        <v>330.7974060652663</v>
+        <v>202.3926259400057</v>
       </c>
       <c r="F54" t="n">
-        <v>29.43323190791053</v>
+        <v>18.69759980876717</v>
       </c>
       <c r="G54" t="n">
         <v>93</v>
@@ -1896,16 +1896,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-0.7493661117904729</v>
+        <v>0.1679996544680157</v>
       </c>
       <c r="D55" t="n">
-        <v>8.272061564983465</v>
+        <v>5.841427313975799</v>
       </c>
       <c r="E55" t="n">
-        <v>11.53256276190246</v>
+        <v>7.953297093774934</v>
       </c>
       <c r="F55" t="n">
-        <v>69.02721341830558</v>
+        <v>91.74964267545977</v>
       </c>
       <c r="G55" t="n">
         <v>78</v>
@@ -1923,16 +1923,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-3.071168959770504</v>
+        <v>0.5643865440694018</v>
       </c>
       <c r="D56" t="n">
-        <v>171.3428501553006</v>
+        <v>46.8013678656684</v>
       </c>
       <c r="E56" t="n">
-        <v>191.3507295828701</v>
+        <v>62.59234145043439</v>
       </c>
       <c r="F56" t="n">
-        <v>60.01040507045793</v>
+        <v>26.44061429241668</v>
       </c>
       <c r="G56" t="n">
         <v>18</v>
@@ -1950,16 +1950,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-0.9474637921688138</v>
+        <v>0.5289436110028369</v>
       </c>
       <c r="D57" t="n">
-        <v>24.47720774104086</v>
+        <v>11.31928677505322</v>
       </c>
       <c r="E57" t="n">
-        <v>31.97463318648046</v>
+        <v>15.72560353078081</v>
       </c>
       <c r="F57" t="n">
-        <v>29.54778872735012</v>
+        <v>15.83085010771276</v>
       </c>
       <c r="G57" t="n">
         <v>89</v>
@@ -1977,16 +1977,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-0.83914022949874</v>
+        <v>0.646563134598378</v>
       </c>
       <c r="D58" t="n">
-        <v>339.9813905966402</v>
+        <v>130.7236201739071</v>
       </c>
       <c r="E58" t="n">
-        <v>406.401144239207</v>
+        <v>178.1572188699538</v>
       </c>
       <c r="F58" t="n">
-        <v>39.42977219262929</v>
+        <v>18.62784977643471</v>
       </c>
       <c r="G58" t="n">
         <v>99</v>
@@ -2004,16 +2004,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.001413163636892922</v>
+        <v>0.6387801702158507</v>
       </c>
       <c r="D59" t="n">
-        <v>260.9485611454133</v>
+        <v>152.2081879646547</v>
       </c>
       <c r="E59" t="n">
-        <v>320.4578019208748</v>
+        <v>192.7363891142468</v>
       </c>
       <c r="F59" t="n">
-        <v>30.09114131111776</v>
+        <v>17.79878917633171</v>
       </c>
       <c r="G59" t="n">
         <v>93</v>
@@ -2031,16 +2031,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-0.573500482287117</v>
+        <v>0.1309759345519484</v>
       </c>
       <c r="D60" t="n">
-        <v>7.748043277324775</v>
+        <v>6.04996901903397</v>
       </c>
       <c r="E60" t="n">
-        <v>10.93752131393213</v>
+        <v>8.128330504549982</v>
       </c>
       <c r="F60" t="n">
-        <v>68.50092680356649</v>
+        <v>100.4959475800492</v>
       </c>
       <c r="G60" t="n">
         <v>78</v>
@@ -2058,16 +2058,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-2.849318707839123</v>
+        <v>0.6400467151151887</v>
       </c>
       <c r="D61" t="n">
-        <v>164.9558842976888</v>
+        <v>46.94417317708334</v>
       </c>
       <c r="E61" t="n">
-        <v>186.0640604692693</v>
+        <v>56.89755774957856</v>
       </c>
       <c r="F61" t="n">
-        <v>57.88403599077412</v>
+        <v>23.11632651345631</v>
       </c>
       <c r="G61" t="n">
         <v>18</v>
@@ -2085,16 +2085,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-0.8605010070335575</v>
+        <v>0.4438968951257127</v>
       </c>
       <c r="D62" t="n">
-        <v>23.13001392664534</v>
+        <v>12.21498176488983</v>
       </c>
       <c r="E62" t="n">
-        <v>31.25257670158128</v>
+        <v>17.08631988435376</v>
       </c>
       <c r="F62" t="n">
-        <v>27.55316720415363</v>
+        <v>16.27841285002495</v>
       </c>
       <c r="G62" t="n">
         <v>89</v>
@@ -2112,16 +2112,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-0.3936570380115552</v>
+        <v>0.3995738626616535</v>
       </c>
       <c r="D63" t="n">
-        <v>288.6277724757339</v>
+        <v>179.9128054223879</v>
       </c>
       <c r="E63" t="n">
-        <v>353.7736285794363</v>
+        <v>232.2080630241575</v>
       </c>
       <c r="F63" t="n">
-        <v>33.98067408835536</v>
+        <v>23.59153732486972</v>
       </c>
       <c r="G63" t="n">
         <v>99</v>
@@ -2139,16 +2139,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.4785468939898412</v>
+        <v>-0.102763185629881</v>
       </c>
       <c r="D64" t="n">
-        <v>177.1591442477319</v>
+        <v>267.9044350244666</v>
       </c>
       <c r="E64" t="n">
-        <v>231.5717408023934</v>
+        <v>336.7588797295632</v>
       </c>
       <c r="F64" t="n">
-        <v>20.45740992457245</v>
+        <v>33.63297803088394</v>
       </c>
       <c r="G64" t="n">
         <v>93</v>
@@ -2166,16 +2166,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-0.2350427910799582</v>
+        <v>0.1408434672215163</v>
       </c>
       <c r="D65" t="n">
-        <v>6.518052960053469</v>
+        <v>5.742295473049849</v>
       </c>
       <c r="E65" t="n">
-        <v>9.690060189923535</v>
+        <v>8.082051262794229</v>
       </c>
       <c r="F65" t="n">
-        <v>60.21703257484342</v>
+        <v>79.35358217901872</v>
       </c>
       <c r="G65" t="n">
         <v>78</v>
@@ -2193,16 +2193,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-2.801511457300116</v>
+        <v>0.6857860995174181</v>
       </c>
       <c r="D66" t="n">
-        <v>168.096151775784</v>
+        <v>40.91447363959418</v>
       </c>
       <c r="E66" t="n">
-        <v>184.905023822695</v>
+        <v>53.15978938123438</v>
       </c>
       <c r="F66" t="n">
-        <v>58.49444609923873</v>
+        <v>24.88011461904437</v>
       </c>
       <c r="G66" t="n">
         <v>18</v>
@@ -2220,16 +2220,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-1.167520736037395</v>
+        <v>0.4345912826182505</v>
       </c>
       <c r="D67" t="n">
-        <v>26.69052359763156</v>
+        <v>12.41585600777958</v>
       </c>
       <c r="E67" t="n">
-        <v>33.73280885910732</v>
+        <v>17.22868469304261</v>
       </c>
       <c r="F67" t="n">
-        <v>32.09591980773539</v>
+        <v>17.32869649828215</v>
       </c>
       <c r="G67" t="n">
         <v>89</v>
@@ -2247,16 +2247,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-0.7723288446861207</v>
+        <v>0.5222231854805637</v>
       </c>
       <c r="D68" t="n">
-        <v>333.8967593414615</v>
+        <v>159.7924283730863</v>
       </c>
       <c r="E68" t="n">
-        <v>398.9510870405131</v>
+        <v>207.1381229224579</v>
       </c>
       <c r="F68" t="n">
-        <v>39.46590773230047</v>
+        <v>23.88486480154102</v>
       </c>
       <c r="G68" t="n">
         <v>99</v>
@@ -2274,16 +2274,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.2808628218168763</v>
+        <v>0.5108905589016994</v>
       </c>
       <c r="D69" t="n">
-        <v>191.603522844212</v>
+        <v>188.586166874055</v>
       </c>
       <c r="E69" t="n">
-        <v>271.9467054783973</v>
+        <v>224.2750434211658</v>
       </c>
       <c r="F69" t="n">
-        <v>20.57708351345929</v>
+        <v>21.9759721585007</v>
       </c>
       <c r="G69" t="n">
         <v>93</v>
@@ -2301,16 +2301,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-0.4064651239950932</v>
+        <v>0.1065861979788275</v>
       </c>
       <c r="D70" t="n">
-        <v>7.028409157043848</v>
+        <v>5.923959230765318</v>
       </c>
       <c r="E70" t="n">
-        <v>10.34070040834416</v>
+        <v>8.241604717578227</v>
       </c>
       <c r="F70" t="n">
-        <v>63.30353320998159</v>
+        <v>98.13117595164121</v>
       </c>
       <c r="G70" t="n">
         <v>78</v>
@@ -2328,16 +2328,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-4.066040080556198</v>
+        <v>0.4863440801663755</v>
       </c>
       <c r="D71" t="n">
-        <v>191.7731191847059</v>
+        <v>53.3012949625651</v>
       </c>
       <c r="E71" t="n">
-        <v>213.454281237801</v>
+        <v>67.96834630708042</v>
       </c>
       <c r="F71" t="n">
-        <v>66.6712322884306</v>
+        <v>29.40068478334365</v>
       </c>
       <c r="G71" t="n">
         <v>18</v>
@@ -2355,16 +2355,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-1.048136907536882</v>
+        <v>0.550595173797976</v>
       </c>
       <c r="D72" t="n">
-        <v>24.66014853488193</v>
+        <v>11.14309730958403</v>
       </c>
       <c r="E72" t="n">
-        <v>32.7906757597757</v>
+        <v>15.3599477693751</v>
       </c>
       <c r="F72" t="n">
-        <v>29.16944956313586</v>
+        <v>15.04914234427065</v>
       </c>
       <c r="G72" t="n">
         <v>89</v>
@@ -2382,16 +2382,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-1.03208565930142</v>
+        <v>0.4699754060906073</v>
       </c>
       <c r="D73" t="n">
-        <v>349.7959106137054</v>
+        <v>167.5277512675584</v>
       </c>
       <c r="E73" t="n">
-        <v>427.1874696562783</v>
+        <v>218.1702413534324</v>
       </c>
       <c r="F73" t="n">
-        <v>40.38978798635378</v>
+        <v>22.92916959262503</v>
       </c>
       <c r="G73" t="n">
         <v>99</v>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-1.478232226446296</v>
+        <v>0.2792554601261753</v>
       </c>
       <c r="D74" t="n">
-        <v>440.1566792149698</v>
+        <v>229.0489288658224</v>
       </c>
       <c r="E74" t="n">
-        <v>504.8343890476452</v>
+        <v>272.2504504365785</v>
       </c>
       <c r="F74" t="n">
-        <v>56.79077265826082</v>
+        <v>28.70203145708993</v>
       </c>
       <c r="G74" t="n">
         <v>93</v>
@@ -2436,16 +2436,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-0.3788650775383002</v>
+        <v>0.146581566099888</v>
       </c>
       <c r="D75" t="n">
-        <v>7.24635429871388</v>
+        <v>5.907221867487981</v>
       </c>
       <c r="E75" t="n">
-        <v>10.23873631218442</v>
+        <v>8.055017014640404</v>
       </c>
       <c r="F75" t="n">
-        <v>73.66590980386488</v>
+        <v>92.86708466690004</v>
       </c>
       <c r="G75" t="n">
         <v>78</v>
@@ -2463,16 +2463,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-4.376380190224774</v>
+        <v>0.7007188827369379</v>
       </c>
       <c r="D76" t="n">
-        <v>200.6302083333333</v>
+        <v>40.80119069417318</v>
       </c>
       <c r="E76" t="n">
-        <v>219.8950966094401</v>
+        <v>51.88122392348669</v>
       </c>
       <c r="F76" t="n">
-        <v>69.87589010279434</v>
+        <v>19.50497701586454</v>
       </c>
       <c r="G76" t="n">
         <v>18</v>
@@ -2490,16 +2490,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-1.771036505002272</v>
+        <v>0.5045751996939949</v>
       </c>
       <c r="D77" t="n">
-        <v>30.2435010202815</v>
+        <v>11.64705152190133</v>
       </c>
       <c r="E77" t="n">
-        <v>38.14099325076334</v>
+        <v>16.12722868763621</v>
       </c>
       <c r="F77" t="n">
-        <v>35.90433907444319</v>
+        <v>15.9149658197813</v>
       </c>
       <c r="G77" t="n">
         <v>89</v>
@@ -2517,16 +2517,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-0.9357644660010294</v>
+        <v>0.6599366613837916</v>
       </c>
       <c r="D78" t="n">
-        <v>351.3308834499783</v>
+        <v>132.2933146158854</v>
       </c>
       <c r="E78" t="n">
-        <v>416.9401867889899</v>
+        <v>174.7541138679649</v>
       </c>
       <c r="F78" t="n">
-        <v>41.27883777410714</v>
+        <v>21.0945341792307</v>
       </c>
       <c r="G78" t="n">
         <v>99</v>
@@ -2544,16 +2544,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.1494137014362729</v>
+        <v>0.6423686557572927</v>
       </c>
       <c r="D79" t="n">
-        <v>202.9841525170111</v>
+        <v>145.5984270649571</v>
       </c>
       <c r="E79" t="n">
-        <v>295.7584233692621</v>
+        <v>191.7766438252596</v>
       </c>
       <c r="F79" t="n">
-        <v>20.79119934264222</v>
+        <v>14.90529196968428</v>
       </c>
       <c r="G79" t="n">
         <v>93</v>
@@ -2571,16 +2571,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-0.6180625931120993</v>
+        <v>0.1729228660368008</v>
       </c>
       <c r="D80" t="n">
-        <v>7.831171023540008</v>
+        <v>5.859921553196052</v>
       </c>
       <c r="E80" t="n">
-        <v>11.09131733394513</v>
+        <v>7.929731081587758</v>
       </c>
       <c r="F80" t="n">
-        <v>71.06094113183956</v>
+        <v>90.72018015800467</v>
       </c>
       <c r="G80" t="n">
         <v>78</v>
@@ -2598,16 +2598,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-5.273265177489796</v>
+        <v>0.6351577037821652</v>
       </c>
       <c r="D81" t="n">
-        <v>218.3342639075385</v>
+        <v>37.54952748616537</v>
       </c>
       <c r="E81" t="n">
-        <v>237.5294056921927</v>
+        <v>57.28265578447014</v>
       </c>
       <c r="F81" t="n">
-        <v>76.10598613053413</v>
+        <v>23.31754717144697</v>
       </c>
       <c r="G81" t="n">
         <v>18</v>
@@ -2625,16 +2625,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-1.331671462446003</v>
+        <v>0.5309874685008719</v>
       </c>
       <c r="D82" t="n">
-        <v>28.34089964963077</v>
+        <v>11.53557050897834</v>
       </c>
       <c r="E82" t="n">
-        <v>34.98682668883706</v>
+        <v>15.6914506850122</v>
       </c>
       <c r="F82" t="n">
-        <v>34.35009675367393</v>
+        <v>15.81557237131166</v>
       </c>
       <c r="G82" t="n">
         <v>89</v>
@@ -2652,16 +2652,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-1.131691870508748</v>
+        <v>0.6166291288074487</v>
       </c>
       <c r="D83" t="n">
-        <v>358.907000146731</v>
+        <v>145.4253900701349</v>
       </c>
       <c r="E83" t="n">
-        <v>437.5318918528021</v>
+        <v>185.5483330255969</v>
       </c>
       <c r="F83" t="n">
-        <v>41.74828712977906</v>
+        <v>24.19153454285421</v>
       </c>
       <c r="G83" t="n">
         <v>99</v>
@@ -2679,16 +2679,16 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.08282013273278843</v>
+        <v>0.590556550061643</v>
       </c>
       <c r="D84" t="n">
-        <v>213.4938459498908</v>
+        <v>157.8605100570186</v>
       </c>
       <c r="E84" t="n">
-        <v>307.1179410894192</v>
+        <v>205.1988348282988</v>
       </c>
       <c r="F84" t="n">
-        <v>21.32619540162688</v>
+        <v>17.26071903695232</v>
       </c>
       <c r="G84" t="n">
         <v>93</v>
@@ -2706,16 +2706,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-0.532219666862956</v>
+        <v>0.1415194769067905</v>
       </c>
       <c r="D85" t="n">
-        <v>7.365130418386215</v>
+        <v>6.124139076624161</v>
       </c>
       <c r="E85" t="n">
-        <v>10.79309471856502</v>
+        <v>8.07887103901392</v>
       </c>
       <c r="F85" t="n">
-        <v>68.03604520476495</v>
+        <v>99.0219462964979</v>
       </c>
       <c r="G85" t="n">
         <v>78</v>
@@ -2733,16 +2733,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-5.718140023321393</v>
+        <v>0.7580860276420172</v>
       </c>
       <c r="D86" t="n">
-        <v>226.9578906165229</v>
+        <v>36.58708614773221</v>
       </c>
       <c r="E86" t="n">
-        <v>245.8074745429912</v>
+        <v>46.64456326508732</v>
       </c>
       <c r="F86" t="n">
-        <v>80.53521177779301</v>
+        <v>19.01715152948839</v>
       </c>
       <c r="G86" t="n">
         <v>18</v>
@@ -2760,16 +2760,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-1.661976362016268</v>
+        <v>0.5367643031595974</v>
       </c>
       <c r="D87" t="n">
-        <v>29.10442543029785</v>
+        <v>11.35120168964515</v>
       </c>
       <c r="E87" t="n">
-        <v>37.3828985666974</v>
+        <v>15.59451535038178</v>
       </c>
       <c r="F87" t="n">
-        <v>34.79943290552116</v>
+        <v>15.86500041252017</v>
       </c>
       <c r="G87" t="n">
         <v>89</v>
@@ -2787,16 +2787,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-1.202413871108631</v>
+        <v>0.5808555679791784</v>
       </c>
       <c r="D88" t="n">
-        <v>376.0615269824712</v>
+        <v>150.4101691968513</v>
       </c>
       <c r="E88" t="n">
-        <v>444.7305532179948</v>
+        <v>194.0123390981547</v>
       </c>
       <c r="F88" t="n">
-        <v>44.36969329582796</v>
+        <v>24.08252308704057</v>
       </c>
       <c r="G88" t="n">
         <v>99</v>
@@ -2814,16 +2814,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>0.1841206177070547</v>
+        <v>0.5652501682642139</v>
       </c>
       <c r="D89" t="n">
-        <v>193.6379781743532</v>
+        <v>175.4206730011971</v>
       </c>
       <c r="E89" t="n">
-        <v>289.6615900097273</v>
+        <v>211.4451060573605</v>
       </c>
       <c r="F89" t="n">
-        <v>20.86475764425462</v>
+        <v>19.31380563152394</v>
       </c>
       <c r="G89" t="n">
         <v>93</v>
@@ -2841,16 +2841,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-0.5031583192291444</v>
+        <v>0.1168629397776423</v>
       </c>
       <c r="D90" t="n">
-        <v>7.010259964527228</v>
+        <v>5.906306291237856</v>
       </c>
       <c r="E90" t="n">
-        <v>10.69024933310838</v>
+        <v>8.19406693791341</v>
       </c>
       <c r="F90" t="n">
-        <v>63.3746028623483</v>
+        <v>87.54226732459733</v>
       </c>
       <c r="G90" t="n">
         <v>78</v>
@@ -2868,16 +2868,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-4.753168489673673</v>
+        <v>0.5629312413757643</v>
       </c>
       <c r="D91" t="n">
-        <v>208.1590353647868</v>
+        <v>45.33734300401476</v>
       </c>
       <c r="E91" t="n">
-        <v>227.4699885177035</v>
+        <v>62.69680889672151</v>
       </c>
       <c r="F91" t="n">
-        <v>72.20801249518254</v>
+        <v>22.7672778330632</v>
       </c>
       <c r="G91" t="n">
         <v>18</v>
@@ -2895,16 +2895,16 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-0.3680810879712231</v>
+        <v>0.6847519434432084</v>
       </c>
       <c r="D92" t="n">
-        <v>18.47897122415264</v>
+        <v>9.435980207464668</v>
       </c>
       <c r="E92" t="n">
-        <v>26.79950637046448</v>
+        <v>12.86462353861667</v>
       </c>
       <c r="F92" t="n">
-        <v>23.26730313964255</v>
+        <v>13.73313745933388</v>
       </c>
       <c r="G92" t="n">
         <v>89</v>
@@ -2922,16 +2922,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-0.2090163509592375</v>
+        <v>0.7217784220055788</v>
       </c>
       <c r="D93" t="n">
-        <v>261.1705067952474</v>
+        <v>110.5426709724195</v>
       </c>
       <c r="E93" t="n">
-        <v>329.5061972614428</v>
+        <v>158.0676169426295</v>
       </c>
       <c r="F93" t="n">
-        <v>31.92903829052065</v>
+        <v>17.05612994324234</v>
       </c>
       <c r="G93" t="n">
         <v>99</v>
@@ -2949,16 +2949,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-0.1923919067754845</v>
+        <v>0.6939263126797693</v>
       </c>
       <c r="D94" t="n">
-        <v>253.1833991594212</v>
+        <v>118.8625878774992</v>
       </c>
       <c r="E94" t="n">
-        <v>350.1768573927458</v>
+        <v>177.4152404846639</v>
       </c>
       <c r="F94" t="n">
-        <v>25.72794160950618</v>
+        <v>11.81882785838948</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
@@ -2976,16 +2976,16 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-0.2051268473983452</v>
+        <v>0.1913060368318533</v>
       </c>
       <c r="D95" t="n">
-        <v>6.17689197185712</v>
+        <v>5.248897625849797</v>
       </c>
       <c r="E95" t="n">
-        <v>9.57198155286315</v>
+        <v>7.841110117920454</v>
       </c>
       <c r="F95" t="n">
-        <v>54.78162893268976</v>
+        <v>57.06260210345159</v>
       </c>
       <c r="G95" t="n">
         <v>78</v>
@@ -3003,16 +3003,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-6.403128501409416</v>
+        <v>0.7725655219904697</v>
       </c>
       <c r="D96" t="n">
-        <v>242.4200292163425</v>
+        <v>33.4616207546658</v>
       </c>
       <c r="E96" t="n">
-        <v>258.0347535127812</v>
+        <v>45.22709630868142</v>
       </c>
       <c r="F96" t="n">
-        <v>88.25368616458532</v>
+        <v>11.6595712707796</v>
       </c>
       <c r="G96" t="n">
         <v>18</v>
@@ -3030,16 +3030,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-0.5396678551145384</v>
+        <v>0.7023783693521839</v>
       </c>
       <c r="D97" t="n">
-        <v>19.22976733861345</v>
+        <v>8.952612587575162</v>
       </c>
       <c r="E97" t="n">
-        <v>28.43049337471401</v>
+        <v>12.49980157025302</v>
       </c>
       <c r="F97" t="n">
-        <v>23.93276935152997</v>
+        <v>13.00504159707637</v>
       </c>
       <c r="G97" t="n">
         <v>89</v>
@@ -3057,16 +3057,16 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-0.465898680829816</v>
+        <v>0.7376848080203795</v>
       </c>
       <c r="D98" t="n">
-        <v>284.1608225504557</v>
+        <v>107.0831866023516</v>
       </c>
       <c r="E98" t="n">
-        <v>362.8268989355907</v>
+        <v>153.4826266051584</v>
       </c>
       <c r="F98" t="n">
-        <v>34.17726241087783</v>
+        <v>16.66395703138957</v>
       </c>
       <c r="G98" t="n">
         <v>99</v>
@@ -3084,16 +3084,16 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-0.262779500238401</v>
+        <v>0.7197618900666303</v>
       </c>
       <c r="D99" t="n">
-        <v>252.0371661442582</v>
+        <v>112.1000677949639</v>
       </c>
       <c r="E99" t="n">
-        <v>360.3642436888967</v>
+        <v>169.7624069101066</v>
       </c>
       <c r="F99" t="n">
-        <v>24.83133565360496</v>
+        <v>11.15549229753781</v>
       </c>
       <c r="G99" t="n">
         <v>93</v>
@@ -3111,16 +3111,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-0.1328304262626649</v>
+        <v>0.1688189723770968</v>
       </c>
       <c r="D100" t="n">
-        <v>6.096722061817463</v>
+        <v>5.016525867657784</v>
       </c>
       <c r="E100" t="n">
-        <v>9.28042626841312</v>
+        <v>7.94938009794204</v>
       </c>
       <c r="F100" t="n">
-        <v>55.0044433349492</v>
+        <v>49.66040036330861</v>
       </c>
       <c r="G100" t="n">
         <v>78</v>
@@ -3138,16 +3138,16 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-6.65250124129068</v>
+        <v>0.7326959505267143</v>
       </c>
       <c r="D101" t="n">
-        <v>245.2689612706502</v>
+        <v>36.91571384006076</v>
       </c>
       <c r="E101" t="n">
-        <v>262.3446810685194</v>
+        <v>49.03129046818326</v>
       </c>
       <c r="F101" t="n">
-        <v>88.30813673595239</v>
+        <v>14.69701134889321</v>
       </c>
       <c r="G101" t="n">
         <v>18</v>
@@ -3165,16 +3165,16 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-0.6105230048210351</v>
+        <v>0.6397616096194014</v>
       </c>
       <c r="D102" t="n">
-        <v>21.23204966341511</v>
+        <v>9.895486295892951</v>
       </c>
       <c r="E102" t="n">
-        <v>29.07731768305414</v>
+        <v>13.75200018768039</v>
       </c>
       <c r="F102" t="n">
-        <v>26.20545300843988</v>
+        <v>14.29468588763907</v>
       </c>
       <c r="G102" t="n">
         <v>89</v>
@@ -3192,16 +3192,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-0.6305797074873616</v>
+        <v>0.7129782713182793</v>
       </c>
       <c r="D103" t="n">
-        <v>304.3984029750631</v>
+        <v>122.3592945445668</v>
       </c>
       <c r="E103" t="n">
-        <v>382.6648014986005</v>
+        <v>160.5479960094188</v>
       </c>
       <c r="F103" t="n">
-        <v>38.61739532235065</v>
+        <v>19.63218544658635</v>
       </c>
       <c r="G103" t="n">
         <v>99</v>
@@ -3219,16 +3219,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-0.4723667180206208</v>
+        <v>0.6650933117943441</v>
       </c>
       <c r="D104" t="n">
-        <v>300.060799547421</v>
+        <v>130.8135720529864</v>
       </c>
       <c r="E104" t="n">
-        <v>389.1221268629725</v>
+        <v>185.5837033088904</v>
       </c>
       <c r="F104" t="n">
-        <v>29.86602709319129</v>
+        <v>13.49157205514467</v>
       </c>
       <c r="G104" t="n">
         <v>93</v>
@@ -3246,16 +3246,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-0.6054362147766987</v>
+        <v>0.2038430857275224</v>
       </c>
       <c r="D105" t="n">
-        <v>7.390923634553567</v>
+        <v>5.490238122450999</v>
       </c>
       <c r="E105" t="n">
-        <v>11.04795762596857</v>
+        <v>7.78009299228574</v>
       </c>
       <c r="F105" t="n">
-        <v>71.46432785134684</v>
+        <v>93.9449581372713</v>
       </c>
       <c r="G105" t="n">
         <v>78</v>
@@ -3273,16 +3273,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>-6.877170957055541</v>
+        <v>0.6374116337718334</v>
       </c>
       <c r="D106" t="n">
-        <v>250.2345217598809</v>
+        <v>36.91522894965278</v>
       </c>
       <c r="E106" t="n">
-        <v>266.1679101043237</v>
+        <v>57.10544069494923</v>
       </c>
       <c r="F106" t="n">
-        <v>91.2008337242217</v>
+        <v>21.46846094843863</v>
       </c>
       <c r="G106" t="n">
         <v>18</v>
@@ -3300,16 +3300,16 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>-0.6405610935862798</v>
+        <v>0.6524097794590664</v>
       </c>
       <c r="D107" t="n">
-        <v>21.36564614799585</v>
+        <v>9.898699042502415</v>
       </c>
       <c r="E107" t="n">
-        <v>29.34722751574721</v>
+        <v>13.50842287034252</v>
       </c>
       <c r="F107" t="n">
-        <v>26.16281808231566</v>
+        <v>14.13965998991472</v>
       </c>
       <c r="G107" t="n">
         <v>89</v>
@@ -3327,16 +3327,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>-0.4226068654313968</v>
+        <v>0.6728840244971029</v>
       </c>
       <c r="D108" t="n">
-        <v>292.7752334132339</v>
+        <v>131.4957185995699</v>
       </c>
       <c r="E108" t="n">
-        <v>357.4291349357281</v>
+        <v>171.3950907542329</v>
       </c>
       <c r="F108" t="n">
-        <v>37.41024216704611</v>
+        <v>20.63459306335193</v>
       </c>
       <c r="G108" t="n">
         <v>99</v>
@@ -3354,16 +3354,16 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>-0.5043186532267536</v>
+        <v>0.6813015944970562</v>
       </c>
       <c r="D109" t="n">
-        <v>303.0115182527932</v>
+        <v>134.5514897172169</v>
       </c>
       <c r="E109" t="n">
-        <v>393.3216491334703</v>
+        <v>181.0372199145226</v>
       </c>
       <c r="F109" t="n">
-        <v>30.56847213527716</v>
+        <v>13.93058685892209</v>
       </c>
       <c r="G109" t="n">
         <v>93</v>
@@ -3381,16 +3381,16 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>-0.6592724614386916</v>
+        <v>0.2076593253322027</v>
       </c>
       <c r="D110" t="n">
-        <v>7.585002672977937</v>
+        <v>5.567375134199094</v>
       </c>
       <c r="E110" t="n">
-        <v>11.23166974041273</v>
+        <v>7.761424333319248</v>
       </c>
       <c r="F110" t="n">
-        <v>72.12605330803041</v>
+        <v>99.13147295167526</v>
       </c>
       <c r="G110" t="n">
         <v>78</v>
@@ -3408,16 +3408,16 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>-6.637238973400845</v>
+        <v>0.6648830366873333</v>
       </c>
       <c r="D111" t="n">
-        <v>247.0020982954237</v>
+        <v>35.1936280992296</v>
       </c>
       <c r="E111" t="n">
-        <v>262.0829383345823</v>
+        <v>54.89954696913743</v>
       </c>
       <c r="F111" t="n">
-        <v>90.60451631097899</v>
+        <v>19.82188346399138</v>
       </c>
       <c r="G111" t="n">
         <v>18</v>
@@ -3435,16 +3435,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>-0.4968916869364484</v>
+        <v>0.7072815836947179</v>
       </c>
       <c r="D112" t="n">
-        <v>19.42545254310865</v>
+        <v>9.041890519388605</v>
       </c>
       <c r="E112" t="n">
-        <v>28.03277319333644</v>
+        <v>12.39640898941673</v>
       </c>
       <c r="F112" t="n">
-        <v>24.32207865199499</v>
+        <v>13.05467821701701</v>
       </c>
       <c r="G112" t="n">
         <v>89</v>
@@ -3462,16 +3462,16 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>-0.3207458834598917</v>
+        <v>0.6977267399047193</v>
       </c>
       <c r="D113" t="n">
-        <v>273.1559184681286</v>
+        <v>118.5877229324495</v>
       </c>
       <c r="E113" t="n">
-        <v>344.3952340377706</v>
+        <v>164.7583242457878</v>
       </c>
       <c r="F113" t="n">
-        <v>32.98985811930012</v>
+        <v>18.58210120158442</v>
       </c>
       <c r="G113" t="n">
         <v>99</v>
@@ -3489,16 +3489,16 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>-0.3798871699013817</v>
+        <v>0.6992394240453643</v>
       </c>
       <c r="D114" t="n">
-        <v>270.4888190812962</v>
+        <v>124.2964562857023</v>
       </c>
       <c r="E114" t="n">
-        <v>376.7035555791625</v>
+        <v>175.8686299562384</v>
       </c>
       <c r="F114" t="n">
-        <v>26.51740610933909</v>
+        <v>12.31184383452933</v>
       </c>
       <c r="G114" t="n">
         <v>93</v>
@@ -3516,16 +3516,16 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>-0.3395805452418252</v>
+        <v>0.2166064080580433</v>
       </c>
       <c r="D115" t="n">
-        <v>6.604273903064239</v>
+        <v>5.176330933204064</v>
       </c>
       <c r="E115" t="n">
-        <v>10.09182911463809</v>
+        <v>7.717479060197255</v>
       </c>
       <c r="F115" t="n">
-        <v>64.17045003936779</v>
+        <v>69.0451328002799</v>
       </c>
       <c r="G115" t="n">
         <v>78</v>
@@ -3543,16 +3543,16 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>-6.724553195188505</v>
+        <v>0.864272375870259</v>
       </c>
       <c r="D116" t="n">
-        <v>245.6571519639757</v>
+        <v>24.43050214979384</v>
       </c>
       <c r="E116" t="n">
-        <v>263.576837759576</v>
+        <v>34.93853398958947</v>
       </c>
       <c r="F116" t="n">
-        <v>87.65566083590554</v>
+        <v>9.892012019750341</v>
       </c>
       <c r="G116" t="n">
         <v>18</v>
@@ -3570,16 +3570,16 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>-0.7640848863776069</v>
+        <v>0.5033312982782623</v>
       </c>
       <c r="D117" t="n">
-        <v>21.86369081561485</v>
+        <v>11.07084334298466</v>
       </c>
       <c r="E117" t="n">
-        <v>30.43200836306427</v>
+        <v>16.1474619363449</v>
       </c>
       <c r="F117" t="n">
-        <v>25.90117134530095</v>
+        <v>14.83670373344854</v>
       </c>
       <c r="G117" t="n">
         <v>89</v>
@@ -3597,16 +3597,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>-1.111224517516397</v>
+        <v>0.6517010852979592</v>
       </c>
       <c r="D118" t="n">
-        <v>356.3497436215179</v>
+        <v>141.1946617665917</v>
       </c>
       <c r="E118" t="n">
-        <v>435.4263532492881</v>
+        <v>176.8575325855709</v>
       </c>
       <c r="F118" t="n">
-        <v>41.03150816647485</v>
+        <v>23.0381305327618</v>
       </c>
       <c r="G118" t="n">
         <v>99</v>
@@ -3624,16 +3624,16 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>-0.6321118830122627</v>
+        <v>0.6264223135665532</v>
       </c>
       <c r="D119" t="n">
-        <v>312.6606757051201</v>
+        <v>145.7634841754872</v>
       </c>
       <c r="E119" t="n">
-        <v>409.6876708347244</v>
+        <v>196.0055598180556</v>
       </c>
       <c r="F119" t="n">
-        <v>28.332791683221</v>
+        <v>14.55952539591164</v>
       </c>
       <c r="G119" t="n">
         <v>93</v>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>-0.5802128288885171</v>
+        <v>0.1727249867666266</v>
       </c>
       <c r="D120" t="n">
-        <v>7.659635287064773</v>
+        <v>5.819104958803226</v>
       </c>
       <c r="E120" t="n">
-        <v>10.96082550264481</v>
+        <v>7.930679624046399</v>
       </c>
       <c r="F120" t="n">
-        <v>69.59439923098216</v>
+        <v>92.82926559810764</v>
       </c>
       <c r="G120" t="n">
         <v>78</v>
@@ -3678,16 +3678,16 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>-5.810030066047833</v>
+        <v>0.643548475755217</v>
       </c>
       <c r="D121" t="n">
-        <v>228.6884284549289</v>
+        <v>43.03056928846571</v>
       </c>
       <c r="E121" t="n">
-        <v>247.4828301056637</v>
+        <v>56.62012095090019</v>
       </c>
       <c r="F121" t="n">
-        <v>80.49451020914391</v>
+        <v>22.18053333769702</v>
       </c>
       <c r="G121" t="n">
         <v>18</v>
@@ -3705,16 +3705,16 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>-0.7929285258524696</v>
+        <v>0.5276967950172697</v>
       </c>
       <c r="D122" t="n">
-        <v>22.48738595341029</v>
+        <v>11.45174300804567</v>
       </c>
       <c r="E122" t="n">
-        <v>30.67978865144136</v>
+        <v>15.74640144086898</v>
       </c>
       <c r="F122" t="n">
-        <v>27.44536352285757</v>
+        <v>15.25860633833175</v>
       </c>
       <c r="G122" t="n">
         <v>89</v>
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>-0.2157605336262309</v>
+        <v>0.5503237409369157</v>
       </c>
       <c r="D123" t="n">
-        <v>269.2971911189532</v>
+        <v>163.6635144166272</v>
       </c>
       <c r="E123" t="n">
-        <v>330.423951407404</v>
+        <v>200.954381965547</v>
       </c>
       <c r="F123" t="n">
-        <v>34.9290583297329</v>
+        <v>22.48772459925814</v>
       </c>
       <c r="G123" t="n">
         <v>99</v>
@@ -3759,16 +3759,16 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>-5.621455468903743</v>
+        <v>0.5453666592995693</v>
       </c>
       <c r="D124" t="n">
-        <v>732.9597909578713</v>
+        <v>175.6676894977529</v>
       </c>
       <c r="E124" t="n">
-        <v>825.1913414992816</v>
+        <v>216.2263251202972</v>
       </c>
       <c r="F124" t="n">
-        <v>88.85349637498675</v>
+        <v>20.23343800584495</v>
       </c>
       <c r="G124" t="n">
         <v>93</v>
@@ -3786,16 +3786,16 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>-0.3998725522180948</v>
+        <v>0.2059722156526347</v>
       </c>
       <c r="D125" t="n">
-        <v>7.04068355071239</v>
+        <v>5.198627728682298</v>
       </c>
       <c r="E125" t="n">
-        <v>10.31643678378333</v>
+        <v>7.769683035399572</v>
       </c>
       <c r="F125" t="n">
-        <v>62.75296199357226</v>
+        <v>74.91108708202661</v>
       </c>
       <c r="G125" t="n">
         <v>78</v>
@@ -3813,16 +3813,16 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>-4.051612108349482</v>
+        <v>0.7155583623950242</v>
       </c>
       <c r="D126" t="n">
-        <v>193.7168742285834</v>
+        <v>39.05882178412543</v>
       </c>
       <c r="E126" t="n">
-        <v>213.1501079333415</v>
+        <v>50.57863910804963</v>
       </c>
       <c r="F126" t="n">
-        <v>67.76856678471694</v>
+        <v>22.62623679154383</v>
       </c>
       <c r="G126" t="n">
         <v>18</v>
@@ -3840,16 +3840,16 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>-0.9547916558402294</v>
+        <v>0.4949994092352311</v>
       </c>
       <c r="D127" t="n">
-        <v>23.67369086019109</v>
+        <v>11.71723457936491</v>
       </c>
       <c r="E127" t="n">
-        <v>32.03473334283605</v>
+        <v>16.28233987777078</v>
       </c>
       <c r="F127" t="n">
-        <v>27.76904022693836</v>
+        <v>16.36006750149</v>
       </c>
       <c r="G127" t="n">
         <v>89</v>
@@ -3867,16 +3867,16 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>-0.7162640963836804</v>
+        <v>0.4960231385760961</v>
       </c>
       <c r="D128" t="n">
-        <v>319.4340892753216</v>
+        <v>159.0027918960109</v>
       </c>
       <c r="E128" t="n">
-        <v>392.5902941918702</v>
+        <v>212.7417855085716</v>
       </c>
       <c r="F128" t="n">
-        <v>39.32166216424348</v>
+        <v>22.16744205075713</v>
       </c>
       <c r="G128" t="n">
         <v>99</v>
@@ -3894,16 +3894,16 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>-3.126422551974676</v>
+        <v>0.204858343557247</v>
       </c>
       <c r="D129" t="n">
-        <v>493.3934372112315</v>
+        <v>238.0165474184098</v>
       </c>
       <c r="E129" t="n">
-        <v>651.4255378782099</v>
+        <v>285.9566361196083</v>
       </c>
       <c r="F129" t="n">
-        <v>63.31144084209374</v>
+        <v>30.05349649382102</v>
       </c>
       <c r="G129" t="n">
         <v>93</v>
@@ -3921,16 +3921,16 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>-0.6005965692179651</v>
+        <v>0.1337739543756128</v>
       </c>
       <c r="D130" t="n">
-        <v>7.92194258249723</v>
+        <v>6.142794804695325</v>
       </c>
       <c r="E130" t="n">
-        <v>11.03129282332148</v>
+        <v>8.115234454011297</v>
       </c>
       <c r="F130" t="n">
-        <v>75.86222281903726</v>
+        <v>91.79126135778407</v>
       </c>
       <c r="G130" t="n">
         <v>78</v>
@@ -3948,16 +3948,16 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>-4.114889802433125</v>
+        <v>0.6000951369404413</v>
       </c>
       <c r="D131" t="n">
-        <v>189.5305701361762</v>
+        <v>46.52263302273221</v>
       </c>
       <c r="E131" t="n">
-        <v>214.4809377903058</v>
+        <v>59.97205041259172</v>
       </c>
       <c r="F131" t="n">
-        <v>64.40307485060785</v>
+        <v>28.97270910339529</v>
       </c>
       <c r="G131" t="n">
         <v>18</v>
@@ -3975,16 +3975,16 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>-0.1850723432893764</v>
+        <v>0.3647596617491747</v>
       </c>
       <c r="D132" t="n">
-        <v>19.6083290228683</v>
+        <v>13.14912834596098</v>
       </c>
       <c r="E132" t="n">
-        <v>24.94269099411932</v>
+        <v>18.26164546488393</v>
       </c>
       <c r="F132" t="n">
-        <v>28.90965427563238</v>
+        <v>17.03261310409479</v>
       </c>
       <c r="G132" t="n">
         <v>89</v>
@@ -4002,16 +4002,16 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>-0.04240186913696875</v>
+        <v>0.4800960165174919</v>
       </c>
       <c r="D133" t="n">
-        <v>242.2717172641947</v>
+        <v>164.4698588053385</v>
       </c>
       <c r="E133" t="n">
-        <v>305.9603088372051</v>
+        <v>216.0772647328837</v>
       </c>
       <c r="F133" t="n">
-        <v>42.7193598365474</v>
+        <v>22.12831933034489</v>
       </c>
       <c r="G133" t="n">
         <v>99</v>
@@ -4029,16 +4029,16 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>-13.0312519738583</v>
+        <v>-0.2341436419126883</v>
       </c>
       <c r="D134" t="n">
-        <v>1156.430094401042</v>
+        <v>313.2239573488953</v>
       </c>
       <c r="E134" t="n">
-        <v>1201.229925467327</v>
+        <v>356.2548467720654</v>
       </c>
       <c r="F134" t="n">
-        <v>139.6627127713542</v>
+        <v>39.21522691914433</v>
       </c>
       <c r="G134" t="n">
         <v>93</v>
@@ -4056,16 +4056,16 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>-0.395943847276002</v>
+        <v>0.1248530706080643</v>
       </c>
       <c r="D135" t="n">
-        <v>7.281949122746785</v>
+        <v>6.190805520766821</v>
       </c>
       <c r="E135" t="n">
-        <v>10.30195021040098</v>
+        <v>8.156915044220668</v>
       </c>
       <c r="F135" t="n">
-        <v>73.9955495354035</v>
+        <v>94.18551477040586</v>
       </c>
       <c r="G135" t="n">
         <v>78</v>
@@ -4083,16 +4083,16 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>-1.189841408131175</v>
+        <v>0.6104782961903857</v>
       </c>
       <c r="D136" t="n">
-        <v>116.0142220391168</v>
+        <v>43.39063178168403</v>
       </c>
       <c r="E136" t="n">
-        <v>140.3385196051105</v>
+        <v>59.18837071665919</v>
       </c>
       <c r="F136" t="n">
-        <v>44.27039522958592</v>
+        <v>26.26884426637769</v>
       </c>
       <c r="G136" t="n">
         <v>18</v>
@@ -4110,16 +4110,16 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>-0.8921087159721524</v>
+        <v>0.4299659217927599</v>
       </c>
       <c r="D137" t="n">
-        <v>23.99865214744311</v>
+        <v>12.10967310358969</v>
       </c>
       <c r="E137" t="n">
-        <v>31.51693079906481</v>
+        <v>17.29901131613803</v>
       </c>
       <c r="F137" t="n">
-        <v>28.87970069666251</v>
+        <v>16.59606596524533</v>
       </c>
       <c r="G137" t="n">
         <v>89</v>
@@ -4137,16 +4137,16 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>-0.8186471422007457</v>
+        <v>0.2825215536107583</v>
       </c>
       <c r="D138" t="n">
-        <v>337.0378348610618</v>
+        <v>203.0594577981968</v>
       </c>
       <c r="E138" t="n">
-        <v>404.1305874524475</v>
+        <v>253.8352490503647</v>
       </c>
       <c r="F138" t="n">
-        <v>40.01558567093836</v>
+        <v>26.07671332296218</v>
       </c>
       <c r="G138" t="n">
         <v>99</v>
@@ -4164,16 +4164,16 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>0.4468806452318094</v>
+        <v>-0.132420744479897</v>
       </c>
       <c r="D139" t="n">
-        <v>197.7466535670783</v>
+        <v>269.7283820695774</v>
       </c>
       <c r="E139" t="n">
-        <v>238.4994373713666</v>
+        <v>341.257209128101</v>
       </c>
       <c r="F139" t="n">
-        <v>24.01573487367146</v>
+        <v>33.28661242225645</v>
       </c>
       <c r="G139" t="n">
         <v>93</v>
@@ -4191,16 +4191,16 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>-0.3861896699118585</v>
+        <v>0.1272814678135916</v>
       </c>
       <c r="D140" t="n">
-        <v>7.122512514774616</v>
+        <v>5.774391064277062</v>
       </c>
       <c r="E140" t="n">
-        <v>10.2658946038678</v>
+        <v>8.145590094475748</v>
       </c>
       <c r="F140" t="n">
-        <v>68.26947567827493</v>
+        <v>95.44591828505841</v>
       </c>
       <c r="G140" t="n">
         <v>78</v>
@@ -4218,16 +4218,16 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>-2.684432482159305</v>
+        <v>0.6635296596476461</v>
       </c>
       <c r="D141" t="n">
-        <v>162.8340509202745</v>
+        <v>43.66075303819444</v>
       </c>
       <c r="E141" t="n">
-        <v>182.035403309194</v>
+        <v>55.01029176909891</v>
       </c>
       <c r="F141" t="n">
-        <v>60.78582093467506</v>
+        <v>23.97905384784499</v>
       </c>
       <c r="G141" t="n">
         <v>18</v>
@@ -4245,16 +4245,16 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>-1.375110159658862</v>
+        <v>0.4949181916822174</v>
       </c>
       <c r="D142" t="n">
-        <v>29.06336885087946</v>
+        <v>11.87575102388189</v>
       </c>
       <c r="E142" t="n">
-        <v>35.31122252287937</v>
+        <v>16.28364914221611</v>
       </c>
       <c r="F142" t="n">
-        <v>35.27891556358686</v>
+        <v>16.6555774705703</v>
       </c>
       <c r="G142" t="n">
         <v>89</v>
@@ -4272,16 +4272,16 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>-0.5773681166649531</v>
+        <v>0.457979896661212</v>
       </c>
       <c r="D143" t="n">
-        <v>311.6756346731475</v>
+        <v>168.6352406511403</v>
       </c>
       <c r="E143" t="n">
-        <v>376.3691593384723</v>
+        <v>220.6252416582415</v>
       </c>
       <c r="F143" t="n">
-        <v>37.95270631772003</v>
+        <v>22.58679960855222</v>
       </c>
       <c r="G143" t="n">
         <v>99</v>
@@ -4299,16 +4299,16 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>0.490650735272455</v>
+        <v>0.598186243070749</v>
       </c>
       <c r="D144" t="n">
-        <v>176.8882636613743</v>
+        <v>169.9465985041793</v>
       </c>
       <c r="E144" t="n">
-        <v>228.8683680361679</v>
+        <v>203.2779757239644</v>
       </c>
       <c r="F144" t="n">
-        <v>19.53229463979732</v>
+        <v>20.11173521025076</v>
       </c>
       <c r="G144" t="n">
         <v>93</v>
@@ -4326,16 +4326,16 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>-0.5572284863737518</v>
+        <v>0.1540243766496681</v>
       </c>
       <c r="D145" t="n">
-        <v>7.711874729547745</v>
+        <v>6.06515620304988</v>
       </c>
       <c r="E145" t="n">
-        <v>10.88082040361029</v>
+        <v>8.019815494952983</v>
       </c>
       <c r="F145" t="n">
-        <v>71.30788989082897</v>
+        <v>102.9250143676124</v>
       </c>
       <c r="G145" t="n">
         <v>78</v>
@@ -4353,16 +4353,16 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>-3.944672139307774</v>
+        <v>0.5543475641506493</v>
       </c>
       <c r="D146" t="n">
-        <v>190.8397095998128</v>
+        <v>48.7422612508138</v>
       </c>
       <c r="E146" t="n">
-        <v>210.8819017498205</v>
+        <v>63.30947279721304</v>
       </c>
       <c r="F146" t="n">
-        <v>66.12566498991531</v>
+        <v>26.8932328409692</v>
       </c>
       <c r="G146" t="n">
         <v>18</v>
@@ -4380,16 +4380,16 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>-0.962292991103153</v>
+        <v>0.4867941414831161</v>
       </c>
       <c r="D147" t="n">
-        <v>24.62734177407254</v>
+        <v>11.69218496258339</v>
       </c>
       <c r="E147" t="n">
-        <v>32.09613967734862</v>
+        <v>16.41408490639951</v>
       </c>
       <c r="F147" t="n">
-        <v>29.39829538600128</v>
+        <v>15.83508278846472</v>
       </c>
       <c r="G147" t="n">
         <v>89</v>
@@ -4407,16 +4407,16 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>-1.082816543098563</v>
+        <v>0.5909007181048812</v>
       </c>
       <c r="D148" t="n">
-        <v>362.0314745662188</v>
+        <v>141.3004147308041</v>
       </c>
       <c r="E148" t="n">
-        <v>432.4869516782883</v>
+        <v>191.6734057475353</v>
       </c>
       <c r="F148" t="n">
-        <v>41.80937108132183</v>
+        <v>19.52734898128766</v>
       </c>
       <c r="G148" t="n">
         <v>99</v>
@@ -4434,16 +4434,16 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>0.1912224425551839</v>
+        <v>0.6173083472711698</v>
       </c>
       <c r="D149" t="n">
-        <v>226.5905938917591</v>
+        <v>158.864995484711</v>
       </c>
       <c r="E149" t="n">
-        <v>288.3981544598179</v>
+        <v>198.3820716708245</v>
       </c>
       <c r="F149" t="n">
-        <v>26.7243620989343</v>
+        <v>18.62225433580234</v>
       </c>
       <c r="G149" t="n">
         <v>93</v>
@@ -4461,16 +4461,16 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>-0.6025571598298576</v>
+        <v>0.1218839155323801</v>
       </c>
       <c r="D150" t="n">
-        <v>7.943279963273269</v>
+        <v>6.092277924219768</v>
       </c>
       <c r="E150" t="n">
-        <v>11.03804693943051</v>
+        <v>8.170740515857306</v>
       </c>
       <c r="F150" t="n">
-        <v>71.79234169214446</v>
+        <v>92.86981761614767</v>
       </c>
       <c r="G150" t="n">
         <v>78</v>
@@ -4488,16 +4488,16 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>-2.630121872904626</v>
+        <v>0.7063614740965158</v>
       </c>
       <c r="D151" t="n">
-        <v>163.4619856940375</v>
+        <v>39.53766632080078</v>
       </c>
       <c r="E151" t="n">
-        <v>180.6887701842875</v>
+        <v>51.38981713265726</v>
       </c>
       <c r="F151" t="n">
-        <v>59.50961899156562</v>
+        <v>17.87857129023833</v>
       </c>
       <c r="G151" t="n">
         <v>18</v>
@@ -4515,16 +4515,16 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>-1.131373334674514</v>
+        <v>0.4014010001655142</v>
       </c>
       <c r="D152" t="n">
-        <v>24.86636138230227</v>
+        <v>12.39470754044779</v>
       </c>
       <c r="E152" t="n">
-        <v>33.45034790291132</v>
+        <v>17.72714782759147</v>
       </c>
       <c r="F152" t="n">
-        <v>29.3827322938527</v>
+        <v>16.64378347070987</v>
       </c>
       <c r="G152" t="n">
         <v>89</v>
@@ -4542,16 +4542,16 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>-0.5826176239187095</v>
+        <v>0.4143688417531337</v>
       </c>
       <c r="D153" t="n">
-        <v>314.5085759018407</v>
+        <v>182.3427228831281</v>
       </c>
       <c r="E153" t="n">
-        <v>376.9949205372935</v>
+        <v>229.3293228272829</v>
       </c>
       <c r="F153" t="n">
-        <v>37.21698386488082</v>
+        <v>23.94963841706501</v>
       </c>
       <c r="G153" t="n">
         <v>99</v>
@@ -4569,16 +4569,16 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>0.349499475750688</v>
+        <v>0.1767803882127368</v>
       </c>
       <c r="D154" t="n">
-        <v>191.1952074932796</v>
+        <v>229.6259394820019</v>
       </c>
       <c r="E154" t="n">
-        <v>258.6436119309387</v>
+        <v>290.9616698917985</v>
       </c>
       <c r="F154" t="n">
-        <v>21.76120792155023</v>
+        <v>29.13360222118156</v>
       </c>
       <c r="G154" t="n">
         <v>93</v>
@@ -4596,16 +4596,16 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>-0.3794389395169082</v>
+        <v>0.1872148917763148</v>
       </c>
       <c r="D155" t="n">
-        <v>7.04024443259606</v>
+        <v>5.520095079373091</v>
       </c>
       <c r="E155" t="n">
-        <v>10.24086669113379</v>
+        <v>7.860919001724564</v>
       </c>
       <c r="F155" t="n">
-        <v>61.96886912339831</v>
+        <v>77.5616728772161</v>
       </c>
       <c r="G155" t="n">
         <v>78</v>
@@ -4623,16 +4623,16 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>-2.648735166623892</v>
+        <v>0.5701212154211805</v>
       </c>
       <c r="D156" t="n">
-        <v>163.630611843533</v>
+        <v>50.3381339179145</v>
       </c>
       <c r="E156" t="n">
-        <v>181.1514148424475</v>
+        <v>62.17897532428869</v>
       </c>
       <c r="F156" t="n">
-        <v>58.78690886752577</v>
+        <v>29.20547891461243</v>
       </c>
       <c r="G156" t="n">
         <v>18</v>
@@ -4650,16 +4650,16 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>-1.403168434485263</v>
+        <v>0.4419440833731526</v>
       </c>
       <c r="D157" t="n">
-        <v>28.17141895079881</v>
+        <v>12.8588040384014</v>
       </c>
       <c r="E157" t="n">
-        <v>35.51918404147411</v>
+        <v>17.11629375517964</v>
       </c>
       <c r="F157" t="n">
-        <v>34.18426412791427</v>
+        <v>17.89930229810535</v>
       </c>
       <c r="G157" t="n">
         <v>89</v>
@@ -4677,16 +4677,16 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>-0.7508773294774611</v>
+        <v>0.47989146802692</v>
       </c>
       <c r="D158" t="n">
-        <v>327.4013237230706</v>
+        <v>167.5224264125631</v>
       </c>
       <c r="E158" t="n">
-        <v>396.5293696581398</v>
+        <v>216.1197667460613</v>
       </c>
       <c r="F158" t="n">
-        <v>38.49670213075475</v>
+        <v>23.5919704107241</v>
       </c>
       <c r="G158" t="n">
         <v>99</v>
@@ -4704,16 +4704,16 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>0.2630877182184792</v>
+        <v>0.4836544320999886</v>
       </c>
       <c r="D159" t="n">
-        <v>199.4486418693296</v>
+        <v>197.69921710927</v>
       </c>
       <c r="E159" t="n">
-        <v>275.2870795257362</v>
+        <v>230.4348461030207</v>
       </c>
       <c r="F159" t="n">
-        <v>22.57385888508666</v>
+        <v>24.63292501637568</v>
       </c>
       <c r="G159" t="n">
         <v>93</v>
@@ -4731,16 +4731,16 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>-0.4849637884661606</v>
+        <v>0.1076924910694033</v>
       </c>
       <c r="D160" t="n">
-        <v>7.290579349566729</v>
+        <v>5.969116382109813</v>
       </c>
       <c r="E160" t="n">
-        <v>10.62535389385913</v>
+        <v>8.236500445280859</v>
       </c>
       <c r="F160" t="n">
-        <v>64.6302077288388</v>
+        <v>96.97234633285134</v>
       </c>
       <c r="G160" t="n">
         <v>78</v>
@@ -4758,16 +4758,16 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>-3.184125382756486</v>
+        <v>0.6243071579500401</v>
       </c>
       <c r="D161" t="n">
-        <v>171.2091181013319</v>
+        <v>43.13447401258681</v>
       </c>
       <c r="E161" t="n">
-        <v>193.9871239520244</v>
+        <v>58.12821876918683</v>
       </c>
       <c r="F161" t="n">
-        <v>60.02441873166796</v>
+        <v>26.19722710496919</v>
       </c>
       <c r="G161" t="n">
         <v>18</v>
@@ -4785,16 +4785,16 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>-0.9642709241582585</v>
+        <v>0.5168896173235962</v>
       </c>
       <c r="D162" t="n">
-        <v>23.90034840615948</v>
+        <v>11.63276445195916</v>
       </c>
       <c r="E162" t="n">
-        <v>32.11231158094653</v>
+        <v>15.92553601145005</v>
       </c>
       <c r="F162" t="n">
-        <v>28.11780138393544</v>
+        <v>15.61587707160156</v>
       </c>
       <c r="G162" t="n">
         <v>89</v>
@@ -4812,16 +4812,16 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>-1.554117729642243</v>
+        <v>0.3483663775548729</v>
       </c>
       <c r="D163" t="n">
-        <v>399.6270463731554</v>
+        <v>186.9812295316446</v>
       </c>
       <c r="E163" t="n">
-        <v>478.9254939163361</v>
+        <v>241.9074499391558</v>
       </c>
       <c r="F163" t="n">
-        <v>45.87206138181642</v>
+        <v>24.92420162066734</v>
       </c>
       <c r="G163" t="n">
         <v>99</v>
@@ -4839,16 +4839,16 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>0.07242579792643189</v>
+        <v>-1.579354425444291</v>
       </c>
       <c r="D164" t="n">
-        <v>256.270751953125</v>
+        <v>440.3839127735425</v>
       </c>
       <c r="E164" t="n">
-        <v>308.8533112269405</v>
+        <v>515.0310797263268</v>
       </c>
       <c r="F164" t="n">
-        <v>31.61860511773386</v>
+        <v>58.42259428657965</v>
       </c>
       <c r="G164" t="n">
         <v>93</v>
@@ -4866,16 +4866,16 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>-0.4364502872544169</v>
+        <v>0.1210886104357523</v>
       </c>
       <c r="D165" t="n">
-        <v>7.377525149247585</v>
+        <v>6.01818681985904</v>
       </c>
       <c r="E165" t="n">
-        <v>10.45034847100338</v>
+        <v>8.174439776696973</v>
       </c>
       <c r="F165" t="n">
-        <v>73.2163505245863</v>
+        <v>93.79522545113906</v>
       </c>
       <c r="G165" t="n">
         <v>78</v>
@@ -4893,16 +4893,16 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>-3.738717499012719</v>
+        <v>0.6738638994870259</v>
       </c>
       <c r="D166" t="n">
-        <v>188.0579630533854</v>
+        <v>43.03183322482639</v>
       </c>
       <c r="E166" t="n">
-        <v>206.443383595205</v>
+        <v>54.1589195532404</v>
       </c>
       <c r="F166" t="n">
-        <v>66.23039657251874</v>
+        <v>20.03358654558926</v>
       </c>
       <c r="G166" t="n">
         <v>18</v>
@@ -4920,16 +4920,16 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>-1.808246009661858</v>
+        <v>0.3560622460606868</v>
       </c>
       <c r="D167" t="n">
-        <v>30.76434574770124</v>
+        <v>13.18950854526477</v>
       </c>
       <c r="E167" t="n">
-        <v>38.39621812819471</v>
+        <v>18.3862354419139</v>
       </c>
       <c r="F167" t="n">
-        <v>37.12236465218499</v>
+        <v>17.91312112761136</v>
       </c>
       <c r="G167" t="n">
         <v>89</v>
@@ -4947,16 +4947,16 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>-1.344260543997093</v>
+        <v>0.5999586344964365</v>
       </c>
       <c r="D168" t="n">
-        <v>384.6456366644965</v>
+        <v>141.7668031634707</v>
       </c>
       <c r="E168" t="n">
-        <v>458.8285557719386</v>
+        <v>189.5395964410286</v>
       </c>
       <c r="F168" t="n">
-        <v>45.66125805593316</v>
+        <v>24.01958533113604</v>
       </c>
       <c r="G168" t="n">
         <v>99</v>
@@ -4974,16 +4974,16 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>-0.6635700294284386</v>
+        <v>0.6009833437635914</v>
       </c>
       <c r="D169" t="n">
-        <v>215.4946860036542</v>
+        <v>162.9718257124706</v>
       </c>
       <c r="E169" t="n">
-        <v>413.6170900520944</v>
+        <v>202.569212111974</v>
       </c>
       <c r="F169" t="n">
-        <v>24.67543044814636</v>
+        <v>17.83743887591655</v>
       </c>
       <c r="G169" t="n">
         <v>93</v>
@@ -5001,16 +5001,16 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>-0.6520014077398946</v>
+        <v>0.1209896609718023</v>
       </c>
       <c r="D170" t="n">
-        <v>8.068228220328306</v>
+        <v>6.101157212868715</v>
       </c>
       <c r="E170" t="n">
-        <v>11.20703372102616</v>
+        <v>8.174899910493876</v>
       </c>
       <c r="F170" t="n">
-        <v>71.52336694688746</v>
+        <v>97.23428768052094</v>
       </c>
       <c r="G170" t="n">
         <v>78</v>
@@ -5028,16 +5028,16 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>-4.756439140300148</v>
+        <v>0.6014676520938013</v>
       </c>
       <c r="D171" t="n">
-        <v>208.2415495978461</v>
+        <v>38.40614657931857</v>
       </c>
       <c r="E171" t="n">
-        <v>227.5346371678544</v>
+        <v>59.86904679429593</v>
       </c>
       <c r="F171" t="n">
-        <v>72.85515619415014</v>
+        <v>25.67629027127893</v>
       </c>
       <c r="G171" t="n">
         <v>18</v>
@@ -5055,16 +5055,16 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>-1.23128304448906</v>
+        <v>0.5444146348833292</v>
       </c>
       <c r="D172" t="n">
-        <v>25.69733934723929</v>
+        <v>11.07835949672742</v>
       </c>
       <c r="E172" t="n">
-        <v>34.22537439505618</v>
+        <v>15.46520763620225</v>
       </c>
       <c r="F172" t="n">
-        <v>30.44916708121425</v>
+        <v>15.90531517250105</v>
       </c>
       <c r="G172" t="n">
         <v>89</v>
@@ -5082,16 +5082,16 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>-1.002107037739293</v>
+        <v>0.6633376682003039</v>
       </c>
       <c r="D173" t="n">
-        <v>346.3102814645478</v>
+        <v>138.5388383961687</v>
       </c>
       <c r="E173" t="n">
-        <v>424.0246907014883</v>
+        <v>173.8780514474243</v>
       </c>
       <c r="F173" t="n">
-        <v>40.75636003653282</v>
+        <v>23.75527600465319</v>
       </c>
       <c r="G173" t="n">
         <v>99</v>
@@ -5109,16 +5109,16 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>-0.08365767759925946</v>
+        <v>0.6373203689746442</v>
       </c>
       <c r="D174" t="n">
-        <v>239.2281172557544</v>
+        <v>148.5833658197875</v>
       </c>
       <c r="E174" t="n">
-        <v>333.8289428909625</v>
+        <v>193.1254501614395</v>
       </c>
       <c r="F174" t="n">
-        <v>25.30975160680656</v>
+        <v>16.25830640271115</v>
       </c>
       <c r="G174" t="n">
         <v>93</v>
@@ -5136,16 +5136,16 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>-0.6086355708727904</v>
+        <v>0.1103708782468514</v>
       </c>
       <c r="D175" t="n">
-        <v>7.564220605752407</v>
+        <v>6.119526374034392</v>
       </c>
       <c r="E175" t="n">
-        <v>11.05896047927166</v>
+        <v>8.224129644684519</v>
       </c>
       <c r="F175" t="n">
-        <v>66.56303616514776</v>
+        <v>90.73074370653276</v>
       </c>
       <c r="G175" t="n">
         <v>78</v>
@@ -5163,16 +5163,16 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>-5.676736146511002</v>
+        <v>0.6674023843259844</v>
       </c>
       <c r="D176" t="n">
-        <v>224.6036987304688</v>
+        <v>42.41661495632596</v>
       </c>
       <c r="E176" t="n">
-        <v>245.0488485199228</v>
+        <v>54.69279531199587</v>
       </c>
       <c r="F176" t="n">
-        <v>78.64438860009913</v>
+        <v>23.16905108331941</v>
       </c>
       <c r="G176" t="n">
         <v>18</v>
@@ -5190,16 +5190,16 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>-1.554216314797547</v>
+        <v>0.4964099290267608</v>
       </c>
       <c r="D177" t="n">
-        <v>28.49674977077527</v>
+        <v>11.52739064077313</v>
       </c>
       <c r="E177" t="n">
-        <v>36.61842933595221</v>
+        <v>16.25958483301185</v>
       </c>
       <c r="F177" t="n">
-        <v>34.2245118185568</v>
+        <v>16.2649079570699</v>
       </c>
       <c r="G177" t="n">
         <v>89</v>
@@ -5217,16 +5217,16 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>-1.095668615860515</v>
+        <v>0.5616509594638904</v>
       </c>
       <c r="D178" t="n">
-        <v>363.2102843005248</v>
+        <v>156.2715346211135</v>
       </c>
       <c r="E178" t="n">
-        <v>433.8192355157416</v>
+        <v>198.407247067693</v>
       </c>
       <c r="F178" t="n">
-        <v>42.5412598525265</v>
+        <v>25.79758281565449</v>
       </c>
       <c r="G178" t="n">
         <v>99</v>
@@ -5244,16 +5244,16 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>0.3280042580188944</v>
+        <v>0.5587891115903894</v>
       </c>
       <c r="D179" t="n">
-        <v>191.1724459740423</v>
+        <v>176.4819148894279</v>
       </c>
       <c r="E179" t="n">
-        <v>262.8822066946469</v>
+        <v>213.0105124993264</v>
       </c>
       <c r="F179" t="n">
-        <v>19.10963056046448</v>
+        <v>20.46724468265511</v>
       </c>
       <c r="G179" t="n">
         <v>93</v>
@@ -5271,16 +5271,16 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>-0.5277804452861246</v>
+        <v>0.1787330231163292</v>
       </c>
       <c r="D180" t="n">
-        <v>7.236536325552525</v>
+        <v>5.518079158587334</v>
       </c>
       <c r="E180" t="n">
-        <v>10.77744823709677</v>
+        <v>7.901829099054482</v>
       </c>
       <c r="F180" t="n">
-        <v>63.78658730660312</v>
+        <v>78.56705613497522</v>
       </c>
       <c r="G180" t="n">
         <v>78</v>
@@ -5298,16 +5298,16 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>-5.543793658126716</v>
+        <v>0.6291426201773671</v>
       </c>
       <c r="D181" t="n">
-        <v>221.8251321580675</v>
+        <v>45.70361921522353</v>
       </c>
       <c r="E181" t="n">
-        <v>242.5969616688006</v>
+        <v>57.75292935447422</v>
       </c>
       <c r="F181" t="n">
-        <v>76.95330360213083</v>
+        <v>25.45468052074613</v>
       </c>
       <c r="G181" t="n">
         <v>18</v>
@@ -5325,16 +5325,16 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>-0.9567829923740074</v>
+        <v>0.2512731109182681</v>
       </c>
       <c r="D182" t="n">
-        <v>24.0301908857367</v>
+        <v>14.02926910057496</v>
       </c>
       <c r="E182" t="n">
-        <v>32.05104600122164</v>
+        <v>19.8258852413955</v>
       </c>
       <c r="F182" t="n">
-        <v>29.17037763268223</v>
+        <v>18.75952533397467</v>
       </c>
       <c r="G182" t="n">
         <v>89</v>
@@ -5352,16 +5352,16 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>-1.144540955552919</v>
+        <v>-0.09960177364518596</v>
       </c>
       <c r="D183" t="n">
-        <v>335.6232236611723</v>
+        <v>252.415413288155</v>
       </c>
       <c r="E183" t="n">
-        <v>438.8485545278575</v>
+        <v>314.2427139784143</v>
       </c>
       <c r="F183" t="n">
-        <v>39.51165217846295</v>
+        <v>36.37852464010356</v>
       </c>
       <c r="G183" t="n">
         <v>99</v>
@@ -5379,16 +5379,16 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>-1.069264752318956</v>
+        <v>-0.3210399204885757</v>
       </c>
       <c r="D184" t="n">
-        <v>339.781239499328</v>
+        <v>271.1736026886971</v>
       </c>
       <c r="E184" t="n">
-        <v>461.3026623706165</v>
+        <v>368.5835064843843</v>
       </c>
       <c r="F184" t="n">
-        <v>31.85554177764128</v>
+        <v>30.1213661384616</v>
       </c>
       <c r="G184" t="n">
         <v>93</v>
@@ -5406,16 +5406,16 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>-0.3868805157608257</v>
+        <v>0.07836442230539542</v>
       </c>
       <c r="D185" t="n">
-        <v>7.266551476258498</v>
+        <v>6.14778210566594</v>
       </c>
       <c r="E185" t="n">
-        <v>10.26845243105583</v>
+        <v>8.370763425989553</v>
       </c>
       <c r="F185" t="n">
-        <v>67.44526002145847</v>
+        <v>87.33843692091679</v>
       </c>
       <c r="G185" t="n">
         <v>78</v>
@@ -5433,16 +5433,16 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>-6.981191962300877</v>
+        <v>0.08926654287295388</v>
       </c>
       <c r="D186" t="n">
-        <v>251.1597185134888</v>
+        <v>60.46464029947916</v>
       </c>
       <c r="E186" t="n">
-        <v>267.9195699206729</v>
+        <v>90.50367203516016</v>
       </c>
       <c r="F186" t="n">
-        <v>91.68272496493555</v>
+        <v>42.50139485118958</v>
       </c>
       <c r="G186" t="n">
         <v>18</v>
@@ -5460,16 +5460,16 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>-1.071548307740349</v>
+        <v>0.1696141552656076</v>
       </c>
       <c r="D187" t="n">
-        <v>25.34139770336365</v>
+        <v>14.52171921462156</v>
       </c>
       <c r="E187" t="n">
-        <v>32.97755153312815</v>
+        <v>20.87905515517764</v>
       </c>
       <c r="F187" t="n">
-        <v>30.71210703927289</v>
+        <v>19.2939091175333</v>
       </c>
       <c r="G187" t="n">
         <v>89</v>
@@ -5487,16 +5487,16 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>-2.569357144328271</v>
+        <v>-0.06692829674185941</v>
       </c>
       <c r="D188" t="n">
-        <v>475.5268368191189</v>
+        <v>244.4569147283381</v>
       </c>
       <c r="E188" t="n">
-        <v>566.1643278010233</v>
+        <v>309.5388165582497</v>
       </c>
       <c r="F188" t="n">
-        <v>56.0352465945308</v>
+        <v>34.97467147866843</v>
       </c>
       <c r="G188" t="n">
         <v>99</v>
@@ -5514,16 +5514,16 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>-0.513995514978012</v>
+        <v>-0.2949343184652851</v>
       </c>
       <c r="D189" t="n">
-        <v>287.0438645885837</v>
+        <v>306.0525220645371</v>
       </c>
       <c r="E189" t="n">
-        <v>394.5846853582461</v>
+        <v>364.9234708261305</v>
       </c>
       <c r="F189" t="n">
-        <v>26.28627375425111</v>
+        <v>34.68666345254436</v>
       </c>
       <c r="G189" t="n">
         <v>93</v>
@@ -5541,16 +5541,16 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>-0.5330300819968492</v>
+        <v>0.06937146131793182</v>
       </c>
       <c r="D190" t="n">
-        <v>7.859258370521741</v>
+        <v>6.103932319543301</v>
       </c>
       <c r="E190" t="n">
-        <v>10.79594866020431</v>
+        <v>8.4115036100713</v>
       </c>
       <c r="F190" t="n">
-        <v>73.82712597311072</v>
+        <v>86.06200732359616</v>
       </c>
       <c r="G190" t="n">
         <v>78</v>
@@ -5568,16 +5568,16 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>-6.147065152363887</v>
+        <v>-0.2304050747316766</v>
       </c>
       <c r="D191" t="n">
-        <v>235.894521607293</v>
+        <v>80.21707492404514</v>
       </c>
       <c r="E191" t="n">
-        <v>253.5329616581594</v>
+        <v>105.1948821757079</v>
       </c>
       <c r="F191" t="n">
-        <v>85.8818935779037</v>
+        <v>53.48748936850277</v>
       </c>
       <c r="G191" t="n">
         <v>18</v>
@@ -5595,16 +5595,16 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>-0.7005850885877072</v>
+        <v>0.6559049556188393</v>
       </c>
       <c r="D192" t="n">
-        <v>21.65801185436463</v>
+        <v>9.781902613264791</v>
       </c>
       <c r="E192" t="n">
-        <v>29.8792752017196</v>
+        <v>13.44033463655527</v>
       </c>
       <c r="F192" t="n">
-        <v>26.3185306796528</v>
+        <v>14.20147499196414</v>
       </c>
       <c r="G192" t="n">
         <v>89</v>
@@ -5622,16 +5622,16 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>-0.4281337039008297</v>
+        <v>0.6954646144769119</v>
       </c>
       <c r="D193" t="n">
-        <v>285.8900340687145</v>
+        <v>126.0119727548927</v>
       </c>
       <c r="E193" t="n">
-        <v>358.1227693460611</v>
+        <v>165.3736768732572</v>
       </c>
       <c r="F193" t="n">
-        <v>36.97158614476397</v>
+        <v>19.80798145861329</v>
       </c>
       <c r="G193" t="n">
         <v>99</v>
@@ -5649,16 +5649,16 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>-0.3729437671958662</v>
+        <v>0.6724281819275943</v>
       </c>
       <c r="D194" t="n">
-        <v>290.959464124454</v>
+        <v>131.2767534153436</v>
       </c>
       <c r="E194" t="n">
-        <v>375.754600045284</v>
+        <v>183.5401963713847</v>
       </c>
       <c r="F194" t="n">
-        <v>28.85961511191012</v>
+        <v>13.58795003280672</v>
       </c>
       <c r="G194" t="n">
         <v>93</v>
@@ -5676,16 +5676,16 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>-0.610028951744888</v>
+        <v>0.2261801687020968</v>
       </c>
       <c r="D195" t="n">
-        <v>7.470342232630803</v>
+        <v>5.457043446027315</v>
       </c>
       <c r="E195" t="n">
-        <v>11.06374901213551</v>
+        <v>7.670176896950543</v>
       </c>
       <c r="F195" t="n">
-        <v>72.02130406700253</v>
+        <v>94.72560942561546</v>
       </c>
       <c r="G195" t="n">
         <v>78</v>
@@ -5703,16 +5703,16 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>-6.659874574685139</v>
+        <v>0.633096832526713</v>
       </c>
       <c r="D196" t="n">
-        <v>246.0634887483385</v>
+        <v>36.18779500325521</v>
       </c>
       <c r="E196" t="n">
-        <v>262.4710377337489</v>
+        <v>57.44421317502087</v>
       </c>
       <c r="F196" t="n">
-        <v>89.68479143870699</v>
+        <v>19.14085549484954</v>
       </c>
       <c r="G196" t="n">
         <v>18</v>
@@ -5730,16 +5730,16 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>-0.5652410780403949</v>
+        <v>0.6919405482495646</v>
       </c>
       <c r="D197" t="n">
-        <v>20.65105251783735</v>
+        <v>9.570925208959686</v>
       </c>
       <c r="E197" t="n">
-        <v>28.66563016792593</v>
+        <v>12.71710162889732</v>
       </c>
       <c r="F197" t="n">
-        <v>25.35411617961116</v>
+        <v>13.91897663816055</v>
       </c>
       <c r="G197" t="n">
         <v>89</v>
@@ -5757,16 +5757,16 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>-0.4111868560011318</v>
+        <v>0.719184584865443</v>
       </c>
       <c r="D198" t="n">
-        <v>289.7379363088897</v>
+        <v>121.1490879251499</v>
       </c>
       <c r="E198" t="n">
-        <v>355.9916088661117</v>
+        <v>158.8027333274256</v>
       </c>
       <c r="F198" t="n">
-        <v>37.58249884579269</v>
+        <v>19.10435999148327</v>
       </c>
       <c r="G198" t="n">
         <v>99</v>
@@ -5784,16 +5784,16 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>-0.406039266282556</v>
+        <v>0.6766079099098845</v>
       </c>
       <c r="D199" t="n">
-        <v>291.0369466145833</v>
+        <v>127.0816253333963</v>
       </c>
       <c r="E199" t="n">
-        <v>380.2565080927498</v>
+        <v>182.3654753774453</v>
       </c>
       <c r="F199" t="n">
-        <v>29.17161741904529</v>
+        <v>13.08452913200751</v>
       </c>
       <c r="G199" t="n">
         <v>93</v>
@@ -5811,16 +5811,16 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>-0.5911238732536308</v>
+        <v>0.2809162723196404</v>
       </c>
       <c r="D200" t="n">
-        <v>7.41372959736066</v>
+        <v>5.350159192696596</v>
       </c>
       <c r="E200" t="n">
-        <v>10.99860152804351</v>
+        <v>7.39392741679737</v>
       </c>
       <c r="F200" t="n">
-        <v>73.08279798282696</v>
+        <v>91.61566885022549</v>
       </c>
       <c r="G200" t="n">
         <v>78</v>
@@ -5838,16 +5838,16 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>-6.611487219575932</v>
+        <v>0.6628467076698842</v>
       </c>
       <c r="D201" t="n">
-        <v>246.3150435553657</v>
+        <v>33.80334303114149</v>
       </c>
       <c r="E201" t="n">
-        <v>261.640710835345</v>
+        <v>55.06609214468683</v>
       </c>
       <c r="F201" t="n">
-        <v>90.16338637919158</v>
+        <v>18.04267909463055</v>
       </c>
       <c r="G201" t="n">
         <v>18</v>
@@ -5865,16 +5865,16 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>-0.9297799852223465</v>
+        <v>0.4010019171022039</v>
       </c>
       <c r="D202" t="n">
-        <v>23.06489961602715</v>
+        <v>12.74952286280943</v>
       </c>
       <c r="E202" t="n">
-        <v>31.82913043106898</v>
+        <v>17.7330561449312</v>
       </c>
       <c r="F202" t="n">
-        <v>27.67861779135395</v>
+        <v>17.21242686121377</v>
       </c>
       <c r="G202" t="n">
         <v>89</v>
@@ -5892,16 +5892,16 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>-1.003639258083384</v>
+        <v>0.3909781862774019</v>
       </c>
       <c r="D203" t="n">
-        <v>327.2754273077454</v>
+        <v>181.1262074480153</v>
       </c>
       <c r="E203" t="n">
-        <v>424.1869135468312</v>
+        <v>233.8642970796276</v>
       </c>
       <c r="F203" t="n">
-        <v>38.88475467575985</v>
+        <v>29.23965497371809</v>
       </c>
       <c r="G203" t="n">
         <v>99</v>
@@ -5919,16 +5919,16 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>-0.9204751170383259</v>
+        <v>0.3024132878659224</v>
       </c>
       <c r="D204" t="n">
-        <v>326.9422768213416</v>
+        <v>198.4410672751806</v>
       </c>
       <c r="E204" t="n">
-        <v>444.4084144868905</v>
+        <v>267.840980507976</v>
       </c>
       <c r="F204" t="n">
-        <v>30.79597491585612</v>
+        <v>21.65278129140146</v>
       </c>
       <c r="G204" t="n">
         <v>93</v>
@@ -5946,16 +5946,16 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>-0.3683104486906692</v>
+        <v>0.1020171594836738</v>
       </c>
       <c r="D205" t="n">
-        <v>7.122487930151133</v>
+        <v>5.893602915299245</v>
       </c>
       <c r="E205" t="n">
-        <v>10.19947443707636</v>
+        <v>8.262652180197099</v>
       </c>
       <c r="F205" t="n">
-        <v>65.97500139015068</v>
+        <v>80.79886764307017</v>
       </c>
       <c r="G205" t="n">
         <v>78</v>
@@ -5973,16 +5973,16 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>-6.920189049311627</v>
+        <v>0.1773764559349755</v>
       </c>
       <c r="D206" t="n">
-        <v>250.2318079206678</v>
+        <v>57.20124647352431</v>
       </c>
       <c r="E206" t="n">
-        <v>266.8937065762186</v>
+        <v>86.01439168742591</v>
       </c>
       <c r="F206" t="n">
-        <v>90.99599981539926</v>
+        <v>38.26994040845057</v>
       </c>
       <c r="G206" t="n">
         <v>18</v>
@@ -6000,16 +6000,16 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>-1.048459019927811</v>
+        <v>0.2957493096612432</v>
       </c>
       <c r="D207" t="n">
-        <v>24.5370500971762</v>
+        <v>13.47368964720308</v>
       </c>
       <c r="E207" t="n">
-        <v>32.79325416839622</v>
+        <v>19.22801771474793</v>
       </c>
       <c r="F207" t="n">
-        <v>29.80465414215448</v>
+        <v>17.99904518806428</v>
       </c>
       <c r="G207" t="n">
         <v>89</v>
@@ -6027,16 +6027,16 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>-1.262176429740922</v>
+        <v>0.08464414897000294</v>
       </c>
       <c r="D208" t="n">
-        <v>351.5985985958215</v>
+        <v>227.7851713546599</v>
       </c>
       <c r="E208" t="n">
-        <v>450.7240545617461</v>
+        <v>286.709763216085</v>
       </c>
       <c r="F208" t="n">
-        <v>41.26149761313641</v>
+        <v>37.16081613035684</v>
       </c>
       <c r="G208" t="n">
         <v>99</v>
@@ -6054,16 +6054,16 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>-0.7237950125970711</v>
+        <v>-0.04381336712703043</v>
       </c>
       <c r="D209" t="n">
-        <v>293.9646905058174</v>
+        <v>236.9542613696026</v>
       </c>
       <c r="E209" t="n">
-        <v>421.0374638326508</v>
+        <v>327.6342938371358</v>
       </c>
       <c r="F209" t="n">
-        <v>28.32377353708036</v>
+        <v>25.94036116087245</v>
       </c>
       <c r="G209" t="n">
         <v>93</v>
@@ -6081,16 +6081,16 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>-0.3676325792873372</v>
+        <v>0.09044744916701075</v>
       </c>
       <c r="D210" t="n">
-        <v>7.225676243121807</v>
+        <v>5.990546758358295</v>
       </c>
       <c r="E210" t="n">
-        <v>10.1969476829438</v>
+        <v>8.315710288173284</v>
       </c>
       <c r="F210" t="n">
-        <v>68.52784033526767</v>
+        <v>87.84238370707979</v>
       </c>
       <c r="G210" t="n">
         <v>78</v>
@@ -6108,16 +6108,16 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>-7.119786567593868</v>
+        <v>0.3232299243301958</v>
       </c>
       <c r="D211" t="n">
-        <v>253.7697585423788</v>
+        <v>50.50451151529948</v>
       </c>
       <c r="E211" t="n">
-        <v>270.2357897445533</v>
+        <v>78.01733810922005</v>
       </c>
       <c r="F211" t="n">
-        <v>93.01248027478512</v>
+        <v>35.82040081995157</v>
       </c>
       <c r="G211" t="n">
         <v>18</v>
@@ -6135,16 +6135,16 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>-1.578714712341688</v>
+        <v>-0.01401282113523994</v>
       </c>
       <c r="D212" t="n">
-        <v>29.03671650404341</v>
+        <v>16.96017186025555</v>
       </c>
       <c r="E212" t="n">
-        <v>36.79362045121718</v>
+        <v>23.07239063121681</v>
       </c>
       <c r="F212" t="n">
-        <v>34.88002060285481</v>
+        <v>22.72154488198898</v>
       </c>
       <c r="G212" t="n">
         <v>89</v>
@@ -6162,16 +6162,16 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>-1.105233790245549</v>
+        <v>-0.01250820870408975</v>
       </c>
       <c r="D213" t="n">
-        <v>344.4116365066682</v>
+        <v>236.3007269965278</v>
       </c>
       <c r="E213" t="n">
-        <v>434.8081400758538</v>
+        <v>301.541282432614</v>
       </c>
       <c r="F213" t="n">
-        <v>40.75560819988232</v>
+        <v>34.15319005021839</v>
       </c>
       <c r="G213" t="n">
         <v>99</v>
@@ -6189,16 +6189,16 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>-1.464866775022096</v>
+        <v>-0.1741460358877291</v>
       </c>
       <c r="D214" t="n">
-        <v>429.1354442309308</v>
+        <v>255.9363623178133</v>
       </c>
       <c r="E214" t="n">
-        <v>503.4712275606155</v>
+        <v>347.4873383927655</v>
       </c>
       <c r="F214" t="n">
-        <v>54.8862952731662</v>
+        <v>32.67031660462333</v>
       </c>
       <c r="G214" t="n">
         <v>93</v>
@@ -6216,16 +6216,16 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>-0.4486128184669118</v>
+        <v>0.08112393205010138</v>
       </c>
       <c r="D215" t="n">
-        <v>7.761005478027539</v>
+        <v>5.986217046395327</v>
       </c>
       <c r="E215" t="n">
-        <v>10.49449715357075</v>
+        <v>8.358222395497789</v>
       </c>
       <c r="F215" t="n">
-        <v>76.69915421796489</v>
+        <v>86.91688019875656</v>
       </c>
       <c r="G215" t="n">
         <v>78</v>
@@ -6243,16 +6243,16 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>-3.808299579498858</v>
+        <v>-0.4419765796600046</v>
       </c>
       <c r="D216" t="n">
-        <v>187.3452983432346</v>
+        <v>89.64881049262152</v>
       </c>
       <c r="E216" t="n">
-        <v>207.9535402654511</v>
+        <v>113.8805767653429</v>
       </c>
       <c r="F216" t="n">
-        <v>65.22074466248371</v>
+        <v>56.76217901547691</v>
       </c>
       <c r="G216" t="n">
         <v>18</v>
@@ -6270,16 +6270,16 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>-1.242243029174666</v>
+        <v>0.2831504496965085</v>
       </c>
       <c r="D217" t="n">
-        <v>25.6353933998708</v>
+        <v>14.14861143305061</v>
       </c>
       <c r="E217" t="n">
-        <v>34.30932835076226</v>
+        <v>19.39924739052666</v>
       </c>
       <c r="F217" t="n">
-        <v>30.61616609289538</v>
+        <v>19.12277165977827</v>
       </c>
       <c r="G217" t="n">
         <v>89</v>
@@ -6297,16 +6297,16 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>-1.222145742822378</v>
+        <v>0.4358149756350058</v>
       </c>
       <c r="D218" t="n">
-        <v>351.5927025380761</v>
+        <v>181.2779442372948</v>
       </c>
       <c r="E218" t="n">
-        <v>446.7183264572723</v>
+        <v>225.0910764834588</v>
       </c>
       <c r="F218" t="n">
-        <v>40.18193434219356</v>
+        <v>25.54104565979496</v>
       </c>
       <c r="G218" t="n">
         <v>99</v>
@@ -6324,16 +6324,16 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>-0.1532222179430998</v>
+        <v>0.4096989228414529</v>
       </c>
       <c r="D219" t="n">
-        <v>246.5956243699597</v>
+        <v>191.6668310678133</v>
       </c>
       <c r="E219" t="n">
-        <v>344.3772324275123</v>
+        <v>246.3852553026591</v>
       </c>
       <c r="F219" t="n">
-        <v>28.60568940282134</v>
+        <v>23.16889649875903</v>
       </c>
       <c r="G219" t="n">
         <v>93</v>
@@ -6351,16 +6351,16 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>-0.3384844871483301</v>
+        <v>0.09803051050556033</v>
       </c>
       <c r="D220" t="n">
-        <v>7.33597607490344</v>
+        <v>5.954066985692734</v>
       </c>
       <c r="E220" t="n">
-        <v>10.0876996524169</v>
+        <v>8.280973139803276</v>
       </c>
       <c r="F220" t="n">
-        <v>71.74945453715689</v>
+        <v>86.81183518870697</v>
       </c>
       <c r="G220" t="n">
         <v>78</v>
@@ -6378,16 +6378,16 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>-4.525771807776323</v>
+        <v>0.1292977558513915</v>
       </c>
       <c r="D221" t="n">
-        <v>201.7013651529948</v>
+        <v>58.53215026855469</v>
       </c>
       <c r="E221" t="n">
-        <v>222.9292383759808</v>
+        <v>88.49228035832705</v>
       </c>
       <c r="F221" t="n">
-        <v>69.72329645463743</v>
+        <v>40.87025377549251</v>
       </c>
       <c r="G221" t="n">
         <v>18</v>
@@ -6405,16 +6405,16 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>-1.143861527531052</v>
+        <v>0.3639986293138044</v>
       </c>
       <c r="D222" t="n">
-        <v>24.80255193388864</v>
+        <v>12.95980646369163</v>
       </c>
       <c r="E222" t="n">
-        <v>33.54820130926478</v>
+        <v>18.27258112477125</v>
       </c>
       <c r="F222" t="n">
-        <v>29.58477292218192</v>
+        <v>17.29378190674987</v>
       </c>
       <c r="G222" t="n">
         <v>89</v>
@@ -6432,16 +6432,16 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>-0.8997392130427762</v>
+        <v>0.6369027209005951</v>
       </c>
       <c r="D223" t="n">
-        <v>334.8096358174025</v>
+        <v>140.0964642149029</v>
       </c>
       <c r="E223" t="n">
-        <v>413.0422649304267</v>
+        <v>180.5755716336002</v>
       </c>
       <c r="F223" t="n">
-        <v>38.70490072911844</v>
+        <v>20.39032957664233</v>
       </c>
       <c r="G223" t="n">
         <v>99</v>
@@ -6459,16 +6459,16 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>-0.07810377768282017</v>
+        <v>0.4727398036340935</v>
       </c>
       <c r="D224" t="n">
-        <v>216.0594265845514</v>
+        <v>169.3157916325395</v>
       </c>
       <c r="E224" t="n">
-        <v>332.9723835483017</v>
+        <v>232.8576016086389</v>
       </c>
       <c r="F224" t="n">
-        <v>23.20786304887792</v>
+        <v>20.74748110666829</v>
       </c>
       <c r="G224" t="n">
         <v>93</v>
@@ -6486,16 +6486,16 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>-0.343222521455828</v>
+        <v>0.1214155922170254</v>
       </c>
       <c r="D225" t="n">
-        <v>7.027547081311543</v>
+        <v>5.909271937150222</v>
       </c>
       <c r="E225" t="n">
-        <v>10.10553835157395</v>
+        <v>8.172919065077771</v>
       </c>
       <c r="F225" t="n">
-        <v>66.83294565592442</v>
+        <v>88.28926597890506</v>
       </c>
       <c r="G225" t="n">
         <v>78</v>
@@ -6513,16 +6513,16 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>-5.590708650260099</v>
+        <v>0.3405447437113016</v>
       </c>
       <c r="D226" t="n">
-        <v>225.5250918070475</v>
+        <v>49.39165242513021</v>
       </c>
       <c r="E226" t="n">
-        <v>243.4650443486013</v>
+        <v>77.01285465399876</v>
       </c>
       <c r="F226" t="n">
-        <v>80.2015426879982</v>
+        <v>33.84886160236139</v>
       </c>
       <c r="G226" t="n">
         <v>18</v>
@@ -6540,16 +6540,16 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>-1.563762571343993</v>
+        <v>-0.01612575161757124</v>
       </c>
       <c r="D227" t="n">
-        <v>29.43810797273443</v>
+        <v>16.82763744740004</v>
       </c>
       <c r="E227" t="n">
-        <v>36.68679529688841</v>
+        <v>23.09641645574765</v>
       </c>
       <c r="F227" t="n">
-        <v>35.79751854123915</v>
+        <v>22.33726442240797</v>
       </c>
       <c r="G227" t="n">
         <v>89</v>
@@ -6567,16 +6567,16 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>-0.7091749315527529</v>
+        <v>-0.09652050688758229</v>
       </c>
       <c r="D228" t="n">
-        <v>309.0006471884371</v>
+        <v>248.5172942190459</v>
       </c>
       <c r="E228" t="n">
-        <v>391.7786425190006</v>
+        <v>313.8021249788653</v>
       </c>
       <c r="F228" t="n">
-        <v>38.82754392572371</v>
+        <v>34.09780225488399</v>
       </c>
       <c r="G228" t="n">
         <v>99</v>
@@ -6594,16 +6594,16 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>-0.3195010115443957</v>
+        <v>-0.2823097141461721</v>
       </c>
       <c r="D229" t="n">
-        <v>260.3425955823673</v>
+        <v>282.9715310373614</v>
       </c>
       <c r="E229" t="n">
-        <v>368.368762246467</v>
+        <v>363.1402536640722</v>
       </c>
       <c r="F229" t="n">
-        <v>30.29910190050172</v>
+        <v>35.92348471714521</v>
       </c>
       <c r="G229" t="n">
         <v>93</v>
@@ -6621,16 +6621,16 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>-0.4187613532104031</v>
+        <v>0.0882327971434882</v>
       </c>
       <c r="D230" t="n">
-        <v>7.6347722304173</v>
+        <v>5.980495721865923</v>
       </c>
       <c r="E230" t="n">
-        <v>10.3858045911921</v>
+        <v>8.325828014625579</v>
       </c>
       <c r="F230" t="n">
-        <v>76.52840752185163</v>
+        <v>85.5753500332566</v>
       </c>
       <c r="G230" t="n">
         <v>78</v>
@@ -6648,16 +6648,16 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>-3.084189079687083</v>
+        <v>-0.4009756730656571</v>
       </c>
       <c r="D231" t="n">
-        <v>167.6963365342882</v>
+        <v>88.1306660970052</v>
       </c>
       <c r="E231" t="n">
-        <v>191.6564674050001</v>
+        <v>112.2498713034106</v>
       </c>
       <c r="F231" t="n">
-        <v>56.44275941431381</v>
+        <v>56.94760621350986</v>
       </c>
       <c r="G231" t="n">
         <v>18</v>
@@ -6675,16 +6675,16 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>-1.517079766282079</v>
+        <v>0.05630501141455302</v>
       </c>
       <c r="D232" t="n">
-        <v>29.18809502848079</v>
+        <v>16.07387851329332</v>
       </c>
       <c r="E232" t="n">
-        <v>36.35125124485523</v>
+        <v>22.25802865919902</v>
       </c>
       <c r="F232" t="n">
-        <v>35.58848033376072</v>
+        <v>21.57631655961161</v>
       </c>
       <c r="G232" t="n">
         <v>89</v>
@@ -6702,16 +6702,16 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>-1.328481311170317</v>
+        <v>-0.3036017679274778</v>
       </c>
       <c r="D233" t="n">
-        <v>365.2929291388001</v>
+        <v>271.0129169502644</v>
       </c>
       <c r="E233" t="n">
-        <v>457.281759520591</v>
+        <v>342.15270002149</v>
       </c>
       <c r="F233" t="n">
-        <v>42.27792343613099</v>
+        <v>35.18209660830387</v>
       </c>
       <c r="G233" t="n">
         <v>99</v>
@@ -6729,16 +6729,16 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>-0.3227868501894418</v>
+        <v>-1.88091946903165</v>
       </c>
       <c r="D234" t="n">
-        <v>270.1337516538558</v>
+        <v>400.7747904459636</v>
       </c>
       <c r="E234" t="n">
-        <v>368.8271354125904</v>
+        <v>544.3064562855807</v>
       </c>
       <c r="F234" t="n">
-        <v>31.61347102686888</v>
+        <v>50.87972837045184</v>
       </c>
       <c r="G234" t="n">
         <v>93</v>
@@ -6756,16 +6756,16 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>-0.4646485341148578</v>
+        <v>0.09965407420023875</v>
       </c>
       <c r="D235" t="n">
-        <v>7.989189322178181</v>
+        <v>5.958235483903151</v>
       </c>
       <c r="E235" t="n">
-        <v>10.55242278037732</v>
+        <v>8.273516821638925</v>
       </c>
       <c r="F235" t="n">
-        <v>78.55246237512917</v>
+        <v>86.68956763863511</v>
       </c>
       <c r="G235" t="n">
         <v>78</v>
@@ -6783,16 +6783,16 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>-3.067774562377379</v>
+        <v>-0.3367808104028793</v>
       </c>
       <c r="D236" t="n">
-        <v>165.7994151645237</v>
+        <v>81.72373369004991</v>
       </c>
       <c r="E236" t="n">
-        <v>191.2709421965723</v>
+        <v>109.6479852313497</v>
       </c>
       <c r="F236" t="n">
-        <v>56.18888275562121</v>
+        <v>54.14996924068899</v>
       </c>
       <c r="G236" t="n">
         <v>18</v>
@@ -6810,16 +6810,16 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>-1.116040638941978</v>
+        <v>0.4296879154117887</v>
       </c>
       <c r="D237" t="n">
-        <v>25.14804565772582</v>
+        <v>12.36074709088615</v>
       </c>
       <c r="E237" t="n">
-        <v>33.3298130044652</v>
+        <v>17.30322917739363</v>
       </c>
       <c r="F237" t="n">
-        <v>29.41088780149945</v>
+        <v>16.44607786867956</v>
       </c>
       <c r="G237" t="n">
         <v>89</v>
@@ -6837,16 +6837,16 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>-1.163581488255079</v>
+        <v>-0.001840443449747431</v>
       </c>
       <c r="D238" t="n">
-        <v>352.3660748414319</v>
+        <v>233.1027049055003</v>
       </c>
       <c r="E238" t="n">
-        <v>440.7924308869243</v>
+        <v>299.9485597865652</v>
       </c>
       <c r="F238" t="n">
-        <v>40.39150255767689</v>
+        <v>30.28038797660499</v>
       </c>
       <c r="G238" t="n">
         <v>99</v>
@@ -6864,16 +6864,16 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>-0.2028708392898653</v>
+        <v>-0.7713409428174867</v>
       </c>
       <c r="D239" t="n">
-        <v>260.2488094863071</v>
+        <v>320.3557716287592</v>
       </c>
       <c r="E239" t="n">
-        <v>351.7121969370359</v>
+        <v>426.8045169417567</v>
       </c>
       <c r="F239" t="n">
-        <v>29.77827268294045</v>
+        <v>39.50429097980973</v>
       </c>
       <c r="G239" t="n">
         <v>93</v>
@@ -6891,16 +6891,16 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>-0.5935314968919334</v>
+        <v>0.05574677493777447</v>
       </c>
       <c r="D240" t="n">
-        <v>8.34694834244557</v>
+        <v>6.365800863657242</v>
       </c>
       <c r="E240" t="n">
-        <v>11.00691969979111</v>
+        <v>8.472853373625131</v>
       </c>
       <c r="F240" t="n">
-        <v>79.9917425833081</v>
+        <v>93.97746866145891</v>
       </c>
       <c r="G240" t="n">
         <v>78</v>
@@ -6918,16 +6918,16 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>-4.703116895302848</v>
+        <v>0.6004287105964832</v>
       </c>
       <c r="D241" t="n">
-        <v>208.5744520823161</v>
+        <v>41.17191484239366</v>
       </c>
       <c r="E241" t="n">
-        <v>226.4783517937183</v>
+        <v>59.94703287538358</v>
       </c>
       <c r="F241" t="n">
-        <v>74.28881252809532</v>
+        <v>22.44698914338039</v>
       </c>
       <c r="G241" t="n">
         <v>18</v>
@@ -6945,16 +6945,16 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>-1.400697113493282</v>
+        <v>-0.02438202120338917</v>
       </c>
       <c r="D242" t="n">
-        <v>28.26845582683435</v>
+        <v>16.85371643237853</v>
       </c>
       <c r="E242" t="n">
-        <v>35.50091609931479</v>
+        <v>23.19005863288829</v>
       </c>
       <c r="F242" t="n">
-        <v>34.09986073887558</v>
+        <v>22.30918167387964</v>
       </c>
       <c r="G242" t="n">
         <v>89</v>
@@ -6972,16 +6972,16 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>-0.9834193464557068</v>
+        <v>-0.3728660149625913</v>
       </c>
       <c r="D243" t="n">
-        <v>331.9423015864209</v>
+        <v>275.7725925638218</v>
       </c>
       <c r="E243" t="n">
-        <v>422.0411254007336</v>
+        <v>351.1248593414371</v>
       </c>
       <c r="F243" t="n">
-        <v>39.46471041454099</v>
+        <v>34.96620519064342</v>
       </c>
       <c r="G243" t="n">
         <v>99</v>
@@ -6999,16 +6999,16 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>-0.05138345829608815</v>
+        <v>-2.524958768087795</v>
       </c>
       <c r="D244" t="n">
-        <v>244.0733931346606</v>
+        <v>444.3496635190902</v>
       </c>
       <c r="E244" t="n">
-        <v>328.8202089684428</v>
+        <v>602.0810344449349</v>
       </c>
       <c r="F244" t="n">
-        <v>29.03451019985249</v>
+        <v>55.82440737728794</v>
       </c>
       <c r="G244" t="n">
         <v>93</v>
@@ -7026,16 +7026,16 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>-0.4090822653902857</v>
+        <v>0.09247631752388896</v>
       </c>
       <c r="D245" t="n">
-        <v>7.663222960936717</v>
+        <v>5.821124944931421</v>
       </c>
       <c r="E245" t="n">
-        <v>10.35031689176511</v>
+        <v>8.306430505252756</v>
       </c>
       <c r="F245" t="n">
-        <v>75.10522544166326</v>
+        <v>84.32228754594149</v>
       </c>
       <c r="G245" t="n">
         <v>78</v>
@@ -7053,16 +7053,16 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>-4.231282638029538</v>
+        <v>-0.3782735351662843</v>
       </c>
       <c r="D246" t="n">
-        <v>196.9236878289117</v>
+        <v>85.62287224663629</v>
       </c>
       <c r="E246" t="n">
-        <v>216.9075413176093</v>
+        <v>111.3366791078443</v>
       </c>
       <c r="F246" t="n">
-        <v>68.14082618474259</v>
+        <v>55.79017220760304</v>
       </c>
       <c r="G246" t="n">
         <v>18</v>
@@ -7080,16 +7080,16 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>-1.479274618399249</v>
+        <v>0.2440979626564167</v>
       </c>
       <c r="D247" t="n">
-        <v>29.10081685526987</v>
+        <v>14.78596046533477</v>
       </c>
       <c r="E247" t="n">
-        <v>36.07723058412719</v>
+        <v>19.92065576619784</v>
       </c>
       <c r="F247" t="n">
-        <v>35.94429326865054</v>
+        <v>20.07097422985</v>
       </c>
       <c r="G247" t="n">
         <v>89</v>
@@ -7107,16 +7107,16 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>-1.004918632069878</v>
+        <v>-0.1777711841053788</v>
       </c>
       <c r="D248" t="n">
-        <v>338.2327854657414</v>
+        <v>257.0783571185488</v>
       </c>
       <c r="E248" t="n">
-        <v>424.3223189340962</v>
+        <v>325.2205375586622</v>
       </c>
       <c r="F248" t="n">
-        <v>39.29693038920577</v>
+        <v>32.17055400801722</v>
       </c>
       <c r="G248" t="n">
         <v>99</v>
@@ -7134,16 +7134,16 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>-0.3767138742861016</v>
+        <v>-0.3654602994148064</v>
       </c>
       <c r="D249" t="n">
-        <v>284.3496920677923</v>
+        <v>280.1963550198463</v>
       </c>
       <c r="E249" t="n">
-        <v>376.2701579026928</v>
+        <v>374.7291390427911</v>
       </c>
       <c r="F249" t="n">
-        <v>34.24229163326509</v>
+        <v>36.10898746660644</v>
       </c>
       <c r="G249" t="n">
         <v>93</v>
@@ -7161,16 +7161,16 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>-0.4373457706152415</v>
+        <v>0.09547380369563352</v>
       </c>
       <c r="D250" t="n">
-        <v>7.824152821149582</v>
+        <v>5.841148437597813</v>
       </c>
       <c r="E250" t="n">
-        <v>10.45360533803377</v>
+        <v>8.292701384734794</v>
       </c>
       <c r="F250" t="n">
-        <v>75.47591483218629</v>
+        <v>83.71544850088557</v>
       </c>
       <c r="G250" t="n">
         <v>78</v>
@@ -7188,16 +7188,16 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>-4.531400612859817</v>
+        <v>0.1423888489770943</v>
       </c>
       <c r="D251" t="n">
-        <v>202.1124119228787</v>
+        <v>62.36992306179471</v>
       </c>
       <c r="E251" t="n">
-        <v>223.0427524587971</v>
+        <v>87.82451584499769</v>
       </c>
       <c r="F251" t="n">
-        <v>69.27364297296037</v>
+        <v>41.41112549350342</v>
       </c>
       <c r="G251" t="n">
         <v>18</v>
@@ -7215,16 +7215,16 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>-1.173840277578173</v>
+        <v>0.4309241832680648</v>
       </c>
       <c r="D252" t="n">
-        <v>25.91668673311726</v>
+        <v>12.41559720843026</v>
       </c>
       <c r="E252" t="n">
-        <v>33.78194811935559</v>
+        <v>17.284464862405</v>
       </c>
       <c r="F252" t="n">
-        <v>30.49651858711043</v>
+        <v>16.67384147495386</v>
       </c>
       <c r="G252" t="n">
         <v>89</v>
@@ -7242,16 +7242,16 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>-1.749194586162721</v>
+        <v>0.01690623159695537</v>
       </c>
       <c r="D253" t="n">
-        <v>406.3593816275549</v>
+        <v>231.5529896129261</v>
       </c>
       <c r="E253" t="n">
-        <v>496.8785397459374</v>
+        <v>297.1289530562565</v>
       </c>
       <c r="F253" t="n">
-        <v>46.56763087733673</v>
+        <v>32.95981354263699</v>
       </c>
       <c r="G253" t="n">
         <v>99</v>
@@ -7269,16 +7269,16 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>-1.060630369911157</v>
+        <v>-0.6433166080964188</v>
       </c>
       <c r="D254" t="n">
-        <v>402.7707847677252</v>
+        <v>318.7733505413096</v>
       </c>
       <c r="E254" t="n">
-        <v>460.3392217829875</v>
+        <v>411.0915488212128</v>
       </c>
       <c r="F254" t="n">
-        <v>50.49369202727573</v>
+        <v>39.25920772043203</v>
       </c>
       <c r="G254" t="n">
         <v>93</v>
@@ -7296,16 +7296,16 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>-0.5548105305339013</v>
+        <v>0.03099102180584212</v>
       </c>
       <c r="D255" t="n">
-        <v>8.039755115142235</v>
+        <v>6.376352793131119</v>
       </c>
       <c r="E255" t="n">
-        <v>10.87236963218121</v>
+        <v>8.583202383549859</v>
       </c>
       <c r="F255" t="n">
-        <v>77.37490893288351</v>
+        <v>95.27667399838137</v>
       </c>
       <c r="G255" t="n">
         <v>78</v>
@@ -7323,16 +7323,16 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>-2.578201656744629</v>
+        <v>0.5964860751987162</v>
       </c>
       <c r="D256" t="n">
-        <v>155.4479149712457</v>
+        <v>42.52948591444228</v>
       </c>
       <c r="E256" t="n">
-        <v>179.3919560531362</v>
+        <v>60.24206048939762</v>
       </c>
       <c r="F256" t="n">
-        <v>51.41695903766923</v>
+        <v>21.18249173428386</v>
       </c>
       <c r="G256" t="n">
         <v>18</v>
@@ -7350,16 +7350,16 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>-1.404866518601901</v>
+        <v>0.3511385022227267</v>
       </c>
       <c r="D257" t="n">
-        <v>27.42600213811639</v>
+        <v>13.66797007871478</v>
       </c>
       <c r="E257" t="n">
-        <v>35.53173079237041</v>
+        <v>18.45639495507382</v>
       </c>
       <c r="F257" t="n">
-        <v>32.79801818335552</v>
+        <v>18.75757306182443</v>
       </c>
       <c r="G257" t="n">
         <v>89</v>
@@ -7377,16 +7377,16 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>-1.305782444316173</v>
+        <v>0.620468261902815</v>
       </c>
       <c r="D258" t="n">
-        <v>371.2568966643979</v>
+        <v>140.800152711194</v>
       </c>
       <c r="E258" t="n">
-        <v>455.0474280220695</v>
+        <v>184.6169410404234</v>
       </c>
       <c r="F258" t="n">
-        <v>42.44698660470722</v>
+        <v>22.16119277547151</v>
       </c>
       <c r="G258" t="n">
         <v>99</v>
@@ -7404,16 +7404,16 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>0.1329542598896151</v>
+        <v>0.5509727693046589</v>
       </c>
       <c r="D259" t="n">
-        <v>208.3983521820396</v>
+        <v>160.8934539466776</v>
       </c>
       <c r="E259" t="n">
-        <v>298.6062788608312</v>
+        <v>214.8890401407232</v>
       </c>
       <c r="F259" t="n">
-        <v>20.58203139151582</v>
+        <v>17.63604676400474</v>
       </c>
       <c r="G259" t="n">
         <v>93</v>
@@ -7431,16 +7431,16 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>-0.4999673209292852</v>
+        <v>0.08434790298223482</v>
       </c>
       <c r="D260" t="n">
-        <v>8.011011469058502</v>
+        <v>5.961117451007549</v>
       </c>
       <c r="E260" t="n">
-        <v>10.67889634043821</v>
+        <v>8.34354667108301</v>
       </c>
       <c r="F260" t="n">
-        <v>75.97610601853879</v>
+        <v>81.84474131968167</v>
       </c>
       <c r="G260" t="n">
         <v>78</v>
@@ -7458,16 +7458,16 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>-5.166385571269354</v>
+        <v>0.3062025179661669</v>
       </c>
       <c r="D261" t="n">
-        <v>215.6625985039605</v>
+        <v>54.03121354844835</v>
       </c>
       <c r="E261" t="n">
-        <v>235.4972811533491</v>
+        <v>78.99269198313405</v>
       </c>
       <c r="F261" t="n">
-        <v>74.71851153913242</v>
+        <v>36.0312561532134</v>
       </c>
       <c r="G261" t="n">
         <v>18</v>
@@ -7485,16 +7485,16 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>-1.348833618479677</v>
+        <v>0.3818457141561128</v>
       </c>
       <c r="D262" t="n">
-        <v>26.85797747065512</v>
+        <v>12.75386103083578</v>
       </c>
       <c r="E262" t="n">
-        <v>35.11535005530283</v>
+        <v>18.01437981752455</v>
       </c>
       <c r="F262" t="n">
-        <v>32.39378287967574</v>
+        <v>17.2979954321941</v>
       </c>
       <c r="G262" t="n">
         <v>89</v>
@@ -7512,16 +7512,16 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>-0.9609618524672632</v>
+        <v>0.6214826546054451</v>
       </c>
       <c r="D263" t="n">
-        <v>336.9483107749862</v>
+        <v>141.2294622864386</v>
       </c>
       <c r="E263" t="n">
-        <v>419.6450189190776</v>
+        <v>184.3700586843865</v>
       </c>
       <c r="F263" t="n">
-        <v>38.55156848568426</v>
+        <v>22.54898570618904</v>
       </c>
       <c r="G263" t="n">
         <v>99</v>
@@ -7539,16 +7539,16 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>-0.0437347742342824</v>
+        <v>0.5845677690247428</v>
       </c>
       <c r="D264" t="n">
-        <v>225.4765401860719</v>
+        <v>158.2015259445355</v>
       </c>
       <c r="E264" t="n">
-        <v>327.6219626291866</v>
+        <v>206.6940716204849</v>
       </c>
       <c r="F264" t="n">
-        <v>23.56923552516053</v>
+        <v>16.93268002238702</v>
       </c>
       <c r="G264" t="n">
         <v>93</v>
@@ -7566,16 +7566,16 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>-0.4258005892926617</v>
+        <v>0.1090510501449048</v>
       </c>
       <c r="D265" t="n">
-        <v>7.908362345817761</v>
+        <v>5.92121236752241</v>
       </c>
       <c r="E265" t="n">
-        <v>10.41153748572022</v>
+        <v>8.230227924464694</v>
       </c>
       <c r="F265" t="n">
-        <v>77.6668832992615</v>
+        <v>82.70106577497921</v>
       </c>
       <c r="G265" t="n">
         <v>78</v>
@@ -7593,16 +7593,16 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>-5.477058782013901</v>
+        <v>0.307933673328407</v>
       </c>
       <c r="D266" t="n">
-        <v>222.1002368927002</v>
+        <v>51.66827477349175</v>
       </c>
       <c r="E266" t="n">
-        <v>241.3567662085897</v>
+        <v>78.89407961005058</v>
       </c>
       <c r="F266" t="n">
-        <v>78.19560741140185</v>
+        <v>36.40293044745252</v>
       </c>
       <c r="G266" t="n">
         <v>18</v>
@@ -7620,16 +7620,16 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>-1.062538822243805</v>
+        <v>0.4350076780642105</v>
       </c>
       <c r="D267" t="n">
-        <v>25.29296358515707</v>
+        <v>12.41400065047018</v>
       </c>
       <c r="E267" t="n">
-        <v>32.90576114311657</v>
+        <v>17.2223394891876</v>
       </c>
       <c r="F267" t="n">
-        <v>30.87127650149488</v>
+        <v>17.22736742261007</v>
       </c>
       <c r="G267" t="n">
         <v>89</v>
@@ -7647,16 +7647,16 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>-0.8417049521010016</v>
+        <v>0.5191886105123713</v>
       </c>
       <c r="D268" t="n">
-        <v>321.1523892181088</v>
+        <v>160.4096204969618</v>
       </c>
       <c r="E268" t="n">
-        <v>406.6844133061239</v>
+        <v>207.7948952987221</v>
       </c>
       <c r="F268" t="n">
-        <v>38.30790183700496</v>
+        <v>25.08933903776313</v>
       </c>
       <c r="G268" t="n">
         <v>99</v>
@@ -7674,16 +7674,16 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>-0.1330689767557518</v>
+        <v>0.4561400135422525</v>
       </c>
       <c r="D269" t="n">
-        <v>248.528324250252</v>
+        <v>184.2384253060946</v>
       </c>
       <c r="E269" t="n">
-        <v>341.3548718068078</v>
+        <v>236.494736960695</v>
       </c>
       <c r="F269" t="n">
-        <v>29.45168967684375</v>
+        <v>20.15112900494206</v>
       </c>
       <c r="G269" t="n">
         <v>93</v>
@@ -7701,16 +7701,16 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>-0.3549022635977639</v>
+        <v>0.1140206904461233</v>
       </c>
       <c r="D270" t="n">
-        <v>7.284344086280236</v>
+        <v>5.779340132688865</v>
       </c>
       <c r="E270" t="n">
-        <v>10.14937867310893</v>
+        <v>8.207242057539739</v>
       </c>
       <c r="F270" t="n">
-        <v>71.79342031297065</v>
+        <v>79.94383638689294</v>
       </c>
       <c r="G270" t="n">
         <v>78</v>
@@ -7728,16 +7728,16 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>-5.046203355513168</v>
+        <v>0.4452463136805013</v>
       </c>
       <c r="D271" t="n">
-        <v>214.2656497955322</v>
+        <v>51.50632731119791</v>
       </c>
       <c r="E271" t="n">
-        <v>233.1910801546183</v>
+        <v>70.63511443143177</v>
       </c>
       <c r="F271" t="n">
-        <v>75.24543279446294</v>
+        <v>30.51017449898825</v>
       </c>
       <c r="G271" t="n">
         <v>18</v>
@@ -7755,16 +7755,16 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>-0.7245668318634335</v>
+        <v>0.3093625523928891</v>
       </c>
       <c r="D272" t="n">
-        <v>21.71481483973814</v>
+        <v>13.58673352873727</v>
       </c>
       <c r="E272" t="n">
-        <v>30.089217220264</v>
+        <v>19.04127101155133</v>
       </c>
       <c r="F272" t="n">
-        <v>26.39620429645159</v>
+        <v>18.14572428642598</v>
       </c>
       <c r="G272" t="n">
         <v>89</v>
@@ -7782,16 +7782,16 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>-0.5670799915687996</v>
+        <v>0.5187722029858598</v>
       </c>
       <c r="D273" t="n">
-        <v>287.2273448597301</v>
+        <v>164.7348232076626</v>
       </c>
       <c r="E273" t="n">
-        <v>375.1397483133298</v>
+        <v>207.8848563874992</v>
       </c>
       <c r="F273" t="n">
-        <v>33.94208988173621</v>
+        <v>26.638620441314</v>
       </c>
       <c r="G273" t="n">
         <v>99</v>
@@ -7809,16 +7809,16 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>-0.5598129197997315</v>
+        <v>0.595553027850543</v>
       </c>
       <c r="D274" t="n">
-        <v>278.8616838352655</v>
+        <v>164.0839643580939</v>
       </c>
       <c r="E274" t="n">
-        <v>400.5107595330105</v>
+        <v>203.9429611248773</v>
       </c>
       <c r="F274" t="n">
-        <v>26.66119750166183</v>
+        <v>18.08219535982741</v>
       </c>
       <c r="G274" t="n">
         <v>93</v>
@@ -7836,16 +7836,16 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>-0.4526558816222486</v>
+        <v>0.1817292845399415</v>
       </c>
       <c r="D275" t="n">
-        <v>7.05973923817659</v>
+        <v>6.046421576768924</v>
       </c>
       <c r="E275" t="n">
-        <v>10.50913196492804</v>
+        <v>7.88740164712267</v>
       </c>
       <c r="F275" t="n">
-        <v>65.03655407177452</v>
+        <v>97.0839756993326</v>
       </c>
       <c r="G275" t="n">
         <v>78</v>
@@ -7863,16 +7863,16 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>-7.094142708071995</v>
+        <v>0.678222641280776</v>
       </c>
       <c r="D276" t="n">
-        <v>253.3656511306763</v>
+        <v>41.56181250678168</v>
       </c>
       <c r="E276" t="n">
-        <v>269.8087237920088</v>
+        <v>53.79579078572051</v>
       </c>
       <c r="F276" t="n">
-        <v>92.11425295984293</v>
+        <v>22.25138648464743</v>
       </c>
       <c r="G276" t="n">
         <v>18</v>
@@ -7890,16 +7890,16 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>-0.9801371403985848</v>
+        <v>0.3919963603821107</v>
       </c>
       <c r="D277" t="n">
-        <v>23.33493787786934</v>
+        <v>12.59693102890186</v>
       </c>
       <c r="E277" t="n">
-        <v>32.24174284884008</v>
+        <v>17.86586147884252</v>
       </c>
       <c r="F277" t="n">
-        <v>28.29100660461934</v>
+        <v>16.74787601396011</v>
       </c>
       <c r="G277" t="n">
         <v>89</v>
@@ -7917,16 +7917,16 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>-0.8003722133600231</v>
+        <v>0.5207946898397473</v>
       </c>
       <c r="D278" t="n">
-        <v>316.2520563915522</v>
+        <v>161.5284880050505</v>
       </c>
       <c r="E278" t="n">
-        <v>402.0949795507859</v>
+        <v>207.4475509370891</v>
       </c>
       <c r="F278" t="n">
-        <v>37.18786403466713</v>
+        <v>25.72887372957187</v>
       </c>
       <c r="G278" t="n">
         <v>99</v>
@@ -7944,16 +7944,16 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>-0.6565230967997862</v>
+        <v>0.6248173144691512</v>
       </c>
       <c r="D279" t="n">
-        <v>276.8389679283224</v>
+        <v>155.1138276130922</v>
       </c>
       <c r="E279" t="n">
-        <v>412.740113130786</v>
+        <v>196.4261571804874</v>
       </c>
       <c r="F279" t="n">
-        <v>26.09825698389173</v>
+        <v>17.15367412997691</v>
       </c>
       <c r="G279" t="n">
         <v>93</v>
@@ -7971,16 +7971,16 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>-0.4381901748074502</v>
+        <v>0.1404444469224925</v>
       </c>
       <c r="D280" t="n">
-        <v>7.007214537033668</v>
+        <v>6.005885698856452</v>
       </c>
       <c r="E280" t="n">
-        <v>10.45667550121668</v>
+        <v>8.083927828960025</v>
       </c>
       <c r="F280" t="n">
-        <v>64.64948528203615</v>
+        <v>94.45602646756947</v>
       </c>
       <c r="G280" t="n">
         <v>78</v>
@@ -7998,16 +7998,16 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>-7.133027768163172</v>
+        <v>0.6853500947757871</v>
       </c>
       <c r="D281" t="n">
-        <v>253.5720478693644</v>
+        <v>39.49494001600478</v>
       </c>
       <c r="E281" t="n">
-        <v>270.456041142836</v>
+        <v>53.19665898713593</v>
       </c>
       <c r="F281" t="n">
-        <v>91.98980734803227</v>
+        <v>20.30528079030364</v>
       </c>
       <c r="G281" t="n">
         <v>18</v>
@@ -8025,16 +8025,16 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>-0.5537336176365171</v>
+        <v>0.6405013093758483</v>
       </c>
       <c r="D282" t="n">
-        <v>20.54246163100339</v>
+        <v>9.847571640871884</v>
       </c>
       <c r="E282" t="n">
-        <v>28.56006268183801</v>
+        <v>13.73787401636061</v>
       </c>
       <c r="F282" t="n">
-        <v>25.6883907140482</v>
+        <v>14.28402116581895</v>
       </c>
       <c r="G282" t="n">
         <v>89</v>
@@ -8052,16 +8052,16 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>-0.366173748294119</v>
+        <v>0.6606803567098509</v>
       </c>
       <c r="D283" t="n">
-        <v>286.5529214878275</v>
+        <v>132.5369518549755</v>
       </c>
       <c r="E283" t="n">
-        <v>350.2680042493372</v>
+        <v>174.5629216160647</v>
       </c>
       <c r="F283" t="n">
-        <v>37.62905778532713</v>
+        <v>21.14908416076942</v>
       </c>
       <c r="G283" t="n">
         <v>99</v>
@@ -8079,16 +8079,16 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>-0.3805394272062506</v>
+        <v>0.6690114421432806</v>
       </c>
       <c r="D284" t="n">
-        <v>291.7579037245883</v>
+        <v>138.2593465825563</v>
       </c>
       <c r="E284" t="n">
-        <v>376.7925768492702</v>
+        <v>184.4949218137426</v>
       </c>
       <c r="F284" t="n">
-        <v>29.39104227193242</v>
+        <v>14.35747933785387</v>
       </c>
       <c r="G284" t="n">
         <v>93</v>
@@ -8106,16 +8106,16 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>-0.5623737711560339</v>
+        <v>0.1987023842237469</v>
       </c>
       <c r="D285" t="n">
-        <v>7.313107010645744</v>
+        <v>5.698017187607594</v>
       </c>
       <c r="E285" t="n">
-        <v>10.89878140002665</v>
+        <v>7.805170198504183</v>
       </c>
       <c r="F285" t="n">
-        <v>71.11649069091051</v>
+        <v>102.3554591279583</v>
       </c>
       <c r="G285" t="n">
         <v>78</v>
@@ -8133,16 +8133,16 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>-6.659385147218567</v>
+        <v>0.7137700095084408</v>
       </c>
       <c r="D286" t="n">
-        <v>247.1716629664103</v>
+        <v>31.60067070855035</v>
       </c>
       <c r="E286" t="n">
-        <v>262.4626523100807</v>
+        <v>50.73738999825723</v>
       </c>
       <c r="F286" t="n">
-        <v>90.56991846591377</v>
+        <v>17.93392960035057</v>
       </c>
       <c r="G286" t="n">
         <v>18</v>
@@ -8160,16 +8160,16 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>-0.5021535455839283</v>
+        <v>0.6624322004016481</v>
       </c>
       <c r="D287" t="n">
-        <v>20.47346194406574</v>
+        <v>9.739707303850839</v>
       </c>
       <c r="E287" t="n">
-        <v>28.08200023230058</v>
+        <v>13.31224737478443</v>
       </c>
       <c r="F287" t="n">
-        <v>25.59239223333319</v>
+        <v>14.06799004817786</v>
       </c>
       <c r="G287" t="n">
         <v>89</v>
@@ -8187,16 +8187,16 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>-0.5474763420117186</v>
+        <v>0.6919661124825836</v>
       </c>
       <c r="D288" t="n">
-        <v>306.0283013546106</v>
+        <v>123.4684719509549</v>
       </c>
       <c r="E288" t="n">
-        <v>372.785927016937</v>
+        <v>166.3208705618888</v>
       </c>
       <c r="F288" t="n">
-        <v>39.6915077959551</v>
+        <v>19.2256729190314</v>
       </c>
       <c r="G288" t="n">
         <v>99</v>
@@ -8214,16 +8214,16 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>-0.2657205061686603</v>
+        <v>0.6703007078847568</v>
       </c>
       <c r="D289" t="n">
-        <v>283.3550526608703</v>
+        <v>132.3392022245674</v>
       </c>
       <c r="E289" t="n">
-        <v>360.7836427243927</v>
+        <v>184.1352491610836</v>
       </c>
       <c r="F289" t="n">
-        <v>28.4610359065537</v>
+        <v>13.57797636291326</v>
       </c>
       <c r="G289" t="n">
         <v>93</v>
@@ -8241,16 +8241,16 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>-0.5555531363265231</v>
+        <v>0.269940000880576</v>
       </c>
       <c r="D290" t="n">
-        <v>7.253400833178789</v>
+        <v>5.354592518928723</v>
       </c>
       <c r="E290" t="n">
-        <v>10.87496574298746</v>
+        <v>7.450145065451094</v>
       </c>
       <c r="F290" t="n">
-        <v>70.94009619255611</v>
+        <v>94.43943766030711</v>
       </c>
       <c r="G290" t="n">
         <v>78</v>
@@ -8268,16 +8268,16 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>-6.636358663693772</v>
+        <v>0.6612048362968936</v>
       </c>
       <c r="D291" t="n">
-        <v>247.0018249087863</v>
+        <v>35.97426350911459</v>
       </c>
       <c r="E291" t="n">
-        <v>262.0678333467586</v>
+        <v>55.20000991741743</v>
       </c>
       <c r="F291" t="n">
-        <v>90.60150222516583</v>
+        <v>19.44893171715307</v>
       </c>
       <c r="G291" t="n">
         <v>18</v>
@@ -8295,16 +8295,16 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>-0.5994280143709345</v>
+        <v>0.4090229544514181</v>
       </c>
       <c r="D292" t="n">
-        <v>20.92498337820675</v>
+        <v>12.60566441396649</v>
       </c>
       <c r="E292" t="n">
-        <v>28.97698688754483</v>
+        <v>17.61392647513344</v>
       </c>
       <c r="F292" t="n">
-        <v>25.78201965039486</v>
+        <v>16.96435972464529</v>
       </c>
       <c r="G292" t="n">
         <v>89</v>
@@ -8322,16 +8322,16 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>-0.5498977791477555</v>
+        <v>0.501849250085306</v>
       </c>
       <c r="D293" t="n">
-        <v>301.0952962239583</v>
+        <v>167.4438063496291</v>
       </c>
       <c r="E293" t="n">
-        <v>373.077474234597</v>
+        <v>211.5085341101619</v>
       </c>
       <c r="F293" t="n">
-        <v>36.21184919178158</v>
+        <v>29.04994727297664</v>
       </c>
       <c r="G293" t="n">
         <v>99</v>
@@ -8349,16 +8349,16 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>0.101215820068993</v>
+        <v>0.4768233892140782</v>
       </c>
       <c r="D294" t="n">
-        <v>237.4432665096816</v>
+        <v>201.8899696924353</v>
       </c>
       <c r="E294" t="n">
-        <v>304.0224404318058</v>
+        <v>231.9541176519256</v>
       </c>
       <c r="F294" t="n">
-        <v>23.26905503759552</v>
+        <v>23.49009386971215</v>
       </c>
       <c r="G294" t="n">
         <v>93</v>
@@ -8376,16 +8376,16 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>-0.5381244266172787</v>
+        <v>0.1445095533338761</v>
       </c>
       <c r="D295" t="n">
-        <v>7.347975199039166</v>
+        <v>5.967268491402651</v>
       </c>
       <c r="E295" t="n">
-        <v>10.81387155317032</v>
+        <v>8.064789465784063</v>
       </c>
       <c r="F295" t="n">
-        <v>68.87216671172773</v>
+        <v>99.38578175897842</v>
       </c>
       <c r="G295" t="n">
         <v>78</v>
@@ -8403,16 +8403,16 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>-6.73166429383926</v>
+        <v>0.6328801419231154</v>
       </c>
       <c r="D296" t="n">
-        <v>246.7997284995185</v>
+        <v>42.22713131374783</v>
       </c>
       <c r="E296" t="n">
-        <v>263.6981321360326</v>
+        <v>57.46117375890388</v>
       </c>
       <c r="F296" t="n">
-        <v>89.41077061534482</v>
+        <v>22.9532327755344</v>
       </c>
       <c r="G296" t="n">
         <v>18</v>
@@ -8430,16 +8430,16 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>-1.59136912401529</v>
+        <v>0.336657685684654</v>
       </c>
       <c r="D297" t="n">
-        <v>27.45272002059422</v>
+        <v>13.74728149242615</v>
       </c>
       <c r="E297" t="n">
-        <v>36.88378781417818</v>
+        <v>18.66120671542343</v>
       </c>
       <c r="F297" t="n">
-        <v>31.96424414078532</v>
+        <v>18.52319789553703</v>
       </c>
       <c r="G297" t="n">
         <v>89</v>
@@ -8457,16 +8457,16 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>-3.355810503376864</v>
+        <v>0.526677151092138</v>
       </c>
       <c r="D298" t="n">
-        <v>555.8388237230705</v>
+        <v>168.7265732890428</v>
       </c>
       <c r="E298" t="n">
-        <v>625.4347229893536</v>
+        <v>206.1703632082602</v>
       </c>
       <c r="F298" t="n">
-        <v>67.38667982635826</v>
+        <v>27.80494493543836</v>
       </c>
       <c r="G298" t="n">
         <v>99</v>
@@ -8484,16 +8484,16 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>0.06644789258549544</v>
+        <v>0.5411735175286564</v>
       </c>
       <c r="D299" t="n">
-        <v>246.1549833564348</v>
+        <v>171.8921203613281</v>
       </c>
       <c r="E299" t="n">
-        <v>309.8469410152019</v>
+        <v>217.2211780736728</v>
       </c>
       <c r="F299" t="n">
-        <v>29.98598722150887</v>
+        <v>17.82304702261868</v>
       </c>
       <c r="G299" t="n">
         <v>93</v>
@@ -8511,16 +8511,16 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>-0.8028907166689636</v>
+        <v>0.112507406694877</v>
       </c>
       <c r="D300" t="n">
-        <v>8.4611819371199</v>
+        <v>6.300284923651279</v>
       </c>
       <c r="E300" t="n">
-        <v>11.70766193359035</v>
+        <v>8.214248195853814</v>
       </c>
       <c r="F300" t="n">
-        <v>73.06062065356915</v>
+        <v>98.33980201743995</v>
       </c>
       <c r="G300" t="n">
         <v>78</v>
@@ -8538,16 +8538,16 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>-7.318117901366197</v>
+        <v>0.5709516180707335</v>
       </c>
       <c r="D301" t="n">
-        <v>257.1924441655477</v>
+        <v>45.17663998074002</v>
       </c>
       <c r="E301" t="n">
-        <v>273.5162257577184</v>
+        <v>62.11889031062243</v>
       </c>
       <c r="F301" t="n">
-        <v>93.69754619242075</v>
+        <v>25.60296510932936</v>
       </c>
       <c r="G301" t="n">
         <v>18</v>
@@ -8565,16 +8565,16 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>-1.922464412147399</v>
+        <v>-41.7567959479989</v>
       </c>
       <c r="D302" t="n">
-        <v>31.39157830999139</v>
+        <v>148.4861154020502</v>
       </c>
       <c r="E302" t="n">
-        <v>39.16927117318113</v>
+        <v>149.8212614817643</v>
       </c>
       <c r="F302" t="n">
-        <v>47.31085597302599</v>
+        <v>219.8110937090891</v>
       </c>
       <c r="G302" t="n">
         <v>89</v>
@@ -8592,16 +8592,16 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>-0.2887877266101353</v>
+        <v>-36.28616465151117</v>
       </c>
       <c r="D303" t="n">
-        <v>276.543114093819</v>
+        <v>1818.248930959991</v>
       </c>
       <c r="E303" t="n">
-        <v>340.2030443911871</v>
+        <v>1829.874721154838</v>
       </c>
       <c r="F303" t="n">
-        <v>53.97241403636693</v>
+        <v>292.1202454992875</v>
       </c>
       <c r="G303" t="n">
         <v>99</v>
@@ -8619,16 +8619,16 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>-1.664768729589909</v>
+        <v>-126.7127400662512</v>
       </c>
       <c r="D304" t="n">
-        <v>441.2389900453629</v>
+        <v>3612.95120633033</v>
       </c>
       <c r="E304" t="n">
-        <v>523.4891596107491</v>
+        <v>3624.057151030365</v>
       </c>
       <c r="F304" t="n">
-        <v>54.78038751335404</v>
+        <v>412.1543843491461</v>
       </c>
       <c r="G304" t="n">
         <v>93</v>
@@ -8646,16 +8646,16 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>-0.8355010264646996</v>
+        <v>-142.8444662385535</v>
       </c>
       <c r="D305" t="n">
-        <v>8.658914080032936</v>
+        <v>104.1743234976744</v>
       </c>
       <c r="E305" t="n">
-        <v>11.81307028750553</v>
+        <v>104.5760013847702</v>
       </c>
       <c r="F305" t="n">
-        <v>72.621963315814</v>
+        <v>1259.181882770103</v>
       </c>
       <c r="G305" t="n">
         <v>78</v>
@@ -8673,16 +8673,16 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>-9.739168381038176</v>
+        <v>-16.13291016053152</v>
       </c>
       <c r="D306" t="n">
-        <v>292.464227464464</v>
+        <v>384.6606343587239</v>
       </c>
       <c r="E306" t="n">
-        <v>310.7820199024409</v>
+        <v>392.541993314072</v>
       </c>
       <c r="F306" t="n">
-        <v>106.3310556974009</v>
+        <v>191.4449298547761</v>
       </c>
       <c r="G306" t="n">
         <v>18</v>
@@ -8700,16 +8700,16 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>-0.9399259287378792</v>
+        <v>-0.6938698427048222</v>
       </c>
       <c r="D307" t="n">
-        <v>23.86611730596992</v>
+        <v>21.69644357917014</v>
       </c>
       <c r="E307" t="n">
-        <v>31.91269260115178</v>
+        <v>29.82022327735839</v>
       </c>
       <c r="F307" t="n">
-        <v>29.32095747406085</v>
+        <v>25.27504432041086</v>
       </c>
       <c r="G307" t="n">
         <v>89</v>
@@ -8727,16 +8727,16 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>0.2023859790171801</v>
+        <v>-11.98027914608966</v>
       </c>
       <c r="D308" t="n">
-        <v>197.7307555844085</v>
+        <v>1050.530686503709</v>
       </c>
       <c r="E308" t="n">
-        <v>267.6356051765399</v>
+        <v>1079.666228939244</v>
       </c>
       <c r="F308" t="n">
-        <v>25.68009528229366</v>
+        <v>174.8883178364214</v>
       </c>
       <c r="G308" t="n">
         <v>99</v>
@@ -8754,16 +8754,16 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>-4.401752733710092</v>
+        <v>-4.630730219291356</v>
       </c>
       <c r="D309" t="n">
-        <v>702.5317724084341</v>
+        <v>722.3947100895707</v>
       </c>
       <c r="E309" t="n">
-        <v>745.3243006712632</v>
+        <v>760.9572977652282</v>
       </c>
       <c r="F309" t="n">
-        <v>83.68737632035212</v>
+        <v>86.94430483827118</v>
       </c>
       <c r="G309" t="n">
         <v>93</v>
@@ -8781,16 +8781,16 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>-0.4610347634041423</v>
+        <v>-7.172309014785085</v>
       </c>
       <c r="D310" t="n">
-        <v>7.583043923744788</v>
+        <v>22.8722635660416</v>
       </c>
       <c r="E310" t="n">
-        <v>10.5393965877943</v>
+        <v>24.92630142040082</v>
       </c>
       <c r="F310" t="n">
-        <v>75.77768586905057</v>
+        <v>225.9637011615442</v>
       </c>
       <c r="G310" t="n">
         <v>78</v>
@@ -8808,16 +8808,16 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>-3.538574539670187</v>
+        <v>-1.215163411874574</v>
       </c>
       <c r="D311" t="n">
-        <v>178.408040576511</v>
+        <v>118.6335093180339</v>
       </c>
       <c r="E311" t="n">
-        <v>202.0367135383169</v>
+        <v>141.1475809548118</v>
       </c>
       <c r="F311" t="n">
-        <v>60.64952819477565</v>
+        <v>69.67290729606458</v>
       </c>
       <c r="G311" t="n">
         <v>18</v>
@@ -8835,16 +8835,16 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>-1.179520416874973</v>
+        <v>-0.7475313539930151</v>
       </c>
       <c r="D312" t="n">
-        <v>25.34562149476469</v>
+        <v>23.49879116958447</v>
       </c>
       <c r="E312" t="n">
-        <v>33.82605462276179</v>
+        <v>30.28889022088373</v>
       </c>
       <c r="F312" t="n">
-        <v>29.66046468510928</v>
+        <v>27.63397173867849</v>
       </c>
       <c r="G312" t="n">
         <v>89</v>
@@ -8862,16 +8862,16 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>-0.3303834791521283</v>
+        <v>-2.112545746488562</v>
       </c>
       <c r="D313" t="n">
-        <v>281.4249429413767</v>
+        <v>483.1847879429056</v>
       </c>
       <c r="E313" t="n">
-        <v>345.6494908336472</v>
+        <v>528.6952063278898</v>
       </c>
       <c r="F313" t="n">
-        <v>33.93588561825722</v>
+        <v>62.02420741142377</v>
       </c>
       <c r="G313" t="n">
         <v>99</v>
@@ -8889,16 +8889,16 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>-12.44161726375941</v>
+        <v>0.2734294480892123</v>
       </c>
       <c r="D314" t="n">
-        <v>1118.126281081989</v>
+        <v>210.7672056792885</v>
       </c>
       <c r="E314" t="n">
-        <v>1175.71942517315</v>
+        <v>273.3485801438809</v>
       </c>
       <c r="F314" t="n">
-        <v>137.5466167814023</v>
+        <v>19.92898944684094</v>
       </c>
       <c r="G314" t="n">
         <v>93</v>
@@ -8916,16 +8916,16 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>-1.2950474824231</v>
+        <v>-0.2011233170233961</v>
       </c>
       <c r="D315" t="n">
-        <v>10.01498823899489</v>
+        <v>7.233609278996785</v>
       </c>
       <c r="E315" t="n">
-        <v>13.20934580732404</v>
+        <v>9.556068437029474</v>
       </c>
       <c r="F315" t="n">
-        <v>68.89307518112932</v>
+        <v>75.567937265181</v>
       </c>
       <c r="G315" t="n">
         <v>78</v>
@@ -8943,16 +8943,16 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>-2.463329760257188</v>
+        <v>-2.904884620215297</v>
       </c>
       <c r="D316" t="n">
-        <v>153.2469359503852</v>
+        <v>175.2422807481554</v>
       </c>
       <c r="E316" t="n">
-        <v>176.4889346313495</v>
+        <v>187.4021882403921</v>
       </c>
       <c r="F316" t="n">
-        <v>54.93233431421815</v>
+        <v>94.73663194408375</v>
       </c>
       <c r="G316" t="n">
         <v>18</v>
@@ -8970,16 +8970,16 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>-0.8006065110842515</v>
+        <v>-23.80126574750834</v>
       </c>
       <c r="D317" t="n">
-        <v>22.35375899411319</v>
+        <v>112.1174640869826</v>
       </c>
       <c r="E317" t="n">
-        <v>30.74540959271259</v>
+        <v>114.1058198748055</v>
       </c>
       <c r="F317" t="n">
-        <v>27.72318374425111</v>
+        <v>167.2399874451683</v>
       </c>
       <c r="G317" t="n">
         <v>89</v>
@@ -8997,16 +8997,16 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>-0.62734849586384</v>
+        <v>-159.43604123015</v>
       </c>
       <c r="D318" t="n">
-        <v>318.1465902617483</v>
+        <v>3790.258884006076</v>
       </c>
       <c r="E318" t="n">
-        <v>382.2854627534187</v>
+        <v>3795.757595035632</v>
       </c>
       <c r="F318" t="n">
-        <v>37.78826894988935</v>
+        <v>596.3680485028765</v>
       </c>
       <c r="G318" t="n">
         <v>99</v>
@@ -9024,16 +9024,16 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>0.133442862958603</v>
+        <v>-225.000074209837</v>
       </c>
       <c r="D319" t="n">
-        <v>248.9875055128528</v>
+        <v>4814.817538025559</v>
       </c>
       <c r="E319" t="n">
-        <v>298.5221307600291</v>
+        <v>4820.945449605144</v>
       </c>
       <c r="F319" t="n">
-        <v>29.17868147786507</v>
+        <v>542.1866937093013</v>
       </c>
       <c r="G319" t="n">
         <v>93</v>
@@ -9051,16 +9051,16 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>-0.3096603029377447</v>
+        <v>-106.422238926853</v>
       </c>
       <c r="D320" t="n">
-        <v>7.787125776975583</v>
+        <v>90.03473374782465</v>
       </c>
       <c r="E320" t="n">
-        <v>9.978489486358765</v>
+        <v>90.37172088536788</v>
       </c>
       <c r="F320" t="n">
-        <v>128.970521400037</v>
+        <v>1070.818970720475</v>
       </c>
       <c r="G320" t="n">
         <v>78</v>
@@ -9078,16 +9078,16 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>-1.033513064943824</v>
+        <v>-6.165078802320818</v>
       </c>
       <c r="D321" t="n">
-        <v>109.1487528483073</v>
+        <v>235.7357855902778</v>
       </c>
       <c r="E321" t="n">
-        <v>135.2365374248067</v>
+        <v>253.8522635456582</v>
       </c>
       <c r="F321" t="n">
-        <v>40.60587721877004</v>
+        <v>123.3466021603323</v>
       </c>
       <c r="G321" t="n">
         <v>18</v>
@@ -9105,16 +9105,16 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>-0.1312036458147339</v>
+        <v>-11.37199472053125</v>
       </c>
       <c r="D322" t="n">
-        <v>18.33314439152064</v>
+        <v>77.88719404413459</v>
       </c>
       <c r="E322" t="n">
-        <v>24.36920004638205</v>
+        <v>80.59177775698912</v>
       </c>
       <c r="F322" t="n">
-        <v>24.90799450779089</v>
+        <v>105.5120676552468</v>
       </c>
       <c r="G322" t="n">
         <v>89</v>
@@ -9132,16 +9132,16 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>-0.2329392495281248</v>
+        <v>-5.68880586331279</v>
       </c>
       <c r="D323" t="n">
-        <v>264.4947949033795</v>
+        <v>751.7811871152935</v>
       </c>
       <c r="E323" t="n">
-        <v>332.7502105875989</v>
+        <v>775.035858907836</v>
       </c>
       <c r="F323" t="n">
-        <v>31.05719753703102</v>
+        <v>126.2177173614759</v>
       </c>
       <c r="G323" t="n">
         <v>99</v>
@@ -9159,16 +9159,16 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>0.2823264276856096</v>
+        <v>-9.409478569398953</v>
       </c>
       <c r="D324" t="n">
-        <v>201.425786500336</v>
+        <v>1014.918869510774</v>
       </c>
       <c r="E324" t="n">
-        <v>271.6698281808385</v>
+        <v>1034.647503489362</v>
       </c>
       <c r="F324" t="n">
-        <v>20.57099598191811</v>
+        <v>118.6328764469225</v>
       </c>
       <c r="G324" t="n">
         <v>93</v>
@@ -9186,16 +9186,16 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>-1.059407602879726</v>
+        <v>-12.61191774464199</v>
       </c>
       <c r="D325" t="n">
-        <v>9.300091911584904</v>
+        <v>30.97280354377551</v>
       </c>
       <c r="E325" t="n">
-        <v>12.51286122535322</v>
+        <v>32.16955922663368</v>
       </c>
       <c r="F325" t="n">
-        <v>67.30082023991049</v>
+        <v>313.4188518762526</v>
       </c>
       <c r="G325" t="n">
         <v>78</v>
@@ -9213,16 +9213,16 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>-5.221682602982495</v>
+        <v>-7.369584460250291</v>
       </c>
       <c r="D326" t="n">
-        <v>215.7528122795953</v>
+        <v>258.7108629014757</v>
       </c>
       <c r="E326" t="n">
-        <v>236.5508348349391</v>
+        <v>274.3610794254128</v>
       </c>
       <c r="F326" t="n">
-        <v>76.17694594764187</v>
+        <v>104.8125662762245</v>
       </c>
       <c r="G326" t="n">
         <v>18</v>
@@ -9240,16 +9240,16 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>-1.92451631924865</v>
+        <v>-0.9908993137431492</v>
       </c>
       <c r="D327" t="n">
-        <v>31.7388562406047</v>
+        <v>28.11269987299201</v>
       </c>
       <c r="E327" t="n">
-        <v>39.1830194335082</v>
+        <v>32.3292419394635</v>
       </c>
       <c r="F327" t="n">
-        <v>38.41612005221312</v>
+        <v>35.67120333747387</v>
       </c>
       <c r="G327" t="n">
         <v>89</v>
@@ -9267,16 +9267,16 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>-2.452693202936123</v>
+        <v>-2.757814471249398</v>
       </c>
       <c r="D328" t="n">
-        <v>499.5785149468316</v>
+        <v>547.9873632565893</v>
       </c>
       <c r="E328" t="n">
-        <v>556.834961114428</v>
+        <v>580.9184479358458</v>
       </c>
       <c r="F328" t="n">
-        <v>61.7878578547507</v>
+        <v>75.41568078513818</v>
       </c>
       <c r="G328" t="n">
         <v>99</v>
@@ -9294,16 +9294,16 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>-0.4273059009333364</v>
+        <v>-8.725092052149323</v>
       </c>
       <c r="D329" t="n">
-        <v>321.5246037308888</v>
+        <v>977.4408684187038</v>
       </c>
       <c r="E329" t="n">
-        <v>383.121444717875</v>
+        <v>1000.057075497455</v>
       </c>
       <c r="F329" t="n">
-        <v>40.75876393724337</v>
+        <v>115.7625516639505</v>
       </c>
       <c r="G329" t="n">
         <v>93</v>
@@ -9321,16 +9321,16 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>-1.031539495232889</v>
+        <v>-39.1963970029038</v>
       </c>
       <c r="D330" t="n">
-        <v>9.200932010626181</v>
+        <v>54.71339846880008</v>
       </c>
       <c r="E330" t="n">
-        <v>12.4279102164095</v>
+        <v>55.28139781911888</v>
       </c>
       <c r="F330" t="n">
-        <v>66.77775222049547</v>
+        <v>619.9552934258701</v>
       </c>
       <c r="G330" t="n">
         <v>78</v>
@@ -9348,16 +9348,16 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>-0.907023634137788</v>
+        <v>-64.94693441045574</v>
       </c>
       <c r="D331" t="n">
-        <v>108.8437983194987</v>
+        <v>766.9727630615234</v>
       </c>
       <c r="E331" t="n">
-        <v>130.9629945147114</v>
+        <v>770.1367725500959</v>
       </c>
       <c r="F331" t="n">
-        <v>42.54532955162038</v>
+        <v>332.8252535070077</v>
       </c>
       <c r="G331" t="n">
         <v>18</v>
@@ -9375,16 +9375,16 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>-6.531533471162424</v>
+        <v>-15.48454359900989</v>
       </c>
       <c r="D332" t="n">
-        <v>58.3555615671565</v>
+        <v>90.85453423489345</v>
       </c>
       <c r="E332" t="n">
-        <v>62.88000683688097</v>
+        <v>93.02706873533249</v>
       </c>
       <c r="F332" t="n">
-        <v>91.13090137824476</v>
+        <v>136.2546668434714</v>
       </c>
       <c r="G332" t="n">
         <v>89</v>
@@ -9402,16 +9402,16 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>-7.679873862168096</v>
+        <v>-27.84006592228961</v>
       </c>
       <c r="D333" t="n">
-        <v>835.679572673759</v>
+        <v>1596.273210621843</v>
       </c>
       <c r="E333" t="n">
-        <v>882.8851393823981</v>
+        <v>1609.331920622604</v>
       </c>
       <c r="F333" t="n">
-        <v>112.9099681956137</v>
+        <v>236.2322692229141</v>
       </c>
       <c r="G333" t="n">
         <v>99</v>
@@ -9429,16 +9429,16 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>-1.243477471977259</v>
+        <v>-194.8616456339531</v>
       </c>
       <c r="D334" t="n">
-        <v>425.6302319598454</v>
+        <v>4479.240804364605</v>
       </c>
       <c r="E334" t="n">
-        <v>480.3289772556403</v>
+        <v>4487.997703649689</v>
       </c>
       <c r="F334" t="n">
-        <v>50.84535472789713</v>
+        <v>507.2204376367606</v>
       </c>
       <c r="G334" t="n">
         <v>93</v>
@@ -9456,16 +9456,16 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>-0.6272173421650122</v>
+        <v>-3.632929026328867</v>
       </c>
       <c r="D335" t="n">
-        <v>7.781140703421372</v>
+        <v>16.80294127342028</v>
       </c>
       <c r="E335" t="n">
-        <v>11.12264956121508</v>
+        <v>18.76779607858597</v>
       </c>
       <c r="F335" t="n">
-        <v>68.82459309650454</v>
+        <v>288.9383034802933</v>
       </c>
       <c r="G335" t="n">
         <v>78</v>
@@ -9483,16 +9483,16 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>-2.65655425999814</v>
+        <v>-7.96109144382258</v>
       </c>
       <c r="D336" t="n">
-        <v>156.97107357449</v>
+        <v>275.4571270412869</v>
       </c>
       <c r="E336" t="n">
-        <v>181.3454110810644</v>
+        <v>283.8905977454318</v>
       </c>
       <c r="F336" t="n">
-        <v>54.08329544664137</v>
+        <v>115.4297225329189</v>
       </c>
       <c r="G336" t="n">
         <v>18</v>
@@ -9510,16 +9510,16 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>-0.1970241779676571</v>
+        <v>-0.07426435039589108</v>
       </c>
       <c r="D337" t="n">
-        <v>18.93434861001004</v>
+        <v>19.09300471959489</v>
       </c>
       <c r="E337" t="n">
-        <v>25.06815297597209</v>
+        <v>23.74796798692648</v>
       </c>
       <c r="F337" t="n">
-        <v>26.21572051845386</v>
+        <v>29.63370047181275</v>
       </c>
       <c r="G337" t="n">
         <v>89</v>
@@ -9537,16 +9537,16 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>-1.463354225723834</v>
+        <v>-0.812183239629571</v>
       </c>
       <c r="D338" t="n">
-        <v>401.9775549378058</v>
+        <v>334.3159450954861</v>
       </c>
       <c r="E338" t="n">
-        <v>470.3389371564971</v>
+        <v>403.41176136582</v>
       </c>
       <c r="F338" t="n">
-        <v>47.62128947835865</v>
+        <v>39.55317376725559</v>
       </c>
       <c r="G338" t="n">
         <v>99</v>
@@ -9564,16 +9564,16 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>-1.810045781060024</v>
+        <v>-0.2091948755895721</v>
       </c>
       <c r="D339" t="n">
-        <v>460.4117090368783</v>
+        <v>284.2613535235005</v>
       </c>
       <c r="E339" t="n">
-        <v>537.5695105901759</v>
+        <v>352.6355362650614</v>
       </c>
       <c r="F339" t="n">
-        <v>59.77988775413727</v>
+        <v>33.04224017909847</v>
       </c>
       <c r="G339" t="n">
         <v>93</v>
@@ -9591,16 +9591,16 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>-0.544887068405068</v>
+        <v>-3.680262247923895</v>
       </c>
       <c r="D340" t="n">
-        <v>7.586580514907837</v>
+        <v>16.87277948550689</v>
       </c>
       <c r="E340" t="n">
-        <v>10.83761804985406</v>
+        <v>18.86342486844432</v>
       </c>
       <c r="F340" t="n">
-        <v>67.11079914982641</v>
+        <v>132.2475626910719</v>
       </c>
       <c r="G340" t="n">
         <v>78</v>
@@ -9618,16 +9618,16 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>-2.675412266973527</v>
+        <v>0.3163559888030274</v>
       </c>
       <c r="D341" t="n">
-        <v>160.4565823872884</v>
+        <v>68.05837164984808</v>
       </c>
       <c r="E341" t="n">
-        <v>181.8124375291012</v>
+        <v>78.41254711924317</v>
       </c>
       <c r="F341" t="n">
-        <v>57.12220945431442</v>
+        <v>38.66943415984442</v>
       </c>
       <c r="G341" t="n">
         <v>18</v>
@@ -9645,16 +9645,16 @@
         </is>
       </c>
       <c r="C342" t="n">
-        <v>-0.7574985709306563</v>
+        <v>0.1346172154959623</v>
       </c>
       <c r="D342" t="n">
-        <v>22.34377432405279</v>
+        <v>16.01720428466797</v>
       </c>
       <c r="E342" t="n">
-        <v>30.37514538493303</v>
+        <v>21.31449259936512</v>
       </c>
       <c r="F342" t="n">
-        <v>26.54652890103539</v>
+        <v>19.64713080971402</v>
       </c>
       <c r="G342" t="n">
         <v>89</v>
@@ -9672,16 +9672,16 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>-0.4394401622188595</v>
+        <v>-8.003074728307313</v>
       </c>
       <c r="D343" t="n">
-        <v>288.8700649377071</v>
+        <v>871.2507478347933</v>
       </c>
       <c r="E343" t="n">
-        <v>359.537594020192</v>
+        <v>899.1723187493931</v>
       </c>
       <c r="F343" t="n">
-        <v>33.8000482617419</v>
+        <v>121.3129755198536</v>
       </c>
       <c r="G343" t="n">
         <v>99</v>
@@ -9699,16 +9699,16 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>0.2653372804943984</v>
+        <v>-0.6946495875287595</v>
       </c>
       <c r="D344" t="n">
-        <v>196.1483600575437</v>
+        <v>352.1859226021716</v>
       </c>
       <c r="E344" t="n">
-        <v>274.8665757692664</v>
+        <v>417.4628960404082</v>
       </c>
       <c r="F344" t="n">
-        <v>21.08905335565285</v>
+        <v>46.91544367610753</v>
       </c>
       <c r="G344" t="n">
         <v>93</v>
@@ -9726,16 +9726,16 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>-1.518775580397132</v>
+        <v>-175.0311629232787</v>
       </c>
       <c r="D345" t="n">
-        <v>10.54307125164912</v>
+        <v>115.3728817181709</v>
       </c>
       <c r="E345" t="n">
-        <v>13.83821931492177</v>
+        <v>115.6858472164712</v>
       </c>
       <c r="F345" t="n">
-        <v>76.22838281024234</v>
+        <v>1397.007291206414</v>
       </c>
       <c r="G345" t="n">
         <v>78</v>
@@ -9753,16 +9753,16 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>-2.974966838847194</v>
+        <v>-56.10964554204686</v>
       </c>
       <c r="D346" t="n">
-        <v>170.339352077908</v>
+        <v>714.0951894124349</v>
       </c>
       <c r="E346" t="n">
-        <v>189.0763953413982</v>
+        <v>716.6800032946782</v>
       </c>
       <c r="F346" t="n">
-        <v>60.48985417137148</v>
+        <v>312.0572552482889</v>
       </c>
       <c r="G346" t="n">
         <v>18</v>
@@ -9780,16 +9780,16 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>-1.170363985079215</v>
+        <v>-0.04756042088650814</v>
       </c>
       <c r="D347" t="n">
-        <v>26.16670822829343</v>
+        <v>19.77292645915171</v>
       </c>
       <c r="E347" t="n">
-        <v>33.75492614331672</v>
+        <v>23.45094853702939</v>
       </c>
       <c r="F347" t="n">
-        <v>31.13225935356248</v>
+        <v>31.17022593100995</v>
       </c>
       <c r="G347" t="n">
         <v>89</v>
@@ -9807,16 +9807,16 @@
         </is>
       </c>
       <c r="C348" t="n">
-        <v>-2.465714334040271</v>
+        <v>-9.813033066155466</v>
       </c>
       <c r="D348" t="n">
-        <v>485.1432430382931</v>
+        <v>960.2302874940815</v>
       </c>
       <c r="E348" t="n">
-        <v>557.8839679918519</v>
+        <v>985.4197599227687</v>
       </c>
       <c r="F348" t="n">
-        <v>57.70115447333048</v>
+        <v>159.3319138392295</v>
       </c>
       <c r="G348" t="n">
         <v>99</v>
@@ -9834,16 +9834,16 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>-0.3293986540843752</v>
+        <v>-6.982094306273204</v>
       </c>
       <c r="D349" t="n">
-        <v>276.8514689783896</v>
+        <v>877.8627394809517</v>
       </c>
       <c r="E349" t="n">
-        <v>369.7477572792819</v>
+        <v>906.0170148686412</v>
       </c>
       <c r="F349" t="n">
-        <v>26.01376763261845</v>
+        <v>105.3181496836835</v>
       </c>
       <c r="G349" t="n">
         <v>93</v>
@@ -9861,16 +9861,16 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>-1.267400844568888</v>
+        <v>-1.726452845748616</v>
       </c>
       <c r="D350" t="n">
-        <v>10.04170159193186</v>
+        <v>11.80236538862571</v>
       </c>
       <c r="E350" t="n">
-        <v>13.12954343316646</v>
+        <v>14.39741250260066</v>
       </c>
       <c r="F350" t="n">
-        <v>68.09251002321504</v>
+        <v>83.14932905956792</v>
       </c>
       <c r="G350" t="n">
         <v>78</v>
@@ -9888,16 +9888,16 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>-5.119862829266934</v>
+        <v>-2.751532268232836</v>
       </c>
       <c r="D351" t="n">
-        <v>216.2550307379828</v>
+        <v>168.9681837293837</v>
       </c>
       <c r="E351" t="n">
-        <v>234.6072360861777</v>
+        <v>183.6855097579165</v>
       </c>
       <c r="F351" t="n">
-        <v>75.99202613438082</v>
+        <v>91.84479957930249</v>
       </c>
       <c r="G351" t="n">
         <v>18</v>
@@ -9915,16 +9915,16 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>-0.5562582109772414</v>
+        <v>-0.9356836082283433</v>
       </c>
       <c r="D352" t="n">
-        <v>21.37206703357482</v>
+        <v>28.36010017823637</v>
       </c>
       <c r="E352" t="n">
-        <v>28.58325625824904</v>
+        <v>31.87777926545</v>
       </c>
       <c r="F352" t="n">
-        <v>26.14848722198703</v>
+        <v>45.4327576985261</v>
       </c>
       <c r="G352" t="n">
         <v>89</v>
@@ -9942,16 +9942,16 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>-1.961363878045254</v>
+        <v>-17.69833917346569</v>
       </c>
       <c r="D353" t="n">
-        <v>437.0993228488499</v>
+        <v>1277.438175702336</v>
       </c>
       <c r="E353" t="n">
-        <v>515.6955540375247</v>
+        <v>1295.832946700327</v>
       </c>
       <c r="F353" t="n">
-        <v>50.75843167437033</v>
+        <v>210.7735769976476</v>
       </c>
       <c r="G353" t="n">
         <v>99</v>
@@ -9969,16 +9969,16 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>-0.09349184481544137</v>
+        <v>-15.01310389473757</v>
       </c>
       <c r="D354" t="n">
-        <v>260.9300038327453</v>
+        <v>1262.76767820953</v>
       </c>
       <c r="E354" t="n">
-        <v>335.3402666199524</v>
+        <v>1283.263043220299</v>
       </c>
       <c r="F354" t="n">
-        <v>27.25203824935338</v>
+        <v>148.4267843375896</v>
       </c>
       <c r="G354" t="n">
         <v>93</v>
@@ -9996,16 +9996,16 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>-0.8742361163459411</v>
+        <v>-5.429272583110184</v>
       </c>
       <c r="D355" t="n">
-        <v>8.821903693370331</v>
+        <v>20.53690833311815</v>
       </c>
       <c r="E355" t="n">
-        <v>11.93706677761165</v>
+        <v>22.10886113554009</v>
       </c>
       <c r="F355" t="n">
-        <v>68.03064394417191</v>
+        <v>182.828944537578</v>
       </c>
       <c r="G355" t="n">
         <v>78</v>
@@ -10023,16 +10023,16 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>-4.766457524699846</v>
+        <v>-4.535537760444623</v>
       </c>
       <c r="D356" t="n">
-        <v>208.3832685682509</v>
+        <v>205.2493709988064</v>
       </c>
       <c r="E356" t="n">
-        <v>227.7325493193445</v>
+        <v>223.1261457180332</v>
       </c>
       <c r="F356" t="n">
-        <v>72.14998390685405</v>
+        <v>112.8749777434094</v>
       </c>
       <c r="G356" t="n">
         <v>18</v>
@@ -10050,16 +10050,16 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>-1.588835747085712</v>
+        <v>0.242128345091866</v>
       </c>
       <c r="D357" t="n">
-        <v>28.98271344217022</v>
+        <v>15.36897479282336</v>
       </c>
       <c r="E357" t="n">
-        <v>36.86575422243974</v>
+        <v>19.94659202904333</v>
       </c>
       <c r="F357" t="n">
-        <v>36.64915180377663</v>
+        <v>21.31834261894755</v>
       </c>
       <c r="G357" t="n">
         <v>89</v>
@@ -10077,16 +10077,16 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>-1.345158863882544</v>
+        <v>0.3081704779704079</v>
       </c>
       <c r="D358" t="n">
-        <v>388.4749446059718</v>
+        <v>190.6574109010022</v>
       </c>
       <c r="E358" t="n">
-        <v>458.9164588290386</v>
+        <v>249.2568178777828</v>
       </c>
       <c r="F358" t="n">
-        <v>46.30168774396746</v>
+        <v>30.98028604555128</v>
       </c>
       <c r="G358" t="n">
         <v>99</v>
@@ -10104,16 +10104,16 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>-0.7252051683003251</v>
+        <v>-0.5189256253429102</v>
       </c>
       <c r="D359" t="n">
-        <v>338.2837898500504</v>
+        <v>340.9665314048849</v>
       </c>
       <c r="E359" t="n">
-        <v>421.2096441095652</v>
+        <v>395.2266133646757</v>
       </c>
       <c r="F359" t="n">
-        <v>32.08605571292005</v>
+        <v>43.1389975523823</v>
       </c>
       <c r="G359" t="n">
         <v>93</v>
@@ -10131,16 +10131,16 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>-0.8484091693341975</v>
+        <v>-0.09907699624488941</v>
       </c>
       <c r="D360" t="n">
-        <v>8.680920417492207</v>
+        <v>7.141204222654685</v>
       </c>
       <c r="E360" t="n">
-        <v>11.85453516504549</v>
+        <v>9.141122132314178</v>
       </c>
       <c r="F360" t="n">
-        <v>71.81077394800639</v>
+        <v>100.1886663326802</v>
       </c>
       <c r="G360" t="n">
         <v>78</v>
@@ -10158,18 +10158,153 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>-5.120973166142416</v>
+        <v>-0.3079071905719204</v>
       </c>
       <c r="D361" t="n">
-        <v>214.6291478474935</v>
+        <v>94.51902940538194</v>
       </c>
       <c r="E361" t="n">
-        <v>234.628517711142</v>
+        <v>108.4573573747184</v>
       </c>
       <c r="F361" t="n">
-        <v>75.85463937737394</v>
+        <v>56.50928387268108</v>
       </c>
       <c r="G361" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>TiAlloyNet</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>YM</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>0.6515747030873701</v>
+      </c>
+      <c r="D362" t="n">
+        <v>10.27885852770859</v>
+      </c>
+      <c r="E362" t="n">
+        <v>13.52463995140972</v>
+      </c>
+      <c r="F362" t="n">
+        <v>14.38797063005773</v>
+      </c>
+      <c r="G362" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>TiAlloyNet</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>YS</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>0.7340625828595753</v>
+      </c>
+      <c r="D363" t="n">
+        <v>116.6312067821772</v>
+      </c>
+      <c r="E363" t="n">
+        <v>154.5386892314451</v>
+      </c>
+      <c r="F363" t="n">
+        <v>18.16391254593445</v>
+      </c>
+      <c r="G363" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>TiAlloyNet</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>UTS</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>0.7092922524258163</v>
+      </c>
+      <c r="D364" t="n">
+        <v>120.2684788857737</v>
+      </c>
+      <c r="E364" t="n">
+        <v>172.9044734145354</v>
+      </c>
+      <c r="F364" t="n">
+        <v>12.81726989937662</v>
+      </c>
+      <c r="G364" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>TiAlloyNet</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>El</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>0.1310510418025334</v>
+      </c>
+      <c r="D365" t="n">
+        <v>5.653394411771726</v>
+      </c>
+      <c r="E365" t="n">
+        <v>8.127979242846337</v>
+      </c>
+      <c r="F365" t="n">
+        <v>75.21453608759478</v>
+      </c>
+      <c r="G365" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>TiAlloyNet</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>0.6539824691104517</v>
+      </c>
+      <c r="D366" t="n">
+        <v>40.91187710232205</v>
+      </c>
+      <c r="E366" t="n">
+        <v>55.78527856297358</v>
+      </c>
+      <c r="F366" t="n">
+        <v>24.06978677925016</v>
+      </c>
+      <c r="G366" t="n">
         <v>18</v>
       </c>
     </row>

--- a/results/surrogate_comparison.xlsx
+++ b/results/surrogate_comparison.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H376"/>
+  <dimension ref="A1:H381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,16 +473,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.6906053710854196</v>
+        <v>0.6906053901074334</v>
       </c>
       <c r="E2" t="n">
-        <v>9.239215979415379</v>
+        <v>9.239216793788954</v>
       </c>
       <c r="F2" t="n">
-        <v>12.74463077192712</v>
+        <v>12.74463038014827</v>
       </c>
       <c r="G2" t="n">
-        <v>13.42595919270845</v>
+        <v>13.42595985459552</v>
       </c>
       <c r="H2" t="n">
         <v>89</v>
@@ -503,16 +503,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7279585986684967</v>
+        <v>0.7279585865014603</v>
       </c>
       <c r="E3" t="n">
-        <v>109.3448113335504</v>
+        <v>109.3448239721433</v>
       </c>
       <c r="F3" t="n">
-        <v>156.3021682787094</v>
+        <v>156.3021717740122</v>
       </c>
       <c r="G3" t="n">
-        <v>17.12015553933064</v>
+        <v>17.12015755892581</v>
       </c>
       <c r="H3" t="n">
         <v>99</v>
@@ -533,16 +533,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7174037458389865</v>
+        <v>0.7174037263273597</v>
       </c>
       <c r="E4" t="n">
-        <v>117.6879301994078</v>
+        <v>117.6879347934518</v>
       </c>
       <c r="F4" t="n">
-        <v>170.4751679330726</v>
+        <v>170.4751738182316</v>
       </c>
       <c r="G4" t="n">
-        <v>11.80778752629052</v>
+        <v>11.80778806477645</v>
       </c>
       <c r="H4" t="n">
         <v>93</v>
@@ -563,16 +563,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1093536879190491</v>
+        <v>0.1093537511305451</v>
       </c>
       <c r="E5" t="n">
-        <v>5.381431738535563</v>
+        <v>5.38143148789039</v>
       </c>
       <c r="F5" t="n">
-        <v>8.228829982745859</v>
+        <v>8.22882969073507</v>
       </c>
       <c r="G5" t="n">
-        <v>54.63129325860025</v>
+        <v>54.63128894216651</v>
       </c>
       <c r="H5" t="n">
         <v>78</v>
@@ -593,16 +593,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8391963098957026</v>
+        <v>0.839196446372223</v>
       </c>
       <c r="E6" t="n">
-        <v>28.28731197781033</v>
+        <v>28.2873043484158</v>
       </c>
       <c r="F6" t="n">
-        <v>38.02932001089285</v>
+        <v>38.0293038728603</v>
       </c>
       <c r="G6" t="n">
-        <v>9.70776861412129</v>
+        <v>9.707771868737058</v>
       </c>
       <c r="H6" t="n">
         <v>18</v>
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.6583659229829599</v>
+        <v>0.6583659151515574</v>
       </c>
       <c r="E7" t="n">
-        <v>9.482891939999012</v>
+        <v>9.482891382796041</v>
       </c>
       <c r="F7" t="n">
-        <v>13.39218576292153</v>
+        <v>13.39218591641851</v>
       </c>
       <c r="G7" t="n">
-        <v>13.49421432665025</v>
+        <v>13.49421300500009</v>
       </c>
       <c r="H7" t="n">
         <v>89</v>
@@ -653,16 +653,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7016215068254561</v>
+        <v>0.7016215113172027</v>
       </c>
       <c r="E8" t="n">
-        <v>119.1406305486506</v>
+        <v>119.1406308569089</v>
       </c>
       <c r="F8" t="n">
-        <v>163.6934339140801</v>
+        <v>163.6934326819714</v>
       </c>
       <c r="G8" t="n">
-        <v>18.97734581360871</v>
+        <v>18.97734595868049</v>
       </c>
       <c r="H8" t="n">
         <v>99</v>
@@ -683,16 +683,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.6590781892220923</v>
+        <v>0.6590781923025056</v>
       </c>
       <c r="E9" t="n">
-        <v>126.9980143885459</v>
+        <v>126.9980068411878</v>
       </c>
       <c r="F9" t="n">
-        <v>187.2428831404113</v>
+        <v>187.2428822944908</v>
       </c>
       <c r="G9" t="n">
-        <v>12.71970655408111</v>
+        <v>12.71970529133242</v>
       </c>
       <c r="H9" t="n">
         <v>93</v>
@@ -713,16 +713,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1412355316494921</v>
+        <v>0.1412355505726298</v>
       </c>
       <c r="E10" t="n">
-        <v>5.322167708323552</v>
+        <v>5.322167616624099</v>
       </c>
       <c r="F10" t="n">
-        <v>8.080206985143183</v>
+        <v>8.080206896118268</v>
       </c>
       <c r="G10" t="n">
-        <v>58.78812103207387</v>
+        <v>58.78811828970917</v>
       </c>
       <c r="H10" t="n">
         <v>78</v>
@@ -743,16 +743,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.7751017488715731</v>
+        <v>0.7751016183022685</v>
       </c>
       <c r="E11" t="n">
-        <v>34.00810665554471</v>
+        <v>34.00811852349175</v>
       </c>
       <c r="F11" t="n">
-        <v>44.97421521657824</v>
+        <v>44.97422827192911</v>
       </c>
       <c r="G11" t="n">
-        <v>13.2465403477279</v>
+        <v>13.24655138552283</v>
       </c>
       <c r="H11" t="n">
         <v>18</v>
@@ -773,16 +773,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.6330727128824011</v>
+        <v>0.6330727335100685</v>
       </c>
       <c r="E12" t="n">
-        <v>10.02689618742868</v>
+        <v>10.02689653032281</v>
       </c>
       <c r="F12" t="n">
-        <v>13.87908635257032</v>
+        <v>13.87908596244782</v>
       </c>
       <c r="G12" t="n">
-        <v>14.29744293036296</v>
+        <v>14.29744317421267</v>
       </c>
       <c r="H12" t="n">
         <v>89</v>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.655773491309559</v>
+        <v>0.6557734914681445</v>
       </c>
       <c r="E13" t="n">
-        <v>136.1513949307528</v>
+        <v>136.1513927729443</v>
       </c>
       <c r="F13" t="n">
-        <v>175.8205592488698</v>
+        <v>175.8205592083694</v>
       </c>
       <c r="G13" t="n">
-        <v>21.31430679127891</v>
+        <v>21.31430611530694</v>
       </c>
       <c r="H13" t="n">
         <v>99</v>
@@ -833,16 +833,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.6562705745329191</v>
+        <v>0.6562705713734752</v>
       </c>
       <c r="E14" t="n">
-        <v>138.2627317367061</v>
+        <v>138.2627310804141</v>
       </c>
       <c r="F14" t="n">
-        <v>188.0123087710208</v>
+        <v>188.0123096350934</v>
       </c>
       <c r="G14" t="n">
-        <v>14.25765009226387</v>
+        <v>14.25765051557687</v>
       </c>
       <c r="H14" t="n">
         <v>93</v>
@@ -863,16 +863,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.2114795736927698</v>
+        <v>0.2114795515840853</v>
       </c>
       <c r="E15" t="n">
-        <v>5.605153774603819</v>
+        <v>5.60515387241657</v>
       </c>
       <c r="F15" t="n">
-        <v>7.742690980482275</v>
+        <v>7.742691089027789</v>
       </c>
       <c r="G15" t="n">
-        <v>97.76700403818705</v>
+        <v>97.76700858121814</v>
       </c>
       <c r="H15" t="n">
         <v>78</v>
@@ -893,16 +893,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.6732400412062528</v>
+        <v>0.6732400436935475</v>
       </c>
       <c r="E16" t="n">
-        <v>32.05198754204644</v>
+        <v>32.05198838975694</v>
       </c>
       <c r="F16" t="n">
-        <v>54.21069448400422</v>
+        <v>54.21069427767848</v>
       </c>
       <c r="G16" t="n">
-        <v>18.99717283874894</v>
+        <v>18.99717392972954</v>
       </c>
       <c r="H16" t="n">
         <v>18</v>
@@ -923,16 +923,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.6841037750479455</v>
+        <v>0.6841037409320214</v>
       </c>
       <c r="E17" t="n">
-        <v>9.733389393667156</v>
+        <v>9.733389865146593</v>
       </c>
       <c r="F17" t="n">
-        <v>12.87784195589301</v>
+        <v>12.87784265127877</v>
       </c>
       <c r="G17" t="n">
-        <v>14.16911713352287</v>
+        <v>14.16911760619709</v>
       </c>
       <c r="H17" t="n">
         <v>89</v>
@@ -953,16 +953,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.713605902273077</v>
+        <v>0.7136058820842783</v>
       </c>
       <c r="E18" t="n">
-        <v>122.6381897589173</v>
+        <v>122.6381949993095</v>
       </c>
       <c r="F18" t="n">
-        <v>160.3723646408556</v>
+        <v>160.3723702934255</v>
       </c>
       <c r="G18" t="n">
-        <v>19.48505678878116</v>
+        <v>19.4850578610286</v>
       </c>
       <c r="H18" t="n">
         <v>99</v>
@@ -983,16 +983,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.6805106885104837</v>
+        <v>0.6805106831227409</v>
       </c>
       <c r="E19" t="n">
-        <v>128.7072163243448</v>
+        <v>128.7072212465348</v>
       </c>
       <c r="F19" t="n">
-        <v>181.2617185234219</v>
+        <v>181.2617200517853</v>
       </c>
       <c r="G19" t="n">
-        <v>13.33800290179576</v>
+        <v>13.33800344665184</v>
       </c>
       <c r="H19" t="n">
         <v>93</v>
@@ -1013,16 +1013,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.2064077396282572</v>
+        <v>0.2064077295544723</v>
       </c>
       <c r="E20" t="n">
-        <v>5.463785905104417</v>
+        <v>5.463785886764526</v>
       </c>
       <c r="F20" t="n">
-        <v>7.76755190884857</v>
+        <v>7.767551958148853</v>
       </c>
       <c r="G20" t="n">
-        <v>96.14526774885192</v>
+        <v>96.14526488743476</v>
       </c>
       <c r="H20" t="n">
         <v>78</v>
@@ -1043,16 +1043,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.6377842957716464</v>
+        <v>0.6377843477975578</v>
       </c>
       <c r="E21" t="n">
-        <v>33.12752363416884</v>
+        <v>33.12752193874783</v>
       </c>
       <c r="F21" t="n">
-        <v>57.07608716269155</v>
+        <v>57.07608306370368</v>
       </c>
       <c r="G21" t="n">
-        <v>19.73184064050045</v>
+        <v>19.73183678139224</v>
       </c>
       <c r="H21" t="n">
         <v>18</v>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.7067544421322078</v>
+        <v>0.7067545071136404</v>
       </c>
       <c r="E22" t="n">
-        <v>9.162212886167376</v>
+        <v>9.162211557452599</v>
       </c>
       <c r="F22" t="n">
-        <v>12.40756599680324</v>
+        <v>12.40756462208258</v>
       </c>
       <c r="G22" t="n">
-        <v>13.22500929385856</v>
+        <v>13.22500749308393</v>
       </c>
       <c r="H22" t="n">
         <v>89</v>
@@ -1103,16 +1103,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.6916065332202326</v>
+        <v>0.6916065199529504</v>
       </c>
       <c r="E23" t="n">
-        <v>122.6378084433199</v>
+        <v>122.6378112176452</v>
       </c>
       <c r="F23" t="n">
-        <v>166.4179184765067</v>
+        <v>166.4179220562088</v>
       </c>
       <c r="G23" t="n">
-        <v>19.13267210707993</v>
+        <v>19.13267173468377</v>
       </c>
       <c r="H23" t="n">
         <v>99</v>
@@ -1133,16 +1133,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.691404572659196</v>
+        <v>0.6914045784747052</v>
       </c>
       <c r="E24" t="n">
-        <v>125.4827844763315</v>
+        <v>125.4827828356015</v>
       </c>
       <c r="F24" t="n">
-        <v>178.1446030299801</v>
+        <v>178.1446013514044</v>
       </c>
       <c r="G24" t="n">
-        <v>12.75306853523207</v>
+        <v>12.7530684426023</v>
       </c>
       <c r="H24" t="n">
         <v>93</v>
@@ -1163,16 +1163,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.1415900486020614</v>
+        <v>0.1415899484041515</v>
       </c>
       <c r="E25" t="n">
-        <v>5.165652758035904</v>
+        <v>5.16565377284319</v>
       </c>
       <c r="F25" t="n">
-        <v>8.078538968962604</v>
+        <v>8.078539440446361</v>
       </c>
       <c r="G25" t="n">
-        <v>63.02930025636167</v>
+        <v>63.02931982804419</v>
       </c>
       <c r="H25" t="n">
         <v>78</v>
@@ -1193,16 +1193,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.7274025785505454</v>
+        <v>0.7274026733759744</v>
       </c>
       <c r="E26" t="n">
-        <v>37.0952156914605</v>
+        <v>37.09521230061849</v>
       </c>
       <c r="F26" t="n">
-        <v>49.51438924051437</v>
+        <v>49.51438062850405</v>
       </c>
       <c r="G26" t="n">
-        <v>18.22630197315438</v>
+        <v>18.22630202355273</v>
       </c>
       <c r="H26" t="n">
         <v>18</v>
@@ -1223,16 +1223,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.442412816419542</v>
+        <v>0.4424125220070623</v>
       </c>
       <c r="E27" t="n">
-        <v>12.20936070131452</v>
+        <v>12.20936297298817</v>
       </c>
       <c r="F27" t="n">
-        <v>17.1091039219695</v>
+        <v>17.10910843887125</v>
       </c>
       <c r="G27" t="n">
-        <v>16.37298731606689</v>
+        <v>16.37298468257466</v>
       </c>
       <c r="H27" t="n">
         <v>89</v>
@@ -1253,16 +1253,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.586637697764308</v>
+        <v>0.5866378414020714</v>
       </c>
       <c r="E28" t="n">
-        <v>144.453811799637</v>
+        <v>144.4538253630051</v>
       </c>
       <c r="F28" t="n">
-        <v>192.6694842235421</v>
+        <v>192.6694507485299</v>
       </c>
       <c r="G28" t="n">
-        <v>24.24814052589069</v>
+        <v>24.24815500980561</v>
       </c>
       <c r="H28" t="n">
         <v>99</v>
@@ -1283,16 +1283,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.5305099119498338</v>
+        <v>0.5305099214322673</v>
       </c>
       <c r="E29" t="n">
-        <v>156.4042151666457</v>
+        <v>156.4041803831695</v>
       </c>
       <c r="F29" t="n">
-        <v>219.7309029423084</v>
+        <v>219.7309007233225</v>
       </c>
       <c r="G29" t="n">
-        <v>15.50461346212664</v>
+        <v>15.50460943798407</v>
       </c>
       <c r="H29" t="n">
         <v>93</v>
@@ -1313,16 +1313,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.06714890041237276</v>
+        <v>0.06714913352631868</v>
       </c>
       <c r="E30" t="n">
-        <v>6.082058496964284</v>
+        <v>6.082057145925669</v>
       </c>
       <c r="F30" t="n">
-        <v>8.421541949508685</v>
+        <v>8.421540897261977</v>
       </c>
       <c r="G30" t="n">
-        <v>92.59752195216532</v>
+        <v>92.59747377310288</v>
       </c>
       <c r="H30" t="n">
         <v>78</v>
@@ -1343,16 +1343,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.7119078650776534</v>
+        <v>0.7119070821252634</v>
       </c>
       <c r="E31" t="n">
-        <v>36.77689954969618</v>
+        <v>36.77681054009332</v>
       </c>
       <c r="F31" t="n">
-        <v>50.90216514849212</v>
+        <v>50.9022343172405</v>
       </c>
       <c r="G31" t="n">
-        <v>13.79337214149466</v>
+        <v>13.79329000748904</v>
       </c>
       <c r="H31" t="n">
         <v>18</v>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.5979519318386226</v>
+        <v>0.5979520195440402</v>
       </c>
       <c r="E32" t="n">
-        <v>10.42311344789655</v>
+        <v>10.42311370506715</v>
       </c>
       <c r="F32" t="n">
-        <v>14.52813486370588</v>
+        <v>14.52813327907421</v>
       </c>
       <c r="G32" t="n">
-        <v>14.64522297932337</v>
+        <v>14.64522352021916</v>
       </c>
       <c r="H32" t="n">
         <v>89</v>
@@ -1403,16 +1403,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.7045724965413431</v>
+        <v>0.7045724855551245</v>
       </c>
       <c r="E33" t="n">
-        <v>128.7476344253078</v>
+        <v>128.7476359665996</v>
       </c>
       <c r="F33" t="n">
-        <v>162.8819512422347</v>
+        <v>162.8819542708233</v>
       </c>
       <c r="G33" t="n">
-        <v>19.04030463124539</v>
+        <v>19.0403034450394</v>
       </c>
       <c r="H33" t="n">
         <v>99</v>
@@ -1433,16 +1433,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.5313360798753954</v>
+        <v>0.5313360803693483</v>
       </c>
       <c r="E34" t="n">
-        <v>169.0997452274445</v>
+        <v>169.0997481807586</v>
       </c>
       <c r="F34" t="n">
-        <v>219.5374861253686</v>
+        <v>219.5374860096767</v>
       </c>
       <c r="G34" t="n">
-        <v>19.38748517221462</v>
+        <v>19.38748497176609</v>
       </c>
       <c r="H34" t="n">
         <v>93</v>
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.2057415188313154</v>
+        <v>0.2057416858993705</v>
       </c>
       <c r="E35" t="n">
-        <v>5.584961720002004</v>
+        <v>5.584961059765938</v>
       </c>
       <c r="F35" t="n">
-        <v>7.770811655228253</v>
+        <v>7.77081083795372</v>
       </c>
       <c r="G35" t="n">
-        <v>77.39409461979704</v>
+        <v>77.39408641176111</v>
       </c>
       <c r="H35" t="n">
         <v>78</v>
@@ -1493,16 +1493,16 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.6615521568880801</v>
+        <v>0.661552337368507</v>
       </c>
       <c r="E36" t="n">
-        <v>42.30901930067274</v>
+        <v>42.3090082804362</v>
       </c>
       <c r="F36" t="n">
-        <v>55.17170813172314</v>
+        <v>55.17169342131064</v>
       </c>
       <c r="G36" t="n">
-        <v>24.05985075836541</v>
+        <v>24.05984191126272</v>
       </c>
       <c r="H36" t="n">
         <v>18</v>
@@ -1523,16 +1523,16 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.5531681364560638</v>
+        <v>0.5531682313530826</v>
       </c>
       <c r="E37" t="n">
-        <v>11.32614568646034</v>
+        <v>11.32614521498091</v>
       </c>
       <c r="F37" t="n">
-        <v>15.3159147520357</v>
+        <v>15.31591312565803</v>
       </c>
       <c r="G37" t="n">
-        <v>15.67548855417068</v>
+        <v>15.67548780537763</v>
       </c>
       <c r="H37" t="n">
         <v>89</v>
@@ -1553,16 +1553,16 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.4935872140364789</v>
+        <v>0.4935871794185036</v>
       </c>
       <c r="E38" t="n">
-        <v>155.1039333150844</v>
+        <v>155.1039431793521</v>
       </c>
       <c r="F38" t="n">
-        <v>213.2552994106119</v>
+        <v>213.2553066995931</v>
       </c>
       <c r="G38" t="n">
-        <v>20.63641208025756</v>
+        <v>20.63641330824216</v>
       </c>
       <c r="H38" t="n">
         <v>99</v>
@@ -1583,16 +1583,16 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-0.9800092537799749</v>
+        <v>-0.9800093790805646</v>
       </c>
       <c r="E39" t="n">
-        <v>372.9080288794733</v>
+        <v>372.9080387238533</v>
       </c>
       <c r="F39" t="n">
-        <v>451.2440998890784</v>
+        <v>451.24411416708</v>
       </c>
       <c r="G39" t="n">
-        <v>50.03252892636323</v>
+        <v>50.03253028451648</v>
       </c>
       <c r="H39" t="n">
         <v>93</v>
@@ -1613,16 +1613,16 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.126153378282518</v>
+        <v>0.1261533679817445</v>
       </c>
       <c r="E40" t="n">
-        <v>5.856233664048024</v>
+        <v>5.856233517328898</v>
       </c>
       <c r="F40" t="n">
-        <v>8.150852952454796</v>
+        <v>8.150853000495315</v>
       </c>
       <c r="G40" t="n">
-        <v>90.60773787865008</v>
+        <v>90.6077351735552</v>
       </c>
       <c r="H40" t="n">
         <v>78</v>
@@ -1643,16 +1643,16 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.4576052163575042</v>
+        <v>0.4576051940143999</v>
       </c>
       <c r="E41" t="n">
-        <v>56.19036865234375</v>
+        <v>56.19037458631728</v>
       </c>
       <c r="F41" t="n">
-        <v>69.84387183927194</v>
+        <v>69.84387327782642</v>
       </c>
       <c r="G41" t="n">
-        <v>32.91503126037941</v>
+        <v>32.91503520927612</v>
       </c>
       <c r="H41" t="n">
         <v>18</v>
@@ -1673,16 +1673,16 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.3858609520324577</v>
+        <v>0.3858610362528599</v>
       </c>
       <c r="E42" t="n">
-        <v>12.875855135114</v>
+        <v>12.8758544921875</v>
       </c>
       <c r="F42" t="n">
-        <v>17.95577805458029</v>
+        <v>17.95577682339094</v>
       </c>
       <c r="G42" t="n">
-        <v>17.39190588361088</v>
+        <v>17.39190518984572</v>
       </c>
       <c r="H42" t="n">
         <v>89</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.649491509774343</v>
+        <v>0.6494914213745404</v>
       </c>
       <c r="E43" t="n">
-        <v>133.4136682375513</v>
+        <v>133.4137089276554</v>
       </c>
       <c r="F43" t="n">
-        <v>177.4176294575569</v>
+        <v>177.4176518303137</v>
       </c>
       <c r="G43" t="n">
-        <v>19.95018557205411</v>
+        <v>19.95018434707734</v>
       </c>
       <c r="H43" t="n">
         <v>99</v>
@@ -1733,16 +1733,16 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.6752538681448321</v>
+        <v>0.675254063524102</v>
       </c>
       <c r="E44" t="n">
-        <v>138.4354494156376</v>
+        <v>138.4353700043053</v>
       </c>
       <c r="F44" t="n">
-        <v>182.746858446377</v>
+        <v>182.7468034727381</v>
       </c>
       <c r="G44" t="n">
-        <v>15.5981662420177</v>
+        <v>15.59815762178519</v>
       </c>
       <c r="H44" t="n">
         <v>93</v>
@@ -1763,16 +1763,16 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.1363431659861806</v>
+        <v>0.1363430243628023</v>
       </c>
       <c r="E45" t="n">
-        <v>6.077720801035563</v>
+        <v>6.077720959981282</v>
       </c>
       <c r="F45" t="n">
-        <v>8.103190693805468</v>
+        <v>8.10319135819041</v>
       </c>
       <c r="G45" t="n">
-        <v>99.24917568306458</v>
+        <v>99.24911425941725</v>
       </c>
       <c r="H45" t="n">
         <v>78</v>
@@ -1793,16 +1793,16 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.6863887961149896</v>
+        <v>0.686388517033774</v>
       </c>
       <c r="E46" t="n">
-        <v>39.93372684054904</v>
+        <v>39.9337404039171</v>
       </c>
       <c r="F46" t="n">
-        <v>53.10878176735407</v>
+        <v>53.10880539798315</v>
       </c>
       <c r="G46" t="n">
-        <v>21.25157557030805</v>
+        <v>21.25159073395798</v>
       </c>
       <c r="H46" t="n">
         <v>18</v>
@@ -1823,16 +1823,16 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.6032297088765498</v>
+        <v>0.6032297044911212</v>
       </c>
       <c r="E47" t="n">
-        <v>10.90435701005914</v>
+        <v>10.90435683861207</v>
       </c>
       <c r="F47" t="n">
-        <v>14.43246277285853</v>
+        <v>14.4324628526182</v>
       </c>
       <c r="G47" t="n">
-        <v>15.39363758050536</v>
+        <v>15.39363769514772</v>
       </c>
       <c r="H47" t="n">
         <v>89</v>
@@ -1853,16 +1853,16 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.5328772589503901</v>
+        <v>0.5328773009389027</v>
       </c>
       <c r="E48" t="n">
-        <v>164.4133901885062</v>
+        <v>164.4133760086214</v>
       </c>
       <c r="F48" t="n">
-        <v>204.8155879074215</v>
+        <v>204.8155787022369</v>
       </c>
       <c r="G48" t="n">
-        <v>22.63604842483763</v>
+        <v>22.63604653287608</v>
       </c>
       <c r="H48" t="n">
         <v>99</v>
@@ -1883,16 +1883,16 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.4625393156479254</v>
+        <v>0.4625393936176044</v>
       </c>
       <c r="E49" t="n">
-        <v>181.0553959672169</v>
+        <v>181.0553874354209</v>
       </c>
       <c r="F49" t="n">
-        <v>235.0992679686514</v>
+        <v>235.099250915669</v>
       </c>
       <c r="G49" t="n">
-        <v>21.58812403592558</v>
+        <v>21.58812309817549</v>
       </c>
       <c r="H49" t="n">
         <v>93</v>
@@ -1913,16 +1913,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.1137775359525861</v>
+        <v>0.11377761076304</v>
       </c>
       <c r="E50" t="n">
-        <v>5.794667372336755</v>
+        <v>5.794667127804878</v>
       </c>
       <c r="F50" t="n">
-        <v>8.208368207360349</v>
+        <v>8.208367860905712</v>
       </c>
       <c r="G50" t="n">
-        <v>75.96682599566186</v>
+        <v>75.9668173867021</v>
       </c>
       <c r="H50" t="n">
         <v>78</v>
@@ -1943,16 +1943,16 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.4814516888984579</v>
+        <v>0.4814518269817363</v>
       </c>
       <c r="E51" t="n">
-        <v>50.63839297824435</v>
+        <v>50.63838195800781</v>
       </c>
       <c r="F51" t="n">
-        <v>68.29126645395438</v>
+        <v>68.29125736137574</v>
       </c>
       <c r="G51" t="n">
-        <v>30.17801447645281</v>
+        <v>30.17801045992601</v>
       </c>
       <c r="H51" t="n">
         <v>18</v>
@@ -1973,16 +1973,16 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.4715563290312957</v>
+        <v>0.4715563488226866</v>
       </c>
       <c r="E52" t="n">
-        <v>12.37408275818557</v>
+        <v>12.3740824581532</v>
       </c>
       <c r="F52" t="n">
-        <v>16.65598125120922</v>
+        <v>16.65598093930745</v>
       </c>
       <c r="G52" t="n">
-        <v>18.06438550553724</v>
+        <v>18.06438606531849</v>
       </c>
       <c r="H52" t="n">
         <v>89</v>
@@ -2003,16 +2003,16 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.6341620848341825</v>
+        <v>0.634162047372787</v>
       </c>
       <c r="E53" t="n">
-        <v>138.6831495496962</v>
+        <v>138.6831535570549</v>
       </c>
       <c r="F53" t="n">
-        <v>181.2557771970449</v>
+        <v>181.2557864772397</v>
       </c>
       <c r="G53" t="n">
-        <v>19.04241827694666</v>
+        <v>19.04241928256164</v>
       </c>
       <c r="H53" t="n">
         <v>99</v>
@@ -2033,16 +2033,16 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.5986598725564161</v>
+        <v>0.5986599066162155</v>
       </c>
       <c r="E54" t="n">
         <v>162.9088597451487</v>
       </c>
       <c r="F54" t="n">
-        <v>203.1581355869507</v>
+        <v>203.1581269664253</v>
       </c>
       <c r="G54" t="n">
-        <v>18.49973593207389</v>
+        <v>18.49973608288801</v>
       </c>
       <c r="H54" t="n">
         <v>93</v>
@@ -2063,16 +2063,16 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.1326891453963508</v>
+        <v>0.1326890871613965</v>
       </c>
       <c r="E55" t="n">
-        <v>5.577681186871651</v>
+        <v>5.577681272457808</v>
       </c>
       <c r="F55" t="n">
-        <v>8.120314377858893</v>
+        <v>8.12031465047518</v>
       </c>
       <c r="G55" t="n">
-        <v>86.71102052353923</v>
+        <v>86.71102681362134</v>
       </c>
       <c r="H55" t="n">
         <v>78</v>
@@ -2093,16 +2093,16 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.5530516148822473</v>
+        <v>0.5530516017449587</v>
       </c>
       <c r="E56" t="n">
-        <v>42.19253285725912</v>
+        <v>42.19253709581163</v>
       </c>
       <c r="F56" t="n">
-        <v>63.40145737751961</v>
+        <v>63.40145830930867</v>
       </c>
       <c r="G56" t="n">
-        <v>25.17457369250287</v>
+        <v>25.17457297392428</v>
       </c>
       <c r="H56" t="n">
         <v>18</v>
@@ -2123,16 +2123,16 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.512587159368554</v>
+        <v>0.5125875450729793</v>
       </c>
       <c r="E57" t="n">
-        <v>11.59424513913272</v>
+        <v>11.59424089581779</v>
       </c>
       <c r="F57" t="n">
-        <v>15.99629320692665</v>
+        <v>15.99628687775168</v>
       </c>
       <c r="G57" t="n">
-        <v>15.51843912158047</v>
+        <v>15.51843747440068</v>
       </c>
       <c r="H57" t="n">
         <v>89</v>
@@ -2153,16 +2153,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.6409089152886496</v>
+        <v>0.6409087456368354</v>
       </c>
       <c r="E58" t="n">
-        <v>133.3550741792929</v>
+        <v>133.3551287410235</v>
       </c>
       <c r="F58" t="n">
-        <v>179.5766280796998</v>
+        <v>179.5766704999916</v>
       </c>
       <c r="G58" t="n">
-        <v>19.33272041864876</v>
+        <v>19.33272526751666</v>
       </c>
       <c r="H58" t="n">
         <v>99</v>
@@ -2183,16 +2183,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.6694529469307196</v>
+        <v>0.6694529008518048</v>
       </c>
       <c r="E59" t="n">
-        <v>140.8157233781712</v>
+        <v>140.8157319099672</v>
       </c>
       <c r="F59" t="n">
-        <v>184.3718321015445</v>
+        <v>184.3718449524436</v>
       </c>
       <c r="G59" t="n">
-        <v>15.94799187972211</v>
+        <v>15.94799147188358</v>
       </c>
       <c r="H59" t="n">
         <v>93</v>
@@ -2213,16 +2213,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.1256247021095542</v>
+        <v>0.1256250739132316</v>
       </c>
       <c r="E60" t="n">
-        <v>6.049460056500557</v>
+        <v>6.049458246964675</v>
       </c>
       <c r="F60" t="n">
-        <v>8.153318207841645</v>
+        <v>8.153316474356023</v>
       </c>
       <c r="G60" t="n">
-        <v>98.415496672773</v>
+        <v>98.41556784325741</v>
       </c>
       <c r="H60" t="n">
         <v>78</v>
@@ -2243,16 +2243,16 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.7541920091104496</v>
+        <v>0.7541919182851082</v>
       </c>
       <c r="E61" t="n">
-        <v>35.52630869547526</v>
+        <v>35.5262942843967</v>
       </c>
       <c r="F61" t="n">
-        <v>47.01847653206313</v>
+        <v>47.01848521865783</v>
       </c>
       <c r="G61" t="n">
-        <v>16.30015928718577</v>
+        <v>16.30015179902945</v>
       </c>
       <c r="H61" t="n">
         <v>18</v>
@@ -2273,16 +2273,16 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.6012054814696597</v>
+        <v>0.6012054882609728</v>
       </c>
       <c r="E62" t="n">
-        <v>11.07238259476222</v>
+        <v>11.07238143749451</v>
       </c>
       <c r="F62" t="n">
-        <v>14.46923142796003</v>
+        <v>14.46923130475738</v>
       </c>
       <c r="G62" t="n">
-        <v>15.80385892841606</v>
+        <v>15.80385694379792</v>
       </c>
       <c r="H62" t="n">
         <v>89</v>
@@ -2303,16 +2303,16 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.493140450257055</v>
+        <v>0.4931404753386556</v>
       </c>
       <c r="E63" t="n">
-        <v>166.1734736278804</v>
+        <v>166.1734720865885</v>
       </c>
       <c r="F63" t="n">
-        <v>213.3493469369623</v>
+        <v>213.3493416582384</v>
       </c>
       <c r="G63" t="n">
-        <v>22.29820718747084</v>
+        <v>22.29820820671153</v>
       </c>
       <c r="H63" t="n">
         <v>99</v>
@@ -2333,16 +2333,16 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-0.01450676697886522</v>
+        <v>-0.01450674552149933</v>
       </c>
       <c r="E64" t="n">
-        <v>261.1655535954301</v>
+        <v>261.1655434229041</v>
       </c>
       <c r="F64" t="n">
-        <v>323.0021406575536</v>
+        <v>323.0021372417188</v>
       </c>
       <c r="G64" t="n">
-        <v>31.68859811827052</v>
+        <v>31.68859714644396</v>
       </c>
       <c r="H64" t="n">
         <v>93</v>
@@ -2363,16 +2363,16 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.2486197313158403</v>
+        <v>0.2486197588482799</v>
       </c>
       <c r="E65" t="n">
-        <v>5.19190728970063</v>
+        <v>5.191907136868208</v>
       </c>
       <c r="F65" t="n">
-        <v>7.558147194792516</v>
+        <v>7.55814705631787</v>
       </c>
       <c r="G65" t="n">
-        <v>61.07975137042906</v>
+        <v>61.07973748218597</v>
       </c>
       <c r="H65" t="n">
         <v>78</v>
@@ -2393,16 +2393,16 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.7245922831502999</v>
+        <v>0.7245923387202755</v>
       </c>
       <c r="E66" t="n">
-        <v>37.2518073187934</v>
+        <v>37.25180986192491</v>
       </c>
       <c r="F66" t="n">
-        <v>49.7689647618335</v>
+        <v>49.76895974080443</v>
       </c>
       <c r="G66" t="n">
-        <v>21.05521227365363</v>
+        <v>21.05520982815354</v>
       </c>
       <c r="H66" t="n">
         <v>18</v>
@@ -2423,16 +2423,16 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.2371884562144375</v>
+        <v>0.2371884714308463</v>
       </c>
       <c r="E67" t="n">
-        <v>13.46348918957657</v>
+        <v>13.46349060401488</v>
       </c>
       <c r="F67" t="n">
-        <v>20.01149345721935</v>
+        <v>20.01149325762676</v>
       </c>
       <c r="G67" t="n">
-        <v>18.34481101458142</v>
+        <v>18.34481326282897</v>
       </c>
       <c r="H67" t="n">
         <v>89</v>
@@ -2453,16 +2453,16 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.6302732918645808</v>
+        <v>0.6302732861698244</v>
       </c>
       <c r="E68" t="n">
-        <v>138.4788679643111</v>
+        <v>138.4788707386364</v>
       </c>
       <c r="F68" t="n">
-        <v>182.2165892149579</v>
+        <v>182.2165906182635</v>
       </c>
       <c r="G68" t="n">
-        <v>21.85598261918106</v>
+        <v>21.85598295503661</v>
       </c>
       <c r="H68" t="n">
         <v>99</v>
@@ -2483,16 +2483,16 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.6053896734215145</v>
+        <v>0.6053896171726829</v>
       </c>
       <c r="E69" t="n">
-        <v>165.9381106797085</v>
+        <v>165.9381238055485</v>
       </c>
       <c r="F69" t="n">
-        <v>201.4476240575402</v>
+        <v>201.4476384149864</v>
       </c>
       <c r="G69" t="n">
-        <v>19.83400218772734</v>
+        <v>19.83400417634542</v>
       </c>
       <c r="H69" t="n">
         <v>93</v>
@@ -2513,16 +2513,16 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.05404028826505258</v>
+        <v>0.05404015873135659</v>
       </c>
       <c r="E70" t="n">
-        <v>5.746318395321186</v>
+        <v>5.746318321961623</v>
       </c>
       <c r="F70" t="n">
-        <v>8.480506132578101</v>
+        <v>8.480506713211323</v>
       </c>
       <c r="G70" t="n">
-        <v>80.36161343092878</v>
+        <v>80.36162083384582</v>
       </c>
       <c r="H70" t="n">
         <v>78</v>
@@ -2543,16 +2543,16 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.5962259460644341</v>
+        <v>0.5962260849193728</v>
       </c>
       <c r="E71" t="n">
-        <v>48.82241482204861</v>
+        <v>48.82240295410156</v>
       </c>
       <c r="F71" t="n">
-        <v>60.26147517291148</v>
+        <v>60.2614648111707</v>
       </c>
       <c r="G71" t="n">
-        <v>25.87979662138491</v>
+        <v>25.87979474991086</v>
       </c>
       <c r="H71" t="n">
         <v>18</v>
@@ -2573,16 +2573,16 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.6170036557323804</v>
+        <v>0.61700369490906</v>
       </c>
       <c r="E72" t="n">
-        <v>10.61711892117275</v>
+        <v>10.61711844969332</v>
       </c>
       <c r="F72" t="n">
-        <v>14.17973737176605</v>
+        <v>14.17973664654367</v>
       </c>
       <c r="G72" t="n">
-        <v>14.73145180859191</v>
+        <v>14.73145185371579</v>
       </c>
       <c r="H72" t="n">
         <v>89</v>
@@ -2603,16 +2603,16 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.2402084703371856</v>
+        <v>0.240209527259766</v>
       </c>
       <c r="E73" t="n">
-        <v>199.1090217359138</v>
+        <v>199.1088336983112</v>
       </c>
       <c r="F73" t="n">
-        <v>261.2129626371988</v>
+        <v>261.2127809544847</v>
       </c>
       <c r="G73" t="n">
-        <v>24.98007656498878</v>
+        <v>24.98005921515448</v>
       </c>
       <c r="H73" t="n">
         <v>99</v>
@@ -2633,16 +2633,16 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>-0.8523117698198437</v>
+        <v>-0.8523135066563294</v>
       </c>
       <c r="E74" t="n">
-        <v>375.8494896017095</v>
+        <v>375.8496582687542</v>
       </c>
       <c r="F74" t="n">
-        <v>436.4504741276738</v>
+        <v>436.4506787484461</v>
       </c>
       <c r="G74" t="n">
-        <v>48.90467024116471</v>
+        <v>48.90469339875111</v>
       </c>
       <c r="H74" t="n">
         <v>93</v>
@@ -2663,16 +2663,16 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.1498076814070576</v>
+        <v>0.1498076627969936</v>
       </c>
       <c r="E75" t="n">
-        <v>5.919184635847043</v>
+        <v>5.919184929285294</v>
       </c>
       <c r="F75" t="n">
-        <v>8.039777703054966</v>
+        <v>8.039777791047277</v>
       </c>
       <c r="G75" t="n">
-        <v>98.57237547453721</v>
+        <v>98.57233205824016</v>
       </c>
       <c r="H75" t="n">
         <v>78</v>
@@ -2693,16 +2693,16 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.7334401110308385</v>
+        <v>0.7334401995709223</v>
       </c>
       <c r="E76" t="n">
-        <v>37.16413709852431</v>
+        <v>37.1640870836046</v>
       </c>
       <c r="F76" t="n">
-        <v>48.96299262553106</v>
+        <v>48.96298449379779</v>
       </c>
       <c r="G76" t="n">
-        <v>18.13469778337329</v>
+        <v>18.13466028860678</v>
       </c>
       <c r="H76" t="n">
         <v>18</v>
@@ -2723,16 +2723,16 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.4060940659457375</v>
+        <v>0.406094174225195</v>
       </c>
       <c r="E77" t="n">
-        <v>12.66986739769411</v>
+        <v>12.66986684049113</v>
       </c>
       <c r="F77" t="n">
-        <v>17.65751993269275</v>
+        <v>17.65751832305505</v>
       </c>
       <c r="G77" t="n">
-        <v>17.42197388926038</v>
+        <v>17.42197333442914</v>
       </c>
       <c r="H77" t="n">
         <v>89</v>
@@ -2753,16 +2753,16 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.6361595079849343</v>
+        <v>0.6361594953538046</v>
       </c>
       <c r="E78" t="n">
-        <v>138.5235312105429</v>
+        <v>138.5235275114426</v>
       </c>
       <c r="F78" t="n">
-        <v>180.7602845182733</v>
+        <v>180.760287655921</v>
       </c>
       <c r="G78" t="n">
-        <v>22.47702034529922</v>
+        <v>22.47701905849241</v>
       </c>
       <c r="H78" t="n">
         <v>99</v>
@@ -2783,16 +2783,16 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.5727870682138936</v>
+        <v>0.5727871173153255</v>
       </c>
       <c r="E79" t="n">
-        <v>158.3336289928805</v>
+        <v>158.3336237425445</v>
       </c>
       <c r="F79" t="n">
-        <v>209.6042680310154</v>
+        <v>209.604255985652</v>
       </c>
       <c r="G79" t="n">
-        <v>16.48919928459848</v>
+        <v>16.48919899433138</v>
       </c>
       <c r="H79" t="n">
         <v>93</v>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.2105312087947707</v>
+        <v>0.2105311854481973</v>
       </c>
       <c r="E80" t="n">
-        <v>5.735103436005422</v>
+        <v>5.735103558271359</v>
       </c>
       <c r="F80" t="n">
-        <v>7.747345704425938</v>
+        <v>7.747345818980165</v>
       </c>
       <c r="G80" t="n">
-        <v>95.91882206892376</v>
+        <v>95.91883209980364</v>
       </c>
       <c r="H80" t="n">
         <v>78</v>
@@ -2843,16 +2843,16 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.5215606385022546</v>
+        <v>0.5215606837722786</v>
       </c>
       <c r="E81" t="n">
-        <v>45.53804948594835</v>
+        <v>45.53803931342231</v>
       </c>
       <c r="F81" t="n">
-        <v>65.5970042059829</v>
+        <v>65.59700110258228</v>
       </c>
       <c r="G81" t="n">
-        <v>29.30533184187119</v>
+        <v>29.30532781097751</v>
       </c>
       <c r="H81" t="n">
         <v>18</v>
@@ -2873,16 +2873,16 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.563463415217013</v>
+        <v>0.5634633426094038</v>
       </c>
       <c r="E82" t="n">
-        <v>11.37915343381046</v>
+        <v>11.3791545482164</v>
       </c>
       <c r="F82" t="n">
-        <v>15.13844251736767</v>
+        <v>15.13844377632982</v>
       </c>
       <c r="G82" t="n">
-        <v>16.11191399425668</v>
+        <v>16.11191555397725</v>
       </c>
       <c r="H82" t="n">
         <v>89</v>
@@ -2903,16 +2903,16 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.6957345458942685</v>
+        <v>0.6957345852337342</v>
       </c>
       <c r="E83" t="n">
-        <v>121.5063729334359</v>
+        <v>121.5063673847853</v>
       </c>
       <c r="F83" t="n">
-        <v>165.3003693869934</v>
+        <v>165.3003587008831</v>
       </c>
       <c r="G83" t="n">
-        <v>18.44661636687152</v>
+        <v>18.44661502731629</v>
       </c>
       <c r="H83" t="n">
         <v>99</v>
@@ -2933,16 +2933,16 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.6559207916266666</v>
+        <v>0.6559208543764645</v>
       </c>
       <c r="E84" t="n">
-        <v>143.9864111459383</v>
+        <v>143.9864039267263</v>
       </c>
       <c r="F84" t="n">
-        <v>188.1079461604803</v>
+        <v>188.1079290078366</v>
       </c>
       <c r="G84" t="n">
-        <v>15.00649009534856</v>
+        <v>15.00648974653479</v>
       </c>
       <c r="H84" t="n">
         <v>93</v>
@@ -2963,16 +2963,16 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.2061904337925027</v>
+        <v>0.2061904158260977</v>
       </c>
       <c r="E85" t="n">
-        <v>5.648824410560803</v>
+        <v>5.64882449614696</v>
       </c>
       <c r="F85" t="n">
-        <v>7.768615313136596</v>
+        <v>7.768615401050685</v>
       </c>
       <c r="G85" t="n">
-        <v>96.89775689661118</v>
+        <v>96.89775728347217</v>
       </c>
       <c r="H85" t="n">
         <v>78</v>
@@ -2993,16 +2993,16 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.7053896099557376</v>
+        <v>0.7053896046092911</v>
       </c>
       <c r="E86" t="n">
-        <v>36.22334713406033</v>
+        <v>36.22334967719184</v>
       </c>
       <c r="F86" t="n">
-        <v>51.47479008255632</v>
+        <v>51.47479054962609</v>
       </c>
       <c r="G86" t="n">
-        <v>20.9752870594245</v>
+        <v>20.97528711103145</v>
       </c>
       <c r="H86" t="n">
         <v>18</v>
@@ -3023,16 +3023,16 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.4813294875211183</v>
+        <v>0.481329467341998</v>
       </c>
       <c r="E87" t="n">
-        <v>11.86462140886971</v>
+        <v>11.86462149459325</v>
       </c>
       <c r="F87" t="n">
-        <v>16.50124270051763</v>
+        <v>16.50124302151193</v>
       </c>
       <c r="G87" t="n">
-        <v>16.39275543540974</v>
+        <v>16.39275570019987</v>
       </c>
       <c r="H87" t="n">
         <v>89</v>
@@ -3053,16 +3053,16 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.5148451908172594</v>
+        <v>0.5148451640357632</v>
       </c>
       <c r="E88" t="n">
-        <v>159.4729891690341</v>
+        <v>159.4729959507181</v>
       </c>
       <c r="F88" t="n">
-        <v>208.731344950057</v>
+        <v>208.7313507112466</v>
       </c>
       <c r="G88" t="n">
-        <v>25.8986293830778</v>
+        <v>25.89863025399857</v>
       </c>
       <c r="H88" t="n">
         <v>99</v>
@@ -3083,16 +3083,16 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.5173682525137016</v>
+        <v>0.5173682817762688</v>
       </c>
       <c r="E89" t="n">
-        <v>181.0233551353537</v>
+        <v>181.0233479161416</v>
       </c>
       <c r="F89" t="n">
-        <v>222.784960497137</v>
+        <v>222.7849537432713</v>
       </c>
       <c r="G89" t="n">
-        <v>20.50832777594528</v>
+        <v>20.50832720856858</v>
       </c>
       <c r="H89" t="n">
         <v>93</v>
@@ -3113,16 +3113,16 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.06205772255066055</v>
+        <v>0.06205769220451252</v>
       </c>
       <c r="E90" t="n">
-        <v>6.126514642666548</v>
+        <v>6.126514801612267</v>
       </c>
       <c r="F90" t="n">
-        <v>8.444491607311344</v>
+        <v>8.44449174391772</v>
       </c>
       <c r="G90" t="n">
-        <v>85.83199842582545</v>
+        <v>85.83200661756561</v>
       </c>
       <c r="H90" t="n">
         <v>78</v>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.6632265635255792</v>
+        <v>0.6632264903430019</v>
       </c>
       <c r="E91" t="n">
-        <v>46.72027248806424</v>
+        <v>46.72027418348524</v>
       </c>
       <c r="F91" t="n">
-        <v>55.03506312470438</v>
+        <v>55.03506910440334</v>
       </c>
       <c r="G91" t="n">
-        <v>24.03874164677612</v>
+        <v>24.03874200472949</v>
       </c>
       <c r="H91" t="n">
         <v>18</v>
@@ -3173,16 +3173,16 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.6999757072578361</v>
+        <v>0.6999757618569209</v>
       </c>
       <c r="E92" t="n">
-        <v>9.233777078349938</v>
+        <v>9.233775963943996</v>
       </c>
       <c r="F92" t="n">
-        <v>12.55015481579983</v>
+        <v>12.5501536738473</v>
       </c>
       <c r="G92" t="n">
-        <v>13.42452858795689</v>
+        <v>13.42452732371545</v>
       </c>
       <c r="H92" t="n">
         <v>89</v>
@@ -3203,16 +3203,16 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.7210795362564426</v>
+        <v>0.7210794940450805</v>
       </c>
       <c r="E93" t="n">
-        <v>112.9532402886285</v>
+        <v>112.953251694188</v>
       </c>
       <c r="F93" t="n">
-        <v>158.2660234023992</v>
+        <v>158.266035378258</v>
       </c>
       <c r="G93" t="n">
-        <v>17.39540261317149</v>
+        <v>17.39540469958726</v>
       </c>
       <c r="H93" t="n">
         <v>99</v>
@@ -3233,16 +3233,16 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.7096182296517302</v>
+        <v>0.7096182037711725</v>
       </c>
       <c r="E94" t="n">
-        <v>114.5336687641759</v>
+        <v>114.5336740145119</v>
       </c>
       <c r="F94" t="n">
-        <v>172.8075053595317</v>
+        <v>172.8075130603499</v>
       </c>
       <c r="G94" t="n">
-        <v>11.56409304106834</v>
+        <v>11.5640932851531</v>
       </c>
       <c r="H94" t="n">
         <v>93</v>
@@ -3263,16 +3263,16 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.2571245396260986</v>
+        <v>0.2571244870868503</v>
       </c>
       <c r="E95" t="n">
-        <v>4.93421126023317</v>
+        <v>4.934211755410219</v>
       </c>
       <c r="F95" t="n">
-        <v>7.515250455847511</v>
+        <v>7.51525072160242</v>
       </c>
       <c r="G95" t="n">
-        <v>54.88128451001582</v>
+        <v>54.88128798872047</v>
       </c>
       <c r="H95" t="n">
         <v>78</v>
@@ -3293,16 +3293,16 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.8381145305697212</v>
+        <v>0.8381144921628589</v>
       </c>
       <c r="E96" t="n">
         <v>29.79917738172743</v>
       </c>
       <c r="F96" t="n">
-        <v>38.15702346857772</v>
+        <v>38.15702799489952</v>
       </c>
       <c r="G96" t="n">
-        <v>12.36054816823168</v>
+        <v>12.36054869302713</v>
       </c>
       <c r="H96" t="n">
         <v>18</v>
@@ -3323,16 +3323,16 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.7152653679005794</v>
+        <v>0.7152653729087871</v>
       </c>
       <c r="E97" t="n">
-        <v>8.948057024666433</v>
+        <v>8.948057196113501</v>
       </c>
       <c r="F97" t="n">
-        <v>12.22618659168126</v>
+        <v>12.22618648415784</v>
       </c>
       <c r="G97" t="n">
-        <v>13.138413763204</v>
+        <v>13.13841410214621</v>
       </c>
       <c r="H97" t="n">
         <v>89</v>
@@ -3353,16 +3353,16 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.7214525927137095</v>
+        <v>0.7214525905009574</v>
       </c>
       <c r="E98" t="n">
-        <v>111.0683914338699</v>
+        <v>111.0683988320707</v>
       </c>
       <c r="F98" t="n">
-        <v>158.1601474894993</v>
+        <v>158.1601481177033</v>
       </c>
       <c r="G98" t="n">
-        <v>17.2539724055632</v>
+        <v>17.25397322989446</v>
       </c>
       <c r="H98" t="n">
         <v>99</v>
@@ -3383,16 +3383,16 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.702271440855101</v>
+        <v>0.7022714416212908</v>
       </c>
       <c r="E99" t="n">
-        <v>117.7518067718834</v>
+        <v>117.7518038185694</v>
       </c>
       <c r="F99" t="n">
-        <v>174.9799041495382</v>
+        <v>174.9799039243871</v>
       </c>
       <c r="G99" t="n">
-        <v>11.76480274475444</v>
+        <v>11.76480247017463</v>
       </c>
       <c r="H99" t="n">
         <v>93</v>
@@ -3413,16 +3413,16 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.147761065341426</v>
+        <v>0.1477610383809628</v>
       </c>
       <c r="E100" t="n">
-        <v>5.307228387930454</v>
+        <v>5.307228455176721</v>
       </c>
       <c r="F100" t="n">
-        <v>8.049448719465831</v>
+        <v>8.04944884678744</v>
       </c>
       <c r="G100" t="n">
-        <v>52.91713213165396</v>
+        <v>52.9171327580717</v>
       </c>
       <c r="H100" t="n">
         <v>78</v>
@@ -3443,16 +3443,16 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.8140069420622591</v>
+        <v>0.8140068213115039</v>
       </c>
       <c r="E101" t="n">
-        <v>31.34379747178819</v>
+        <v>31.34381018744575</v>
       </c>
       <c r="F101" t="n">
-        <v>40.89958695308368</v>
+        <v>40.89960022953405</v>
       </c>
       <c r="G101" t="n">
-        <v>11.08818520466549</v>
+        <v>11.08819119843787</v>
       </c>
       <c r="H101" t="n">
         <v>18</v>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.6678902580119752</v>
+        <v>0.6678902642368361</v>
       </c>
       <c r="E102" t="n">
-        <v>9.759175847085674</v>
+        <v>9.759174604094431</v>
       </c>
       <c r="F102" t="n">
-        <v>13.2041874329769</v>
+        <v>13.20418730923132</v>
       </c>
       <c r="G102" t="n">
-        <v>14.22940422934748</v>
+        <v>14.22940285324852</v>
       </c>
       <c r="H102" t="n">
         <v>89</v>
@@ -3503,16 +3503,16 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.668885727123737</v>
+        <v>0.6688857162818844</v>
       </c>
       <c r="E103" t="n">
-        <v>132.4097804830532</v>
+        <v>132.4097783252446</v>
       </c>
       <c r="F103" t="n">
-        <v>172.4393796978524</v>
+        <v>172.43938252099</v>
       </c>
       <c r="G103" t="n">
-        <v>20.99481121160702</v>
+        <v>20.99481067712119</v>
       </c>
       <c r="H103" t="n">
         <v>99</v>
@@ -3533,16 +3533,16 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.6657376225278091</v>
+        <v>0.6657375963757024</v>
       </c>
       <c r="E104" t="n">
-        <v>137.4463832404024</v>
+        <v>137.4463911159064</v>
       </c>
       <c r="F104" t="n">
-        <v>185.4050996230767</v>
+        <v>185.4051068759627</v>
       </c>
       <c r="G104" t="n">
-        <v>14.25724071232669</v>
+        <v>14.25724214330717</v>
       </c>
       <c r="H104" t="n">
         <v>93</v>
@@ -3563,16 +3563,16 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.2581984289391944</v>
+        <v>0.2581984467751691</v>
       </c>
       <c r="E105" t="n">
-        <v>5.46857868708097</v>
+        <v>5.468578418095906</v>
       </c>
       <c r="F105" t="n">
-        <v>7.50981652623541</v>
+        <v>7.5098164359519</v>
       </c>
       <c r="G105" t="n">
-        <v>98.11486300137562</v>
+        <v>98.1148556122553</v>
       </c>
       <c r="H105" t="n">
         <v>78</v>
@@ -3593,16 +3593,16 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.6705042979828379</v>
+        <v>0.670504305920842</v>
       </c>
       <c r="E106" t="n">
-        <v>31.51260884602864</v>
+        <v>31.51260715060764</v>
       </c>
       <c r="F106" t="n">
-        <v>54.43715646450443</v>
+        <v>54.4371558087715</v>
       </c>
       <c r="G106" t="n">
-        <v>18.44481605879977</v>
+        <v>18.4448125271634</v>
       </c>
       <c r="H106" t="n">
         <v>18</v>
@@ -3623,16 +3623,16 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.6840224252631992</v>
+        <v>0.6840223945936789</v>
       </c>
       <c r="E107" t="n">
-        <v>9.591277776139506</v>
+        <v>9.59127871909838</v>
       </c>
       <c r="F107" t="n">
-        <v>12.87950000393503</v>
+        <v>12.87950062899217</v>
       </c>
       <c r="G107" t="n">
-        <v>13.90755630819228</v>
+        <v>13.90755683037752</v>
       </c>
       <c r="H107" t="n">
         <v>89</v>
@@ -3653,16 +3653,16 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.6956977645668363</v>
+        <v>0.6956977801930632</v>
       </c>
       <c r="E108" t="n">
         <v>129.4922220249369</v>
       </c>
       <c r="F108" t="n">
-        <v>165.3103603064274</v>
+        <v>165.3103560620004</v>
       </c>
       <c r="G108" t="n">
-        <v>20.79653537322159</v>
+        <v>20.79653594725471</v>
       </c>
       <c r="H108" t="n">
         <v>99</v>
@@ -3683,16 +3683,16 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.6734743412576201</v>
+        <v>0.6734744162698394</v>
       </c>
       <c r="E109" t="n">
-        <v>130.9698469920825</v>
+        <v>130.9698269751764</v>
       </c>
       <c r="F109" t="n">
-        <v>183.2468777310444</v>
+        <v>183.2468566825366</v>
       </c>
       <c r="G109" t="n">
-        <v>13.45802974961719</v>
+        <v>13.45802775881707</v>
       </c>
       <c r="H109" t="n">
         <v>93</v>
@@ -3713,16 +3713,16 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.2607010492884813</v>
+        <v>0.2607009979845234</v>
       </c>
       <c r="E110" t="n">
-        <v>5.344849824905396</v>
+        <v>5.344850044984084</v>
       </c>
       <c r="F110" t="n">
-        <v>7.497137867460585</v>
+        <v>7.497138127594078</v>
       </c>
       <c r="G110" t="n">
-        <v>90.07277146593432</v>
+        <v>90.07277026683718</v>
       </c>
       <c r="H110" t="n">
         <v>78</v>
@@ -3743,16 +3743,16 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.647840933361979</v>
+        <v>0.6478410203708147</v>
       </c>
       <c r="E111" t="n">
-        <v>34.12241702609592</v>
+        <v>34.1224110921224</v>
       </c>
       <c r="F111" t="n">
-        <v>56.27817320593392</v>
+        <v>56.27816625353785</v>
       </c>
       <c r="G111" t="n">
-        <v>19.26157889165874</v>
+        <v>19.26157483985579</v>
       </c>
       <c r="H111" t="n">
         <v>18</v>
@@ -3773,16 +3773,16 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.6960012359237613</v>
+        <v>0.6960011490003015</v>
       </c>
       <c r="E112" t="n">
-        <v>9.383304938841402</v>
+        <v>9.383306010385578</v>
       </c>
       <c r="F112" t="n">
-        <v>12.63300831139517</v>
+        <v>12.63301011749579</v>
       </c>
       <c r="G112" t="n">
-        <v>13.68593057847585</v>
+        <v>13.68593253809424</v>
       </c>
       <c r="H112" t="n">
         <v>89</v>
@@ -3803,16 +3803,16 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.6959974753330411</v>
+        <v>0.6959974489541001</v>
       </c>
       <c r="E113" t="n">
-        <v>120.8560017287129</v>
+        <v>120.8560048112966</v>
       </c>
       <c r="F113" t="n">
-        <v>165.2289322154994</v>
+        <v>165.2289393841309</v>
       </c>
       <c r="G113" t="n">
-        <v>18.95204239363053</v>
+        <v>18.95204253348938</v>
       </c>
       <c r="H113" t="n">
         <v>99</v>
@@ -3833,16 +3833,16 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.7087521628157124</v>
+        <v>0.7087521379977103</v>
       </c>
       <c r="E114" t="n">
-        <v>120.6929081742481</v>
+        <v>120.6929101431242</v>
       </c>
       <c r="F114" t="n">
-        <v>173.0650136434644</v>
+        <v>173.0650210171291</v>
       </c>
       <c r="G114" t="n">
-        <v>12.01642013545505</v>
+        <v>12.01642012403171</v>
       </c>
       <c r="H114" t="n">
         <v>93</v>
@@ -3863,16 +3863,16 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.1722116753763901</v>
+        <v>0.1722117248518831</v>
       </c>
       <c r="E115" t="n">
-        <v>5.205970745820266</v>
+        <v>5.20597069691389</v>
       </c>
       <c r="F115" t="n">
-        <v>7.93313967471282</v>
+        <v>7.933139437637719</v>
       </c>
       <c r="G115" t="n">
-        <v>62.84674681491143</v>
+        <v>62.84674394076897</v>
       </c>
       <c r="H115" t="n">
         <v>78</v>
@@ -3893,16 +3893,16 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.7121547930991465</v>
+        <v>0.7121546632401866</v>
       </c>
       <c r="E116" t="n">
-        <v>35.55419582790799</v>
+        <v>35.55420091417101</v>
       </c>
       <c r="F116" t="n">
-        <v>50.88034597353692</v>
+        <v>50.8803574506571</v>
       </c>
       <c r="G116" t="n">
-        <v>12.30592760005625</v>
+        <v>12.30592442092645</v>
       </c>
       <c r="H116" t="n">
         <v>18</v>
@@ -3923,16 +3923,16 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.6741112656102413</v>
+        <v>0.6741112531052849</v>
       </c>
       <c r="E117" t="n">
-        <v>9.384485223320093</v>
+        <v>9.384484923287724</v>
       </c>
       <c r="F117" t="n">
-        <v>13.07993382293216</v>
+        <v>13.07993407388285</v>
       </c>
       <c r="G117" t="n">
-        <v>13.48424891977066</v>
+        <v>13.48424477361822</v>
       </c>
       <c r="H117" t="n">
         <v>89</v>
@@ -3953,16 +3953,16 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.6859207055989073</v>
+        <v>0.685920693647853</v>
       </c>
       <c r="E118" t="n">
-        <v>120.5072930846551</v>
+        <v>120.5072822956124</v>
       </c>
       <c r="F118" t="n">
-        <v>167.9450292668053</v>
+        <v>167.9450324620496</v>
       </c>
       <c r="G118" t="n">
-        <v>19.07631358906764</v>
+        <v>19.07630909508743</v>
       </c>
       <c r="H118" t="n">
         <v>99</v>
@@ -3983,16 +3983,16 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.6986116739793418</v>
+        <v>0.6986117247258911</v>
       </c>
       <c r="E119" t="n">
-        <v>119.8776629048009</v>
+        <v>119.8776684832829</v>
       </c>
       <c r="F119" t="n">
-        <v>176.052071545938</v>
+        <v>176.0520567244689</v>
       </c>
       <c r="G119" t="n">
-        <v>12.22507953779222</v>
+        <v>12.22508170787321</v>
       </c>
       <c r="H119" t="n">
         <v>93</v>
@@ -4013,16 +4013,16 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.1670069944367484</v>
+        <v>0.1670069668624371</v>
       </c>
       <c r="E120" t="n">
-        <v>5.399429192909827</v>
+        <v>5.3994286549397</v>
       </c>
       <c r="F120" t="n">
-        <v>7.958040220823866</v>
+        <v>7.958040352540144</v>
       </c>
       <c r="G120" t="n">
-        <v>74.85915765076891</v>
+        <v>74.85912735688731</v>
       </c>
       <c r="H120" t="n">
         <v>78</v>
@@ -4043,16 +4043,16 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.7428079887720684</v>
+        <v>0.742807899216118</v>
       </c>
       <c r="E121" t="n">
-        <v>34.44596523708768</v>
+        <v>34.44594573974609</v>
       </c>
       <c r="F121" t="n">
-        <v>48.09492944777253</v>
+        <v>48.09493782125723</v>
       </c>
       <c r="G121" t="n">
-        <v>16.07748466055155</v>
+        <v>16.0774744725161</v>
       </c>
       <c r="H121" t="n">
         <v>18</v>
@@ -4073,16 +4073,16 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.6204972478275363</v>
+        <v>0.6204972334145571</v>
       </c>
       <c r="E122" t="n">
-        <v>10.61603447560514</v>
+        <v>10.61603383267863</v>
       </c>
       <c r="F122" t="n">
-        <v>14.11491729452059</v>
+        <v>14.11491756255291</v>
       </c>
       <c r="G122" t="n">
-        <v>14.97706836067294</v>
+        <v>14.97706802657793</v>
       </c>
       <c r="H122" t="n">
         <v>89</v>
@@ -4103,16 +4103,16 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.6917218343820593</v>
+        <v>0.6917218752031693</v>
       </c>
       <c r="E123" t="n">
-        <v>126.9748898901121</v>
+        <v>126.9748824919113</v>
       </c>
       <c r="F123" t="n">
-        <v>166.3868056689161</v>
+        <v>166.3867946527381</v>
       </c>
       <c r="G123" t="n">
-        <v>18.89132736346471</v>
+        <v>18.89132630169492</v>
       </c>
       <c r="H123" t="n">
         <v>99</v>
@@ -4133,16 +4133,16 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.6364116193202279</v>
+        <v>0.6364116428617224</v>
       </c>
       <c r="E124" t="n">
-        <v>147.8759155273438</v>
+        <v>147.8759066674017</v>
       </c>
       <c r="F124" t="n">
-        <v>193.3672515632224</v>
+        <v>193.3672453031844</v>
       </c>
       <c r="G124" t="n">
-        <v>16.62114134530133</v>
+        <v>16.62114141594033</v>
       </c>
       <c r="H124" t="n">
         <v>93</v>
@@ -4163,16 +4163,16 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.1094209616983559</v>
+        <v>0.1094209302853364</v>
       </c>
       <c r="E125" t="n">
-        <v>5.825982839633257</v>
+        <v>5.825982692914131</v>
       </c>
       <c r="F125" t="n">
-        <v>8.228519200037468</v>
+        <v>8.228519345158013</v>
       </c>
       <c r="G125" t="n">
-        <v>80.39390718264133</v>
+        <v>80.39391632276131</v>
       </c>
       <c r="H125" t="n">
         <v>78</v>
@@ -4193,16 +4193,16 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.6371393611549646</v>
+        <v>0.6371391704305515</v>
       </c>
       <c r="E126" t="n">
-        <v>43.83292473687066</v>
+        <v>43.83293914794922</v>
       </c>
       <c r="F126" t="n">
-        <v>57.12687730388405</v>
+        <v>57.12689231720811</v>
       </c>
       <c r="G126" t="n">
-        <v>23.11161743537008</v>
+        <v>23.1116267203007</v>
       </c>
       <c r="H126" t="n">
         <v>18</v>
@@ -4223,16 +4223,16 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.621687176185917</v>
+        <v>0.6216873071679621</v>
       </c>
       <c r="E127" t="n">
-        <v>10.69367869516437</v>
+        <v>10.69367693783192</v>
       </c>
       <c r="F127" t="n">
-        <v>14.09277130653647</v>
+        <v>14.09276886688858</v>
       </c>
       <c r="G127" t="n">
-        <v>14.82370089523578</v>
+        <v>14.82369844955588</v>
       </c>
       <c r="H127" t="n">
         <v>89</v>
@@ -4253,16 +4253,16 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.6648502395561585</v>
+        <v>0.6648502468213031</v>
       </c>
       <c r="E128" t="n">
-        <v>128.6688947581281</v>
+        <v>128.6688861268939</v>
       </c>
       <c r="F128" t="n">
-        <v>173.4870082440981</v>
+        <v>173.4870063637324</v>
       </c>
       <c r="G128" t="n">
-        <v>21.21942919528125</v>
+        <v>21.21942896055773</v>
       </c>
       <c r="H128" t="n">
         <v>99</v>
@@ -4283,16 +4283,16 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.6099734702890112</v>
+        <v>0.6099734945553044</v>
       </c>
       <c r="E129" t="n">
-        <v>166.1793058662004</v>
+        <v>166.1792947092364</v>
       </c>
       <c r="F129" t="n">
-        <v>200.2741978252206</v>
+        <v>200.2741915949873</v>
       </c>
       <c r="G129" t="n">
-        <v>19.86267501846824</v>
+        <v>19.86267392569282</v>
       </c>
       <c r="H129" t="n">
         <v>93</v>
@@ -4313,16 +4313,16 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.1124092410562685</v>
+        <v>0.1124093064988317</v>
       </c>
       <c r="E130" t="n">
-        <v>5.907395821351272</v>
+        <v>5.907396047543257</v>
       </c>
       <c r="F130" t="n">
-        <v>8.214702472672206</v>
+        <v>8.214702169834895</v>
       </c>
       <c r="G130" t="n">
-        <v>96.3346139681525</v>
+        <v>96.33461776184353</v>
       </c>
       <c r="H130" t="n">
         <v>78</v>
@@ -4343,16 +4343,16 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.5976867017330123</v>
+        <v>0.5976867077007113</v>
       </c>
       <c r="E131" t="n">
-        <v>46.18474409315321</v>
+        <v>46.18474494086372</v>
       </c>
       <c r="F131" t="n">
-        <v>60.15237077376203</v>
+        <v>60.15237032762808</v>
       </c>
       <c r="G131" t="n">
-        <v>25.97517172757877</v>
+        <v>25.97517271338884</v>
       </c>
       <c r="H131" t="n">
         <v>18</v>
@@ -4373,16 +4373,16 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.3596319778598738</v>
+        <v>0.3596321903690503</v>
       </c>
       <c r="E132" t="n">
-        <v>13.22081255109123</v>
+        <v>13.22081096520585</v>
       </c>
       <c r="F132" t="n">
-        <v>18.33520167044202</v>
+        <v>18.33519862812979</v>
       </c>
       <c r="G132" t="n">
-        <v>17.83251502539163</v>
+        <v>17.83251889433128</v>
       </c>
       <c r="H132" t="n">
         <v>89</v>
@@ -4403,16 +4403,16 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.4379849585702831</v>
+        <v>0.4379856065139305</v>
       </c>
       <c r="E133" t="n">
-        <v>169.5145981913865</v>
+        <v>169.5145303745462</v>
       </c>
       <c r="F133" t="n">
-        <v>224.6577839061974</v>
+        <v>224.6576544028788</v>
       </c>
       <c r="G133" t="n">
-        <v>22.9044239495161</v>
+        <v>22.90442473216112</v>
       </c>
       <c r="H133" t="n">
         <v>99</v>
@@ -4433,16 +4433,16 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.3175696076796145</v>
+        <v>0.3175699524355804</v>
       </c>
       <c r="E134" t="n">
-        <v>226.7491399293305</v>
+        <v>226.7490690497942</v>
       </c>
       <c r="F134" t="n">
-        <v>264.9153397131751</v>
+        <v>264.915272797079</v>
       </c>
       <c r="G134" t="n">
-        <v>27.64310447755459</v>
+        <v>27.64309574873011</v>
       </c>
       <c r="H134" t="n">
         <v>93</v>
@@ -4463,16 +4463,16 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.1189714541611508</v>
+        <v>0.1189711535398537</v>
       </c>
       <c r="E135" t="n">
-        <v>6.108882610614483</v>
+        <v>6.108884334564209</v>
       </c>
       <c r="F135" t="n">
-        <v>8.184279310590556</v>
+        <v>8.184280706895175</v>
       </c>
       <c r="G135" t="n">
-        <v>99.65577818375448</v>
+        <v>99.65586622741554</v>
       </c>
       <c r="H135" t="n">
         <v>78</v>
@@ -4493,16 +4493,16 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.6557052997467989</v>
+        <v>0.6557052286827226</v>
       </c>
       <c r="E136" t="n">
-        <v>41.25409444173177</v>
+        <v>41.25413343641493</v>
       </c>
       <c r="F136" t="n">
-        <v>55.64622705699062</v>
+        <v>55.6462327998143</v>
       </c>
       <c r="G136" t="n">
-        <v>23.73618885389454</v>
+        <v>23.73620426255804</v>
       </c>
       <c r="H136" t="n">
         <v>18</v>
@@ -4523,16 +4523,16 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.5180502571148224</v>
+        <v>0.5180502231575448</v>
       </c>
       <c r="E137" t="n">
-        <v>11.59119959627644</v>
+        <v>11.59119946769114</v>
       </c>
       <c r="F137" t="n">
-        <v>15.90639450017828</v>
+        <v>15.90639506054567</v>
       </c>
       <c r="G137" t="n">
-        <v>16.94674127984138</v>
+        <v>16.94674085087284</v>
       </c>
       <c r="H137" t="n">
         <v>89</v>
@@ -4553,16 +4553,16 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.6885732104716074</v>
+        <v>0.6885731907086103</v>
       </c>
       <c r="E138" t="n">
-        <v>130.9476182725695</v>
+        <v>130.9476278285788</v>
       </c>
       <c r="F138" t="n">
-        <v>167.2343495824667</v>
+        <v>167.2343548887731</v>
       </c>
       <c r="G138" t="n">
-        <v>19.95309969223148</v>
+        <v>19.95310045995113</v>
       </c>
       <c r="H138" t="n">
         <v>99</v>
@@ -4583,16 +4583,16 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.6139558501080808</v>
+        <v>0.6139558232535894</v>
       </c>
       <c r="E139" t="n">
-        <v>160.8081569876722</v>
+        <v>160.8081586284022</v>
       </c>
       <c r="F139" t="n">
-        <v>199.2491210389637</v>
+        <v>199.2491279691732</v>
       </c>
       <c r="G139" t="n">
-        <v>18.15336931928844</v>
+        <v>18.1533695690756</v>
       </c>
       <c r="H139" t="n">
         <v>93</v>
@@ -4613,16 +4613,16 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.1191665636835036</v>
+        <v>0.1191665360862464</v>
       </c>
       <c r="E140" t="n">
-        <v>5.516492965893868</v>
+        <v>5.516493106499697</v>
       </c>
       <c r="F140" t="n">
-        <v>8.183373029374371</v>
+        <v>8.183373157570372</v>
       </c>
       <c r="G140" t="n">
-        <v>71.87511613842304</v>
+        <v>71.87512348525212</v>
       </c>
       <c r="H140" t="n">
         <v>78</v>
@@ -4643,16 +4643,16 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.799589605948368</v>
+        <v>0.7995895937230457</v>
       </c>
       <c r="E141" t="n">
-        <v>34.45900217692057</v>
+        <v>34.45900641547309</v>
       </c>
       <c r="F141" t="n">
-        <v>42.45517893735771</v>
+        <v>42.45518023227118</v>
       </c>
       <c r="G141" t="n">
-        <v>16.81645561810196</v>
+        <v>16.81645468722119</v>
       </c>
       <c r="H141" t="n">
         <v>18</v>
@@ -4673,16 +4673,16 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0.4376807302542074</v>
+        <v>0.437680789148065</v>
       </c>
       <c r="E142" t="n">
-        <v>12.74842281555862</v>
+        <v>12.74842161542914</v>
       </c>
       <c r="F142" t="n">
-        <v>17.18155062311306</v>
+        <v>17.18154972336813</v>
       </c>
       <c r="G142" t="n">
-        <v>17.87886937182365</v>
+        <v>17.87886779931229</v>
       </c>
       <c r="H142" t="n">
         <v>89</v>
@@ -4703,16 +4703,16 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.6237780512181453</v>
+        <v>0.6237780869358526</v>
       </c>
       <c r="E143" t="n">
-        <v>147.4275574346985</v>
+        <v>147.4275555851484</v>
       </c>
       <c r="F143" t="n">
-        <v>183.8101821558512</v>
+        <v>183.8101734305782</v>
       </c>
       <c r="G143" t="n">
-        <v>20.64656383948916</v>
+        <v>20.64656422161033</v>
       </c>
       <c r="H143" t="n">
         <v>99</v>
@@ -4733,16 +4733,16 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0.5893625358949215</v>
+        <v>0.5893625953553066</v>
       </c>
       <c r="E144" t="n">
-        <v>162.9732078634283</v>
+        <v>162.9732058945523</v>
       </c>
       <c r="F144" t="n">
-        <v>205.4978162282261</v>
+        <v>205.4978013501637</v>
       </c>
       <c r="G144" t="n">
-        <v>18.98667803139166</v>
+        <v>18.98667799753609</v>
       </c>
       <c r="H144" t="n">
         <v>93</v>
@@ -4763,16 +4763,16 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.1138269503825389</v>
+        <v>0.1138270351697436</v>
       </c>
       <c r="E145" t="n">
-        <v>5.824503586842463</v>
+        <v>5.824503220044649</v>
       </c>
       <c r="F145" t="n">
-        <v>8.208139361045514</v>
+        <v>8.208138968376606</v>
       </c>
       <c r="G145" t="n">
-        <v>88.45371640696462</v>
+        <v>88.45370886656468</v>
       </c>
       <c r="H145" t="n">
         <v>78</v>
@@ -4793,16 +4793,16 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0.5670215646155132</v>
+        <v>0.5670216911276109</v>
       </c>
       <c r="E146" t="n">
-        <v>48.11236657036675</v>
+        <v>48.1123530069987</v>
       </c>
       <c r="F146" t="n">
-        <v>62.40274413794331</v>
+        <v>62.40273502120446</v>
       </c>
       <c r="G146" t="n">
-        <v>23.57422541218219</v>
+        <v>23.57422087734685</v>
       </c>
       <c r="H146" t="n">
         <v>18</v>
@@ -4823,16 +4823,16 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0.5067720347770088</v>
+        <v>0.5067720297780366</v>
       </c>
       <c r="E147" t="n">
-        <v>11.40804620807091</v>
+        <v>11.4080455651444</v>
       </c>
       <c r="F147" t="n">
-        <v>16.09143291788832</v>
+        <v>16.0914329994334</v>
       </c>
       <c r="G147" t="n">
-        <v>15.45699288855743</v>
+        <v>15.45699398832405</v>
       </c>
       <c r="H147" t="n">
         <v>89</v>
@@ -4853,16 +4853,16 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0.5807750539955847</v>
+        <v>0.5807754628602937</v>
       </c>
       <c r="E148" t="n">
-        <v>146.2761809994476</v>
+        <v>146.2760919127801</v>
       </c>
       <c r="F148" t="n">
-        <v>194.030972241071</v>
+        <v>194.0308776230895</v>
       </c>
       <c r="G148" t="n">
-        <v>20.48252007437068</v>
+        <v>20.48251133712648</v>
       </c>
       <c r="H148" t="n">
         <v>99</v>
@@ -4883,16 +4883,16 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0.5747546500797388</v>
+        <v>0.5747549305901001</v>
       </c>
       <c r="E149" t="n">
-        <v>171.3906778315062</v>
+        <v>171.3906069519699</v>
       </c>
       <c r="F149" t="n">
-        <v>209.1210318294621</v>
+        <v>209.1209628567786</v>
       </c>
       <c r="G149" t="n">
-        <v>20.46862409674598</v>
+        <v>20.46861679715295</v>
       </c>
       <c r="H149" t="n">
         <v>93</v>
@@ -4913,16 +4913,16 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.1426544385174324</v>
+        <v>0.1426543043829024</v>
       </c>
       <c r="E150" t="n">
-        <v>6.067212789486616</v>
+        <v>6.067213779840714</v>
       </c>
       <c r="F150" t="n">
-        <v>8.073528902062241</v>
+        <v>8.073529533627278</v>
       </c>
       <c r="G150" t="n">
-        <v>100.185217833266</v>
+        <v>100.18514158987</v>
       </c>
       <c r="H150" t="n">
         <v>78</v>
@@ -4943,16 +4943,16 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0.7141666336211032</v>
+        <v>0.7141664166250397</v>
       </c>
       <c r="E151" t="n">
-        <v>39.65429517957899</v>
+        <v>39.65428500705295</v>
       </c>
       <c r="F151" t="n">
-        <v>50.70222483554048</v>
+        <v>50.70224408133613</v>
       </c>
       <c r="G151" t="n">
-        <v>18.49871611422533</v>
+        <v>18.49870942497667</v>
       </c>
       <c r="H151" t="n">
         <v>18</v>
@@ -4973,16 +4973,16 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>0.5222931836039185</v>
+        <v>0.5222930641896415</v>
       </c>
       <c r="E152" t="n">
-        <v>11.44137963284268</v>
+        <v>11.4413831046458</v>
       </c>
       <c r="F152" t="n">
-        <v>15.83622239176495</v>
+        <v>15.83622437108665</v>
       </c>
       <c r="G152" t="n">
-        <v>15.73455508149235</v>
+        <v>15.73455918900373</v>
       </c>
       <c r="H152" t="n">
         <v>89</v>
@@ -5003,16 +5003,16 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>0.5693739833533222</v>
+        <v>0.5693739760925381</v>
       </c>
       <c r="E153" t="n">
-        <v>152.6537111841067</v>
+        <v>152.6537145749487</v>
       </c>
       <c r="F153" t="n">
-        <v>196.6516675138596</v>
+        <v>196.6516691717312</v>
       </c>
       <c r="G153" t="n">
-        <v>20.82591356652708</v>
+        <v>20.82591417561921</v>
       </c>
       <c r="H153" t="n">
         <v>99</v>
@@ -5033,16 +5033,16 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>0.1229445660699154</v>
+        <v>0.1229446234959657</v>
       </c>
       <c r="E154" t="n">
-        <v>233.4843996109501</v>
+        <v>233.4843930480301</v>
       </c>
       <c r="F154" t="n">
-        <v>300.324974095336</v>
+        <v>300.3249642633021</v>
       </c>
       <c r="G154" t="n">
-        <v>28.65158504043517</v>
+        <v>28.65158425407689</v>
       </c>
       <c r="H154" t="n">
         <v>93</v>
@@ -5063,16 +5063,16 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>-0.003319285861339338</v>
+        <v>-0.003319347048153398</v>
       </c>
       <c r="E155" t="n">
-        <v>6.032736698786418</v>
+        <v>6.032737517968203</v>
       </c>
       <c r="F155" t="n">
-        <v>8.733835998229983</v>
+        <v>8.733836264543807</v>
       </c>
       <c r="G155" t="n">
-        <v>60.41300490664211</v>
+        <v>60.41301096274115</v>
       </c>
       <c r="H155" t="n">
         <v>78</v>
@@ -5093,16 +5093,16 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>0.6019353389673466</v>
+        <v>0.6019351673501</v>
       </c>
       <c r="E156" t="n">
-        <v>48.19707828097873</v>
+        <v>48.19708845350478</v>
       </c>
       <c r="F156" t="n">
-        <v>59.83390763063775</v>
+        <v>59.8339205287048</v>
       </c>
       <c r="G156" t="n">
-        <v>26.28599571926663</v>
+        <v>26.28599843336522</v>
       </c>
       <c r="H156" t="n">
         <v>18</v>
@@ -5123,16 +5123,16 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>0.3620341633081745</v>
+        <v>0.3620341897720706</v>
       </c>
       <c r="E157" t="n">
-        <v>15.03034291642435</v>
+        <v>15.03034244494492</v>
       </c>
       <c r="F157" t="n">
-        <v>18.30077932548214</v>
+        <v>18.30077894590858</v>
       </c>
       <c r="G157" t="n">
-        <v>22.12486269674258</v>
+        <v>22.12486149950058</v>
       </c>
       <c r="H157" t="n">
         <v>89</v>
@@ -5153,16 +5153,16 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0.4013911015924876</v>
+        <v>0.4013911268752175</v>
       </c>
       <c r="E158" t="n">
-        <v>178.2110530968868</v>
+        <v>178.2110543299203</v>
       </c>
       <c r="F158" t="n">
-        <v>231.8563983668334</v>
+        <v>231.8563934705123</v>
       </c>
       <c r="G158" t="n">
-        <v>23.62150906575669</v>
+        <v>23.62150863295483</v>
       </c>
       <c r="H158" t="n">
         <v>99</v>
@@ -5183,16 +5183,16 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>-0.876446923786361</v>
+        <v>-0.8764468910237118</v>
       </c>
       <c r="E159" t="n">
-        <v>336.6419372558594</v>
+        <v>336.6419352869834</v>
       </c>
       <c r="F159" t="n">
-        <v>439.2846913796905</v>
+        <v>439.2846875447485</v>
       </c>
       <c r="G159" t="n">
-        <v>41.97916948094233</v>
+        <v>41.97916880867784</v>
       </c>
       <c r="H159" t="n">
         <v>93</v>
@@ -5213,16 +5213,16 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>-0.007606228266188619</v>
+        <v>-0.007606143108009</v>
       </c>
       <c r="E160" t="n">
-        <v>6.296834481068147</v>
+        <v>6.296834016457582</v>
       </c>
       <c r="F160" t="n">
-        <v>8.75247490164662</v>
+        <v>8.75247453178743</v>
       </c>
       <c r="G160" t="n">
-        <v>76.35239897224444</v>
+        <v>76.35238958710006</v>
       </c>
       <c r="H160" t="n">
         <v>78</v>
@@ -5243,16 +5243,16 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>0.5555819096829216</v>
+        <v>0.5555818381777047</v>
       </c>
       <c r="E161" t="n">
         <v>43.88543616400825</v>
       </c>
       <c r="F161" t="n">
-        <v>63.22173631837999</v>
+        <v>63.22174140445084</v>
       </c>
       <c r="G161" t="n">
-        <v>20.95934897796068</v>
+        <v>20.9593517393991</v>
       </c>
       <c r="H161" t="n">
         <v>18</v>
@@ -5273,16 +5273,16 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>0.4935284360738249</v>
+        <v>0.4935281813238228</v>
       </c>
       <c r="E162" t="n">
-        <v>11.87764782852001</v>
+        <v>11.8776498001613</v>
       </c>
       <c r="F162" t="n">
-        <v>16.30603635420601</v>
+        <v>16.30604045509002</v>
       </c>
       <c r="G162" t="n">
-        <v>16.01169118115011</v>
+        <v>16.01169484036501</v>
       </c>
       <c r="H162" t="n">
         <v>89</v>
@@ -5303,16 +5303,16 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>-0.04783720422227278</v>
+        <v>-0.04783694608571554</v>
       </c>
       <c r="E163" t="n">
-        <v>245.8940059777462</v>
+        <v>245.8939837831439</v>
       </c>
       <c r="F163" t="n">
-        <v>306.7569480291816</v>
+        <v>306.7569102441196</v>
       </c>
       <c r="G163" t="n">
-        <v>29.35411507846216</v>
+        <v>29.35411259012542</v>
       </c>
       <c r="H163" t="n">
         <v>99</v>
@@ -5333,16 +5333,16 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>-4.055399256750778</v>
+        <v>-4.055395333482989</v>
       </c>
       <c r="E164" t="n">
-        <v>614.305168233892</v>
+        <v>614.3048427130586</v>
       </c>
       <c r="F164" t="n">
-        <v>721.0338546472267</v>
+        <v>721.0335748662142</v>
       </c>
       <c r="G164" t="n">
-        <v>80.46247680676754</v>
+        <v>80.46244234976587</v>
       </c>
       <c r="H164" t="n">
         <v>93</v>
@@ -5363,16 +5363,16 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>0.1260446179581705</v>
+        <v>0.1260445101030701</v>
       </c>
       <c r="E165" t="n">
-        <v>6.035865245721279</v>
+        <v>6.035866309434939</v>
       </c>
       <c r="F165" t="n">
-        <v>8.151360170659363</v>
+        <v>8.151360673640271</v>
       </c>
       <c r="G165" t="n">
-        <v>97.9536086936952</v>
+        <v>97.95356521826938</v>
       </c>
       <c r="H165" t="n">
         <v>78</v>
@@ -5393,16 +5393,16 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0.7076617439014101</v>
+        <v>0.7076616693419921</v>
       </c>
       <c r="E166" t="n">
-        <v>39.58287811279297</v>
+        <v>39.58290015326606</v>
       </c>
       <c r="F166" t="n">
-        <v>51.27591047796059</v>
+        <v>51.27591701679312</v>
       </c>
       <c r="G166" t="n">
-        <v>20.57167053066098</v>
+        <v>20.57168245237701</v>
       </c>
       <c r="H166" t="n">
         <v>18</v>
@@ -5423,16 +5423,16 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>0.5194229519996914</v>
+        <v>0.5194229381920514</v>
       </c>
       <c r="E167" t="n">
-        <v>11.15605493609825</v>
+        <v>11.15605600764242</v>
       </c>
       <c r="F167" t="n">
-        <v>15.88372595819879</v>
+        <v>15.88372618637944</v>
       </c>
       <c r="G167" t="n">
-        <v>15.45996878216593</v>
+        <v>15.45997034210322</v>
       </c>
       <c r="H167" t="n">
         <v>89</v>
@@ -5453,16 +5453,16 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0.6773938571553622</v>
+        <v>0.6773938209931287</v>
       </c>
       <c r="E168" t="n">
-        <v>129.5442138055358</v>
+        <v>129.5442227450284</v>
       </c>
       <c r="F168" t="n">
-        <v>170.2095084177791</v>
+        <v>170.2095179575166</v>
       </c>
       <c r="G168" t="n">
-        <v>21.55443237194794</v>
+        <v>21.55443337393855</v>
       </c>
       <c r="H168" t="n">
         <v>99</v>
@@ -5483,16 +5483,16 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0.6803343185758773</v>
+        <v>0.6803342342297658</v>
       </c>
       <c r="E169" t="n">
-        <v>136.3733221894951</v>
+        <v>136.3733307212912</v>
       </c>
       <c r="F169" t="n">
-        <v>181.311743212005</v>
+        <v>181.3117671322135</v>
       </c>
       <c r="G169" t="n">
-        <v>14.86820862453297</v>
+        <v>14.8682091567804</v>
       </c>
       <c r="H169" t="n">
         <v>93</v>
@@ -5513,16 +5513,16 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0.1756207188038977</v>
+        <v>0.1756206622991262</v>
       </c>
       <c r="E170" t="n">
-        <v>5.747331350277632</v>
+        <v>5.747331545903132</v>
       </c>
       <c r="F170" t="n">
-        <v>7.916787475547426</v>
+        <v>7.916787746864446</v>
       </c>
       <c r="G170" t="n">
-        <v>90.75492386999284</v>
+        <v>90.75492484634461</v>
       </c>
       <c r="H170" t="n">
         <v>78</v>
@@ -5543,16 +5543,16 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0.6385059128744459</v>
+        <v>0.6385059282479469</v>
       </c>
       <c r="E171" t="n">
-        <v>41.3746829562717</v>
+        <v>41.37468126085069</v>
       </c>
       <c r="F171" t="n">
-        <v>57.01920446244786</v>
+        <v>57.0192032500009</v>
       </c>
       <c r="G171" t="n">
-        <v>23.27312597021047</v>
+        <v>23.27312697559593</v>
       </c>
       <c r="H171" t="n">
         <v>18</v>
@@ -5573,16 +5573,16 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>0.5246516082080417</v>
+        <v>0.5246516434520074</v>
       </c>
       <c r="E172" t="n">
-        <v>11.78289910648646</v>
+        <v>11.78289812066582</v>
       </c>
       <c r="F172" t="n">
-        <v>15.79708254014185</v>
+        <v>15.79708195451681</v>
       </c>
       <c r="G172" t="n">
-        <v>16.27399670323215</v>
+        <v>16.27399540868887</v>
       </c>
       <c r="H172" t="n">
         <v>89</v>
@@ -5603,16 +5603,16 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>0.5784187911367022</v>
+        <v>0.5784187999232402</v>
       </c>
       <c r="E173" t="n">
-        <v>147.0631914235125</v>
+        <v>147.0631895739623</v>
       </c>
       <c r="F173" t="n">
-        <v>194.5754858345682</v>
+        <v>194.5754838069104</v>
       </c>
       <c r="G173" t="n">
-        <v>22.86844102600197</v>
+        <v>22.86844100593882</v>
       </c>
       <c r="H173" t="n">
         <v>99</v>
@@ -5633,16 +5633,16 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>0.5563161105898121</v>
+        <v>0.5563161133707146</v>
       </c>
       <c r="E174" t="n">
-        <v>171.7515117686282</v>
+        <v>171.7515052057082</v>
       </c>
       <c r="F174" t="n">
-        <v>213.6066436668496</v>
+        <v>213.6066429974323</v>
       </c>
       <c r="G174" t="n">
-        <v>19.39519901057572</v>
+        <v>19.39519879046587</v>
       </c>
       <c r="H174" t="n">
         <v>93</v>
@@ -5663,16 +5663,16 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>0.1505643520912114</v>
+        <v>0.1505644039619629</v>
       </c>
       <c r="E175" t="n">
-        <v>5.941029194073799</v>
+        <v>5.941029108487642</v>
       </c>
       <c r="F175" t="n">
-        <v>8.036199207851865</v>
+        <v>8.036198962486782</v>
       </c>
       <c r="G175" t="n">
-        <v>101.7251649336375</v>
+        <v>101.725165179501</v>
       </c>
       <c r="H175" t="n">
         <v>78</v>
@@ -5693,16 +5693,16 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>0.6863390988243214</v>
+        <v>0.6863391641001992</v>
       </c>
       <c r="E176" t="n">
-        <v>40.22003512912326</v>
+        <v>40.22003343370226</v>
       </c>
       <c r="F176" t="n">
-        <v>53.11298961767413</v>
+        <v>53.11298409100954</v>
       </c>
       <c r="G176" t="n">
-        <v>21.83701242799336</v>
+        <v>21.83701123237568</v>
       </c>
       <c r="H176" t="n">
         <v>18</v>
@@ -5723,16 +5723,16 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0.5649511730010364</v>
+        <v>0.5649511881279541</v>
       </c>
       <c r="E177" t="n">
-        <v>11.70301000187906</v>
+        <v>11.70300991615553</v>
       </c>
       <c r="F177" t="n">
-        <v>15.11262388176086</v>
+        <v>15.1126236190232</v>
       </c>
       <c r="G177" t="n">
-        <v>16.47806963398876</v>
+        <v>16.47806945269117</v>
       </c>
       <c r="H177" t="n">
         <v>89</v>
@@ -5753,16 +5753,16 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>0.5919254545817773</v>
+        <v>0.5919254984753637</v>
       </c>
       <c r="E178" t="n">
-        <v>149.0319645428898</v>
+        <v>149.0319534455887</v>
       </c>
       <c r="F178" t="n">
-        <v>191.4331976961373</v>
+        <v>191.4331874006044</v>
       </c>
       <c r="G178" t="n">
-        <v>24.03268068649286</v>
+        <v>24.03267912044017</v>
       </c>
       <c r="H178" t="n">
         <v>99</v>
@@ -5783,16 +5783,16 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>0.5707910765423095</v>
+        <v>0.5707910913465395</v>
       </c>
       <c r="E179" t="n">
-        <v>173.2947016890331</v>
+        <v>173.2946964386971</v>
       </c>
       <c r="F179" t="n">
-        <v>210.0933459746599</v>
+        <v>210.0933423514008</v>
       </c>
       <c r="G179" t="n">
-        <v>19.28923955965059</v>
+        <v>19.28923878311592</v>
       </c>
       <c r="H179" t="n">
         <v>93</v>
@@ -5813,16 +5813,16 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>0.191254057396573</v>
+        <v>0.1912540028600126</v>
       </c>
       <c r="E180" t="n">
-        <v>5.825178427573962</v>
+        <v>5.825178757691995</v>
       </c>
       <c r="F180" t="n">
-        <v>7.84136211060579</v>
+        <v>7.841362374990987</v>
       </c>
       <c r="G180" t="n">
-        <v>83.61661459242185</v>
+        <v>83.6166083612479</v>
       </c>
       <c r="H180" t="n">
         <v>78</v>
@@ -5843,16 +5843,16 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>0.650939689212382</v>
+        <v>0.650939848806289</v>
       </c>
       <c r="E181" t="n">
-        <v>43.91906060112847</v>
+        <v>43.91904873318143</v>
       </c>
       <c r="F181" t="n">
-        <v>56.03002163875555</v>
+        <v>56.03000883000759</v>
       </c>
       <c r="G181" t="n">
-        <v>25.12105138337352</v>
+        <v>25.12104534004874</v>
       </c>
       <c r="H181" t="n">
         <v>18</v>
@@ -5873,16 +5873,16 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>0.2876337346842407</v>
+        <v>0.2876340203819503</v>
       </c>
       <c r="E182" t="n">
-        <v>13.75642652190133</v>
+        <v>13.75642335013057</v>
       </c>
       <c r="F182" t="n">
-        <v>19.33848933744917</v>
+        <v>19.33848545955451</v>
       </c>
       <c r="G182" t="n">
-        <v>18.38787251946003</v>
+        <v>18.38786712968215</v>
       </c>
       <c r="H182" t="n">
         <v>89</v>
@@ -5903,16 +5903,16 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>0.05792809693588763</v>
+        <v>0.05792805489239428</v>
       </c>
       <c r="E183" t="n">
-        <v>230.1041531032986</v>
+        <v>230.1041558776239</v>
       </c>
       <c r="F183" t="n">
-        <v>290.8637016012335</v>
+        <v>290.8637080916754</v>
       </c>
       <c r="G183" t="n">
-        <v>36.88271477749589</v>
+        <v>36.88271524484447</v>
       </c>
       <c r="H183" t="n">
         <v>99</v>
@@ -5933,16 +5933,16 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>0.02427341527819094</v>
+        <v>0.02427345880971676</v>
       </c>
       <c r="E184" t="n">
-        <v>248.9011935982653</v>
+        <v>248.9011712843372</v>
       </c>
       <c r="F184" t="n">
-        <v>316.7685053769252</v>
+        <v>316.7684983106955</v>
       </c>
       <c r="G184" t="n">
-        <v>26.88092664893117</v>
+        <v>26.88092295676892</v>
       </c>
       <c r="H184" t="n">
         <v>93</v>
@@ -5963,16 +5963,16 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>0.07397020549824729</v>
+        <v>0.07397014700878679</v>
       </c>
       <c r="E185" t="n">
-        <v>6.0047670511099</v>
+        <v>6.004767222282214</v>
       </c>
       <c r="F185" t="n">
-        <v>8.390694953467321</v>
+        <v>8.39069521845189</v>
       </c>
       <c r="G185" t="n">
-        <v>85.66388990561364</v>
+        <v>85.66388287427307</v>
       </c>
       <c r="H185" t="n">
         <v>78</v>
@@ -5993,16 +5993,16 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>0.2424010808158132</v>
+        <v>0.2424010559125624</v>
       </c>
       <c r="E186" t="n">
-        <v>57.27896796332465</v>
+        <v>57.27898491753472</v>
       </c>
       <c r="F186" t="n">
-        <v>82.54489660753907</v>
+        <v>82.54489796421751</v>
       </c>
       <c r="G186" t="n">
-        <v>37.95101141195872</v>
+        <v>37.95101858684491</v>
       </c>
       <c r="H186" t="n">
         <v>18</v>
@@ -6023,16 +6023,16 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>0.2458666074238541</v>
+        <v>0.2458665433687824</v>
       </c>
       <c r="E187" t="n">
-        <v>13.84062177679512</v>
+        <v>13.8406231055099</v>
       </c>
       <c r="F187" t="n">
-        <v>19.89733713818501</v>
+        <v>19.89733798321146</v>
       </c>
       <c r="G187" t="n">
-        <v>18.55601562403188</v>
+        <v>18.55601827128264</v>
       </c>
       <c r="H187" t="n">
         <v>89</v>
@@ -6053,16 +6053,16 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>0.1581914106111416</v>
+        <v>0.1581914422130599</v>
       </c>
       <c r="E188" t="n">
-        <v>217.0944078233507</v>
+        <v>217.0944102894176</v>
       </c>
       <c r="F188" t="n">
-        <v>274.9502870803403</v>
+        <v>274.9502819194541</v>
       </c>
       <c r="G188" t="n">
-        <v>35.6715858318042</v>
+        <v>35.67158916493019</v>
       </c>
       <c r="H188" t="n">
         <v>99</v>
@@ -6083,16 +6083,16 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>0.1261717019076339</v>
+        <v>0.1261711291409948</v>
       </c>
       <c r="E189" t="n">
-        <v>228.5643182569935</v>
+        <v>228.5643911054057</v>
       </c>
       <c r="F189" t="n">
-        <v>299.7719402565556</v>
+        <v>299.7720385020227</v>
       </c>
       <c r="G189" t="n">
-        <v>24.49784287706026</v>
+        <v>24.49785400422706</v>
       </c>
       <c r="H189" t="n">
         <v>93</v>
@@ -6113,16 +6113,16 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0.04667729445282598</v>
+        <v>0.04667737083531087</v>
       </c>
       <c r="E190" t="n">
-        <v>6.017064858705569</v>
+        <v>6.017064583607209</v>
       </c>
       <c r="F190" t="n">
-        <v>8.513446689092214</v>
+        <v>8.513446348033398</v>
       </c>
       <c r="G190" t="n">
-        <v>84.2160109140234</v>
+        <v>84.21601154211837</v>
       </c>
       <c r="H190" t="n">
         <v>78</v>
@@ -6143,16 +6143,16 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>0.3605765904042556</v>
+        <v>0.360576839194593</v>
       </c>
       <c r="E191" t="n">
-        <v>54.89951409233941</v>
+        <v>54.89950731065538</v>
       </c>
       <c r="F191" t="n">
-        <v>75.83414954431683</v>
+        <v>75.83413479133375</v>
       </c>
       <c r="G191" t="n">
-        <v>33.83161184525201</v>
+        <v>33.83160400304555</v>
       </c>
       <c r="H191" t="n">
         <v>18</v>
@@ -6173,16 +6173,16 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>0.6283315990861829</v>
+        <v>0.6283316189730235</v>
       </c>
       <c r="E192" t="n">
-        <v>10.01864512582843</v>
+        <v>10.01864469721076</v>
       </c>
       <c r="F192" t="n">
-        <v>13.96846527355663</v>
+        <v>13.96846489985168</v>
       </c>
       <c r="G192" t="n">
-        <v>14.35808591148295</v>
+        <v>14.35808485797399</v>
       </c>
       <c r="H192" t="n">
         <v>89</v>
@@ -6203,16 +6203,16 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>0.6857131264873786</v>
+        <v>0.6857131066609852</v>
       </c>
       <c r="E193" t="n">
-        <v>126.9830411660551</v>
+        <v>126.983050413806</v>
       </c>
       <c r="F193" t="n">
-        <v>168.0005186325751</v>
+        <v>168.0005239316261</v>
       </c>
       <c r="G193" t="n">
-        <v>20.01200867271574</v>
+        <v>20.01200981687203</v>
       </c>
       <c r="H193" t="n">
         <v>99</v>
@@ -6233,16 +6233,16 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>0.6760655140139309</v>
+        <v>0.6760654939706406</v>
       </c>
       <c r="E194" t="n">
-        <v>131.8791198730469</v>
+        <v>131.8791179041709</v>
       </c>
       <c r="F194" t="n">
-        <v>182.5183437502625</v>
+        <v>182.5183493968797</v>
       </c>
       <c r="G194" t="n">
-        <v>13.5590133598798</v>
+        <v>13.5590134106698</v>
       </c>
       <c r="H194" t="n">
         <v>93</v>
@@ -6263,16 +6263,16 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>0.2371523632336776</v>
+        <v>0.2371523453709382</v>
       </c>
       <c r="E195" t="n">
-        <v>5.49248977807852</v>
+        <v>5.492489680265769</v>
       </c>
       <c r="F195" t="n">
-        <v>7.61560402964461</v>
+        <v>7.615604118807598</v>
       </c>
       <c r="G195" t="n">
-        <v>97.14601039843186</v>
+        <v>97.14600889959198</v>
       </c>
       <c r="H195" t="n">
         <v>78</v>
@@ -6293,16 +6293,16 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>0.6965787331506035</v>
+        <v>0.6965788312189758</v>
       </c>
       <c r="E196" t="n">
-        <v>34.37768385145399</v>
+        <v>34.37767622205946</v>
       </c>
       <c r="F196" t="n">
-        <v>52.23884466273678</v>
+        <v>52.23883622071335</v>
       </c>
       <c r="G196" t="n">
-        <v>19.93099849790104</v>
+        <v>19.93099183789065</v>
       </c>
       <c r="H196" t="n">
         <v>18</v>
@@ -6323,16 +6323,16 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>0.6260740442085874</v>
+        <v>0.6260740111439829</v>
       </c>
       <c r="E197" t="n">
-        <v>10.13350806075536</v>
+        <v>10.13350801789359</v>
       </c>
       <c r="F197" t="n">
-        <v>14.01082404765677</v>
+        <v>14.0108246671141</v>
       </c>
       <c r="G197" t="n">
-        <v>14.50064462338724</v>
+        <v>14.50064439852566</v>
       </c>
       <c r="H197" t="n">
         <v>89</v>
@@ -6353,16 +6353,16 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>0.6752942064446084</v>
+        <v>0.6752941929580754</v>
       </c>
       <c r="E198" t="n">
-        <v>129.5630314374211</v>
+        <v>129.5630363695549</v>
       </c>
       <c r="F198" t="n">
-        <v>170.7625061113963</v>
+        <v>170.7625096576745</v>
       </c>
       <c r="G198" t="n">
-        <v>20.2552135161157</v>
+        <v>20.25521522775268</v>
       </c>
       <c r="H198" t="n">
         <v>99</v>
@@ -6383,16 +6383,16 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>0.6688739039204018</v>
+        <v>0.6688738572566274</v>
       </c>
       <c r="E199" t="n">
-        <v>134.485827046056</v>
+        <v>134.48584148448</v>
       </c>
       <c r="F199" t="n">
-        <v>184.5332501298485</v>
+        <v>184.5332631324746</v>
       </c>
       <c r="G199" t="n">
-        <v>13.84387874411233</v>
+        <v>13.8438805729896</v>
       </c>
       <c r="H199" t="n">
         <v>93</v>
@@ -6413,16 +6413,16 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>0.1725593980724804</v>
+        <v>0.1725593403114599</v>
       </c>
       <c r="E200" t="n">
-        <v>5.671213431236072</v>
+        <v>5.671213351763212</v>
       </c>
       <c r="F200" t="n">
-        <v>7.931473293112676</v>
+        <v>7.931473569948247</v>
       </c>
       <c r="G200" t="n">
-        <v>98.73341738947175</v>
+        <v>98.73341830191326</v>
       </c>
       <c r="H200" t="n">
         <v>78</v>
@@ -6443,16 +6443,16 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>0.7370658829291856</v>
+        <v>0.7370658866250719</v>
       </c>
       <c r="E201" t="n">
-        <v>30.96595255533854</v>
+        <v>30.96594831678603</v>
       </c>
       <c r="F201" t="n">
-        <v>48.62885294201109</v>
+        <v>48.62885260023972</v>
       </c>
       <c r="G201" t="n">
-        <v>17.72087194696431</v>
+        <v>17.72086973635341</v>
       </c>
       <c r="H201" t="n">
         <v>18</v>
@@ -6473,16 +6473,16 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0.3555236409138873</v>
+        <v>0.3555237292381562</v>
       </c>
       <c r="E202" t="n">
-        <v>12.74811626820082</v>
+        <v>12.7481134393242</v>
       </c>
       <c r="F202" t="n">
-        <v>18.39392318120506</v>
+        <v>18.39392192077878</v>
       </c>
       <c r="G202" t="n">
-        <v>17.13809395284968</v>
+        <v>17.13808970648639</v>
       </c>
       <c r="H202" t="n">
         <v>89</v>
@@ -6503,16 +6503,16 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0.3351813202160588</v>
+        <v>0.3351811617676759</v>
       </c>
       <c r="E203" t="n">
-        <v>190.4007805718316</v>
+        <v>190.4008039994673</v>
       </c>
       <c r="F203" t="n">
-        <v>244.3425533427286</v>
+        <v>244.3425824602018</v>
       </c>
       <c r="G203" t="n">
-        <v>30.990967405465</v>
+        <v>30.99097191482827</v>
       </c>
       <c r="H203" t="n">
         <v>99</v>
@@ -6533,16 +6533,16 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0.3428202038682222</v>
+        <v>0.3428195838543343</v>
       </c>
       <c r="E204" t="n">
-        <v>185.6513412639659</v>
+        <v>185.65135242093</v>
       </c>
       <c r="F204" t="n">
-        <v>259.9680808571346</v>
+        <v>259.9682034900757</v>
       </c>
       <c r="G204" t="n">
-        <v>20.03194864813577</v>
+        <v>20.03194903558174</v>
       </c>
       <c r="H204" t="n">
         <v>93</v>
@@ -6563,16 +6563,16 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>0.07110331207035159</v>
+        <v>0.0711033673341539</v>
       </c>
       <c r="E205" t="n">
-        <v>6.076196254828037</v>
+        <v>6.076196144788693</v>
       </c>
       <c r="F205" t="n">
-        <v>8.40367328256303</v>
+        <v>8.403673032578856</v>
       </c>
       <c r="G205" t="n">
-        <v>83.39122366059203</v>
+        <v>83.39119872766426</v>
       </c>
       <c r="H205" t="n">
         <v>78</v>
@@ -6593,16 +6593,16 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>0.2056110226727581</v>
+        <v>0.20561138077805</v>
       </c>
       <c r="E206" t="n">
-        <v>56.18772803412543</v>
+        <v>56.18770768907335</v>
       </c>
       <c r="F206" t="n">
-        <v>84.52538534944719</v>
+        <v>84.52536629770299</v>
       </c>
       <c r="G206" t="n">
-        <v>39.00569700491917</v>
+        <v>39.0056850651901</v>
       </c>
       <c r="H206" t="n">
         <v>18</v>
@@ -6623,16 +6623,16 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>0.3071352029289407</v>
+        <v>0.3071353259916592</v>
       </c>
       <c r="E207" t="n">
-        <v>13.69160602869612</v>
+        <v>13.69160354271364</v>
       </c>
       <c r="F207" t="n">
-        <v>19.07195094713982</v>
+        <v>19.07194925341382</v>
       </c>
       <c r="G207" t="n">
-        <v>18.21847578903021</v>
+        <v>18.21847635175173</v>
       </c>
       <c r="H207" t="n">
         <v>89</v>
@@ -6653,16 +6653,16 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>0.09700548371927697</v>
+        <v>0.09700531102725218</v>
       </c>
       <c r="E208" t="n">
-        <v>225.2509186099274</v>
+        <v>225.2509500522806</v>
       </c>
       <c r="F208" t="n">
-        <v>284.7672606765375</v>
+        <v>284.7672879065104</v>
       </c>
       <c r="G208" t="n">
-        <v>36.16382231293995</v>
+        <v>36.1638258781458</v>
       </c>
       <c r="H208" t="n">
         <v>99</v>
@@ -6683,16 +6683,16 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>-0.02416103310207562</v>
+        <v>-0.0241614653375064</v>
       </c>
       <c r="E209" t="n">
-        <v>233.5957461121262</v>
+        <v>233.5957822081863</v>
       </c>
       <c r="F209" t="n">
-        <v>324.5353807974053</v>
+        <v>324.5354492806177</v>
       </c>
       <c r="G209" t="n">
-        <v>24.84305825437282</v>
+        <v>24.84306208569796</v>
       </c>
       <c r="H209" t="n">
         <v>93</v>
@@ -6713,16 +6713,16 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>0.08227353720197395</v>
+        <v>0.08227357021690873</v>
       </c>
       <c r="E210" t="n">
-        <v>5.981631804735232</v>
+        <v>5.981631816961826</v>
       </c>
       <c r="F210" t="n">
-        <v>8.352992276285585</v>
+        <v>8.352992126037385</v>
       </c>
       <c r="G210" t="n">
-        <v>84.42906302161511</v>
+        <v>84.42905407706259</v>
       </c>
       <c r="H210" t="n">
         <v>78</v>
@@ -6743,16 +6743,16 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>0.112963484223259</v>
+        <v>0.1129629723994839</v>
       </c>
       <c r="E211" t="n">
-        <v>65.22130839029948</v>
+        <v>65.22135077582465</v>
       </c>
       <c r="F211" t="n">
-        <v>89.31847591232797</v>
+        <v>89.3185016808911</v>
       </c>
       <c r="G211" t="n">
-        <v>43.22093946725196</v>
+        <v>43.22095156688024</v>
       </c>
       <c r="H211" t="n">
         <v>18</v>
@@ -6773,16 +6773,16 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>0.2874373812596089</v>
+        <v>0.2874373881502674</v>
       </c>
       <c r="E212" t="n">
-        <v>13.96391742149096</v>
+        <v>13.96391604991441</v>
       </c>
       <c r="F212" t="n">
-        <v>19.34115434081207</v>
+        <v>19.34115424729518</v>
       </c>
       <c r="G212" t="n">
-        <v>18.24328066426893</v>
+        <v>18.2432742578396</v>
       </c>
       <c r="H212" t="n">
         <v>89</v>
@@ -6803,16 +6803,16 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>0.6044606489372661</v>
+        <v>0.604460680079324</v>
       </c>
       <c r="E213" t="n">
-        <v>146.2608383641098</v>
+        <v>146.2608149364741</v>
       </c>
       <c r="F213" t="n">
-        <v>188.4700515898973</v>
+        <v>188.4700441704771</v>
       </c>
       <c r="G213" t="n">
-        <v>23.16745923001015</v>
+        <v>23.16744568982014</v>
       </c>
       <c r="H213" t="n">
         <v>99</v>
@@ -6833,16 +6833,16 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>0.5628059073890923</v>
+        <v>0.5628060891645704</v>
       </c>
       <c r="E214" t="n">
-        <v>158.8167773831275</v>
+        <v>158.8167846023395</v>
       </c>
       <c r="F214" t="n">
-        <v>212.0386688007499</v>
+        <v>212.0386247202887</v>
       </c>
       <c r="G214" t="n">
-        <v>18.3802132910462</v>
+        <v>18.38021188295431</v>
       </c>
       <c r="H214" t="n">
         <v>93</v>
@@ -6863,16 +6863,16 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>0.08584578179774205</v>
+        <v>0.08584579150677019</v>
       </c>
       <c r="E215" t="n">
-        <v>5.917333456186148</v>
+        <v>5.917333382826585</v>
       </c>
       <c r="F215" t="n">
-        <v>8.33671943991037</v>
+        <v>8.336719395639149</v>
       </c>
       <c r="G215" t="n">
-        <v>85.20029414985873</v>
+        <v>85.20029025952246</v>
       </c>
       <c r="H215" t="n">
         <v>78</v>
@@ -6893,16 +6893,16 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>0.4270142628821965</v>
+        <v>0.4270139182123356</v>
       </c>
       <c r="E216" t="n">
-        <v>48.05517917209201</v>
+        <v>48.05519443088107</v>
       </c>
       <c r="F216" t="n">
-        <v>71.78644725957845</v>
+        <v>71.78646885053566</v>
       </c>
       <c r="G216" t="n">
-        <v>31.6964237226451</v>
+        <v>31.69642602506</v>
       </c>
       <c r="H216" t="n">
         <v>18</v>
@@ -6923,16 +6923,16 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>0.1553183790862974</v>
+        <v>0.1553182805775751</v>
       </c>
       <c r="E217" t="n">
-        <v>15.39260727100158</v>
+        <v>15.39260795678985</v>
       </c>
       <c r="F217" t="n">
-        <v>21.05801327879798</v>
+        <v>21.05801450671503</v>
       </c>
       <c r="G217" t="n">
-        <v>21.00559643527895</v>
+        <v>21.00559740490265</v>
       </c>
       <c r="H217" t="n">
         <v>89</v>
@@ -6953,16 +6953,16 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>0.400763968468301</v>
+        <v>0.4007640715358757</v>
       </c>
       <c r="E218" t="n">
-        <v>179.1729224619239</v>
+        <v>179.1729209206321</v>
       </c>
       <c r="F218" t="n">
-        <v>231.9778188505751</v>
+        <v>231.9777989006798</v>
       </c>
       <c r="G218" t="n">
-        <v>27.90596289989135</v>
+        <v>27.90596114486831</v>
       </c>
       <c r="H218" t="n">
         <v>99</v>
@@ -6983,16 +6983,16 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>0.2739337962284258</v>
+        <v>0.2739338179035433</v>
       </c>
       <c r="E219" t="n">
-        <v>202.9140792354461</v>
+        <v>202.914069391066</v>
       </c>
       <c r="F219" t="n">
-        <v>273.2536913680888</v>
+        <v>273.2536872893933</v>
       </c>
       <c r="G219" t="n">
-        <v>24.43176970031563</v>
+        <v>24.43176788897096</v>
       </c>
       <c r="H219" t="n">
         <v>93</v>
@@ -7013,16 +7013,16 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>0.08728362615527463</v>
+        <v>0.08728373436201708</v>
       </c>
       <c r="E220" t="n">
-        <v>5.895097255706787</v>
+        <v>5.895096791096223</v>
       </c>
       <c r="F220" t="n">
-        <v>8.330160578213416</v>
+        <v>8.330160084423893</v>
       </c>
       <c r="G220" t="n">
-        <v>88.11576848216288</v>
+        <v>88.11576327873144</v>
       </c>
       <c r="H220" t="n">
         <v>78</v>
@@ -7043,16 +7043,16 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>-0.2095653288179624</v>
+        <v>-0.2095648545123323</v>
       </c>
       <c r="E221" t="n">
-        <v>71.49040222167969</v>
+        <v>71.49039459228516</v>
       </c>
       <c r="F221" t="n">
-        <v>104.3002188037455</v>
+        <v>104.3001983541738</v>
       </c>
       <c r="G221" t="n">
-        <v>50.73233617773855</v>
+        <v>50.73232484019569</v>
       </c>
       <c r="H221" t="n">
         <v>18</v>
@@ -7073,16 +7073,16 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>0.3926780950318184</v>
+        <v>0.3926779759991595</v>
       </c>
       <c r="E222" t="n">
-        <v>13.09644673379619</v>
+        <v>13.0964477624786</v>
       </c>
       <c r="F222" t="n">
-        <v>17.85584246568601</v>
+        <v>17.85584421552269</v>
       </c>
       <c r="G222" t="n">
-        <v>18.00750741399195</v>
+        <v>18.00750885119556</v>
       </c>
       <c r="H222" t="n">
         <v>89</v>
@@ -7103,16 +7103,16 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>0.4980215331185783</v>
+        <v>0.4980216483927645</v>
       </c>
       <c r="E223" t="n">
-        <v>160.0673128378512</v>
+        <v>160.0672958836411</v>
       </c>
       <c r="F223" t="n">
-        <v>212.3195793102248</v>
+        <v>212.3195549317207</v>
       </c>
       <c r="G223" t="n">
-        <v>22.69184814856475</v>
+        <v>22.69184720194841</v>
       </c>
       <c r="H223" t="n">
         <v>99</v>
@@ -7133,16 +7133,16 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>0.2454965216493739</v>
+        <v>0.245496537886564</v>
       </c>
       <c r="E224" t="n">
-        <v>204.0459460186702</v>
+        <v>204.0459394557502</v>
       </c>
       <c r="F224" t="n">
-        <v>278.5534550368021</v>
+        <v>278.553452039516</v>
       </c>
       <c r="G224" t="n">
-        <v>25.64109148708308</v>
+        <v>25.64109031378428</v>
       </c>
       <c r="H224" t="n">
         <v>93</v>
@@ -7163,16 +7163,16 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>0.1164516887271986</v>
+        <v>0.1164515721308091</v>
       </c>
       <c r="E225" t="n">
-        <v>5.885328023861616</v>
+        <v>5.885328421225915</v>
       </c>
       <c r="F225" t="n">
-        <v>8.195974584286919</v>
+        <v>8.195975125072863</v>
       </c>
       <c r="G225" t="n">
-        <v>86.42438422968026</v>
+        <v>86.42438719086304</v>
       </c>
       <c r="H225" t="n">
         <v>78</v>
@@ -7193,16 +7193,16 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>0.3469300660974102</v>
+        <v>0.3469299915826377</v>
       </c>
       <c r="E226" t="n">
         <v>51.32591501871745</v>
       </c>
       <c r="F226" t="n">
-        <v>76.63910065581604</v>
+        <v>76.63910502804687</v>
       </c>
       <c r="G226" t="n">
-        <v>36.26705794542471</v>
+        <v>36.26706203831007</v>
       </c>
       <c r="H226" t="n">
         <v>18</v>
@@ -7223,16 +7223,16 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>0.2834157332605367</v>
+        <v>0.2834155120274432</v>
       </c>
       <c r="E227" t="n">
-        <v>13.40480877308363</v>
+        <v>13.4048083016042</v>
       </c>
       <c r="F227" t="n">
-        <v>19.39565753147297</v>
+        <v>19.39566052551092</v>
       </c>
       <c r="G227" t="n">
-        <v>17.61133809510791</v>
+        <v>17.61133350161784</v>
       </c>
       <c r="H227" t="n">
         <v>89</v>
@@ -7253,16 +7253,16 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>0.6413345126315804</v>
+        <v>0.6413345866165079</v>
       </c>
       <c r="E228" t="n">
-        <v>139.9768479472459</v>
+        <v>139.9768072571417</v>
       </c>
       <c r="F228" t="n">
-        <v>179.470178771982</v>
+        <v>179.4701602615742</v>
       </c>
       <c r="G228" t="n">
-        <v>23.65748870906598</v>
+        <v>23.65748734106856</v>
       </c>
       <c r="H228" t="n">
         <v>99</v>
@@ -7283,16 +7283,16 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>0.5898171481777033</v>
+        <v>0.5898171204848103</v>
       </c>
       <c r="E229" t="n">
-        <v>155.2100505213584</v>
+        <v>155.2100734915785</v>
       </c>
       <c r="F229" t="n">
-        <v>205.3840325255597</v>
+        <v>205.3840394586602</v>
       </c>
       <c r="G229" t="n">
-        <v>17.85073331745714</v>
+        <v>17.85073688318535</v>
       </c>
       <c r="H229" t="n">
         <v>93</v>
@@ -7313,16 +7313,16 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>0.07923640268700127</v>
+        <v>0.07923625975638615</v>
       </c>
       <c r="E230" t="n">
-        <v>5.922844299903283</v>
+        <v>5.922844434395815</v>
       </c>
       <c r="F230" t="n">
-        <v>8.366802604081537</v>
+        <v>8.366803253473085</v>
       </c>
       <c r="G230" t="n">
-        <v>84.04770036302443</v>
+        <v>84.04769265246608</v>
       </c>
       <c r="H230" t="n">
         <v>78</v>
@@ -7343,16 +7343,16 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>0.0685218520734765</v>
+        <v>0.0685209769610361</v>
       </c>
       <c r="E231" t="n">
-        <v>79.24981435139973</v>
+        <v>79.24985504150391</v>
       </c>
       <c r="F231" t="n">
-        <v>91.52861488506902</v>
+        <v>91.52865788007159</v>
       </c>
       <c r="G231" t="n">
-        <v>39.61484077034813</v>
+        <v>39.61486389621633</v>
       </c>
       <c r="H231" t="n">
         <v>18</v>
@@ -7373,16 +7373,16 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>0.380038996883525</v>
+        <v>0.3800390108357183</v>
       </c>
       <c r="E232" t="n">
-        <v>12.46253800124265</v>
+        <v>12.46253778693381</v>
       </c>
       <c r="F232" t="n">
-        <v>18.04068647341154</v>
+        <v>18.04068627040914</v>
       </c>
       <c r="G232" t="n">
-        <v>16.37929333304389</v>
+        <v>16.37929433922515</v>
       </c>
       <c r="H232" t="n">
         <v>89</v>
@@ -7403,16 +7403,16 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>0.4809658899705124</v>
+        <v>0.480965971939504</v>
       </c>
       <c r="E233" t="n">
-        <v>164.9601745605469</v>
+        <v>164.9601656210543</v>
       </c>
       <c r="F233" t="n">
-        <v>215.8964250306291</v>
+        <v>215.8964079827968</v>
       </c>
       <c r="G233" t="n">
-        <v>24.94174420316761</v>
+        <v>24.94174375202004</v>
       </c>
       <c r="H233" t="n">
         <v>99</v>
@@ -7433,16 +7433,16 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>0.437355174835433</v>
+        <v>0.4373552426003339</v>
       </c>
       <c r="E234" t="n">
-        <v>180.5485337780368</v>
+        <v>180.5485186833207</v>
       </c>
       <c r="F234" t="n">
-        <v>240.5443114628229</v>
+        <v>240.544296977253</v>
       </c>
       <c r="G234" t="n">
-        <v>21.21777749821462</v>
+        <v>21.21777640883494</v>
       </c>
       <c r="H234" t="n">
         <v>93</v>
@@ -7463,16 +7463,16 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>0.08180243762438377</v>
+        <v>0.08180239467532679</v>
       </c>
       <c r="E235" t="n">
-        <v>6.004025862767146</v>
+        <v>6.004025642688458</v>
       </c>
       <c r="F235" t="n">
-        <v>8.355135935871905</v>
+        <v>8.355136131279311</v>
       </c>
       <c r="G235" t="n">
-        <v>87.81876930547847</v>
+        <v>87.8187681292695</v>
       </c>
       <c r="H235" t="n">
         <v>78</v>
@@ -7493,16 +7493,16 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>0.4994085555133637</v>
+        <v>0.4994086545760349</v>
       </c>
       <c r="E236" t="n">
-        <v>49.5708745320638</v>
+        <v>49.57088046603732</v>
       </c>
       <c r="F236" t="n">
-        <v>67.09841573332659</v>
+        <v>67.09840909423127</v>
       </c>
       <c r="G236" t="n">
-        <v>27.3021024945409</v>
+        <v>27.30211097561859</v>
       </c>
       <c r="H236" t="n">
         <v>18</v>
@@ -7523,16 +7523,16 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>0.5726089863865398</v>
+        <v>0.5726091333645922</v>
       </c>
       <c r="E237" t="n">
-        <v>11.37195840042629</v>
+        <v>11.37195621447617</v>
       </c>
       <c r="F237" t="n">
-        <v>14.97902570581567</v>
+        <v>14.97902313020207</v>
       </c>
       <c r="G237" t="n">
-        <v>16.00921113160766</v>
+        <v>16.00920864892465</v>
       </c>
       <c r="H237" t="n">
         <v>89</v>
@@ -7553,16 +7553,16 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>0.5946571724979768</v>
+        <v>0.5946572636273326</v>
       </c>
       <c r="E238" t="n">
-        <v>149.5923212224787</v>
+        <v>149.5922950205177</v>
       </c>
       <c r="F238" t="n">
-        <v>190.7913791762475</v>
+        <v>190.7913577293447</v>
       </c>
       <c r="G238" t="n">
-        <v>22.14906341591659</v>
+        <v>22.14906129967112</v>
       </c>
       <c r="H238" t="n">
         <v>99</v>
@@ -7583,16 +7583,16 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>0.6201356713912354</v>
+        <v>0.620135670189109</v>
       </c>
       <c r="E239" t="n">
-        <v>149.4098789666289</v>
+        <v>149.4098907798849</v>
       </c>
       <c r="F239" t="n">
-        <v>197.6478902211342</v>
+        <v>197.6478905338745</v>
       </c>
       <c r="G239" t="n">
-        <v>17.89167697659934</v>
+        <v>17.89167876596158</v>
       </c>
       <c r="H239" t="n">
         <v>93</v>
@@ -7613,16 +7613,16 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>0.05407224608676597</v>
+        <v>0.05407232017018015</v>
       </c>
       <c r="E240" t="n">
-        <v>6.328822117585402</v>
+        <v>6.328821928073198</v>
       </c>
       <c r="F240" t="n">
-        <v>8.480362880815534</v>
+        <v>8.480362548731902</v>
       </c>
       <c r="G240" t="n">
-        <v>88.8170385479707</v>
+        <v>88.8170454965796</v>
       </c>
       <c r="H240" t="n">
         <v>78</v>
@@ -7643,16 +7643,16 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>0.7351618421481594</v>
+        <v>0.7351617244216468</v>
       </c>
       <c r="E241" t="n">
-        <v>37.98472171359592</v>
+        <v>37.9847412109375</v>
       </c>
       <c r="F241" t="n">
-        <v>48.80460856295679</v>
+        <v>48.80461941032819</v>
       </c>
       <c r="G241" t="n">
-        <v>20.3303219094518</v>
+        <v>20.33033415982846</v>
       </c>
       <c r="H241" t="n">
         <v>18</v>
@@ -7673,16 +7673,16 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>0.3715957011539143</v>
+        <v>0.3715956534594779</v>
       </c>
       <c r="E242" t="n">
-        <v>13.2209870413448</v>
+        <v>13.22098369812698</v>
       </c>
       <c r="F242" t="n">
-        <v>18.16311976196278</v>
+        <v>18.16312045123221</v>
       </c>
       <c r="G242" t="n">
-        <v>18.23882070364118</v>
+        <v>18.23881685565837</v>
       </c>
       <c r="H242" t="n">
         <v>89</v>
@@ -7703,16 +7703,16 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>0.1138095007614067</v>
+        <v>0.1138094895193482</v>
       </c>
       <c r="E243" t="n">
-        <v>222.0434724441683</v>
+        <v>222.0434761432686</v>
       </c>
       <c r="F243" t="n">
-        <v>282.1051703995714</v>
+        <v>282.1051721889399</v>
       </c>
       <c r="G243" t="n">
-        <v>33.70490020856538</v>
+        <v>33.70490073911775</v>
       </c>
       <c r="H243" t="n">
         <v>99</v>
@@ -7733,16 +7733,16 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>0.2140986085834131</v>
+        <v>0.2140985783390207</v>
       </c>
       <c r="E244" t="n">
-        <v>221.9705781013735</v>
+        <v>221.9705866331695</v>
       </c>
       <c r="F244" t="n">
-        <v>284.2902433859155</v>
+        <v>284.2902488561855</v>
       </c>
       <c r="G244" t="n">
-        <v>26.04181798818935</v>
+        <v>26.04181933682387</v>
       </c>
       <c r="H244" t="n">
         <v>93</v>
@@ -7763,16 +7763,16 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>-0.0697307464147201</v>
+        <v>-0.06973059861896558</v>
       </c>
       <c r="E245" t="n">
-        <v>6.869416157404582</v>
+        <v>6.869415998458862</v>
       </c>
       <c r="F245" t="n">
-        <v>9.018258746980123</v>
+        <v>9.018258123991393</v>
       </c>
       <c r="G245" t="n">
-        <v>87.24944880990881</v>
+        <v>87.24944961813878</v>
       </c>
       <c r="H245" t="n">
         <v>78</v>
@@ -7793,16 +7793,16 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>0.3917138325305817</v>
+        <v>0.3917128606123008</v>
       </c>
       <c r="E246" t="n">
-        <v>49.63403150770399</v>
+        <v>49.63405185275607</v>
       </c>
       <c r="F246" t="n">
-        <v>73.96470424148916</v>
+        <v>73.96476333178524</v>
       </c>
       <c r="G246" t="n">
-        <v>29.96224581816896</v>
+        <v>29.96225705194556</v>
       </c>
       <c r="H246" t="n">
         <v>18</v>
@@ -7823,16 +7823,16 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>0.2129543701716607</v>
+        <v>0.2129542812688217</v>
       </c>
       <c r="E247" t="n">
-        <v>14.38916439956494</v>
+        <v>14.38916868574164</v>
       </c>
       <c r="F247" t="n">
-        <v>20.32688493622698</v>
+        <v>20.32688608426571</v>
       </c>
       <c r="G247" t="n">
-        <v>17.83495488425605</v>
+        <v>17.83496077637615</v>
       </c>
       <c r="H247" t="n">
         <v>89</v>
@@ -7853,16 +7853,16 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>0.156770838404756</v>
+        <v>0.1567709254130351</v>
       </c>
       <c r="E248" t="n">
-        <v>214.6015951753867</v>
+        <v>214.6015751385929</v>
       </c>
       <c r="F248" t="n">
-        <v>275.182181895059</v>
+        <v>275.1821676977744</v>
       </c>
       <c r="G248" t="n">
-        <v>31.45404678306509</v>
+        <v>31.45404338925356</v>
       </c>
       <c r="H248" t="n">
         <v>99</v>
@@ -7883,16 +7883,16 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>0.1176994099288373</v>
+        <v>0.1176994856060152</v>
       </c>
       <c r="E249" t="n">
-        <v>237.4432802918137</v>
+        <v>237.4432658533896</v>
       </c>
       <c r="F249" t="n">
-        <v>301.2216695452557</v>
+        <v>301.2216566269789</v>
       </c>
       <c r="G249" t="n">
-        <v>28.83756820597964</v>
+        <v>28.83756590114657</v>
       </c>
       <c r="H249" t="n">
         <v>93</v>
@@ -7913,16 +7913,16 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>0.06589305184601979</v>
+        <v>0.06589312304548955</v>
       </c>
       <c r="E250" t="n">
-        <v>6.16870119021489</v>
+        <v>6.168700823417077</v>
       </c>
       <c r="F250" t="n">
-        <v>8.427208783284572</v>
+        <v>8.427208462115347</v>
       </c>
       <c r="G250" t="n">
-        <v>90.61288878909923</v>
+        <v>90.61288630706808</v>
       </c>
       <c r="H250" t="n">
         <v>78</v>
@@ -7943,16 +7943,16 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>-0.1278110810665241</v>
+        <v>-0.1278111951443803</v>
       </c>
       <c r="E251" t="n">
-        <v>76.50513543023004</v>
+        <v>76.50513627794054</v>
       </c>
       <c r="F251" t="n">
-        <v>100.7137422209047</v>
+        <v>100.7137473144916</v>
       </c>
       <c r="G251" t="n">
-        <v>47.17406454879114</v>
+        <v>47.17406586425408</v>
       </c>
       <c r="H251" t="n">
         <v>18</v>
@@ -7973,16 +7973,16 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>0.4687524859123955</v>
+        <v>0.4687525198253002</v>
       </c>
       <c r="E252" t="n">
-        <v>12.04607695675968</v>
+        <v>12.04607597093904</v>
       </c>
       <c r="F252" t="n">
-        <v>16.70010986696203</v>
+        <v>16.70010933392495</v>
       </c>
       <c r="G252" t="n">
-        <v>16.41745979601737</v>
+        <v>16.41745905838647</v>
       </c>
       <c r="H252" t="n">
         <v>89</v>
@@ -8003,16 +8003,16 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>-0.1873175518904329</v>
+        <v>-0.1873176594078476</v>
       </c>
       <c r="E253" t="n">
-        <v>259.3030423251066</v>
+        <v>259.3030565049913</v>
       </c>
       <c r="F253" t="n">
-        <v>326.5359072477884</v>
+        <v>326.5359220325003</v>
       </c>
       <c r="G253" t="n">
-        <v>34.02098414405222</v>
+        <v>34.02098496788989</v>
       </c>
       <c r="H253" t="n">
         <v>99</v>
@@ -8033,16 +8033,16 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>-0.344760009375344</v>
+        <v>-0.3447599493651623</v>
       </c>
       <c r="E254" t="n">
-        <v>294.9098822480889</v>
+        <v>294.9098664970808</v>
       </c>
       <c r="F254" t="n">
-        <v>371.8778566742736</v>
+        <v>371.8778483767121</v>
       </c>
       <c r="G254" t="n">
-        <v>36.48951060126407</v>
+        <v>36.48950738078833</v>
       </c>
       <c r="H254" t="n">
         <v>93</v>
@@ -8063,16 +8063,16 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>0.03948542595482085</v>
+        <v>0.03948542168441149</v>
       </c>
       <c r="E255" t="n">
-        <v>6.03086351736998</v>
+        <v>6.030863664089105</v>
       </c>
       <c r="F255" t="n">
-        <v>8.545499081719507</v>
+        <v>8.545499100715981</v>
       </c>
       <c r="G255" t="n">
-        <v>83.9247649201177</v>
+        <v>83.92477129799414</v>
       </c>
       <c r="H255" t="n">
         <v>78</v>
@@ -8093,16 +8093,16 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>0.5042960579390361</v>
+        <v>0.5042960484556633</v>
       </c>
       <c r="E256" t="n">
         <v>46.24717203776041</v>
       </c>
       <c r="F256" t="n">
-        <v>66.77005607914127</v>
+        <v>66.77005671783431</v>
       </c>
       <c r="G256" t="n">
-        <v>28.54101344122191</v>
+        <v>28.54101328640284</v>
       </c>
       <c r="H256" t="n">
         <v>18</v>
@@ -8123,16 +8123,16 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>0.3744221141937497</v>
+        <v>0.3744221526316138</v>
       </c>
       <c r="E257" t="n">
-        <v>13.29271115078015</v>
+        <v>13.29271067930071</v>
       </c>
       <c r="F257" t="n">
-        <v>18.12222703284483</v>
+        <v>18.12222647609584</v>
       </c>
       <c r="G257" t="n">
-        <v>18.25061483236685</v>
+        <v>18.25061347783404</v>
       </c>
       <c r="H257" t="n">
         <v>89</v>
@@ -8153,16 +8153,16 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>0.6310873046133793</v>
+        <v>0.6310873142000593</v>
       </c>
       <c r="E258" t="n">
-        <v>141.6615310823074</v>
+        <v>141.6615329318576</v>
       </c>
       <c r="F258" t="n">
-        <v>182.0158891375497</v>
+        <v>182.015886772589</v>
       </c>
       <c r="G258" t="n">
-        <v>22.3844442202611</v>
+        <v>22.38444410210668</v>
       </c>
       <c r="H258" t="n">
         <v>99</v>
@@ -8183,16 +8183,16 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>0.5610586379840055</v>
+        <v>0.5610586165090425</v>
       </c>
       <c r="E259" t="n">
-        <v>159.3635578770791</v>
+        <v>159.3635591896631</v>
       </c>
       <c r="F259" t="n">
-        <v>212.4619581971365</v>
+        <v>212.4619633944282</v>
       </c>
       <c r="G259" t="n">
-        <v>17.11459498121457</v>
+        <v>17.11459497166886</v>
       </c>
       <c r="H259" t="n">
         <v>93</v>
@@ -8213,16 +8213,16 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>0.1030228620508081</v>
+        <v>0.1030228469488081</v>
       </c>
       <c r="E260" t="n">
-        <v>5.855323400252905</v>
+        <v>5.855323510292249</v>
       </c>
       <c r="F260" t="n">
-        <v>8.258023974576096</v>
+        <v>8.258024044094411</v>
       </c>
       <c r="G260" t="n">
-        <v>82.50873906570374</v>
+        <v>82.50874080847301</v>
       </c>
       <c r="H260" t="n">
         <v>78</v>
@@ -8243,16 +8243,16 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>0.1956001404707758</v>
+        <v>0.1956003231245893</v>
       </c>
       <c r="E261" t="n">
-        <v>55.89228396945529</v>
+        <v>55.89227803548177</v>
       </c>
       <c r="F261" t="n">
-        <v>85.0563119472752</v>
+        <v>85.05630229047303</v>
       </c>
       <c r="G261" t="n">
-        <v>38.21370204887305</v>
+        <v>38.21369752414576</v>
       </c>
       <c r="H261" t="n">
         <v>18</v>
@@ -8273,16 +8273,16 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>0.4097076917216316</v>
+        <v>0.4097077113127731</v>
       </c>
       <c r="E262" t="n">
-        <v>12.30292686719573</v>
+        <v>12.30292708150457</v>
       </c>
       <c r="F262" t="n">
-        <v>17.60371930410094</v>
+        <v>17.60371901197706</v>
       </c>
       <c r="G262" t="n">
-        <v>16.74824171893653</v>
+        <v>16.74824245325992</v>
       </c>
       <c r="H262" t="n">
         <v>89</v>
@@ -8303,16 +8303,16 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>0.5854442743468413</v>
+        <v>0.5854443116223171</v>
       </c>
       <c r="E263" t="n">
-        <v>153.3482632107205</v>
+        <v>153.3482582785867</v>
       </c>
       <c r="F263" t="n">
-        <v>192.9474129911639</v>
+        <v>192.947404316568</v>
       </c>
       <c r="G263" t="n">
-        <v>23.62410133194479</v>
+        <v>23.62410028593267</v>
       </c>
       <c r="H263" t="n">
         <v>99</v>
@@ -8333,16 +8333,16 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>0.5618673449852909</v>
+        <v>0.5618673850362523</v>
       </c>
       <c r="E264" t="n">
-        <v>161.4976298014323</v>
+        <v>161.4976199570523</v>
       </c>
       <c r="F264" t="n">
-        <v>212.2661476616594</v>
+        <v>212.2661379597308</v>
       </c>
       <c r="G264" t="n">
-        <v>17.93619240106342</v>
+        <v>17.93619187972661</v>
       </c>
       <c r="H264" t="n">
         <v>93</v>
@@ -8363,16 +8363,16 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>0.1050259787210595</v>
+        <v>0.1050260496208677</v>
       </c>
       <c r="E265" t="n">
-        <v>5.898506054511437</v>
+        <v>5.898505699940217</v>
       </c>
       <c r="F265" t="n">
-        <v>8.248797969623814</v>
+        <v>8.248797642889075</v>
       </c>
       <c r="G265" t="n">
-        <v>81.52345873357201</v>
+        <v>81.52345455741093</v>
       </c>
       <c r="H265" t="n">
         <v>78</v>
@@ -8393,16 +8393,16 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>0.3316135255074563</v>
+        <v>0.3316136275835031</v>
       </c>
       <c r="E266" t="n">
-        <v>52.15251159667969</v>
+        <v>52.15250735812717</v>
       </c>
       <c r="F266" t="n">
-        <v>77.53260592041099</v>
+        <v>77.53260000001724</v>
       </c>
       <c r="G266" t="n">
-        <v>35.93656599705738</v>
+        <v>35.93656423513057</v>
       </c>
       <c r="H266" t="n">
         <v>18</v>
@@ -8423,16 +8423,16 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>0.35913044528932</v>
+        <v>0.3591304655760562</v>
       </c>
       <c r="E267" t="n">
-        <v>13.18831994560327</v>
+        <v>13.18831943126207</v>
       </c>
       <c r="F267" t="n">
-        <v>18.34238027767035</v>
+        <v>18.34237998735618</v>
       </c>
       <c r="G267" t="n">
-        <v>17.8273948238255</v>
+        <v>17.82739422677399</v>
       </c>
       <c r="H267" t="n">
         <v>89</v>
@@ -8453,16 +8453,16 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>0.56783578188491</v>
+        <v>0.5678358129449688</v>
       </c>
       <c r="E268" t="n">
-        <v>149.0421392267401</v>
+        <v>149.0421364524148</v>
       </c>
       <c r="F268" t="n">
-        <v>197.0025755280281</v>
+        <v>197.0025684486455</v>
       </c>
       <c r="G268" t="n">
-        <v>23.49588582919194</v>
+        <v>23.49588519842143</v>
       </c>
       <c r="H268" t="n">
         <v>99</v>
@@ -8483,16 +8483,16 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>0.5307239704031518</v>
+        <v>0.5307239380581764</v>
       </c>
       <c r="E269" t="n">
-        <v>165.4651630360593</v>
+        <v>165.4651682863953</v>
       </c>
       <c r="F269" t="n">
-        <v>219.6808053780124</v>
+        <v>219.6808129487913</v>
       </c>
       <c r="G269" t="n">
-        <v>17.93794473340574</v>
+        <v>17.9379462385323</v>
       </c>
       <c r="H269" t="n">
         <v>93</v>
@@ -8513,16 +8513,16 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>0.07048870139824426</v>
+        <v>0.07048878987951623</v>
       </c>
       <c r="E270" t="n">
-        <v>5.878424601677136</v>
+        <v>5.878424332692073</v>
       </c>
       <c r="F270" t="n">
-        <v>8.406452995997235</v>
+        <v>8.406452595887158</v>
       </c>
       <c r="G270" t="n">
-        <v>74.41713625094198</v>
+        <v>74.41712510460027</v>
       </c>
       <c r="H270" t="n">
         <v>78</v>
@@ -8543,16 +8543,16 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>0.4297699006349518</v>
+        <v>0.429769659597404</v>
       </c>
       <c r="E271" t="n">
-        <v>45.17161899142795</v>
+        <v>45.171630859375</v>
       </c>
       <c r="F271" t="n">
-        <v>71.61361934788162</v>
+        <v>71.61363448349915</v>
       </c>
       <c r="G271" t="n">
-        <v>31.76611534343876</v>
+        <v>31.76612425676536</v>
       </c>
       <c r="H271" t="n">
         <v>18</v>
@@ -8573,16 +8573,16 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>0.3525989963612304</v>
+        <v>0.3525989603689766</v>
       </c>
       <c r="E272" t="n">
-        <v>13.27258892273635</v>
+        <v>13.27258939421579</v>
       </c>
       <c r="F272" t="n">
-        <v>18.43561190502895</v>
+        <v>18.4356124174928</v>
       </c>
       <c r="G272" t="n">
-        <v>17.65708820460852</v>
+        <v>17.65708881938215</v>
       </c>
       <c r="H272" t="n">
         <v>89</v>
@@ -8603,16 +8603,16 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>0.632007989926119</v>
+        <v>0.6320079911132633</v>
       </c>
       <c r="E273" t="n">
-        <v>135.8174167209201</v>
+        <v>135.8174154878867</v>
       </c>
       <c r="F273" t="n">
-        <v>181.7886212170011</v>
+        <v>181.7886209237755</v>
       </c>
       <c r="G273" t="n">
-        <v>21.57560238421977</v>
+        <v>21.57560161342597</v>
       </c>
       <c r="H273" t="n">
         <v>99</v>
@@ -8633,16 +8633,16 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>0.596806001536786</v>
+        <v>0.5968059912060708</v>
       </c>
       <c r="E274" t="n">
-        <v>149.1453302855133</v>
+        <v>149.1453322543893</v>
       </c>
       <c r="F274" t="n">
-        <v>203.6268091938973</v>
+        <v>203.6268118025801</v>
       </c>
       <c r="G274" t="n">
-        <v>15.02576799834064</v>
+        <v>15.02576841758416</v>
       </c>
       <c r="H274" t="n">
         <v>93</v>
@@ -8663,16 +8663,16 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>0.142276938120011</v>
+        <v>0.142276953674786</v>
       </c>
       <c r="E275" t="n">
-        <v>6.118605240797385</v>
+        <v>6.118605283590464</v>
       </c>
       <c r="F275" t="n">
-        <v>8.075306146319251</v>
+        <v>8.075306073096565</v>
       </c>
       <c r="G275" t="n">
-        <v>103.1390571409605</v>
+        <v>103.1390542477373</v>
       </c>
       <c r="H275" t="n">
         <v>78</v>
@@ -8693,16 +8693,16 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>0.4555760992064248</v>
+        <v>0.4555760790673929</v>
       </c>
       <c r="E276" t="n">
-        <v>46.85610792371962</v>
+        <v>46.85611216227213</v>
       </c>
       <c r="F276" t="n">
-        <v>69.97439401955246</v>
+        <v>69.97439531377974</v>
       </c>
       <c r="G276" t="n">
-        <v>26.9949265627255</v>
+        <v>26.99492748412801</v>
       </c>
       <c r="H276" t="n">
         <v>18</v>
@@ -8723,16 +8723,16 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>0.2769081145368691</v>
+        <v>0.2769080278647866</v>
       </c>
       <c r="E277" t="n">
-        <v>14.07089430562566</v>
+        <v>14.0708954200316</v>
       </c>
       <c r="F277" t="n">
-        <v>19.48352875607536</v>
+        <v>19.48352992375404</v>
       </c>
       <c r="G277" t="n">
-        <v>19.12699349465911</v>
+        <v>19.12699503714493</v>
       </c>
       <c r="H277" t="n">
         <v>89</v>
@@ -8753,16 +8753,16 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>0.4207169522958355</v>
+        <v>0.4207169560906699</v>
       </c>
       <c r="E278" t="n">
-        <v>176.3575858684501</v>
+        <v>176.3575846354167</v>
       </c>
       <c r="F278" t="n">
-        <v>228.0829969124468</v>
+        <v>228.0829961653706</v>
       </c>
       <c r="G278" t="n">
-        <v>27.3048460158793</v>
+        <v>27.3048457824952</v>
       </c>
       <c r="H278" t="n">
         <v>99</v>
@@ -8783,16 +8783,16 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>0.4422039108368028</v>
+        <v>0.4422039234993544</v>
       </c>
       <c r="E279" t="n">
-        <v>193.2563722672001</v>
+        <v>193.2563762049521</v>
       </c>
       <c r="F279" t="n">
-        <v>239.5055926332697</v>
+        <v>239.5055899147566</v>
       </c>
       <c r="G279" t="n">
-        <v>21.96251272505268</v>
+        <v>21.96251286646932</v>
       </c>
       <c r="H279" t="n">
         <v>93</v>
@@ -8813,16 +8813,16 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>0.05073287784906577</v>
+        <v>0.05073288151970112</v>
       </c>
       <c r="E280" t="n">
         <v>6.299928506215413</v>
       </c>
       <c r="F280" t="n">
-        <v>8.495318623981165</v>
+        <v>8.495318607556275</v>
       </c>
       <c r="G280" t="n">
-        <v>94.71267545600361</v>
+        <v>94.71267547411017</v>
       </c>
       <c r="H280" t="n">
         <v>78</v>
@@ -8843,16 +8843,16 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>0.5689267037010737</v>
+        <v>0.5689267632572568</v>
       </c>
       <c r="E281" t="n">
-        <v>45.51223415798611</v>
+        <v>45.51223839653863</v>
       </c>
       <c r="F281" t="n">
-        <v>62.26530429970403</v>
+        <v>62.26529999848191</v>
       </c>
       <c r="G281" t="n">
-        <v>24.03715273864991</v>
+        <v>24.03714864838265</v>
       </c>
       <c r="H281" t="n">
         <v>18</v>
@@ -8873,16 +8873,16 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>0.6705714805537254</v>
+        <v>0.670571495587659</v>
       </c>
       <c r="E282" t="n">
-        <v>10.01520701204793</v>
+        <v>10.01520624053612</v>
       </c>
       <c r="F282" t="n">
-        <v>13.1507787160187</v>
+        <v>13.15077841594156</v>
       </c>
       <c r="G282" t="n">
-        <v>14.45936173622664</v>
+        <v>14.45936042536854</v>
       </c>
       <c r="H282" t="n">
         <v>89</v>
@@ -8903,16 +8903,16 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>0.7049076333934214</v>
+        <v>0.704907688122087</v>
       </c>
       <c r="E283" t="n">
-        <v>120.2678762108389</v>
+        <v>120.2678570988202</v>
       </c>
       <c r="F283" t="n">
-        <v>162.7895373102009</v>
+        <v>162.789522214496</v>
       </c>
       <c r="G283" t="n">
-        <v>19.24100694474848</v>
+        <v>19.2410032246664</v>
       </c>
       <c r="H283" t="n">
         <v>99</v>
@@ -8933,16 +8933,16 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>0.6755483040330419</v>
+        <v>0.6755482681334859</v>
       </c>
       <c r="E284" t="n">
-        <v>129.1797167049941</v>
+        <v>129.1797199864541</v>
       </c>
       <c r="F284" t="n">
-        <v>182.6639945873218</v>
+        <v>182.6640046929187</v>
       </c>
       <c r="G284" t="n">
-        <v>13.29279440691034</v>
+        <v>13.29279474103391</v>
       </c>
       <c r="H284" t="n">
         <v>93</v>
@@ -8963,16 +8963,16 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>0.1965167176525453</v>
+        <v>0.1965167285619372</v>
       </c>
       <c r="E285" t="n">
-        <v>5.619992164465097</v>
+        <v>5.619992127785316</v>
       </c>
       <c r="F285" t="n">
-        <v>7.815807870428078</v>
+        <v>7.815807817368036</v>
       </c>
       <c r="G285" t="n">
-        <v>96.84496002937377</v>
+        <v>96.84496172267745</v>
       </c>
       <c r="H285" t="n">
         <v>78</v>
@@ -8993,16 +8993,16 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>0.6952634649020089</v>
+        <v>0.6952635019026722</v>
       </c>
       <c r="E286" t="n">
-        <v>33.98877292209201</v>
+        <v>33.98877716064453</v>
       </c>
       <c r="F286" t="n">
-        <v>52.35194450664923</v>
+        <v>52.35194132840095</v>
       </c>
       <c r="G286" t="n">
-        <v>18.07372808726749</v>
+        <v>18.07372868591808</v>
       </c>
       <c r="H286" t="n">
         <v>18</v>
@@ -9023,16 +9023,16 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>0.6841653053979582</v>
+        <v>0.6841652240764478</v>
       </c>
       <c r="E287" t="n">
-        <v>9.782689941063357</v>
+        <v>9.782690841160463</v>
       </c>
       <c r="F287" t="n">
-        <v>12.87658772008862</v>
+        <v>12.87658937782843</v>
       </c>
       <c r="G287" t="n">
-        <v>14.11164677191099</v>
+        <v>14.11164791521034</v>
       </c>
       <c r="H287" t="n">
         <v>89</v>
@@ -9053,16 +9053,16 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>0.7105908209301937</v>
+        <v>0.7105908522690114</v>
       </c>
       <c r="E288" t="n">
-        <v>122.2036049582741</v>
+        <v>122.2035941692314</v>
       </c>
       <c r="F288" t="n">
-        <v>161.214333364242</v>
+        <v>161.2143246356545</v>
       </c>
       <c r="G288" t="n">
-        <v>19.3723490979964</v>
+        <v>19.37234667716893</v>
       </c>
       <c r="H288" t="n">
         <v>99</v>
@@ -9083,16 +9083,16 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>0.6704983796041535</v>
+        <v>0.670498397008275</v>
       </c>
       <c r="E289" t="n">
-        <v>131.0647678170153</v>
+        <v>131.0647619103873</v>
       </c>
       <c r="F289" t="n">
-        <v>184.0800415984973</v>
+        <v>184.0800367369864</v>
       </c>
       <c r="G289" t="n">
-        <v>13.44636024624566</v>
+        <v>13.44635970429138</v>
       </c>
       <c r="H289" t="n">
         <v>93</v>
@@ -9113,16 +9113,16 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>0.2362685411133743</v>
+        <v>0.2362685132224033</v>
       </c>
       <c r="E290" t="n">
-        <v>5.473072620538565</v>
+        <v>5.473072632765159</v>
       </c>
       <c r="F290" t="n">
-        <v>7.620014406334866</v>
+        <v>7.620014545473826</v>
       </c>
       <c r="G290" t="n">
-        <v>97.00872059912734</v>
+        <v>97.00872830600093</v>
       </c>
       <c r="H290" t="n">
         <v>78</v>
@@ -9143,16 +9143,16 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>0.641421882598183</v>
+        <v>0.6414217874322703</v>
       </c>
       <c r="E291" t="n">
-        <v>36.24569702148438</v>
+        <v>36.24570634629991</v>
       </c>
       <c r="F291" t="n">
-        <v>56.78876787559103</v>
+        <v>56.78877541140304</v>
       </c>
       <c r="G291" t="n">
-        <v>20.96272592960415</v>
+        <v>20.96273451554228</v>
       </c>
       <c r="H291" t="n">
         <v>18</v>
@@ -9173,16 +9173,16 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>0.297856268676846</v>
+        <v>0.2978563064250246</v>
       </c>
       <c r="E292" t="n">
-        <v>13.19385781448879</v>
+        <v>13.19385785735055</v>
       </c>
       <c r="F292" t="n">
-        <v>19.19923322620159</v>
+        <v>19.19923271011346</v>
       </c>
       <c r="G292" t="n">
-        <v>17.77139413484766</v>
+        <v>17.7713944155272</v>
       </c>
       <c r="H292" t="n">
         <v>89</v>
@@ -9203,16 +9203,16 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>0.2672857877351829</v>
+        <v>0.267285788391919</v>
       </c>
       <c r="E293" t="n">
-        <v>206.178717719184</v>
+        <v>206.1787195687342</v>
       </c>
       <c r="F293" t="n">
-        <v>256.5162065834065</v>
+        <v>256.516206468448</v>
       </c>
       <c r="G293" t="n">
-        <v>38.32441887262691</v>
+        <v>38.32441907598959</v>
       </c>
       <c r="H293" t="n">
         <v>99</v>
@@ -9233,16 +9233,16 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>-0.1479474504336267</v>
+        <v>-0.1479474111849579</v>
       </c>
       <c r="E294" t="n">
-        <v>284.8633334252142</v>
+        <v>284.8633222682502</v>
       </c>
       <c r="F294" t="n">
-        <v>343.5887459908614</v>
+        <v>343.5887401171601</v>
       </c>
       <c r="G294" t="n">
-        <v>37.48630841643915</v>
+        <v>37.48630745319964</v>
       </c>
       <c r="H294" t="n">
         <v>93</v>
@@ -9263,16 +9263,16 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>0.1107386260212333</v>
+        <v>0.1107386581096397</v>
       </c>
       <c r="E295" t="n">
-        <v>6.107508769402137</v>
+        <v>6.107508683815981</v>
       </c>
       <c r="F295" t="n">
-        <v>8.222429656501328</v>
+        <v>8.222429508150867</v>
       </c>
       <c r="G295" t="n">
-        <v>100.9013852838248</v>
+        <v>100.9013865175194</v>
       </c>
       <c r="H295" t="n">
         <v>78</v>
@@ -9293,16 +9293,16 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>0.5414182158440801</v>
+        <v>0.5414182263090522</v>
       </c>
       <c r="E296" t="n">
-        <v>45.6072514851888</v>
+        <v>45.60724809434679</v>
       </c>
       <c r="F296" t="n">
-        <v>64.22127958865393</v>
+        <v>64.22127885587962</v>
       </c>
       <c r="G296" t="n">
-        <v>26.3784272340283</v>
+        <v>26.37842318308441</v>
       </c>
       <c r="H296" t="n">
         <v>18</v>
@@ -9323,16 +9323,16 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>0.2957339873401285</v>
+        <v>0.2957342473285328</v>
       </c>
       <c r="E297" t="n">
-        <v>13.8140789846356</v>
+        <v>13.81407564141777</v>
       </c>
       <c r="F297" t="n">
-        <v>19.22822688476608</v>
+        <v>19.22822333559829</v>
       </c>
       <c r="G297" t="n">
-        <v>18.39977528392154</v>
+        <v>18.39977364878315</v>
       </c>
       <c r="H297" t="n">
         <v>89</v>
@@ -9353,16 +9353,16 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>0.3504403082146065</v>
+        <v>0.3504403933054334</v>
       </c>
       <c r="E298" t="n">
-        <v>187.3817175662879</v>
+        <v>187.3816972212358</v>
       </c>
       <c r="F298" t="n">
-        <v>241.5221881283231</v>
+        <v>241.5221723088967</v>
       </c>
       <c r="G298" t="n">
-        <v>31.807069221337</v>
+        <v>31.80706726912133</v>
       </c>
       <c r="H298" t="n">
         <v>99</v>
@@ -9383,16 +9383,16 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>0.4423135191749952</v>
+        <v>0.4423140370214811</v>
       </c>
       <c r="E299" t="n">
-        <v>186.7729127945439</v>
+        <v>186.772942983976</v>
       </c>
       <c r="F299" t="n">
-        <v>239.4820597506718</v>
+        <v>239.4819485636732</v>
       </c>
       <c r="G299" t="n">
-        <v>19.53807537846508</v>
+        <v>19.53809492422182</v>
       </c>
       <c r="H299" t="n">
         <v>93</v>
@@ -9413,16 +9413,16 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>0.1120601589571484</v>
+        <v>0.1120602555072265</v>
       </c>
       <c r="E300" t="n">
-        <v>6.418591242570144</v>
+        <v>6.41859046006814</v>
       </c>
       <c r="F300" t="n">
-        <v>8.216317701119529</v>
+        <v>8.216317254419144</v>
       </c>
       <c r="G300" t="n">
-        <v>104.3022138648452</v>
+        <v>104.3022194946653</v>
       </c>
       <c r="H300" t="n">
         <v>78</v>
@@ -9443,16 +9443,16 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>0.5055381477447147</v>
+        <v>0.5055384781423946</v>
       </c>
       <c r="E301" t="n">
-        <v>47.6052500406901</v>
+        <v>47.60524156358507</v>
       </c>
       <c r="F301" t="n">
-        <v>66.68635044710894</v>
+        <v>66.68632816731218</v>
       </c>
       <c r="G301" t="n">
-        <v>28.43433764343907</v>
+        <v>28.43434952279087</v>
       </c>
       <c r="H301" t="n">
         <v>18</v>
@@ -9473,16 +9473,16 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>-87.0474206613828</v>
+        <v>-87.0474728637918</v>
       </c>
       <c r="E302" t="n">
-        <v>213.8140596968404</v>
+        <v>213.8141234751498</v>
       </c>
       <c r="F302" t="n">
-        <v>214.9954118282504</v>
+        <v>214.9954755625238</v>
       </c>
       <c r="G302" t="n">
-        <v>314.055741087897</v>
+        <v>314.0558336055324</v>
       </c>
       <c r="H302" t="n">
         <v>89</v>
@@ -9503,16 +9503,16 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>-484.1838962837774</v>
+        <v>-484.1838094248676</v>
       </c>
       <c r="E303" t="n">
-        <v>6596.241870610401</v>
+        <v>6596.24127875434</v>
       </c>
       <c r="F303" t="n">
-        <v>6600.862557166084</v>
+        <v>6600.861966314083</v>
       </c>
       <c r="G303" t="n">
-        <v>1010.308105351166</v>
+        <v>1010.308017817903</v>
       </c>
       <c r="H303" t="n">
         <v>99</v>
@@ -9533,16 +9533,16 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>-892.5811268689707</v>
+        <v>-892.5810130957818</v>
       </c>
       <c r="E304" t="n">
-        <v>9580.880509899509</v>
+        <v>9580.879906110866</v>
       </c>
       <c r="F304" t="n">
-        <v>9586.165448519216</v>
+        <v>9586.164838250817</v>
       </c>
       <c r="G304" t="n">
-        <v>1062.125391141003</v>
+        <v>1062.125323097916</v>
       </c>
       <c r="H304" t="n">
         <v>93</v>
@@ -9563,16 +9563,16 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>-131.5872013902666</v>
+        <v>-131.587173916023</v>
       </c>
       <c r="E305" t="n">
-        <v>100.0089807265844</v>
+        <v>100.0089703584329</v>
       </c>
       <c r="F305" t="n">
-        <v>100.4005875392244</v>
+        <v>100.4005771368993</v>
       </c>
       <c r="G305" t="n">
-        <v>1213.353317284808</v>
+        <v>1213.353159439491</v>
       </c>
       <c r="H305" t="n">
         <v>78</v>
@@ -9593,16 +9593,16 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>-265.4610992873665</v>
+        <v>-265.4611213528097</v>
       </c>
       <c r="E306" t="n">
-        <v>1546.09967719184</v>
+        <v>1546.099731445312</v>
       </c>
       <c r="F306" t="n">
-        <v>1548.058834972803</v>
+        <v>1548.058899069596</v>
       </c>
       <c r="G306" t="n">
-        <v>689.6595073885698</v>
+        <v>689.6595087731143</v>
       </c>
       <c r="H306" t="n">
         <v>18</v>
@@ -9623,16 +9623,16 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>-6.864520194818825</v>
+        <v>-6.864521637410649</v>
       </c>
       <c r="E307" t="n">
-        <v>61.37081099092291</v>
+        <v>61.37081579144081</v>
       </c>
       <c r="F307" t="n">
-        <v>64.25500901701385</v>
+        <v>64.2550149101735</v>
       </c>
       <c r="G307" t="n">
-        <v>92.84569707670067</v>
+        <v>92.84570619557972</v>
       </c>
       <c r="H307" t="n">
         <v>89</v>
@@ -9653,16 +9653,16 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>0.4455761888949826</v>
+        <v>0.4455763763304871</v>
       </c>
       <c r="E308" t="n">
-        <v>171.1122738616635</v>
+        <v>171.1122405697601</v>
       </c>
       <c r="F308" t="n">
-        <v>223.1353806267108</v>
+        <v>223.1353429087275</v>
       </c>
       <c r="G308" t="n">
-        <v>25.32038675450456</v>
+        <v>25.32037767900056</v>
       </c>
       <c r="H308" t="n">
         <v>99</v>
@@ -9683,16 +9683,16 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>-9.918981226190178</v>
+        <v>-9.91898263552523</v>
       </c>
       <c r="E309" t="n">
-        <v>1035.583157775223</v>
+        <v>1035.583229967343</v>
       </c>
       <c r="F309" t="n">
-        <v>1059.665966174038</v>
+        <v>1059.666034560654</v>
       </c>
       <c r="G309" t="n">
-        <v>110.5845631215591</v>
+        <v>110.5845712504386</v>
       </c>
       <c r="H309" t="n">
         <v>93</v>
@@ -9713,16 +9713,16 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>-47.65603725617587</v>
+        <v>-47.65603280193749</v>
       </c>
       <c r="E310" t="n">
-        <v>60.00652748499162</v>
+        <v>60.00652484404735</v>
       </c>
       <c r="F310" t="n">
-        <v>60.82103692700061</v>
+        <v>60.82103414305623</v>
       </c>
       <c r="G310" t="n">
-        <v>675.0303966097795</v>
+        <v>675.0304061296315</v>
       </c>
       <c r="H310" t="n">
         <v>78</v>
@@ -9743,16 +9743,16 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>-8.159339798402472</v>
+        <v>-8.15934174883496</v>
       </c>
       <c r="E311" t="n">
-        <v>277.9879625108507</v>
+        <v>277.9879964192708</v>
       </c>
       <c r="F311" t="n">
-        <v>287.0137084722901</v>
+        <v>287.0137390313066</v>
       </c>
       <c r="G311" t="n">
-        <v>113.4222959225514</v>
+        <v>113.4223108522328</v>
       </c>
       <c r="H311" t="n">
         <v>18</v>
@@ -9773,16 +9773,16 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>0.1473890569961328</v>
+        <v>0.1473886123538</v>
       </c>
       <c r="E312" t="n">
-        <v>17.50004093298751</v>
+        <v>17.50004710508196</v>
       </c>
       <c r="F312" t="n">
-        <v>21.15662187244206</v>
+        <v>21.15662738910154</v>
       </c>
       <c r="G312" t="n">
-        <v>27.4694566068</v>
+        <v>27.46946780905318</v>
       </c>
       <c r="H312" t="n">
         <v>89</v>
@@ -9803,16 +9803,16 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>0.6211038664388758</v>
+        <v>0.6211035908108009</v>
       </c>
       <c r="E313" t="n">
-        <v>148.3117444587476</v>
+        <v>148.3117145576862</v>
       </c>
       <c r="F313" t="n">
-        <v>184.4622866024656</v>
+        <v>184.4623536960187</v>
       </c>
       <c r="G313" t="n">
-        <v>23.97964851491032</v>
+        <v>23.97962398351875</v>
       </c>
       <c r="H313" t="n">
         <v>99</v>
@@ -9833,16 +9833,16 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>-0.2172341312048884</v>
+        <v>-0.217232051841413</v>
       </c>
       <c r="E314" t="n">
-        <v>309.2305465206023</v>
+        <v>309.230218374601</v>
       </c>
       <c r="F314" t="n">
-        <v>353.8058318528353</v>
+        <v>353.8055296549181</v>
       </c>
       <c r="G314" t="n">
-        <v>39.68637108527397</v>
+        <v>39.68633288924448</v>
       </c>
       <c r="H314" t="n">
         <v>93</v>
@@ -9863,16 +9863,16 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>-153.8211212630554</v>
+        <v>-153.8210765546269</v>
       </c>
       <c r="E315" t="n">
-        <v>108.1903186211219</v>
+        <v>108.1903025798309</v>
       </c>
       <c r="F315" t="n">
-        <v>108.4927098015339</v>
+        <v>108.4926941365559</v>
       </c>
       <c r="G315" t="n">
-        <v>1302.77436287224</v>
+        <v>1302.774111776861</v>
       </c>
       <c r="H315" t="n">
         <v>78</v>
@@ -9893,16 +9893,16 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>-12.46592637358809</v>
+        <v>-12.46593415590309</v>
       </c>
       <c r="E316" t="n">
-        <v>343.2621222601996</v>
+        <v>343.262213812934</v>
       </c>
       <c r="F316" t="n">
-        <v>348.0075551557181</v>
+        <v>348.0076557170887</v>
       </c>
       <c r="G316" t="n">
-        <v>168.5215979610221</v>
+        <v>168.5216542615754</v>
       </c>
       <c r="H316" t="n">
         <v>18</v>
@@ -9923,16 +9923,16 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>-103.8429520373781</v>
+        <v>-103.842961308999</v>
       </c>
       <c r="E317" t="n">
-        <v>232.6287771932195</v>
+        <v>232.6287854226787</v>
       </c>
       <c r="F317" t="n">
-        <v>234.6067445900135</v>
+        <v>234.6067549635518</v>
       </c>
       <c r="G317" t="n">
-        <v>339.4663925084687</v>
+        <v>339.4664069840426</v>
       </c>
       <c r="H317" t="n">
         <v>89</v>
@@ -9953,16 +9953,16 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>-8.452843804116538</v>
+        <v>-8.45285945088089</v>
       </c>
       <c r="E318" t="n">
-        <v>890.5261369185014</v>
+        <v>890.5269778473208</v>
       </c>
       <c r="F318" t="n">
-        <v>921.3587019930693</v>
+        <v>921.3594645295518</v>
       </c>
       <c r="G318" t="n">
-        <v>127.8313092809847</v>
+        <v>127.8314505081188</v>
       </c>
       <c r="H318" t="n">
         <v>99</v>
@@ -9983,16 +9983,16 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>-31.58303988954525</v>
+        <v>-31.58307017182956</v>
       </c>
       <c r="E319" t="n">
-        <v>1801.937202043431</v>
+        <v>1801.938035534274</v>
       </c>
       <c r="F319" t="n">
-        <v>1830.516831354749</v>
+        <v>1830.517681984684</v>
       </c>
       <c r="G319" t="n">
-        <v>195.196859441148</v>
+        <v>195.1969472995543</v>
       </c>
       <c r="H319" t="n">
         <v>93</v>
@@ -10013,16 +10013,16 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>-10.87142868700198</v>
+        <v>-10.87143804930649</v>
       </c>
       <c r="E320" t="n">
-        <v>28.65313275655111</v>
+        <v>28.65314522767678</v>
       </c>
       <c r="F320" t="n">
-        <v>30.04256063673964</v>
+        <v>30.04257248314638</v>
       </c>
       <c r="G320" t="n">
-        <v>448.4674870331945</v>
+        <v>448.4676678608373</v>
       </c>
       <c r="H320" t="n">
         <v>78</v>
@@ -10043,16 +10043,16 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>-1084.000670386622</v>
+        <v>-1084.000782610856</v>
       </c>
       <c r="E321" t="n">
-        <v>3122.318644205729</v>
+        <v>3122.318806966146</v>
       </c>
       <c r="F321" t="n">
-        <v>3123.816812302648</v>
+        <v>3123.816973854594</v>
       </c>
       <c r="G321" t="n">
-        <v>1407.517050655522</v>
+        <v>1407.51707401261</v>
       </c>
       <c r="H321" t="n">
         <v>18</v>
@@ -10073,16 +10073,16 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>-25.18379503418039</v>
+        <v>-25.18379614203029</v>
       </c>
       <c r="E322" t="n">
-        <v>113.0584405191829</v>
+        <v>113.0584417193123</v>
       </c>
       <c r="F322" t="n">
-        <v>117.2430665824811</v>
+        <v>117.2430690627885</v>
       </c>
       <c r="G322" t="n">
-        <v>166.9671631921686</v>
+        <v>166.9671643684734</v>
       </c>
       <c r="H322" t="n">
         <v>89</v>
@@ -10103,16 +10103,16 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>-0.2376891274539545</v>
+        <v>-0.2376890007504655</v>
       </c>
       <c r="E323" t="n">
-        <v>271.6260409884983</v>
+        <v>271.626028966422</v>
       </c>
       <c r="F323" t="n">
-        <v>333.3905526878576</v>
+        <v>333.3905356230929</v>
       </c>
       <c r="G323" t="n">
-        <v>37.60502757083267</v>
+        <v>37.60502783515918</v>
       </c>
       <c r="H323" t="n">
         <v>99</v>
@@ -10133,16 +10133,16 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>-8.090756786388711</v>
+        <v>-8.090756484911342</v>
       </c>
       <c r="E324" t="n">
-        <v>934.4934925366473</v>
+        <v>934.4934623472152</v>
       </c>
       <c r="F324" t="n">
-        <v>966.8919531525333</v>
+        <v>966.8919371199823</v>
       </c>
       <c r="G324" t="n">
-        <v>109.8134975812333</v>
+        <v>109.8134971016131</v>
       </c>
       <c r="H324" t="n">
         <v>93</v>
@@ -10163,16 +10163,16 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>-74.29036238930644</v>
+        <v>-74.2903564513924</v>
       </c>
       <c r="E325" t="n">
-        <v>75.05330829131297</v>
+        <v>75.05330506349222</v>
       </c>
       <c r="F325" t="n">
-        <v>75.65805043634109</v>
+        <v>75.65804745288479</v>
       </c>
       <c r="G325" t="n">
-        <v>870.873997823859</v>
+        <v>870.8739166116478</v>
       </c>
       <c r="H325" t="n">
         <v>78</v>
@@ -10193,16 +10193,16 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>-14.22432530512023</v>
+        <v>-14.22432577410802</v>
       </c>
       <c r="E326" t="n">
-        <v>364.1020363701714</v>
+        <v>364.1020414564344</v>
       </c>
       <c r="F326" t="n">
-        <v>370.0322549322447</v>
+        <v>370.0322606316962</v>
       </c>
       <c r="G326" t="n">
-        <v>160.1494916437018</v>
+        <v>160.1494756318259</v>
       </c>
       <c r="H326" t="n">
         <v>18</v>
@@ -10223,16 +10223,16 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>-9.270640905437558</v>
+        <v>-9.270643072337467</v>
       </c>
       <c r="E327" t="n">
-        <v>71.91747956865289</v>
+        <v>71.91748694087683</v>
       </c>
       <c r="F327" t="n">
-        <v>73.42934351303929</v>
+        <v>73.42935125910064</v>
       </c>
       <c r="G327" t="n">
-        <v>107.390012379996</v>
+        <v>107.3900236320285</v>
       </c>
       <c r="H327" t="n">
         <v>89</v>
@@ -10253,16 +10253,16 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>-38.0522951383657</v>
+        <v>-38.05228600241133</v>
       </c>
       <c r="E328" t="n">
-        <v>1863.7522774128</v>
+        <v>1863.752057932844</v>
       </c>
       <c r="F328" t="n">
-        <v>1872.71109074136</v>
+        <v>1872.710871688882</v>
       </c>
       <c r="G328" t="n">
-        <v>298.4519383935952</v>
+        <v>298.4518985899603</v>
       </c>
       <c r="H328" t="n">
         <v>99</v>
@@ -10283,16 +10283,16 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>-60.60047309844401</v>
+        <v>-60.60046396689099</v>
       </c>
       <c r="E329" t="n">
-        <v>2509.257413802608</v>
+        <v>2509.257230040847</v>
       </c>
       <c r="F329" t="n">
-        <v>2516.923120836561</v>
+        <v>2516.922934284278</v>
       </c>
       <c r="G329" t="n">
-        <v>285.706149663541</v>
+        <v>285.7061254745497</v>
       </c>
       <c r="H329" t="n">
         <v>93</v>
@@ -10313,16 +10313,16 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>-144.8436578725611</v>
+        <v>-144.8436356220578</v>
       </c>
       <c r="E330" t="n">
-        <v>104.9893176249969</v>
+        <v>104.9893097999768</v>
       </c>
       <c r="F330" t="n">
-        <v>105.3002073872799</v>
+        <v>105.300199354765</v>
       </c>
       <c r="G330" t="n">
-        <v>1263.498154516787</v>
+        <v>1263.498112528162</v>
       </c>
       <c r="H330" t="n">
         <v>78</v>
@@ -10343,16 +10343,16 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>-19.05908837300552</v>
+        <v>-19.05909052679946</v>
       </c>
       <c r="E331" t="n">
-        <v>420.0697157118055</v>
+        <v>420.0697394476996</v>
       </c>
       <c r="F331" t="n">
-        <v>424.7429221025955</v>
+        <v>424.7429449054439</v>
       </c>
       <c r="G331" t="n">
-        <v>178.4847263574463</v>
+        <v>178.4847433501709</v>
       </c>
       <c r="H331" t="n">
         <v>18</v>
@@ -10373,16 +10373,16 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>-1.988513208036104</v>
+        <v>-1.988511979953008</v>
       </c>
       <c r="E332" t="n">
-        <v>34.25073006447781</v>
+        <v>34.25073332197211</v>
       </c>
       <c r="F332" t="n">
-        <v>39.60941813865066</v>
+        <v>39.60941000021216</v>
       </c>
       <c r="G332" t="n">
-        <v>51.04208847053151</v>
+        <v>51.04208770681986</v>
       </c>
       <c r="H332" t="n">
         <v>89</v>
@@ -10403,16 +10403,16 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>-171.6176002191228</v>
+        <v>-171.6175943228451</v>
       </c>
       <c r="E333" t="n">
-        <v>3927.825985686948</v>
+        <v>3927.825916637074</v>
       </c>
       <c r="F333" t="n">
-        <v>3937.22322625208</v>
+        <v>3937.22315900818</v>
       </c>
       <c r="G333" t="n">
-        <v>620.2235921260643</v>
+        <v>620.22358047751</v>
       </c>
       <c r="H333" t="n">
         <v>99</v>
@@ -10433,16 +10433,16 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>-14.94747332679016</v>
+        <v>-14.9474812241968</v>
       </c>
       <c r="E334" t="n">
-        <v>1214.518149427188</v>
+        <v>1214.518532701718</v>
       </c>
       <c r="F334" t="n">
-        <v>1280.630581813364</v>
+        <v>1280.630898906203</v>
       </c>
       <c r="G334" t="n">
-        <v>147.0293005950602</v>
+        <v>147.0293361155247</v>
       </c>
       <c r="H334" t="n">
         <v>93</v>
@@ -10463,16 +10463,16 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>-527.998272645651</v>
+        <v>-527.9982921129482</v>
       </c>
       <c r="E335" t="n">
-        <v>200.3380939288017</v>
+        <v>200.3380976456862</v>
       </c>
       <c r="F335" t="n">
-        <v>200.5453420690002</v>
+        <v>200.5453457590649</v>
       </c>
       <c r="G335" t="n">
-        <v>2477.919468526811</v>
+        <v>2477.919602744646</v>
       </c>
       <c r="H335" t="n">
         <v>78</v>
@@ -10493,16 +10493,16 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>-29.82332611437829</v>
+        <v>-29.82331987402958</v>
       </c>
       <c r="E336" t="n">
-        <v>517.8109639485677</v>
+        <v>517.8108961317274</v>
       </c>
       <c r="F336" t="n">
-        <v>526.5144627725196</v>
+        <v>526.5144094746696</v>
       </c>
       <c r="G336" t="n">
-        <v>240.919699866657</v>
+        <v>240.9196015077355</v>
       </c>
       <c r="H336" t="n">
         <v>18</v>
@@ -10523,16 +10523,16 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>-4.190358198532422</v>
+        <v>-4.190360734402503</v>
       </c>
       <c r="E337" t="n">
-        <v>42.76813164185942</v>
+        <v>42.76814265733355</v>
       </c>
       <c r="F337" t="n">
-        <v>52.19988403047964</v>
+        <v>52.19989678221112</v>
       </c>
       <c r="G337" t="n">
-        <v>54.42914527272842</v>
+        <v>54.4291593306158</v>
       </c>
       <c r="H337" t="n">
         <v>89</v>
@@ -10553,16 +10553,16 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>-44.88491382043973</v>
+        <v>-44.88490782959322</v>
       </c>
       <c r="E338" t="n">
-        <v>2010.132795854048</v>
+        <v>2010.132660220368</v>
       </c>
       <c r="F338" t="n">
-        <v>2029.936540427408</v>
+        <v>2029.936407910665</v>
       </c>
       <c r="G338" t="n">
-        <v>309.4221386010096</v>
+        <v>309.4221186469832</v>
       </c>
       <c r="H338" t="n">
         <v>99</v>
@@ -10583,16 +10583,16 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>-40.12199621816293</v>
+        <v>-40.12198856136482</v>
       </c>
       <c r="E339" t="n">
-        <v>2033.389127669796</v>
+        <v>2033.388930782195</v>
       </c>
       <c r="F339" t="n">
-        <v>2056.43516113447</v>
+        <v>2056.434969683287</v>
       </c>
       <c r="G339" t="n">
-        <v>221.0259249391322</v>
+        <v>221.0259036363947</v>
       </c>
       <c r="H339" t="n">
         <v>93</v>
@@ -10613,16 +10613,16 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>-5.772613939624662</v>
+        <v>-5.772615960285065</v>
       </c>
       <c r="E340" t="n">
-        <v>20.64545640578637</v>
+        <v>20.64545966417361</v>
       </c>
       <c r="F340" t="n">
-        <v>22.69152126697291</v>
+        <v>22.69152465206583</v>
       </c>
       <c r="G340" t="n">
-        <v>179.9482161091026</v>
+        <v>179.9482677566662</v>
       </c>
       <c r="H340" t="n">
         <v>78</v>
@@ -10643,16 +10643,16 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>-4.421465261519352</v>
+        <v>-4.421472238967568</v>
       </c>
       <c r="E341" t="n">
-        <v>209.6868413289388</v>
+        <v>209.6869964599609</v>
       </c>
       <c r="F341" t="n">
-        <v>220.8151640210079</v>
+        <v>220.8153061159769</v>
       </c>
       <c r="G341" t="n">
-        <v>83.43783072838582</v>
+        <v>83.43790197084525</v>
       </c>
       <c r="H341" t="n">
         <v>18</v>
@@ -10673,16 +10673,16 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>-10.64587181692653</v>
+        <v>-10.64587389873442</v>
       </c>
       <c r="E342" t="n">
-        <v>76.47759126813224</v>
+        <v>76.47759834032381</v>
       </c>
       <c r="F342" t="n">
-        <v>78.19101949105057</v>
+        <v>78.19102647973619</v>
       </c>
       <c r="G342" t="n">
-        <v>104.0483813537066</v>
+        <v>104.0483906165634</v>
       </c>
       <c r="H342" t="n">
         <v>89</v>
@@ -10703,16 +10703,16 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>-274.9547675587344</v>
+        <v>-274.9547738620907</v>
       </c>
       <c r="E343" t="n">
-        <v>4973.646996083886</v>
+        <v>4973.647055269492</v>
       </c>
       <c r="F343" t="n">
-        <v>4978.132501232944</v>
+        <v>4978.132558088173</v>
       </c>
       <c r="G343" t="n">
-        <v>757.3579778785884</v>
+        <v>757.3579876314878</v>
       </c>
       <c r="H343" t="n">
         <v>99</v>
@@ -10733,16 +10733,16 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>-141.4823467423654</v>
+        <v>-141.482409080462</v>
       </c>
       <c r="E344" t="n">
-        <v>3820.627992363386</v>
+        <v>3820.628837667486</v>
       </c>
       <c r="F344" t="n">
-        <v>3827.881247912148</v>
+        <v>3827.882085288885</v>
       </c>
       <c r="G344" t="n">
-        <v>418.7153032913413</v>
+        <v>418.7153992548018</v>
       </c>
       <c r="H344" t="n">
         <v>93</v>
@@ -10763,16 +10763,16 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>-63.82531973826752</v>
+        <v>-63.82531304973529</v>
       </c>
       <c r="E345" t="n">
-        <v>69.72298798194298</v>
+        <v>69.72298446068397</v>
       </c>
       <c r="F345" t="n">
-        <v>70.20334186174968</v>
+        <v>70.2033382400373</v>
       </c>
       <c r="G345" t="n">
-        <v>809.0462707878777</v>
+        <v>809.0462143351008</v>
       </c>
       <c r="H345" t="n">
         <v>78</v>
@@ -10793,16 +10793,16 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>-48.88552085573765</v>
+        <v>-48.88552186538161</v>
       </c>
       <c r="E346" t="n">
-        <v>667.5402119954427</v>
+        <v>667.5402187771267</v>
       </c>
       <c r="F346" t="n">
-        <v>669.8195362421167</v>
+        <v>669.8195430204286</v>
       </c>
       <c r="G346" t="n">
-        <v>290.581481619329</v>
+        <v>290.5814833266889</v>
       </c>
       <c r="H346" t="n">
         <v>18</v>
@@ -10823,16 +10823,16 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>-0.4172585549568906</v>
+        <v>-0.4172583040403792</v>
       </c>
       <c r="E347" t="n">
-        <v>21.03712579105677</v>
+        <v>21.03712403372433</v>
       </c>
       <c r="F347" t="n">
-        <v>27.27692543358912</v>
+        <v>27.27692301898692</v>
       </c>
       <c r="G347" t="n">
-        <v>24.81084935066896</v>
+        <v>24.81084737309633</v>
       </c>
       <c r="H347" t="n">
         <v>89</v>
@@ -10853,16 +10853,16 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>0.2741396804755265</v>
+        <v>0.2741397956537107</v>
       </c>
       <c r="E348" t="n">
-        <v>204.1128789728338</v>
+        <v>204.1128629433988</v>
       </c>
       <c r="F348" t="n">
-        <v>255.3136467536007</v>
+        <v>255.3136264972493</v>
       </c>
       <c r="G348" t="n">
-        <v>30.33343728435851</v>
+        <v>30.33343485831638</v>
       </c>
       <c r="H348" t="n">
         <v>99</v>
@@ -10883,16 +10883,16 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>0.1832414508020044</v>
+        <v>0.1832412232334925</v>
       </c>
       <c r="E349" t="n">
-        <v>251.7218408071867</v>
+        <v>251.7218828098748</v>
       </c>
       <c r="F349" t="n">
-        <v>289.8176101934994</v>
+        <v>289.8176505685636</v>
       </c>
       <c r="G349" t="n">
-        <v>31.25546286713276</v>
+        <v>31.25546861200518</v>
       </c>
       <c r="H349" t="n">
         <v>93</v>
@@ -10913,16 +10913,16 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>-0.5973197230076652</v>
+        <v>-0.5973197152159198</v>
       </c>
       <c r="E350" t="n">
-        <v>8.323565623699091</v>
+        <v>8.323565550339527</v>
       </c>
       <c r="F350" t="n">
-        <v>11.01999454397853</v>
+        <v>11.0199945171007</v>
       </c>
       <c r="G350" t="n">
-        <v>71.04014791007668</v>
+        <v>71.04013844024979</v>
       </c>
       <c r="H350" t="n">
         <v>78</v>
@@ -10943,16 +10943,16 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>-4.227751204102747</v>
+        <v>-4.227752179551953</v>
       </c>
       <c r="E351" t="n">
-        <v>202.8904537624783</v>
+        <v>202.8904758029514</v>
       </c>
       <c r="F351" t="n">
-        <v>216.8343138480813</v>
+        <v>216.8343340777022</v>
       </c>
       <c r="G351" t="n">
-        <v>74.0086835641753</v>
+        <v>74.00869116687858</v>
       </c>
       <c r="H351" t="n">
         <v>18</v>
@@ -10973,16 +10973,16 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>0.1699912413591373</v>
+        <v>0.1699912283694038</v>
       </c>
       <c r="E352" t="n">
-        <v>16.27839887811896</v>
+        <v>16.27839986393961</v>
       </c>
       <c r="F352" t="n">
-        <v>20.87431392829989</v>
+        <v>20.87431409164261</v>
       </c>
       <c r="G352" t="n">
-        <v>24.48051146724765</v>
+        <v>24.4805121900466</v>
       </c>
       <c r="H352" t="n">
         <v>89</v>
@@ -11003,16 +11003,16 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>-2.238818139136644</v>
+        <v>-2.238818680812696</v>
       </c>
       <c r="E353" t="n">
-        <v>495.115510574495</v>
+        <v>495.1155623619002</v>
       </c>
       <c r="F353" t="n">
-        <v>539.312867836394</v>
+        <v>539.3129129350752</v>
       </c>
       <c r="G353" t="n">
-        <v>90.18004960596893</v>
+        <v>90.1800576840274</v>
       </c>
       <c r="H353" t="n">
         <v>99</v>
@@ -11033,16 +11033,16 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>-4.848823893808637</v>
+        <v>-4.848824462964975</v>
       </c>
       <c r="E354" t="n">
-        <v>744.1369251538348</v>
+        <v>744.1369710942751</v>
       </c>
       <c r="F354" t="n">
-        <v>775.5542802033074</v>
+        <v>775.554317938383</v>
       </c>
       <c r="G354" t="n">
-        <v>89.93341284831993</v>
+        <v>89.93341673120366</v>
       </c>
       <c r="H354" t="n">
         <v>93</v>
@@ -11063,16 +11063,16 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>-1.252602250574319</v>
+        <v>-1.252602122594536</v>
       </c>
       <c r="E355" t="n">
-        <v>10.65714260859367</v>
+        <v>10.65714252300751</v>
       </c>
       <c r="F355" t="n">
-        <v>13.08662655061766</v>
+        <v>13.08662617886458</v>
       </c>
       <c r="G355" t="n">
-        <v>86.52561156021285</v>
+        <v>86.52561436394393</v>
       </c>
       <c r="H355" t="n">
         <v>78</v>
@@ -11093,16 +11093,16 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>-2.667086263704013</v>
+        <v>-2.667086514931539</v>
       </c>
       <c r="E356" t="n">
-        <v>170.4649081759983</v>
+        <v>170.4649183485243</v>
       </c>
       <c r="F356" t="n">
-        <v>181.6063867834029</v>
+        <v>181.6063930042168</v>
       </c>
       <c r="G356" t="n">
-        <v>92.0361810144159</v>
+        <v>92.03618357125605</v>
       </c>
       <c r="H356" t="n">
         <v>18</v>
@@ -11123,16 +11123,16 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>0.09923182669746433</v>
+        <v>0.09923185028130699</v>
       </c>
       <c r="E357" t="n">
-        <v>17.4663793156656</v>
+        <v>17.46637858701556</v>
       </c>
       <c r="F357" t="n">
-        <v>21.74590013909382</v>
+        <v>21.74589985441908</v>
       </c>
       <c r="G357" t="n">
-        <v>26.84505633252097</v>
+        <v>26.84505504766256</v>
       </c>
       <c r="H357" t="n">
         <v>89</v>
@@ -11153,16 +11153,16 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>-0.1907557051088014</v>
+        <v>-0.1907556355938054</v>
       </c>
       <c r="E358" t="n">
-        <v>258.8181660970052</v>
+        <v>258.8181583905461</v>
       </c>
       <c r="F358" t="n">
-        <v>327.0083456901634</v>
+        <v>327.0083361449712</v>
       </c>
       <c r="G358" t="n">
-        <v>31.48402233804205</v>
+        <v>31.4840215761948</v>
       </c>
       <c r="H358" t="n">
         <v>99</v>
@@ -11183,16 +11183,16 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>0.5356056244305655</v>
+        <v>0.5356056408184144</v>
       </c>
       <c r="E359" t="n">
-        <v>164.0539724698631</v>
+        <v>164.0539718135711</v>
       </c>
       <c r="F359" t="n">
-        <v>218.5352011362686</v>
+        <v>218.5351972803628</v>
       </c>
       <c r="G359" t="n">
-        <v>16.47476470666303</v>
+        <v>16.47476434296582</v>
       </c>
       <c r="H359" t="n">
         <v>93</v>
@@ -11213,16 +11213,16 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>-0.4443805440169579</v>
+        <v>-0.4443805040546418</v>
       </c>
       <c r="E360" t="n">
-        <v>8.967778804974678</v>
+        <v>8.967778450403458</v>
       </c>
       <c r="F360" t="n">
-        <v>10.47915507565227</v>
+        <v>10.47915493068656</v>
       </c>
       <c r="G360" t="n">
-        <v>167.8085285689373</v>
+        <v>167.8085282737169</v>
       </c>
       <c r="H360" t="n">
         <v>78</v>
@@ -11243,16 +11243,16 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>-0.2367666734078788</v>
+        <v>-0.2367666883814343</v>
       </c>
       <c r="E361" t="n">
-        <v>84.94487169053819</v>
+        <v>84.94487423366971</v>
       </c>
       <c r="F361" t="n">
-        <v>105.466477628317</v>
+        <v>105.4664782667592</v>
       </c>
       <c r="G361" t="n">
-        <v>34.00105164675941</v>
+        <v>34.0010529272353</v>
       </c>
       <c r="H361" t="n">
         <v>18</v>
@@ -11273,16 +11273,16 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>0.7360046115678466</v>
+        <v>0.7360046139124158</v>
       </c>
       <c r="E362" t="n">
-        <v>8.922263199023986</v>
+        <v>8.922262770406316</v>
       </c>
       <c r="F362" t="n">
-        <v>11.77250932571641</v>
+        <v>11.77250927344</v>
       </c>
       <c r="G362" t="n">
-        <v>13.40399660486614</v>
+        <v>13.40399535203833</v>
       </c>
       <c r="H362" t="n">
         <v>89</v>
@@ -11303,16 +11303,16 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>0.7147351727047534</v>
+        <v>0.7147351512970219</v>
       </c>
       <c r="E363" t="n">
-        <v>115.7598735154277</v>
+        <v>115.7598741319444</v>
       </c>
       <c r="F363" t="n">
-        <v>160.0558730481668</v>
+        <v>160.0558790538723</v>
       </c>
       <c r="G363" t="n">
-        <v>18.45216644656125</v>
+        <v>18.45216585865424</v>
       </c>
       <c r="H363" t="n">
         <v>99</v>
@@ -11333,16 +11333,16 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>0.6897014552630933</v>
+        <v>0.6897014715290636</v>
       </c>
       <c r="E364" t="n">
-        <v>126.9264365575647</v>
+        <v>126.9264329479587</v>
       </c>
       <c r="F364" t="n">
-        <v>178.6355106781721</v>
+        <v>178.6355059961006</v>
       </c>
       <c r="G364" t="n">
-        <v>12.6709027266101</v>
+        <v>12.67090246804503</v>
       </c>
       <c r="H364" t="n">
         <v>93</v>
@@ -11363,16 +11363,16 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>0.1922923391752612</v>
+        <v>0.1922923762369061</v>
       </c>
       <c r="E365" t="n">
-        <v>5.004912987733499</v>
+        <v>5.004912951053718</v>
       </c>
       <c r="F365" t="n">
-        <v>7.836327057128462</v>
+        <v>7.836326877343629</v>
       </c>
       <c r="G365" t="n">
-        <v>55.79331363386659</v>
+        <v>55.7933042328218</v>
       </c>
       <c r="H365" t="n">
         <v>78</v>
@@ -11393,16 +11393,16 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>0.8283257845914574</v>
+        <v>0.8283259258808535</v>
       </c>
       <c r="E366" t="n">
-        <v>26.40848202175564</v>
+        <v>26.40847778320312</v>
       </c>
       <c r="F366" t="n">
-        <v>39.29371494969594</v>
+        <v>39.29369878015533</v>
       </c>
       <c r="G366" t="n">
-        <v>10.82165927171135</v>
+        <v>10.82165856485228</v>
       </c>
       <c r="H366" t="n">
         <v>18</v>
@@ -11423,16 +11423,16 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>0.7178665405795663</v>
+        <v>0.7178665701628542</v>
       </c>
       <c r="E367" t="n">
-        <v>9.455428005604261</v>
+        <v>9.455427834157193</v>
       </c>
       <c r="F367" t="n">
-        <v>12.17021273955656</v>
+        <v>12.17021210149874</v>
       </c>
       <c r="G367" t="n">
-        <v>14.10068722850333</v>
+        <v>14.10068686383553</v>
       </c>
       <c r="H367" t="n">
         <v>89</v>
@@ -11453,16 +11453,16 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>0.7107466994150963</v>
+        <v>0.710746716565079</v>
       </c>
       <c r="E368" t="n">
-        <v>114.4192270606455</v>
+        <v>114.4192218202533</v>
       </c>
       <c r="F368" t="n">
-        <v>161.1709117443505</v>
+        <v>161.1709069663957</v>
       </c>
       <c r="G368" t="n">
-        <v>18.09210193986336</v>
+        <v>18.09210115686556</v>
       </c>
       <c r="H368" t="n">
         <v>99</v>
@@ -11483,16 +11483,16 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>0.6884832630394784</v>
+        <v>0.6884832649419717</v>
       </c>
       <c r="E369" t="n">
-        <v>119.3431655719716</v>
+        <v>119.3431586809056</v>
       </c>
       <c r="F369" t="n">
-        <v>178.9858172334273</v>
+        <v>178.9858166868767</v>
       </c>
       <c r="G369" t="n">
-        <v>11.81809455149779</v>
+        <v>11.81809382012143</v>
       </c>
       <c r="H369" t="n">
         <v>93</v>
@@ -11513,16 +11513,16 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>0.2109115043192152</v>
+        <v>0.2109115364832868</v>
       </c>
       <c r="E370" t="n">
-        <v>5.117976928368593</v>
+        <v>5.117976763309577</v>
       </c>
       <c r="F370" t="n">
-        <v>7.745479490188118</v>
+        <v>7.745479332331199</v>
       </c>
       <c r="G370" t="n">
-        <v>54.95197630585042</v>
+        <v>54.95196729971311</v>
       </c>
       <c r="H370" t="n">
         <v>78</v>
@@ -11543,16 +11543,16 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>0.8060739996573705</v>
+        <v>0.8060742910630508</v>
       </c>
       <c r="E371" t="n">
-        <v>27.04113091362847</v>
+        <v>27.04110124376085</v>
       </c>
       <c r="F371" t="n">
-        <v>41.76270061496981</v>
+        <v>41.76266923729808</v>
       </c>
       <c r="G371" t="n">
-        <v>8.872801872111276</v>
+        <v>8.872778649133743</v>
       </c>
       <c r="H371" t="n">
         <v>18</v>
@@ -11573,16 +11573,16 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>0.7497723517436501</v>
+        <v>0.7497723208508509</v>
       </c>
       <c r="E372" t="n">
-        <v>8.740160695622476</v>
+        <v>8.74016108137838</v>
       </c>
       <c r="F372" t="n">
-        <v>11.46142244408056</v>
+        <v>11.46142315158713</v>
       </c>
       <c r="G372" t="n">
-        <v>13.09689513945696</v>
+        <v>13.09689534564318</v>
       </c>
       <c r="H372" t="n">
         <v>89</v>
@@ -11603,16 +11603,16 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>0.7268723609176264</v>
+        <v>0.7268723570769</v>
       </c>
       <c r="E373" t="n">
-        <v>110.9290003921046</v>
+        <v>110.9290013168797</v>
       </c>
       <c r="F373" t="n">
-        <v>156.6139079107907</v>
+        <v>156.6139090119446</v>
       </c>
       <c r="G373" t="n">
-        <v>17.25127901135601</v>
+        <v>17.2512790012759</v>
       </c>
       <c r="H373" t="n">
         <v>99</v>
@@ -11633,16 +11633,16 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>0.6964968977712118</v>
+        <v>0.6964969083248533</v>
       </c>
       <c r="E374" t="n">
-        <v>117.2086312899026</v>
+        <v>117.2086270240045</v>
       </c>
       <c r="F374" t="n">
-        <v>176.6686513463834</v>
+        <v>176.6686482747548</v>
       </c>
       <c r="G374" t="n">
-        <v>11.60206651322842</v>
+        <v>11.60206592193321</v>
       </c>
       <c r="H374" t="n">
         <v>93</v>
@@ -11663,16 +11663,16 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>0.2569682998742163</v>
+        <v>0.2569683240634377</v>
       </c>
       <c r="E375" t="n">
-        <v>4.962814490000407</v>
+        <v>4.962814410527547</v>
       </c>
       <c r="F375" t="n">
-        <v>7.516040708856233</v>
+        <v>7.516040586514768</v>
       </c>
       <c r="G375" t="n">
-        <v>55.36987170595692</v>
+        <v>55.36987576622375</v>
       </c>
       <c r="H375" t="n">
         <v>78</v>
@@ -11693,18 +11693,168 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>0.8373221239408939</v>
+        <v>0.8373220682864757</v>
       </c>
       <c r="E376" t="n">
-        <v>28.51315816243489</v>
+        <v>28.51316663953993</v>
       </c>
       <c r="F376" t="n">
-        <v>38.25029610331148</v>
+        <v>38.25030264629643</v>
       </c>
       <c r="G376" t="n">
-        <v>10.52700089257955</v>
+        <v>10.52701125576872</v>
       </c>
       <c r="H376" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>376</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>TiAlloyNet_sep_all</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>YM</t>
+        </is>
+      </c>
+      <c r="D377" t="n">
+        <v>0.7417478149740446</v>
+      </c>
+      <c r="E377" t="n">
+        <v>8.618832191724456</v>
+      </c>
+      <c r="F377" t="n">
+        <v>11.64375008023541</v>
+      </c>
+      <c r="G377" t="n">
+        <v>12.73189632800748</v>
+      </c>
+      <c r="H377" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>377</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>TiAlloyNet_sep_all</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>YS</t>
+        </is>
+      </c>
+      <c r="D378" t="n">
+        <v>0.6365155777027383</v>
+      </c>
+      <c r="E378" t="n">
+        <v>137.8252430925466</v>
+      </c>
+      <c r="F378" t="n">
+        <v>180.6718130317626</v>
+      </c>
+      <c r="G378" t="n">
+        <v>21.43692391259026</v>
+      </c>
+      <c r="H378" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>378</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>TiAlloyNet_sep_all</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>UTS</t>
+        </is>
+      </c>
+      <c r="D379" t="n">
+        <v>0.6310495273289165</v>
+      </c>
+      <c r="E379" t="n">
+        <v>152.9419175014701</v>
+      </c>
+      <c r="F379" t="n">
+        <v>194.7878939413981</v>
+      </c>
+      <c r="G379" t="n">
+        <v>16.29188561244983</v>
+      </c>
+      <c r="H379" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>379</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>TiAlloyNet_sep_all</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>El</t>
+        </is>
+      </c>
+      <c r="D380" t="n">
+        <v>0.1561166720428524</v>
+      </c>
+      <c r="E380" t="n">
+        <v>5.112671882678301</v>
+      </c>
+      <c r="F380" t="n">
+        <v>8.009891916479479</v>
+      </c>
+      <c r="G380" t="n">
+        <v>57.7619741725812</v>
+      </c>
+      <c r="H380" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>380</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>TiAlloyNet_sep_all</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="D381" t="n">
+        <v>0.7176993387828614</v>
+      </c>
+      <c r="E381" t="n">
+        <v>34.1076397365994</v>
+      </c>
+      <c r="F381" t="n">
+        <v>50.38792826082764</v>
+      </c>
+      <c r="G381" t="n">
+        <v>11.47722166315809</v>
+      </c>
+      <c r="H381" t="n">
         <v>18</v>
       </c>
     </row>
